--- a/jogos_2026-10-13.xlsx
+++ b/jogos_2026-10-13.xlsx
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G25">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G33">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G35">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G37">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.31</v>
+        <v>1.46</v>
       </c>
       <c r="O38">
-        <v>6.04</v>
+        <v>4.87</v>
       </c>
       <c r="P38">
-        <v>11.9</v>
+        <v>7.9</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6548,10 +6548,10 @@
         <v>0</v>
       </c>
       <c r="AC38">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AD38">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AE38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.46</v>
+        <v>2.45</v>
       </c>
       <c r="O39">
-        <v>4.87</v>
+        <v>3.64</v>
       </c>
       <c r="P39">
-        <v>7.9</v>
+        <v>3.01</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -6705,16 +6705,16 @@
         <v>0</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC39">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD39">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.45</v>
+        <v>1.99</v>
       </c>
       <c r="O40">
-        <v>3.64</v>
+        <v>4.09</v>
       </c>
       <c r="P40">
-        <v>3.01</v>
+        <v>3.72</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -6868,16 +6868,16 @@
         <v>0</v>
       </c>
       <c r="AA40">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB40">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.99</v>
+        <v>2.27</v>
       </c>
       <c r="O41">
-        <v>4.09</v>
+        <v>3.96</v>
       </c>
       <c r="P41">
-        <v>3.72</v>
+        <v>3.11</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7037,10 +7037,10 @@
         <v>0</v>
       </c>
       <c r="AC41">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AD41">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AE41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.27</v>
+        <v>34</v>
       </c>
       <c r="O42">
-        <v>3.96</v>
+        <v>15.5</v>
       </c>
       <c r="P42">
-        <v>3.11</v>
+        <v>1.09</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -7200,13 +7200,13 @@
         <v>0</v>
       </c>
       <c r="AC42">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD42">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>34</v>
+        <v>7.5</v>
       </c>
       <c r="O43">
-        <v>15.5</v>
+        <v>5.74</v>
       </c>
       <c r="P43">
-        <v>1.09</v>
+        <v>1.41</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -7363,13 +7363,13 @@
         <v>0</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE43">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>7.5</v>
+        <v>1.31</v>
       </c>
       <c r="O44">
-        <v>5.74</v>
+        <v>6.04</v>
       </c>
       <c r="P44">
-        <v>1.41</v>
+        <v>11.9</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -7526,10 +7526,10 @@
         <v>0</v>
       </c>
       <c r="AC44">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="AD44">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="AE44">
         <v>0</v>

--- a/jogos_2026-10-13.xlsx
+++ b/jogos_2026-10-13.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU48"/>
+  <dimension ref="A1:AU50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="G25">
@@ -5315,12 +5315,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="O31">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="P31">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>2026-10-13 15:45:00</t>
+          <t>2026-10-13 15:00:00</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G33">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G34">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G37">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="O38">
-        <v>4.87</v>
+        <v>0</v>
       </c>
       <c r="P38">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6548,10 +6548,10 @@
         <v>0</v>
       </c>
       <c r="AC38">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD38">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE38">
         <v>0</v>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>2026-10-13 16:00:00</t>
+          <t>2026-10-13 15:45:00</t>
         </is>
       </c>
     </row>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.45</v>
+        <v>1.46</v>
       </c>
       <c r="O39">
-        <v>3.64</v>
+        <v>4.87</v>
       </c>
       <c r="P39">
-        <v>3.01</v>
+        <v>7.9</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -6705,16 +6705,16 @@
         <v>0</v>
       </c>
       <c r="AA39">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB39">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.99</v>
+        <v>34</v>
       </c>
       <c r="O40">
-        <v>4.09</v>
+        <v>15.5</v>
       </c>
       <c r="P40">
-        <v>3.72</v>
+        <v>1.09</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -6874,13 +6874,13 @@
         <v>0</v>
       </c>
       <c r="AC40">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD40">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.27</v>
+        <v>1.31</v>
       </c>
       <c r="O41">
-        <v>3.96</v>
+        <v>6.04</v>
       </c>
       <c r="P41">
-        <v>3.11</v>
+        <v>11.9</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7037,10 +7037,10 @@
         <v>0</v>
       </c>
       <c r="AC41">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AD41">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AE41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>34</v>
+        <v>2.45</v>
       </c>
       <c r="O42">
-        <v>15.5</v>
+        <v>3.64</v>
       </c>
       <c r="P42">
-        <v>1.09</v>
+        <v>3.01</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -7194,10 +7194,10 @@
         <v>0</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC42">
         <v>0</v>
@@ -7206,7 +7206,7 @@
         <v>0</v>
       </c>
       <c r="AE42">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>7.5</v>
+        <v>1.99</v>
       </c>
       <c r="O43">
-        <v>5.74</v>
+        <v>4.09</v>
       </c>
       <c r="P43">
-        <v>1.41</v>
+        <v>3.72</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -7363,10 +7363,10 @@
         <v>0</v>
       </c>
       <c r="AC43">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AD43">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AE43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.31</v>
+        <v>2.27</v>
       </c>
       <c r="O44">
-        <v>6.04</v>
+        <v>3.96</v>
       </c>
       <c r="P44">
-        <v>11.9</v>
+        <v>3.11</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -7526,10 +7526,10 @@
         <v>0</v>
       </c>
       <c r="AC44">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AD44">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AE44">
         <v>0</v>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>5.74</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -7689,10 +7689,10 @@
         <v>0</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE45">
         <v>0</v>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G46">
@@ -8086,156 +8086,482 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Stoke City</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Middlesbrough</t>
+        </is>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+      <c r="Q48">
+        <v>0</v>
+      </c>
+      <c r="R48">
+        <v>0</v>
+      </c>
+      <c r="S48">
+        <v>0</v>
+      </c>
+      <c r="T48">
+        <v>0</v>
+      </c>
+      <c r="U48">
+        <v>0</v>
+      </c>
+      <c r="V48">
+        <v>0</v>
+      </c>
+      <c r="W48">
+        <v>0</v>
+      </c>
+      <c r="X48">
+        <v>0</v>
+      </c>
+      <c r="Y48">
+        <v>0</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+      <c r="AA48">
+        <v>0</v>
+      </c>
+      <c r="AB48">
+        <v>0</v>
+      </c>
+      <c r="AC48">
+        <v>0</v>
+      </c>
+      <c r="AD48">
+        <v>0</v>
+      </c>
+      <c r="AE48">
+        <v>0</v>
+      </c>
+      <c r="AF48">
+        <v>0</v>
+      </c>
+      <c r="AG48">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ48">
+        <v>0</v>
+      </c>
+      <c r="AK48">
+        <v>0</v>
+      </c>
+      <c r="AL48">
+        <v>0</v>
+      </c>
+      <c r="AM48">
+        <v>-1</v>
+      </c>
+      <c r="AN48">
+        <v>-1</v>
+      </c>
+      <c r="AO48">
+        <v>-1</v>
+      </c>
+      <c r="AP48">
+        <v>-1</v>
+      </c>
+      <c r="AQ48">
+        <v>0</v>
+      </c>
+      <c r="AR48">
+        <v>0</v>
+      </c>
+      <c r="AS48">
+        <v>0</v>
+      </c>
+      <c r="AT48">
+        <v>0</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>2026-10-13 16:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Morocco Botola Pro</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>FUS Rabat</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Raja Casablanca</t>
+        </is>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
+      </c>
+      <c r="Q49">
+        <v>0</v>
+      </c>
+      <c r="R49">
+        <v>0</v>
+      </c>
+      <c r="S49">
+        <v>0</v>
+      </c>
+      <c r="T49">
+        <v>0</v>
+      </c>
+      <c r="U49">
+        <v>0</v>
+      </c>
+      <c r="V49">
+        <v>0</v>
+      </c>
+      <c r="W49">
+        <v>0</v>
+      </c>
+      <c r="X49">
+        <v>0</v>
+      </c>
+      <c r="Y49">
+        <v>0</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+      <c r="AA49">
+        <v>0</v>
+      </c>
+      <c r="AB49">
+        <v>0</v>
+      </c>
+      <c r="AC49">
+        <v>0</v>
+      </c>
+      <c r="AD49">
+        <v>0</v>
+      </c>
+      <c r="AE49">
+        <v>0</v>
+      </c>
+      <c r="AF49">
+        <v>0</v>
+      </c>
+      <c r="AG49">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ49">
+        <v>0</v>
+      </c>
+      <c r="AK49">
+        <v>0</v>
+      </c>
+      <c r="AL49">
+        <v>0</v>
+      </c>
+      <c r="AM49">
+        <v>-1</v>
+      </c>
+      <c r="AN49">
+        <v>-1</v>
+      </c>
+      <c r="AO49">
+        <v>-1</v>
+      </c>
+      <c r="AP49">
+        <v>-1</v>
+      </c>
+      <c r="AQ49">
+        <v>0</v>
+      </c>
+      <c r="AR49">
+        <v>0</v>
+      </c>
+      <c r="AS49">
+        <v>0</v>
+      </c>
+      <c r="AT49">
+        <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>2026-10-13 17:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>Athletic Club</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>Londrina</t>
         </is>
       </c>
-      <c r="G48">
-        <v>0</v>
-      </c>
-      <c r="H48">
-        <v>0</v>
-      </c>
-      <c r="I48">
-        <v>0</v>
-      </c>
-      <c r="J48">
-        <v>0</v>
-      </c>
-      <c r="K48">
-        <v>0</v>
-      </c>
-      <c r="L48">
-        <v>0</v>
-      </c>
-      <c r="M48" t="inlineStr">
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N48">
-        <v>0</v>
-      </c>
-      <c r="O48">
-        <v>0</v>
-      </c>
-      <c r="P48">
-        <v>0</v>
-      </c>
-      <c r="Q48">
-        <v>0</v>
-      </c>
-      <c r="R48">
-        <v>0</v>
-      </c>
-      <c r="S48">
-        <v>0</v>
-      </c>
-      <c r="T48">
-        <v>0</v>
-      </c>
-      <c r="U48">
-        <v>0</v>
-      </c>
-      <c r="V48">
-        <v>0</v>
-      </c>
-      <c r="W48">
-        <v>0</v>
-      </c>
-      <c r="X48">
-        <v>0</v>
-      </c>
-      <c r="Y48">
-        <v>0</v>
-      </c>
-      <c r="Z48">
-        <v>0</v>
-      </c>
-      <c r="AA48">
-        <v>0</v>
-      </c>
-      <c r="AB48">
-        <v>0</v>
-      </c>
-      <c r="AC48">
-        <v>0</v>
-      </c>
-      <c r="AD48">
-        <v>0</v>
-      </c>
-      <c r="AE48">
-        <v>0</v>
-      </c>
-      <c r="AF48">
-        <v>0</v>
-      </c>
-      <c r="AG48">
-        <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ48">
-        <v>0</v>
-      </c>
-      <c r="AK48">
-        <v>0</v>
-      </c>
-      <c r="AL48">
-        <v>0</v>
-      </c>
-      <c r="AM48">
-        <v>-1</v>
-      </c>
-      <c r="AN48">
-        <v>-1</v>
-      </c>
-      <c r="AO48">
-        <v>-1</v>
-      </c>
-      <c r="AP48">
-        <v>-1</v>
-      </c>
-      <c r="AQ48">
-        <v>0</v>
-      </c>
-      <c r="AR48">
-        <v>0</v>
-      </c>
-      <c r="AS48">
-        <v>0</v>
-      </c>
-      <c r="AT48">
-        <v>0</v>
-      </c>
-      <c r="AU48" t="inlineStr">
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
+      </c>
+      <c r="Q50">
+        <v>0</v>
+      </c>
+      <c r="R50">
+        <v>0</v>
+      </c>
+      <c r="S50">
+        <v>0</v>
+      </c>
+      <c r="T50">
+        <v>0</v>
+      </c>
+      <c r="U50">
+        <v>0</v>
+      </c>
+      <c r="V50">
+        <v>0</v>
+      </c>
+      <c r="W50">
+        <v>0</v>
+      </c>
+      <c r="X50">
+        <v>0</v>
+      </c>
+      <c r="Y50">
+        <v>0</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+      <c r="AA50">
+        <v>0</v>
+      </c>
+      <c r="AB50">
+        <v>0</v>
+      </c>
+      <c r="AC50">
+        <v>0</v>
+      </c>
+      <c r="AD50">
+        <v>0</v>
+      </c>
+      <c r="AE50">
+        <v>0</v>
+      </c>
+      <c r="AF50">
+        <v>0</v>
+      </c>
+      <c r="AG50">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ50">
+        <v>0</v>
+      </c>
+      <c r="AK50">
+        <v>0</v>
+      </c>
+      <c r="AL50">
+        <v>0</v>
+      </c>
+      <c r="AM50">
+        <v>-1</v>
+      </c>
+      <c r="AN50">
+        <v>-1</v>
+      </c>
+      <c r="AO50">
+        <v>-1</v>
+      </c>
+      <c r="AP50">
+        <v>-1</v>
+      </c>
+      <c r="AQ50">
+        <v>0</v>
+      </c>
+      <c r="AR50">
+        <v>0</v>
+      </c>
+      <c r="AS50">
+        <v>0</v>
+      </c>
+      <c r="AT50">
+        <v>0</v>
+      </c>
+      <c r="AU50" t="inlineStr">
         <is>
           <t>2026-10-13 19:30:00</t>
         </is>

--- a/jogos_2026-10-13.xlsx
+++ b/jogos_2026-10-13.xlsx
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G33">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G34">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G35">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G37">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G38">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.45</v>
+        <v>1.99</v>
       </c>
       <c r="O42">
-        <v>3.64</v>
+        <v>4.09</v>
       </c>
       <c r="P42">
-        <v>3.01</v>
+        <v>3.72</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -7194,16 +7194,16 @@
         <v>0</v>
       </c>
       <c r="AA42">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB42">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.99</v>
+        <v>2.27</v>
       </c>
       <c r="O43">
-        <v>4.09</v>
+        <v>3.96</v>
       </c>
       <c r="P43">
-        <v>3.72</v>
+        <v>3.11</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -7363,10 +7363,10 @@
         <v>0</v>
       </c>
       <c r="AC43">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AD43">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AE43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.27</v>
+        <v>7.5</v>
       </c>
       <c r="O44">
-        <v>3.96</v>
+        <v>5.74</v>
       </c>
       <c r="P44">
-        <v>3.11</v>
+        <v>1.41</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -7526,10 +7526,10 @@
         <v>0</v>
       </c>
       <c r="AC44">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AD44">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="AE44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>7.5</v>
+        <v>2.45</v>
       </c>
       <c r="O45">
-        <v>5.74</v>
+        <v>3.64</v>
       </c>
       <c r="P45">
-        <v>1.41</v>
+        <v>3.01</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -7683,16 +7683,16 @@
         <v>0</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC45">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD45">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE45">
         <v>0</v>

--- a/jogos_2026-10-13.xlsx
+++ b/jogos_2026-10-13.xlsx
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G33">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G34">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G35">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G37">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G38">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G47">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G48">

--- a/jogos_2026-10-13.xlsx
+++ b/jogos_2026-10-13.xlsx
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G47">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G48">

--- a/jogos_2026-10-13.xlsx
+++ b/jogos_2026-10-13.xlsx
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>11.9</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>6.83</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q48">
         <v>0</v>

--- a/jogos_2026-10-13.xlsx
+++ b/jogos_2026-10-13.xlsx
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G30">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="O35">
-        <v>4.7</v>
+        <v>3.45</v>
       </c>
       <c r="P35">
-        <v>6.83</v>
+        <v>3.56</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="O36">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P36">
-        <v>3.56</v>
+        <v>2.87</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,10 +6340,10 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="O37">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P37">
         <v>2.87</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.38</v>
+        <v>1.4</v>
       </c>
       <c r="O38">
-        <v>3.25</v>
+        <v>4.7</v>
       </c>
       <c r="P38">
-        <v>2.87</v>
+        <v>6.83</v>
       </c>
       <c r="Q38">
         <v>0</v>

--- a/jogos_2026-10-13.xlsx
+++ b/jogos_2026-10-13.xlsx
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="O35">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P35">
-        <v>3.56</v>
+        <v>2.87</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="O36">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P36">
         <v>2.87</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.38</v>
+        <v>1.4</v>
       </c>
       <c r="O37">
-        <v>3.25</v>
+        <v>4.7</v>
       </c>
       <c r="P37">
-        <v>2.87</v>
+        <v>6.83</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="O38">
-        <v>4.7</v>
+        <v>3.45</v>
       </c>
       <c r="P38">
-        <v>6.83</v>
+        <v>3.56</v>
       </c>
       <c r="Q38">
         <v>0</v>

--- a/jogos_2026-10-13.xlsx
+++ b/jogos_2026-10-13.xlsx
@@ -970,55 +970,55 @@
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1622,55 +1622,55 @@
         <v>4.32</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1785,55 +1785,55 @@
         <v>4.46</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q11">
         <v>0</v>

--- a/jogos_2026-10-13.xlsx
+++ b/jogos_2026-10-13.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -2763,34 +2763,34 @@
         <v>2.81</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA15">
         <v>1.57</v>
@@ -2799,19 +2799,19 @@
         <v>2.25</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2926,34 +2926,34 @@
         <v>2.06</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA16">
         <v>1.6</v>
@@ -2962,19 +2962,19 @@
         <v>2.2</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3578,55 +3578,55 @@
         <v>11.9</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="Q26">
         <v>0</v>

--- a/jogos_2026-10-13.xlsx
+++ b/jogos_2026-10-13.xlsx
@@ -3252,55 +3252,55 @@
         <v>3.25</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3415,55 +3415,55 @@
         <v>2.52</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.86</v>
+        <v>1.71</v>
       </c>
       <c r="O33">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P33">
-        <v>3.65</v>
+        <v>4.57</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.71</v>
+        <v>2.36</v>
       </c>
       <c r="O34">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="P34">
-        <v>4.57</v>
+        <v>2.87</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="O35">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P35">
         <v>2.87</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.38</v>
+        <v>1.4</v>
       </c>
       <c r="O36">
-        <v>3.25</v>
+        <v>4.7</v>
       </c>
       <c r="P36">
-        <v>2.87</v>
+        <v>6.83</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="O37">
-        <v>4.7</v>
+        <v>3.45</v>
       </c>
       <c r="P37">
-        <v>6.83</v>
+        <v>3.56</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="O38">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="P38">
-        <v>3.56</v>
+        <v>3.65</v>
       </c>
       <c r="Q38">
         <v>0</v>

--- a/jogos_2026-10-13.xlsx
+++ b/jogos_2026-10-13.xlsx
@@ -644,55 +644,55 @@
         <v>2.8</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Abu Qair Semad</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Asyut Petroleum</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,25 +1613,25 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="O8">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="P8">
-        <v>4.32</v>
+        <v>4.46</v>
       </c>
       <c r="Q8">
-        <v>2.82</v>
+        <v>2.6</v>
       </c>
       <c r="R8">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="S8">
-        <v>1.61</v>
+        <v>1.45</v>
       </c>
       <c r="T8">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="U8">
         <v>3.5</v>
@@ -1640,37 +1640,37 @@
         <v>1.22</v>
       </c>
       <c r="W8">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X8">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y8">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="Z8">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="AA8">
-        <v>2.73</v>
+        <v>2.41</v>
       </c>
       <c r="AB8">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AC8">
-        <v>4.75</v>
+        <v>4.65</v>
       </c>
       <c r="AD8">
         <v>1.12</v>
       </c>
       <c r="AE8">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AF8">
         <v>2.15</v>
       </c>
       <c r="AG8">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>1.33</v>
       </c>
       <c r="AK8">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Abu Qair Semad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Asyut Petroleum</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,25 +1776,25 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="O9">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="P9">
-        <v>4.46</v>
+        <v>4.32</v>
       </c>
       <c r="Q9">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="R9">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="S9">
-        <v>1.45</v>
+        <v>1.61</v>
       </c>
       <c r="T9">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="U9">
         <v>3.5</v>
@@ -1803,37 +1803,37 @@
         <v>1.22</v>
       </c>
       <c r="W9">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X9">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y9">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="Z9">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="AA9">
-        <v>2.41</v>
+        <v>2.73</v>
       </c>
       <c r="AB9">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AC9">
-        <v>4.65</v>
+        <v>4.75</v>
       </c>
       <c r="AD9">
         <v>1.12</v>
       </c>
       <c r="AE9">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AF9">
         <v>2.15</v>
       </c>
       <c r="AG9">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>1.33</v>
       </c>
       <c r="AK9">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1948,55 +1948,55 @@
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2026-10-13 14:00:00</t>
+          <t>2026-10-13 13:45:00</t>
         </is>
       </c>
     </row>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.33</v>
+        <v>2.99</v>
       </c>
       <c r="O18">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="P18">
+        <v>2.52</v>
+      </c>
+      <c r="Q18">
+        <v>3.5</v>
+      </c>
+      <c r="R18">
+        <v>1.82</v>
+      </c>
+      <c r="S18">
+        <v>1.41</v>
+      </c>
+      <c r="T18">
+        <v>2.75</v>
+      </c>
+      <c r="U18">
+        <v>3.3</v>
+      </c>
+      <c r="V18">
+        <v>1.34</v>
+      </c>
+      <c r="W18">
+        <v>1.03</v>
+      </c>
+      <c r="X18">
+        <v>1.06</v>
+      </c>
+      <c r="Y18">
+        <v>1.33</v>
+      </c>
+      <c r="Z18">
         <v>3.25</v>
       </c>
-      <c r="Q18">
-        <v>3.04</v>
-      </c>
-      <c r="R18">
-        <v>1.83</v>
-      </c>
-      <c r="S18">
-        <v>1.7</v>
-      </c>
-      <c r="T18">
-        <v>1.99</v>
-      </c>
-      <c r="U18">
-        <v>4.25</v>
-      </c>
-      <c r="V18">
-        <v>1.15</v>
-      </c>
-      <c r="W18">
-        <v>1.01</v>
-      </c>
-      <c r="X18">
-        <v>1.15</v>
-      </c>
-      <c r="Y18">
-        <v>1.68</v>
-      </c>
-      <c r="Z18">
-        <v>2.15</v>
-      </c>
       <c r="AA18">
-        <v>3.17</v>
+        <v>2.12</v>
       </c>
       <c r="AB18">
-        <v>1.3</v>
+        <v>1.65</v>
       </c>
       <c r="AC18">
-        <v>6.35</v>
+        <v>3.34</v>
       </c>
       <c r="AD18">
-        <v>1.06</v>
+        <v>1.27</v>
       </c>
       <c r="AE18">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF18">
-        <v>2.42</v>
+        <v>1.78</v>
       </c>
       <c r="AG18">
-        <v>1.49</v>
+        <v>1.91</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AK18">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.99</v>
+        <v>2.33</v>
       </c>
       <c r="O19">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="P19">
-        <v>2.52</v>
+        <v>3.25</v>
       </c>
       <c r="Q19">
-        <v>3.5</v>
+        <v>3.04</v>
       </c>
       <c r="R19">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="S19">
-        <v>1.41</v>
+        <v>1.7</v>
       </c>
       <c r="T19">
-        <v>2.75</v>
+        <v>1.99</v>
       </c>
       <c r="U19">
-        <v>3.3</v>
+        <v>4.25</v>
       </c>
       <c r="V19">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="W19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X19">
+        <v>1.15</v>
+      </c>
+      <c r="Y19">
+        <v>1.68</v>
+      </c>
+      <c r="Z19">
+        <v>2.15</v>
+      </c>
+      <c r="AA19">
+        <v>3.17</v>
+      </c>
+      <c r="AB19">
+        <v>1.3</v>
+      </c>
+      <c r="AC19">
+        <v>6.35</v>
+      </c>
+      <c r="AD19">
         <v>1.06</v>
       </c>
-      <c r="Y19">
-        <v>1.33</v>
-      </c>
-      <c r="Z19">
-        <v>3.25</v>
-      </c>
-      <c r="AA19">
-        <v>2.12</v>
-      </c>
-      <c r="AB19">
-        <v>1.65</v>
-      </c>
-      <c r="AC19">
-        <v>3.34</v>
-      </c>
-      <c r="AD19">
-        <v>1.27</v>
-      </c>
       <c r="AE19">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF19">
-        <v>1.78</v>
+        <v>2.42</v>
       </c>
       <c r="AG19">
-        <v>1.91</v>
+        <v>1.49</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AK19">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3741,55 +3741,55 @@
         <v>0</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3904,55 +3904,55 @@
         <v>0</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4067,55 +4067,55 @@
         <v>0</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4230,55 +4230,55 @@
         <v>0</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X24">
         <v>0</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -5534,55 +5534,55 @@
         <v>1.65</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>6.02</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -6675,40 +6675,40 @@
         <v>7.9</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC39">
         <v>2.25</v>
@@ -6717,13 +6717,13 @@
         <v>1.57</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>34</v>
+        <v>1.31</v>
       </c>
       <c r="O40">
-        <v>15.5</v>
+        <v>6.04</v>
       </c>
       <c r="P40">
-        <v>1.09</v>
+        <v>11.9</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE40">
-        <v>1.71</v>
+        <v>1.19</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.31</v>
+        <v>1.99</v>
       </c>
       <c r="O41">
-        <v>6.04</v>
+        <v>4.09</v>
       </c>
       <c r="P41">
-        <v>11.9</v>
+        <v>3.72</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AC41">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AD41">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.99</v>
+        <v>2.27</v>
       </c>
       <c r="O42">
-        <v>4.09</v>
+        <v>3.96</v>
       </c>
       <c r="P42">
-        <v>3.72</v>
+        <v>3.11</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AC42">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AD42">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,80 +7318,80 @@
         </is>
       </c>
       <c r="N43">
+        <v>2.45</v>
+      </c>
+      <c r="O43">
+        <v>3.64</v>
+      </c>
+      <c r="P43">
+        <v>3.01</v>
+      </c>
+      <c r="Q43">
+        <v>2.75</v>
+      </c>
+      <c r="R43">
+        <v>2.39</v>
+      </c>
+      <c r="S43">
+        <v>1.3</v>
+      </c>
+      <c r="T43">
+        <v>3.3</v>
+      </c>
+      <c r="U43">
+        <v>2.45</v>
+      </c>
+      <c r="V43">
+        <v>1.5</v>
+      </c>
+      <c r="W43">
+        <v>1.11</v>
+      </c>
+      <c r="X43">
+        <v>1.01</v>
+      </c>
+      <c r="Y43">
+        <v>1.2</v>
+      </c>
+      <c r="Z43">
+        <v>4.15</v>
+      </c>
+      <c r="AA43">
+        <v>1.66</v>
+      </c>
+      <c r="AB43">
+        <v>2.1</v>
+      </c>
+      <c r="AC43">
+        <v>2.56</v>
+      </c>
+      <c r="AD43">
+        <v>1.41</v>
+      </c>
+      <c r="AE43">
+        <v>1.13</v>
+      </c>
+      <c r="AF43">
+        <v>1.56</v>
+      </c>
+      <c r="AG43">
         <v>2.27</v>
       </c>
-      <c r="O43">
-        <v>3.96</v>
-      </c>
-      <c r="P43">
-        <v>3.11</v>
-      </c>
-      <c r="Q43">
-        <v>0</v>
-      </c>
-      <c r="R43">
-        <v>0</v>
-      </c>
-      <c r="S43">
-        <v>0</v>
-      </c>
-      <c r="T43">
-        <v>0</v>
-      </c>
-      <c r="U43">
-        <v>0</v>
-      </c>
-      <c r="V43">
-        <v>0</v>
-      </c>
-      <c r="W43">
-        <v>0</v>
-      </c>
-      <c r="X43">
-        <v>0</v>
-      </c>
-      <c r="Y43">
-        <v>0</v>
-      </c>
-      <c r="Z43">
-        <v>0</v>
-      </c>
-      <c r="AA43">
-        <v>0</v>
-      </c>
-      <c r="AB43">
-        <v>0</v>
-      </c>
-      <c r="AC43">
-        <v>2.05</v>
-      </c>
-      <c r="AD43">
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ43">
+        <v>1.33</v>
+      </c>
+      <c r="AK43">
         <v>1.68</v>
-      </c>
-      <c r="AE43">
-        <v>0</v>
-      </c>
-      <c r="AF43">
-        <v>0</v>
-      </c>
-      <c r="AG43">
-        <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ43">
-        <v>0</v>
-      </c>
-      <c r="AK43">
-        <v>0</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>7.5</v>
+        <v>34</v>
       </c>
       <c r="O44">
-        <v>5.74</v>
+        <v>15.5</v>
       </c>
       <c r="P44">
+        <v>1.09</v>
+      </c>
+      <c r="Q44">
+        <v>11</v>
+      </c>
+      <c r="R44">
+        <v>4.09</v>
+      </c>
+      <c r="S44">
+        <v>1.08</v>
+      </c>
+      <c r="T44">
+        <v>6</v>
+      </c>
+      <c r="U44">
+        <v>1.58</v>
+      </c>
+      <c r="V44">
+        <v>2.35</v>
+      </c>
+      <c r="W44">
+        <v>1.43</v>
+      </c>
+      <c r="X44">
+        <v>1</v>
+      </c>
+      <c r="Y44">
+        <v>1.04</v>
+      </c>
+      <c r="Z44">
+        <v>13</v>
+      </c>
+      <c r="AA44">
+        <v>1.16</v>
+      </c>
+      <c r="AB44">
+        <v>4.95</v>
+      </c>
+      <c r="AC44">
         <v>1.41</v>
       </c>
-      <c r="Q44">
-        <v>0</v>
-      </c>
-      <c r="R44">
-        <v>0</v>
-      </c>
-      <c r="S44">
-        <v>0</v>
-      </c>
-      <c r="T44">
-        <v>0</v>
-      </c>
-      <c r="U44">
-        <v>0</v>
-      </c>
-      <c r="V44">
-        <v>0</v>
-      </c>
-      <c r="W44">
-        <v>0</v>
-      </c>
-      <c r="X44">
-        <v>0</v>
-      </c>
-      <c r="Y44">
-        <v>0</v>
-      </c>
-      <c r="Z44">
-        <v>0</v>
-      </c>
-      <c r="AA44">
-        <v>0</v>
-      </c>
-      <c r="AB44">
-        <v>0</v>
-      </c>
-      <c r="AC44">
-        <v>1.65</v>
-      </c>
       <c r="AD44">
-        <v>2.1</v>
+        <v>2.64</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.45</v>
+        <v>7.5</v>
       </c>
       <c r="O45">
-        <v>3.64</v>
+        <v>5.74</v>
       </c>
       <c r="P45">
-        <v>3.01</v>
+        <v>1.41</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA45">
-        <v>1.66</v>
+        <v>1.18</v>
       </c>
       <c r="AB45">
+        <v>4.5</v>
+      </c>
+      <c r="AC45">
+        <v>1.65</v>
+      </c>
+      <c r="AD45">
         <v>2.1</v>
       </c>
-      <c r="AC45">
-        <v>0</v>
-      </c>
-      <c r="AD45">
-        <v>0</v>
-      </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL50">
         <v>0</v>

--- a/jogos_2026-10-13.xlsx
+++ b/jogos_2026-10-13.xlsx
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.46</v>
+        <v>2.27</v>
       </c>
       <c r="O39">
-        <v>4.87</v>
+        <v>3.96</v>
       </c>
       <c r="P39">
-        <v>7.9</v>
+        <v>3.11</v>
       </c>
       <c r="Q39">
-        <v>1.62</v>
+        <v>2.64</v>
       </c>
       <c r="R39">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="S39">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T39">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="U39">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="V39">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="W39">
         <v>1.17</v>
       </c>
       <c r="X39">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
         <v>1.11</v>
       </c>
       <c r="Z39">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="AA39">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AB39">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="AC39">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AD39">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AE39">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AF39">
-        <v>1.85</v>
+        <v>1.42</v>
       </c>
       <c r="AG39">
-        <v>1.83</v>
+        <v>2.69</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>3.6</v>
+        <v>1.59</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.31</v>
+        <v>2.45</v>
       </c>
       <c r="O40">
-        <v>6.04</v>
+        <v>3.64</v>
       </c>
       <c r="P40">
-        <v>11.9</v>
+        <v>3.01</v>
       </c>
       <c r="Q40">
-        <v>1.7</v>
+        <v>2.75</v>
       </c>
       <c r="R40">
-        <v>2.52</v>
+        <v>2.39</v>
       </c>
       <c r="S40">
         <v>1.3</v>
       </c>
       <c r="T40">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U40">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="V40">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W40">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X40">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z40">
-        <v>4.33</v>
+        <v>4.15</v>
       </c>
       <c r="AA40">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AB40">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="AC40">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="AD40">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="AE40">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AF40">
-        <v>2.11</v>
+        <v>1.56</v>
       </c>
       <c r="AG40">
-        <v>1.66</v>
+        <v>2.27</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="AK40">
-        <v>3.92</v>
+        <v>1.68</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,65 +6992,65 @@
         </is>
       </c>
       <c r="N41">
+        <v>34</v>
+      </c>
+      <c r="O41">
+        <v>15.5</v>
+      </c>
+      <c r="P41">
+        <v>1.09</v>
+      </c>
+      <c r="Q41">
+        <v>11</v>
+      </c>
+      <c r="R41">
+        <v>4.09</v>
+      </c>
+      <c r="S41">
+        <v>1.08</v>
+      </c>
+      <c r="T41">
+        <v>6</v>
+      </c>
+      <c r="U41">
+        <v>1.58</v>
+      </c>
+      <c r="V41">
+        <v>2.35</v>
+      </c>
+      <c r="W41">
+        <v>1.43</v>
+      </c>
+      <c r="X41">
+        <v>1</v>
+      </c>
+      <c r="Y41">
+        <v>1.04</v>
+      </c>
+      <c r="Z41">
+        <v>13</v>
+      </c>
+      <c r="AA41">
+        <v>1.16</v>
+      </c>
+      <c r="AB41">
+        <v>4.95</v>
+      </c>
+      <c r="AC41">
+        <v>1.41</v>
+      </c>
+      <c r="AD41">
+        <v>2.64</v>
+      </c>
+      <c r="AE41">
+        <v>1.71</v>
+      </c>
+      <c r="AF41">
+        <v>1.73</v>
+      </c>
+      <c r="AG41">
         <v>1.99</v>
       </c>
-      <c r="O41">
-        <v>4.09</v>
-      </c>
-      <c r="P41">
-        <v>3.72</v>
-      </c>
-      <c r="Q41">
-        <v>2.47</v>
-      </c>
-      <c r="R41">
-        <v>2.5</v>
-      </c>
-      <c r="S41">
-        <v>1.21</v>
-      </c>
-      <c r="T41">
-        <v>4.2</v>
-      </c>
-      <c r="U41">
-        <v>2.03</v>
-      </c>
-      <c r="V41">
-        <v>1.75</v>
-      </c>
-      <c r="W41">
-        <v>1.2</v>
-      </c>
-      <c r="X41">
-        <v>1.01</v>
-      </c>
-      <c r="Y41">
-        <v>1.07</v>
-      </c>
-      <c r="Z41">
-        <v>5.95</v>
-      </c>
-      <c r="AA41">
-        <v>1.4</v>
-      </c>
-      <c r="AB41">
-        <v>2.97</v>
-      </c>
-      <c r="AC41">
-        <v>1.9</v>
-      </c>
-      <c r="AD41">
-        <v>1.8</v>
-      </c>
-      <c r="AE41">
-        <v>1.34</v>
-      </c>
-      <c r="AF41">
-        <v>1.36</v>
-      </c>
-      <c r="AG41">
-        <v>3.1</v>
-      </c>
       <c r="AH41" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.22</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AK41">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.27</v>
+        <v>7.5</v>
       </c>
       <c r="O42">
-        <v>3.96</v>
+        <v>5.74</v>
       </c>
       <c r="P42">
-        <v>3.11</v>
+        <v>1.41</v>
       </c>
       <c r="Q42">
-        <v>2.64</v>
+        <v>6.8</v>
       </c>
       <c r="R42">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="S42">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="T42">
-        <v>3.35</v>
+        <v>6.5</v>
       </c>
       <c r="U42">
-        <v>2.18</v>
+        <v>1.65</v>
       </c>
       <c r="V42">
-        <v>1.69</v>
+        <v>2.07</v>
       </c>
       <c r="W42">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="X42">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y42">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="Z42">
-        <v>4.95</v>
+        <v>10</v>
       </c>
       <c r="AA42">
-        <v>1.46</v>
+        <v>1.18</v>
       </c>
       <c r="AB42">
-        <v>2.44</v>
+        <v>4.5</v>
       </c>
       <c r="AC42">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AD42">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="AE42">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="AF42">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AG42">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK42">
-        <v>1.59</v>
+        <v>1.06</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,65 +7318,65 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.45</v>
+        <v>1.31</v>
       </c>
       <c r="O43">
-        <v>3.64</v>
+        <v>6.04</v>
       </c>
       <c r="P43">
-        <v>3.01</v>
+        <v>11.9</v>
       </c>
       <c r="Q43">
-        <v>2.75</v>
+        <v>1.7</v>
       </c>
       <c r="R43">
-        <v>2.39</v>
+        <v>2.52</v>
       </c>
       <c r="S43">
         <v>1.3</v>
       </c>
       <c r="T43">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U43">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="V43">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W43">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X43">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z43">
-        <v>4.15</v>
+        <v>4.33</v>
       </c>
       <c r="AA43">
+        <v>1.57</v>
+      </c>
+      <c r="AB43">
+        <v>2.37</v>
+      </c>
+      <c r="AC43">
+        <v>2.3</v>
+      </c>
+      <c r="AD43">
+        <v>1.55</v>
+      </c>
+      <c r="AE43">
+        <v>1.19</v>
+      </c>
+      <c r="AF43">
+        <v>2.11</v>
+      </c>
+      <c r="AG43">
         <v>1.66</v>
       </c>
-      <c r="AB43">
-        <v>2.1</v>
-      </c>
-      <c r="AC43">
-        <v>2.56</v>
-      </c>
-      <c r="AD43">
-        <v>1.41</v>
-      </c>
-      <c r="AE43">
-        <v>1.13</v>
-      </c>
-      <c r="AF43">
-        <v>1.56</v>
-      </c>
-      <c r="AG43">
-        <v>2.27</v>
-      </c>
       <c r="AH43" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="AK43">
-        <v>1.68</v>
+        <v>3.92</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>34</v>
+        <v>1.46</v>
       </c>
       <c r="O44">
-        <v>15.5</v>
+        <v>4.87</v>
       </c>
       <c r="P44">
-        <v>1.09</v>
+        <v>7.9</v>
       </c>
       <c r="Q44">
-        <v>11</v>
+        <v>1.62</v>
       </c>
       <c r="R44">
-        <v>4.09</v>
+        <v>2.67</v>
       </c>
       <c r="S44">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="T44">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="U44">
-        <v>1.58</v>
+        <v>2.23</v>
       </c>
       <c r="V44">
-        <v>2.35</v>
+        <v>1.62</v>
       </c>
       <c r="W44">
-        <v>1.43</v>
+        <v>1.17</v>
       </c>
       <c r="X44">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y44">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="Z44">
-        <v>13</v>
+        <v>4.9</v>
       </c>
       <c r="AA44">
-        <v>1.16</v>
+        <v>1.47</v>
       </c>
       <c r="AB44">
-        <v>4.95</v>
+        <v>2.62</v>
       </c>
       <c r="AC44">
-        <v>1.41</v>
+        <v>2.25</v>
       </c>
       <c r="AD44">
-        <v>2.64</v>
+        <v>1.57</v>
       </c>
       <c r="AE44">
-        <v>1.71</v>
+        <v>1.23</v>
       </c>
       <c r="AF44">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AG44">
-        <v>1.99</v>
+        <v>1.83</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>8.699999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="AK44">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>7.5</v>
+        <v>1.99</v>
       </c>
       <c r="O45">
-        <v>5.74</v>
+        <v>4.09</v>
       </c>
       <c r="P45">
-        <v>1.41</v>
+        <v>3.72</v>
       </c>
       <c r="Q45">
-        <v>6.8</v>
+        <v>2.47</v>
       </c>
       <c r="R45">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="S45">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="T45">
-        <v>6.5</v>
+        <v>4.2</v>
       </c>
       <c r="U45">
-        <v>1.65</v>
+        <v>2.03</v>
       </c>
       <c r="V45">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="W45">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="X45">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Z45">
-        <v>10</v>
+        <v>5.95</v>
       </c>
       <c r="AA45">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="AB45">
-        <v>4.5</v>
+        <v>2.97</v>
       </c>
       <c r="AC45">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AD45">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AE45">
-        <v>1.75</v>
+        <v>1.34</v>
       </c>
       <c r="AF45">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG45">
-        <v>2.77</v>
+        <v>3.1</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AK45">
-        <v>1.06</v>
+        <v>1.8</v>
       </c>
       <c r="AL45">
         <v>0</v>

--- a/jogos_2026-10-13.xlsx
+++ b/jogos_2026-10-13.xlsx
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,80 +6666,80 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.27</v>
+        <v>2.45</v>
       </c>
       <c r="O39">
-        <v>3.96</v>
+        <v>3.64</v>
       </c>
       <c r="P39">
-        <v>3.11</v>
+        <v>3.01</v>
       </c>
       <c r="Q39">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="R39">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="S39">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T39">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="U39">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="V39">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="W39">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X39">
         <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="Z39">
-        <v>4.95</v>
+        <v>4.15</v>
       </c>
       <c r="AA39">
-        <v>1.46</v>
+        <v>1.66</v>
       </c>
       <c r="AB39">
-        <v>2.44</v>
+        <v>2.1</v>
       </c>
       <c r="AC39">
-        <v>2.05</v>
+        <v>2.56</v>
       </c>
       <c r="AD39">
+        <v>1.41</v>
+      </c>
+      <c r="AE39">
+        <v>1.13</v>
+      </c>
+      <c r="AF39">
+        <v>1.56</v>
+      </c>
+      <c r="AG39">
+        <v>2.27</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39">
+        <v>1.33</v>
+      </c>
+      <c r="AK39">
         <v>1.68</v>
-      </c>
-      <c r="AE39">
-        <v>1.25</v>
-      </c>
-      <c r="AF39">
-        <v>1.42</v>
-      </c>
-      <c r="AG39">
-        <v>2.69</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39">
-        <v>1.25</v>
-      </c>
-      <c r="AK39">
-        <v>1.59</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.45</v>
+        <v>34</v>
       </c>
       <c r="O40">
-        <v>3.64</v>
+        <v>15.5</v>
       </c>
       <c r="P40">
-        <v>3.01</v>
+        <v>1.09</v>
       </c>
       <c r="Q40">
-        <v>2.75</v>
+        <v>11</v>
       </c>
       <c r="R40">
-        <v>2.39</v>
+        <v>4.09</v>
       </c>
       <c r="S40">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="T40">
-        <v>3.3</v>
+        <v>6</v>
       </c>
       <c r="U40">
-        <v>2.45</v>
+        <v>1.58</v>
       </c>
       <c r="V40">
-        <v>1.5</v>
+        <v>2.35</v>
       </c>
       <c r="W40">
-        <v>1.11</v>
+        <v>1.43</v>
       </c>
       <c r="X40">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y40">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="Z40">
-        <v>4.15</v>
+        <v>13</v>
       </c>
       <c r="AA40">
-        <v>1.66</v>
+        <v>1.16</v>
       </c>
       <c r="AB40">
-        <v>2.1</v>
+        <v>4.95</v>
       </c>
       <c r="AC40">
-        <v>2.56</v>
+        <v>1.41</v>
       </c>
       <c r="AD40">
-        <v>1.41</v>
+        <v>2.64</v>
       </c>
       <c r="AE40">
-        <v>1.13</v>
+        <v>1.71</v>
       </c>
       <c r="AF40">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="AG40">
-        <v>2.27</v>
+        <v>1.99</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.33</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AK40">
-        <v>1.68</v>
+        <v>1</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>34</v>
+        <v>7.5</v>
       </c>
       <c r="O41">
-        <v>15.5</v>
+        <v>5.74</v>
       </c>
       <c r="P41">
-        <v>1.09</v>
+        <v>1.41</v>
       </c>
       <c r="Q41">
-        <v>11</v>
+        <v>6.8</v>
       </c>
       <c r="R41">
-        <v>4.09</v>
+        <v>3.2</v>
       </c>
       <c r="S41">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="T41">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="U41">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="V41">
-        <v>2.35</v>
+        <v>2.07</v>
       </c>
       <c r="W41">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="X41">
         <v>1</v>
       </c>
       <c r="Y41">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Z41">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AA41">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AB41">
-        <v>4.95</v>
+        <v>4.5</v>
       </c>
       <c r="AC41">
-        <v>1.41</v>
+        <v>1.65</v>
       </c>
       <c r="AD41">
-        <v>2.64</v>
+        <v>2.1</v>
       </c>
       <c r="AE41">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AF41">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AG41">
-        <v>1.99</v>
+        <v>2.77</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>8.699999999999999</v>
+        <v>1.14</v>
       </c>
       <c r="AK41">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>7.5</v>
+        <v>1.46</v>
       </c>
       <c r="O42">
-        <v>5.74</v>
+        <v>4.87</v>
       </c>
       <c r="P42">
-        <v>1.41</v>
+        <v>7.9</v>
       </c>
       <c r="Q42">
-        <v>6.8</v>
+        <v>1.62</v>
       </c>
       <c r="R42">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="S42">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="T42">
-        <v>6.5</v>
+        <v>3.6</v>
       </c>
       <c r="U42">
-        <v>1.65</v>
+        <v>2.23</v>
       </c>
       <c r="V42">
-        <v>2.07</v>
+        <v>1.62</v>
       </c>
       <c r="W42">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="X42">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="Z42">
-        <v>10</v>
+        <v>4.9</v>
       </c>
       <c r="AA42">
-        <v>1.18</v>
+        <v>1.47</v>
       </c>
       <c r="AB42">
-        <v>4.5</v>
+        <v>2.62</v>
       </c>
       <c r="AC42">
-        <v>1.65</v>
+        <v>2.25</v>
       </c>
       <c r="AD42">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AE42">
-        <v>1.75</v>
+        <v>1.23</v>
       </c>
       <c r="AF42">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
       <c r="AG42">
-        <v>2.77</v>
+        <v>1.83</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AK42">
-        <v>1.06</v>
+        <v>3.6</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.31</v>
+        <v>1.99</v>
       </c>
       <c r="O43">
-        <v>6.04</v>
+        <v>4.09</v>
       </c>
       <c r="P43">
-        <v>11.9</v>
+        <v>3.72</v>
       </c>
       <c r="Q43">
-        <v>1.7</v>
+        <v>2.47</v>
       </c>
       <c r="R43">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="S43">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="T43">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="U43">
-        <v>2.35</v>
+        <v>2.03</v>
       </c>
       <c r="V43">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="W43">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="X43">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="Z43">
-        <v>4.33</v>
+        <v>5.95</v>
       </c>
       <c r="AA43">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AB43">
-        <v>2.37</v>
+        <v>2.97</v>
       </c>
       <c r="AC43">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AD43">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AE43">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="AF43">
-        <v>2.11</v>
+        <v>1.36</v>
       </c>
       <c r="AG43">
-        <v>1.66</v>
+        <v>3.1</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AK43">
-        <v>3.92</v>
+        <v>1.8</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.46</v>
+        <v>2.27</v>
       </c>
       <c r="O44">
-        <v>4.87</v>
+        <v>3.96</v>
       </c>
       <c r="P44">
-        <v>7.9</v>
+        <v>3.11</v>
       </c>
       <c r="Q44">
-        <v>1.62</v>
+        <v>2.64</v>
       </c>
       <c r="R44">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="S44">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T44">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="U44">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="V44">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="W44">
         <v>1.17</v>
       </c>
       <c r="X44">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y44">
         <v>1.11</v>
       </c>
       <c r="Z44">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="AA44">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AB44">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="AC44">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AD44">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AE44">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AF44">
-        <v>1.85</v>
+        <v>1.42</v>
       </c>
       <c r="AG44">
-        <v>1.83</v>
+        <v>2.69</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AK44">
-        <v>3.6</v>
+        <v>1.59</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.99</v>
+        <v>1.31</v>
       </c>
       <c r="O45">
-        <v>4.09</v>
+        <v>6.04</v>
       </c>
       <c r="P45">
-        <v>3.72</v>
+        <v>11.9</v>
       </c>
       <c r="Q45">
-        <v>2.47</v>
+        <v>1.7</v>
       </c>
       <c r="R45">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="S45">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="T45">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="U45">
-        <v>2.03</v>
+        <v>2.35</v>
       </c>
       <c r="V45">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="W45">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="X45">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y45">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="Z45">
-        <v>5.95</v>
+        <v>4.33</v>
       </c>
       <c r="AA45">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AB45">
-        <v>2.97</v>
+        <v>2.37</v>
       </c>
       <c r="AC45">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AD45">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AE45">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="AF45">
-        <v>1.36</v>
+        <v>2.11</v>
       </c>
       <c r="AG45">
-        <v>3.1</v>
+        <v>1.66</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AK45">
-        <v>1.8</v>
+        <v>3.92</v>
       </c>
       <c r="AL45">
         <v>0</v>

--- a/jogos_2026-10-13.xlsx
+++ b/jogos_2026-10-13.xlsx
@@ -635,10 +635,10 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="O2">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P2">
         <v>2.8</v>
@@ -656,13 +656,13 @@
         <v>2.77</v>
       </c>
       <c r="U2">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="V2">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W2">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X2">
         <v>1.01</v>
@@ -692,7 +692,7 @@
         <v>1.77</v>
       </c>
       <c r="AG2">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK2">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1954,10 +1954,10 @@
         <v>2.06</v>
       </c>
       <c r="S10">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T10">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="U10">
         <v>2.69</v>
@@ -1966,7 +1966,7 @@
         <v>1.37</v>
       </c>
       <c r="W10">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X10">
         <v>1.01</v>
@@ -1996,7 +1996,7 @@
         <v>1.74</v>
       </c>
       <c r="AG10">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q21">
         <v>3.3</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q22">
         <v>1.97</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q23">
         <v>3.28</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -4556,55 +4556,55 @@
         <v>4.11</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AL26">
         <v>0</v>

--- a/jogos_2026-10-13.xlsx
+++ b/jogos_2026-10-13.xlsx
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="O23">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P23">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="Q23">
-        <v>3.28</v>
+        <v>2.63</v>
       </c>
       <c r="R23">
-        <v>2.31</v>
+        <v>2.49</v>
       </c>
       <c r="S23">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="T23">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="U23">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="V23">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="W23">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y23">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="Z23">
-        <v>4.7</v>
+        <v>6.65</v>
       </c>
       <c r="AA23">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AB23">
-        <v>2.3</v>
+        <v>2.97</v>
       </c>
       <c r="AC23">
-        <v>2.29</v>
+        <v>1.85</v>
       </c>
       <c r="AD23">
-        <v>1.53</v>
+        <v>1.82</v>
       </c>
       <c r="AE23">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="AF23">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AG23">
-        <v>2.55</v>
+        <v>3.11</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK23">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,80 +4221,80 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="O24">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="P24">
-        <v>2.62</v>
+        <v>4.8</v>
       </c>
       <c r="Q24">
-        <v>2.63</v>
+        <v>1.96</v>
       </c>
       <c r="R24">
+        <v>2.48</v>
+      </c>
+      <c r="S24">
+        <v>1.17</v>
+      </c>
+      <c r="T24">
+        <v>4</v>
+      </c>
+      <c r="U24">
+        <v>2.06</v>
+      </c>
+      <c r="V24">
+        <v>1.65</v>
+      </c>
+      <c r="W24">
+        <v>1.15</v>
+      </c>
+      <c r="X24">
+        <v>1.01</v>
+      </c>
+      <c r="Y24">
+        <v>1.09</v>
+      </c>
+      <c r="Z24">
+        <v>5.35</v>
+      </c>
+      <c r="AA24">
+        <v>1.42</v>
+      </c>
+      <c r="AB24">
         <v>2.49</v>
       </c>
-      <c r="S24">
+      <c r="AC24">
+        <v>2.13</v>
+      </c>
+      <c r="AD24">
+        <v>1.61</v>
+      </c>
+      <c r="AE24">
+        <v>1.21</v>
+      </c>
+      <c r="AF24">
+        <v>1.53</v>
+      </c>
+      <c r="AG24">
+        <v>2.32</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24">
         <v>1.13</v>
       </c>
-      <c r="T24">
-        <v>4.6</v>
-      </c>
-      <c r="U24">
-        <v>1.88</v>
-      </c>
-      <c r="V24">
-        <v>1.79</v>
-      </c>
-      <c r="W24">
-        <v>1.2</v>
-      </c>
-      <c r="X24">
-        <v>0</v>
-      </c>
-      <c r="Y24">
-        <v>1.05</v>
-      </c>
-      <c r="Z24">
-        <v>6.65</v>
-      </c>
-      <c r="AA24">
-        <v>1.3</v>
-      </c>
-      <c r="AB24">
-        <v>2.97</v>
-      </c>
-      <c r="AC24">
-        <v>1.85</v>
-      </c>
-      <c r="AD24">
-        <v>1.82</v>
-      </c>
-      <c r="AE24">
-        <v>1.31</v>
-      </c>
-      <c r="AF24">
-        <v>1.31</v>
-      </c>
-      <c r="AG24">
-        <v>3.11</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ24">
-        <v>1.17</v>
-      </c>
       <c r="AK24">
-        <v>1.52</v>
+        <v>2.36</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="O25">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="P25">
-        <v>4.8</v>
+        <v>2.25</v>
       </c>
       <c r="Q25">
-        <v>1.96</v>
+        <v>3.28</v>
       </c>
       <c r="R25">
-        <v>2.48</v>
+        <v>2.31</v>
       </c>
       <c r="S25">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="T25">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="U25">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="V25">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="W25">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X25">
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="Z25">
-        <v>5.35</v>
+        <v>4.7</v>
       </c>
       <c r="AA25">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="AB25">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="AC25">
-        <v>2.13</v>
+        <v>2.29</v>
       </c>
       <c r="AD25">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AE25">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AF25">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AG25">
-        <v>2.32</v>
+        <v>2.55</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AK25">
-        <v>2.36</v>
+        <v>1.36</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -5694,7 +5694,7 @@
         <v>3.75</v>
       </c>
       <c r="P33">
-        <v>4.57</v>
+        <v>4.56</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="O36">
         <v>4.7</v>
       </c>
       <c r="P36">
-        <v>6.83</v>
+        <v>7.24</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O37">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P37">
-        <v>3.56</v>
+        <v>3.61</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>3.8</v>
       </c>
       <c r="P38">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>34</v>
+        <v>7.5</v>
       </c>
       <c r="O40">
-        <v>15.5</v>
+        <v>5.74</v>
       </c>
       <c r="P40">
-        <v>1.09</v>
+        <v>1.41</v>
       </c>
       <c r="Q40">
-        <v>11</v>
+        <v>6.8</v>
       </c>
       <c r="R40">
-        <v>4.09</v>
+        <v>3.2</v>
       </c>
       <c r="S40">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="T40">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="U40">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="V40">
-        <v>2.35</v>
+        <v>2.07</v>
       </c>
       <c r="W40">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="X40">
         <v>1</v>
       </c>
       <c r="Y40">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Z40">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AA40">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AB40">
-        <v>4.95</v>
+        <v>4.5</v>
       </c>
       <c r="AC40">
-        <v>1.41</v>
+        <v>1.65</v>
       </c>
       <c r="AD40">
-        <v>2.64</v>
+        <v>2.1</v>
       </c>
       <c r="AE40">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AF40">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AG40">
-        <v>1.99</v>
+        <v>2.77</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>8.699999999999999</v>
+        <v>1.14</v>
       </c>
       <c r="AK40">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>7.5</v>
+        <v>1.46</v>
       </c>
       <c r="O41">
-        <v>5.74</v>
+        <v>4.87</v>
       </c>
       <c r="P41">
-        <v>1.41</v>
+        <v>7.9</v>
       </c>
       <c r="Q41">
-        <v>6.8</v>
+        <v>1.62</v>
       </c>
       <c r="R41">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="S41">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="T41">
-        <v>6.5</v>
+        <v>3.6</v>
       </c>
       <c r="U41">
-        <v>1.65</v>
+        <v>2.23</v>
       </c>
       <c r="V41">
-        <v>2.07</v>
+        <v>1.62</v>
       </c>
       <c r="W41">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="X41">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="Z41">
-        <v>10</v>
+        <v>4.9</v>
       </c>
       <c r="AA41">
-        <v>1.18</v>
+        <v>1.47</v>
       </c>
       <c r="AB41">
-        <v>4.5</v>
+        <v>2.62</v>
       </c>
       <c r="AC41">
-        <v>1.65</v>
+        <v>2.25</v>
       </c>
       <c r="AD41">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AE41">
-        <v>1.75</v>
+        <v>1.23</v>
       </c>
       <c r="AF41">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
       <c r="AG41">
-        <v>2.77</v>
+        <v>1.83</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AK41">
-        <v>1.06</v>
+        <v>3.6</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.46</v>
+        <v>1.99</v>
       </c>
       <c r="O42">
-        <v>4.87</v>
+        <v>4.09</v>
       </c>
       <c r="P42">
-        <v>7.9</v>
+        <v>3.72</v>
       </c>
       <c r="Q42">
-        <v>1.62</v>
+        <v>2.47</v>
       </c>
       <c r="R42">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="S42">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="T42">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="U42">
-        <v>2.23</v>
+        <v>2.03</v>
       </c>
       <c r="V42">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="W42">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X42">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z42">
-        <v>4.9</v>
+        <v>5.95</v>
       </c>
       <c r="AA42">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AB42">
-        <v>2.62</v>
+        <v>2.97</v>
       </c>
       <c r="AC42">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AD42">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AE42">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="AF42">
-        <v>1.85</v>
+        <v>1.36</v>
       </c>
       <c r="AG42">
-        <v>1.83</v>
+        <v>3.1</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AK42">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.99</v>
+        <v>2.27</v>
       </c>
       <c r="O43">
-        <v>4.09</v>
+        <v>3.96</v>
       </c>
       <c r="P43">
-        <v>3.72</v>
+        <v>3.11</v>
       </c>
       <c r="Q43">
-        <v>2.47</v>
+        <v>2.64</v>
       </c>
       <c r="R43">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S43">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="T43">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="U43">
-        <v>2.03</v>
+        <v>2.18</v>
       </c>
       <c r="V43">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="W43">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X43">
         <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z43">
-        <v>5.95</v>
+        <v>4.95</v>
       </c>
       <c r="AA43">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AB43">
-        <v>2.97</v>
+        <v>2.44</v>
       </c>
       <c r="AC43">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AD43">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AE43">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AF43">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AG43">
-        <v>3.1</v>
+        <v>2.69</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK43">
-        <v>1.8</v>
+        <v>1.59</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.27</v>
+        <v>1.31</v>
       </c>
       <c r="O44">
-        <v>3.96</v>
+        <v>6.04</v>
       </c>
       <c r="P44">
-        <v>3.11</v>
+        <v>11.9</v>
       </c>
       <c r="Q44">
-        <v>2.64</v>
+        <v>1.7</v>
       </c>
       <c r="R44">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="S44">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T44">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="U44">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="V44">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="W44">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X44">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y44">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z44">
-        <v>4.95</v>
+        <v>4.33</v>
       </c>
       <c r="AA44">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AB44">
-        <v>2.44</v>
+        <v>2.37</v>
       </c>
       <c r="AC44">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AD44">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AE44">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AF44">
-        <v>1.42</v>
+        <v>2.11</v>
       </c>
       <c r="AG44">
-        <v>2.69</v>
+        <v>1.66</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AK44">
-        <v>1.59</v>
+        <v>3.92</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.31</v>
+        <v>34</v>
       </c>
       <c r="O45">
-        <v>6.04</v>
+        <v>15.5</v>
       </c>
       <c r="P45">
-        <v>11.9</v>
+        <v>1.09</v>
       </c>
       <c r="Q45">
-        <v>1.7</v>
+        <v>11</v>
       </c>
       <c r="R45">
-        <v>2.52</v>
+        <v>4.09</v>
       </c>
       <c r="S45">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="T45">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="U45">
+        <v>1.58</v>
+      </c>
+      <c r="V45">
         <v>2.35</v>
       </c>
-      <c r="V45">
-        <v>1.55</v>
-      </c>
       <c r="W45">
-        <v>1.12</v>
+        <v>1.43</v>
       </c>
       <c r="X45">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y45">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="Z45">
-        <v>4.33</v>
+        <v>13</v>
       </c>
       <c r="AA45">
-        <v>1.57</v>
+        <v>1.16</v>
       </c>
       <c r="AB45">
-        <v>2.37</v>
+        <v>4.95</v>
       </c>
       <c r="AC45">
-        <v>2.3</v>
+        <v>1.41</v>
       </c>
       <c r="AD45">
-        <v>1.55</v>
+        <v>2.64</v>
       </c>
       <c r="AE45">
-        <v>1.19</v>
+        <v>1.71</v>
       </c>
       <c r="AF45">
-        <v>2.11</v>
+        <v>1.73</v>
       </c>
       <c r="AG45">
-        <v>1.66</v>
+        <v>1.99</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.08</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AK45">
-        <v>3.92</v>
+        <v>1</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7976,7 +7976,7 @@
         <v>3.85</v>
       </c>
       <c r="P47">
-        <v>4.86</v>
+        <v>4.85</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="N48">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="O48">
         <v>3.6</v>

--- a/jogos_2026-10-13.xlsx
+++ b/jogos_2026-10-13.xlsx
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.48</v>
+        <v>3.58</v>
       </c>
       <c r="O15">
-        <v>3.91</v>
+        <v>3.98</v>
       </c>
       <c r="P15">
-        <v>2.81</v>
+        <v>2.06</v>
       </c>
       <c r="Q15">
-        <v>2.97</v>
+        <v>3.59</v>
       </c>
       <c r="R15">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="S15">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T15">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="U15">
         <v>2.25</v>
       </c>
       <c r="V15">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W15">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X15">
         <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z15">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AA15">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB15">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC15">
-        <v>2.33</v>
+        <v>2.53</v>
       </c>
       <c r="AD15">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="AE15">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF15">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AG15">
-        <v>2.63</v>
+        <v>2.32</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.3</v>
+        <v>1.75</v>
       </c>
       <c r="AK15">
-        <v>1.55</v>
+        <v>1.2</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,80 +2917,80 @@
         </is>
       </c>
       <c r="N16">
-        <v>3.58</v>
+        <v>2.48</v>
       </c>
       <c r="O16">
-        <v>3.98</v>
+        <v>3.91</v>
       </c>
       <c r="P16">
-        <v>2.06</v>
+        <v>2.81</v>
       </c>
       <c r="Q16">
-        <v>3.59</v>
+        <v>2.97</v>
       </c>
       <c r="R16">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="S16">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T16">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="U16">
         <v>2.25</v>
       </c>
       <c r="V16">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W16">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X16">
         <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z16">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AA16">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB16">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC16">
-        <v>2.53</v>
+        <v>2.33</v>
       </c>
       <c r="AD16">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="AE16">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF16">
+        <v>1.47</v>
+      </c>
+      <c r="AG16">
+        <v>2.63</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16">
+        <v>1.3</v>
+      </c>
+      <c r="AK16">
         <v>1.55</v>
-      </c>
-      <c r="AG16">
-        <v>2.32</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16">
-        <v>1.75</v>
-      </c>
-      <c r="AK16">
-        <v>1.2</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>5.06</v>
+        <v>5.36</v>
       </c>
       <c r="O32">
-        <v>4.07</v>
+        <v>3.6</v>
       </c>
       <c r="P32">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="Q32">
         <v>6.02</v>
@@ -5564,7 +5564,7 @@
         <v>3.28</v>
       </c>
       <c r="AA32">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AB32">
         <v>1.85</v>
@@ -5582,7 +5582,7 @@
         <v>1.87</v>
       </c>
       <c r="AG32">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.19</v>
+        <v>2.4</v>
       </c>
       <c r="AK32">
         <v>1.08</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.31</v>
+        <v>34</v>
       </c>
       <c r="O44">
-        <v>6.04</v>
+        <v>15.5</v>
       </c>
       <c r="P44">
-        <v>11.9</v>
+        <v>1.09</v>
       </c>
       <c r="Q44">
-        <v>1.7</v>
+        <v>11</v>
       </c>
       <c r="R44">
-        <v>2.52</v>
+        <v>4.09</v>
       </c>
       <c r="S44">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="T44">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="U44">
+        <v>1.58</v>
+      </c>
+      <c r="V44">
         <v>2.35</v>
       </c>
-      <c r="V44">
-        <v>1.55</v>
-      </c>
       <c r="W44">
-        <v>1.12</v>
+        <v>1.43</v>
       </c>
       <c r="X44">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y44">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="Z44">
-        <v>4.33</v>
+        <v>13</v>
       </c>
       <c r="AA44">
-        <v>1.57</v>
+        <v>1.16</v>
       </c>
       <c r="AB44">
-        <v>2.37</v>
+        <v>4.95</v>
       </c>
       <c r="AC44">
-        <v>2.3</v>
+        <v>1.41</v>
       </c>
       <c r="AD44">
-        <v>1.55</v>
+        <v>2.64</v>
       </c>
       <c r="AE44">
-        <v>1.19</v>
+        <v>1.71</v>
       </c>
       <c r="AF44">
-        <v>2.11</v>
+        <v>1.73</v>
       </c>
       <c r="AG44">
-        <v>1.66</v>
+        <v>1.99</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.08</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AK44">
-        <v>3.92</v>
+        <v>1</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,80 +7644,80 @@
         </is>
       </c>
       <c r="N45">
-        <v>34</v>
+        <v>1.31</v>
       </c>
       <c r="O45">
-        <v>15.5</v>
+        <v>6.04</v>
       </c>
       <c r="P45">
-        <v>1.09</v>
+        <v>11.9</v>
       </c>
       <c r="Q45">
-        <v>11</v>
+        <v>1.7</v>
       </c>
       <c r="R45">
-        <v>4.09</v>
+        <v>2.52</v>
       </c>
       <c r="S45">
+        <v>1.3</v>
+      </c>
+      <c r="T45">
+        <v>3.5</v>
+      </c>
+      <c r="U45">
+        <v>2.35</v>
+      </c>
+      <c r="V45">
+        <v>1.55</v>
+      </c>
+      <c r="W45">
+        <v>1.12</v>
+      </c>
+      <c r="X45">
+        <v>1.02</v>
+      </c>
+      <c r="Y45">
+        <v>1.14</v>
+      </c>
+      <c r="Z45">
+        <v>4.33</v>
+      </c>
+      <c r="AA45">
+        <v>1.57</v>
+      </c>
+      <c r="AB45">
+        <v>2.37</v>
+      </c>
+      <c r="AC45">
+        <v>2.3</v>
+      </c>
+      <c r="AD45">
+        <v>1.55</v>
+      </c>
+      <c r="AE45">
+        <v>1.19</v>
+      </c>
+      <c r="AF45">
+        <v>2.11</v>
+      </c>
+      <c r="AG45">
+        <v>1.66</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ45">
         <v>1.08</v>
       </c>
-      <c r="T45">
-        <v>6</v>
-      </c>
-      <c r="U45">
-        <v>1.58</v>
-      </c>
-      <c r="V45">
-        <v>2.35</v>
-      </c>
-      <c r="W45">
-        <v>1.43</v>
-      </c>
-      <c r="X45">
-        <v>1</v>
-      </c>
-      <c r="Y45">
-        <v>1.04</v>
-      </c>
-      <c r="Z45">
-        <v>13</v>
-      </c>
-      <c r="AA45">
-        <v>1.16</v>
-      </c>
-      <c r="AB45">
-        <v>4.95</v>
-      </c>
-      <c r="AC45">
-        <v>1.41</v>
-      </c>
-      <c r="AD45">
-        <v>2.64</v>
-      </c>
-      <c r="AE45">
-        <v>1.71</v>
-      </c>
-      <c r="AF45">
-        <v>1.73</v>
-      </c>
-      <c r="AG45">
-        <v>1.99</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ45">
-        <v>8.699999999999999</v>
-      </c>
       <c r="AK45">
-        <v>1</v>
+        <v>3.92</v>
       </c>
       <c r="AL45">
         <v>0</v>

--- a/jogos_2026-10-13.xlsx
+++ b/jogos_2026-10-13.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="O2">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P2">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="Q2">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="R2">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="S2">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T2">
-        <v>2.77</v>
+        <v>3.01</v>
       </c>
       <c r="U2">
-        <v>3</v>
+        <v>2.59</v>
       </c>
       <c r="V2">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="W2">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z2">
-        <v>3.04</v>
+        <v>3.71</v>
       </c>
       <c r="AA2">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AB2">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="AC2">
-        <v>3.48</v>
+        <v>3.14</v>
       </c>
       <c r="AD2">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AE2">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF2">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AG2">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AK2">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="O8">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="P8">
-        <v>4.46</v>
+        <v>3.5</v>
       </c>
       <c r="Q8">
         <v>2.6</v>
@@ -1628,28 +1628,28 @@
         <v>1.91</v>
       </c>
       <c r="S8">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T8">
         <v>2.55</v>
       </c>
       <c r="U8">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="V8">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="W8">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X8">
         <v>1.05</v>
       </c>
       <c r="Y8">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="Z8">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="AA8">
         <v>2.41</v>
@@ -1658,10 +1658,10 @@
         <v>1.48</v>
       </c>
       <c r="AC8">
-        <v>4.65</v>
+        <v>4.67</v>
       </c>
       <c r="AD8">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AE8">
         <v>1.01</v>
@@ -1686,7 +1686,7 @@
         <v>1.33</v>
       </c>
       <c r="AK8">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,19 +1776,19 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="O9">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="P9">
-        <v>4.32</v>
+        <v>3.6</v>
       </c>
       <c r="Q9">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="R9">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="S9">
         <v>1.61</v>
@@ -1806,16 +1806,16 @@
         <v>1.02</v>
       </c>
       <c r="X9">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Y9">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="Z9">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AA9">
-        <v>2.73</v>
+        <v>2.64</v>
       </c>
       <c r="AB9">
         <v>1.42</v>
@@ -1824,7 +1824,7 @@
         <v>4.75</v>
       </c>
       <c r="AD9">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AE9">
         <v>1</v>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK9">
         <v>1.62</v>
@@ -1948,55 +1948,55 @@
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>2.96</v>
+        <v>2.75</v>
       </c>
       <c r="R10">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S10">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T10">
-        <v>2.75</v>
+        <v>2.57</v>
       </c>
       <c r="U10">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="V10">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W10">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Z10">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AA10">
-        <v>1.94</v>
+        <v>2.09</v>
       </c>
       <c r="AB10">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AC10">
-        <v>3.28</v>
+        <v>3.68</v>
       </c>
       <c r="AD10">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE10">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF10">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AG10">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK10">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2600,22 +2600,22 @@
         <v>5.25</v>
       </c>
       <c r="Q14">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="R14">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="S14">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T14">
-        <v>3.12</v>
+        <v>2.92</v>
       </c>
       <c r="U14">
         <v>2.4</v>
       </c>
       <c r="V14">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W14">
         <v>1.08</v>
@@ -2624,28 +2624,28 @@
         <v>1</v>
       </c>
       <c r="Y14">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="Z14">
-        <v>4.2</v>
+        <v>3.58</v>
       </c>
       <c r="AA14">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB14">
         <v>2</v>
       </c>
       <c r="AC14">
-        <v>2.64</v>
+        <v>2.46</v>
       </c>
       <c r="AD14">
         <v>1.32</v>
       </c>
       <c r="AE14">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF14">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AG14">
         <v>1.84</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK14">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="N15">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="O15">
-        <v>3.98</v>
+        <v>3.8</v>
       </c>
       <c r="P15">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="Q15">
-        <v>3.59</v>
+        <v>3.66</v>
       </c>
       <c r="R15">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="S15">
         <v>1.3</v>
@@ -2781,7 +2781,7 @@
         <v>1.57</v>
       </c>
       <c r="W15">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X15">
         <v>1.01</v>
@@ -2793,16 +2793,16 @@
         <v>4.4</v>
       </c>
       <c r="AA15">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB15">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AC15">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="AD15">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AE15">
         <v>1.13</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AK15">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,34 +2917,34 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="O16">
-        <v>3.91</v>
+        <v>3.7</v>
       </c>
       <c r="P16">
-        <v>2.81</v>
+        <v>2.52</v>
       </c>
       <c r="Q16">
-        <v>2.97</v>
+        <v>2.8</v>
       </c>
       <c r="R16">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="S16">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T16">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="U16">
         <v>2.25</v>
       </c>
       <c r="V16">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W16">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X16">
         <v>1.01</v>
@@ -2959,10 +2959,10 @@
         <v>1.57</v>
       </c>
       <c r="AB16">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="AC16">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="AD16">
         <v>1.54</v>
@@ -2974,7 +2974,7 @@
         <v>1.47</v>
       </c>
       <c r="AG16">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AK16">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.99</v>
+        <v>2.13</v>
       </c>
       <c r="O18">
-        <v>2.67</v>
+        <v>2.61</v>
       </c>
       <c r="P18">
-        <v>2.52</v>
+        <v>3.94</v>
       </c>
       <c r="Q18">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="R18">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="S18">
-        <v>1.41</v>
+        <v>1.7</v>
       </c>
       <c r="T18">
-        <v>2.75</v>
+        <v>1.99</v>
       </c>
       <c r="U18">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="V18">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="W18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X18">
+        <v>1.1</v>
+      </c>
+      <c r="Y18">
+        <v>1.64</v>
+      </c>
+      <c r="Z18">
+        <v>2.08</v>
+      </c>
+      <c r="AA18">
+        <v>3.11</v>
+      </c>
+      <c r="AB18">
+        <v>1.3</v>
+      </c>
+      <c r="AC18">
+        <v>6.35</v>
+      </c>
+      <c r="AD18">
         <v>1.06</v>
       </c>
-      <c r="Y18">
-        <v>1.33</v>
-      </c>
-      <c r="Z18">
-        <v>3.25</v>
-      </c>
-      <c r="AA18">
-        <v>2.12</v>
-      </c>
-      <c r="AB18">
-        <v>1.65</v>
-      </c>
-      <c r="AC18">
-        <v>3.34</v>
-      </c>
-      <c r="AD18">
-        <v>1.27</v>
-      </c>
       <c r="AE18">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF18">
-        <v>1.78</v>
+        <v>2.45</v>
       </c>
       <c r="AG18">
-        <v>1.91</v>
+        <v>1.5</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AK18">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.33</v>
+        <v>2.99</v>
       </c>
       <c r="O19">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="P19">
-        <v>3.25</v>
+        <v>2.49</v>
       </c>
       <c r="Q19">
-        <v>3.04</v>
+        <v>3.84</v>
       </c>
       <c r="R19">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="S19">
-        <v>1.7</v>
+        <v>1.41</v>
       </c>
       <c r="T19">
-        <v>1.99</v>
+        <v>2.75</v>
       </c>
       <c r="U19">
-        <v>4.25</v>
+        <v>3.3</v>
       </c>
       <c r="V19">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="W19">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X19">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="Y19">
-        <v>1.68</v>
+        <v>1.33</v>
       </c>
       <c r="Z19">
-        <v>2.15</v>
+        <v>3.27</v>
       </c>
       <c r="AA19">
-        <v>3.17</v>
+        <v>2.11</v>
       </c>
       <c r="AB19">
-        <v>1.3</v>
+        <v>1.65</v>
       </c>
       <c r="AC19">
-        <v>6.35</v>
+        <v>3.34</v>
       </c>
       <c r="AD19">
-        <v>1.06</v>
+        <v>1.27</v>
       </c>
       <c r="AE19">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF19">
-        <v>2.42</v>
+        <v>1.85</v>
       </c>
       <c r="AG19">
-        <v>1.49</v>
+        <v>1.85</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="AK19">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3744,7 +3744,7 @@
         <v>3.3</v>
       </c>
       <c r="R21">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="S21">
         <v>1.24</v>
@@ -3759,7 +3759,7 @@
         <v>1.55</v>
       </c>
       <c r="W21">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X21">
         <v>1.01</v>
@@ -3907,22 +3907,22 @@
         <v>1.97</v>
       </c>
       <c r="R22">
-        <v>2.49</v>
+        <v>2.6</v>
       </c>
       <c r="S22">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T22">
         <v>3.76</v>
       </c>
       <c r="U22">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="V22">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="W22">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X22">
         <v>1.01</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AK22">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4073,10 +4073,10 @@
         <v>2.49</v>
       </c>
       <c r="S23">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="T23">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="U23">
         <v>1.88</v>
@@ -4085,7 +4085,7 @@
         <v>1.79</v>
       </c>
       <c r="W23">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X23">
         <v>0</v>
@@ -4230,25 +4230,25 @@
         <v>4.8</v>
       </c>
       <c r="Q24">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="R24">
         <v>2.48</v>
       </c>
       <c r="S24">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T24">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="U24">
         <v>2.06</v>
       </c>
       <c r="V24">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="W24">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X24">
         <v>1.01</v>
@@ -4384,34 +4384,34 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="O25">
         <v>3.6</v>
       </c>
       <c r="P25">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q25">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="R25">
         <v>2.31</v>
       </c>
       <c r="S25">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="T25">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U25">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="V25">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W25">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X25">
         <v>1.01</v>
@@ -4441,7 +4441,7 @@
         <v>1.44</v>
       </c>
       <c r="AG25">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK25">
         <v>1.36</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="O26">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P26">
-        <v>4.11</v>
+        <v>4.33</v>
       </c>
       <c r="Q26">
-        <v>2.09</v>
+        <v>2.19</v>
       </c>
       <c r="R26">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="S26">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="T26">
-        <v>3.12</v>
+        <v>2.94</v>
       </c>
       <c r="U26">
-        <v>2.45</v>
+        <v>2.61</v>
       </c>
       <c r="V26">
         <v>1.44</v>
       </c>
       <c r="W26">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y26">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z26">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="AA26">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AB26">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC26">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AD26">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AE26">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF26">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="AG26">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AK26">
-        <v>2.18</v>
+        <v>2.07</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5564,7 +5564,7 @@
         <v>3.28</v>
       </c>
       <c r="AA32">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AB32">
         <v>1.85</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="O38">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P38">
-        <v>3.7</v>
+        <v>3.69</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="O39">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="P39">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="Q39">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="R39">
-        <v>2.39</v>
+        <v>2.2</v>
       </c>
       <c r="S39">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T39">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="U39">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="V39">
         <v>1.5</v>
       </c>
       <c r="W39">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y39">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z39">
-        <v>4.15</v>
+        <v>4.45</v>
       </c>
       <c r="AA39">
         <v>1.66</v>
       </c>
       <c r="AB39">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AC39">
-        <v>2.56</v>
+        <v>2.39</v>
       </c>
       <c r="AD39">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AE39">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF39">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="AG39">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AK39">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,19 +6829,19 @@
         </is>
       </c>
       <c r="N40">
-        <v>7.5</v>
+        <v>7.75</v>
       </c>
       <c r="O40">
-        <v>5.74</v>
+        <v>6.5</v>
       </c>
       <c r="P40">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="Q40">
-        <v>6.8</v>
+        <v>5.03</v>
       </c>
       <c r="R40">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="S40">
         <v>1.15</v>
@@ -6850,10 +6850,10 @@
         <v>6.5</v>
       </c>
       <c r="U40">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="V40">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="W40">
         <v>1.3</v>
@@ -6874,13 +6874,13 @@
         <v>4.5</v>
       </c>
       <c r="AC40">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="AD40">
-        <v>2.1</v>
+        <v>2.48</v>
       </c>
       <c r="AE40">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AF40">
         <v>1.4</v>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AK40">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,22 +6992,22 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.46</v>
+        <v>1.27</v>
       </c>
       <c r="O41">
-        <v>4.87</v>
+        <v>5.6</v>
       </c>
       <c r="P41">
-        <v>7.9</v>
+        <v>9.5</v>
       </c>
       <c r="Q41">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="R41">
         <v>2.67</v>
       </c>
       <c r="S41">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T41">
         <v>3.6</v>
@@ -7022,7 +7022,7 @@
         <v>1.17</v>
       </c>
       <c r="X41">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
         <v>1.11</v>
@@ -7031,25 +7031,25 @@
         <v>4.9</v>
       </c>
       <c r="AA41">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB41">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AC41">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AD41">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AE41">
         <v>1.23</v>
       </c>
       <c r="AF41">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG41">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AK41">
         <v>3.6</v>
@@ -7155,34 +7155,34 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="O42">
-        <v>4.09</v>
+        <v>4.05</v>
       </c>
       <c r="P42">
-        <v>3.72</v>
+        <v>3.52</v>
       </c>
       <c r="Q42">
-        <v>2.47</v>
+        <v>2.26</v>
       </c>
       <c r="R42">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="S42">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="T42">
         <v>4.2</v>
       </c>
       <c r="U42">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="V42">
         <v>1.75</v>
       </c>
       <c r="W42">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X42">
         <v>1.01</v>
@@ -7191,28 +7191,28 @@
         <v>1.07</v>
       </c>
       <c r="Z42">
-        <v>5.95</v>
+        <v>6.1</v>
       </c>
       <c r="AA42">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB42">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="AC42">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AD42">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AE42">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AF42">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AG42">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK42">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,19 +7318,19 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="O43">
-        <v>3.96</v>
+        <v>3.8</v>
       </c>
       <c r="P43">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="Q43">
-        <v>2.64</v>
+        <v>2.48</v>
       </c>
       <c r="R43">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="S43">
         <v>1.25</v>
@@ -7363,19 +7363,19 @@
         <v>2.44</v>
       </c>
       <c r="AC43">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="AD43">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AE43">
         <v>1.25</v>
       </c>
       <c r="AF43">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AG43">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>1.25</v>
       </c>
       <c r="AK43">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,34 +7481,34 @@
         </is>
       </c>
       <c r="N44">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="O44">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="P44">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Q44">
-        <v>11</v>
+        <v>11.18</v>
       </c>
       <c r="R44">
         <v>4.09</v>
       </c>
       <c r="S44">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="T44">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="U44">
         <v>1.58</v>
       </c>
       <c r="V44">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="W44">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="X44">
         <v>1</v>
@@ -7517,7 +7517,7 @@
         <v>1.04</v>
       </c>
       <c r="Z44">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AA44">
         <v>1.16</v>
@@ -7532,7 +7532,7 @@
         <v>2.64</v>
       </c>
       <c r="AE44">
-        <v>1.71</v>
+        <v>1.84</v>
       </c>
       <c r="AF44">
         <v>1.73</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>8.699999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AK44">
         <v>1</v>
@@ -7644,37 +7644,37 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="O45">
-        <v>6.04</v>
+        <v>6.5</v>
       </c>
       <c r="P45">
-        <v>11.9</v>
+        <v>13</v>
       </c>
       <c r="Q45">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="R45">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="S45">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T45">
         <v>3.5</v>
       </c>
       <c r="U45">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="V45">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W45">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X45">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y45">
         <v>1.14</v>
@@ -7689,19 +7689,19 @@
         <v>2.37</v>
       </c>
       <c r="AC45">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AD45">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AE45">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AF45">
         <v>2.11</v>
       </c>
       <c r="AG45">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AK45">
         <v>3.92</v>
@@ -8462,22 +8462,22 @@
         <v>2</v>
       </c>
       <c r="O50">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P50">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="Q50">
         <v>2.75</v>
       </c>
       <c r="R50">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="S50">
         <v>1.4</v>
       </c>
       <c r="T50">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="U50">
         <v>3</v>
@@ -8498,7 +8498,7 @@
         <v>2.74</v>
       </c>
       <c r="AA50">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AB50">
         <v>1.61</v>
@@ -8507,16 +8507,16 @@
         <v>3.95</v>
       </c>
       <c r="AD50">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE50">
         <v>1.02</v>
       </c>
       <c r="AF50">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AG50">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK50">
         <v>1.57</v>

--- a/jogos_2026-10-13.xlsx
+++ b/jogos_2026-10-13.xlsx
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Abu Qair Semad</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Asyut Petroleum</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,80 +1613,80 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="O8">
-        <v>3.1</v>
+        <v>2.77</v>
       </c>
       <c r="P8">
+        <v>3.6</v>
+      </c>
+      <c r="Q8">
+        <v>2.7</v>
+      </c>
+      <c r="R8">
+        <v>1.95</v>
+      </c>
+      <c r="S8">
+        <v>1.61</v>
+      </c>
+      <c r="T8">
+        <v>2.4</v>
+      </c>
+      <c r="U8">
         <v>3.5</v>
       </c>
-      <c r="Q8">
-        <v>2.6</v>
-      </c>
-      <c r="R8">
-        <v>1.91</v>
-      </c>
-      <c r="S8">
-        <v>1.44</v>
-      </c>
-      <c r="T8">
-        <v>2.55</v>
-      </c>
-      <c r="U8">
-        <v>3.25</v>
-      </c>
       <c r="V8">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="W8">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X8">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Y8">
+        <v>1.52</v>
+      </c>
+      <c r="Z8">
+        <v>2.5</v>
+      </c>
+      <c r="AA8">
+        <v>2.64</v>
+      </c>
+      <c r="AB8">
         <v>1.42</v>
       </c>
-      <c r="Z8">
-        <v>2.62</v>
-      </c>
-      <c r="AA8">
-        <v>2.41</v>
-      </c>
-      <c r="AB8">
-        <v>1.48</v>
-      </c>
       <c r="AC8">
-        <v>4.67</v>
+        <v>4.75</v>
       </c>
       <c r="AD8">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AE8">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AF8">
         <v>2.15</v>
       </c>
       <c r="AG8">
+        <v>1.61</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8">
+        <v>1.25</v>
+      </c>
+      <c r="AK8">
         <v>1.62</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8">
-        <v>1.33</v>
-      </c>
-      <c r="AK8">
-        <v>1.72</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Abu Qair Semad</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Asyut Petroleum</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="O9">
-        <v>2.77</v>
+        <v>3.1</v>
       </c>
       <c r="P9">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q9">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="R9">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="S9">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="T9">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="U9">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="V9">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="W9">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X9">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Y9">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="Z9">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AA9">
-        <v>2.64</v>
+        <v>2.41</v>
       </c>
       <c r="AB9">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AC9">
-        <v>4.75</v>
+        <v>4.67</v>
       </c>
       <c r="AD9">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AE9">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AF9">
         <v>2.15</v>
       </c>
       <c r="AG9">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK9">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="O20">
-        <v>6.35</v>
+        <v>6.1</v>
       </c>
       <c r="P20">
-        <v>11.9</v>
+        <v>11</v>
       </c>
       <c r="Q20">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="R20">
         <v>3</v>
       </c>
       <c r="S20">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T20">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U20">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="V20">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="W20">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z20">
-        <v>5.55</v>
+        <v>7</v>
       </c>
       <c r="AA20">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AB20">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AC20">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="AD20">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AE20">
         <v>1.28</v>
       </c>
       <c r="AF20">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AG20">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>

--- a/jogos_2026-10-13.xlsx
+++ b/jogos_2026-10-13.xlsx
@@ -644,16 +644,16 @@
         <v>3</v>
       </c>
       <c r="Q2">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="R2">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S2">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T2">
-        <v>3.01</v>
+        <v>2.86</v>
       </c>
       <c r="U2">
         <v>2.59</v>
@@ -677,19 +677,19 @@
         <v>1.87</v>
       </c>
       <c r="AB2">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AC2">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="AD2">
         <v>1.27</v>
       </c>
       <c r="AE2">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF2">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AG2">
         <v>1.95</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>4.65</v>
+        <v>4.13</v>
       </c>
       <c r="O3">
-        <v>3.11</v>
+        <v>3.15</v>
       </c>
       <c r="P3">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1954,19 +1954,19 @@
         <v>2.1</v>
       </c>
       <c r="S10">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="T10">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="U10">
         <v>2.77</v>
       </c>
       <c r="V10">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W10">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X10">
         <v>1.02</v>
@@ -1975,19 +1975,19 @@
         <v>1.31</v>
       </c>
       <c r="Z10">
-        <v>3.14</v>
+        <v>2.92</v>
       </c>
       <c r="AA10">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="AB10">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AC10">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="AD10">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE10">
         <v>1.05</v>
@@ -1996,7 +1996,7 @@
         <v>1.8</v>
       </c>
       <c r="AG10">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -3590,10 +3590,10 @@
         <v>4</v>
       </c>
       <c r="U20">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="V20">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="W20">
         <v>1.2</v>
@@ -3602,7 +3602,7 @@
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z20">
         <v>7</v>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AK20">
         <v>4.4</v>
@@ -4565,7 +4565,7 @@
         <v>1.31</v>
       </c>
       <c r="T26">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="U26">
         <v>2.61</v>
@@ -4583,7 +4583,7 @@
         <v>1.21</v>
       </c>
       <c r="Z26">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="AA26">
         <v>1.77</v>
@@ -4601,7 +4601,7 @@
         <v>1.08</v>
       </c>
       <c r="AF26">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AG26">
         <v>1.92</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="O38">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="P38">
-        <v>3.69</v>
+        <v>3.88</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="N50">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="O50">
         <v>3.1</v>
@@ -8480,10 +8480,10 @@
         <v>2.62</v>
       </c>
       <c r="U50">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="V50">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W50">
         <v>1.05</v>
@@ -8513,10 +8513,10 @@
         <v>1.02</v>
       </c>
       <c r="AF50">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AG50">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>1.26</v>
       </c>
       <c r="AK50">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AL50">
         <v>0</v>

--- a/jogos_2026-10-13.xlsx
+++ b/jogos_2026-10-13.xlsx
@@ -807,22 +807,22 @@
         <v>1.82</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>5.09</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W3">
         <v>0</v>
@@ -831,16 +831,16 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AC3">
         <v>0</v>
@@ -852,10 +852,10 @@
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1133,22 +1133,22 @@
         <v>3.72</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W5">
         <v>0</v>
@@ -1157,16 +1157,16 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC5">
         <v>0</v>
@@ -1178,10 +1178,10 @@
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1296,22 +1296,22 @@
         <v>2.63</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W6">
         <v>0</v>
@@ -1320,16 +1320,16 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC6">
         <v>0</v>
@@ -1341,10 +1341,10 @@
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.19</v>
+        <v>1.96</v>
       </c>
       <c r="O11">
-        <v>3.69</v>
+        <v>3.32</v>
       </c>
       <c r="P11">
-        <v>3.11</v>
+        <v>3.36</v>
       </c>
       <c r="Q11">
         <v>0</v>

--- a/jogos_2026-10-13.xlsx
+++ b/jogos_2026-10-13.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O2">
         <v>3.2</v>
       </c>
       <c r="P2">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q2">
         <v>2.5</v>
@@ -1655,7 +1655,7 @@
         <v>2.64</v>
       </c>
       <c r="AB8">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AC8">
         <v>4.75</v>
@@ -1776,43 +1776,43 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="O9">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P9">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q9">
         <v>2.6</v>
       </c>
       <c r="R9">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="S9">
         <v>1.44</v>
       </c>
       <c r="T9">
-        <v>2.55</v>
+        <v>2.27</v>
       </c>
       <c r="U9">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="V9">
         <v>1.3</v>
       </c>
       <c r="W9">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X9">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y9">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="Z9">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="AA9">
         <v>2.41</v>
@@ -1821,13 +1821,13 @@
         <v>1.48</v>
       </c>
       <c r="AC9">
-        <v>4.67</v>
+        <v>4.8</v>
       </c>
       <c r="AD9">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AE9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF9">
         <v>2.15</v>
@@ -1849,7 +1849,7 @@
         <v>1.33</v>
       </c>
       <c r="AK9">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1954,10 +1954,10 @@
         <v>2.1</v>
       </c>
       <c r="S10">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="T10">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="U10">
         <v>2.77</v>
@@ -1966,7 +1966,7 @@
         <v>1.34</v>
       </c>
       <c r="W10">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X10">
         <v>1.02</v>
@@ -3246,10 +3246,10 @@
         <v>2.13</v>
       </c>
       <c r="O18">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="P18">
-        <v>3.94</v>
+        <v>3.7</v>
       </c>
       <c r="Q18">
         <v>2.88</v>
@@ -3267,37 +3267,37 @@
         <v>4</v>
       </c>
       <c r="V18">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W18">
         <v>1.01</v>
       </c>
       <c r="X18">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Y18">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Z18">
         <v>2.08</v>
       </c>
       <c r="AA18">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="AB18">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AC18">
-        <v>6.35</v>
+        <v>7</v>
       </c>
       <c r="AD18">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AE18">
         <v>1.02</v>
       </c>
       <c r="AF18">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AG18">
         <v>1.5</v>
@@ -3415,19 +3415,19 @@
         <v>2.49</v>
       </c>
       <c r="Q19">
-        <v>3.84</v>
+        <v>3.5</v>
       </c>
       <c r="R19">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="S19">
         <v>1.41</v>
       </c>
       <c r="T19">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="U19">
-        <v>3.3</v>
+        <v>2.91</v>
       </c>
       <c r="V19">
         <v>1.36</v>
@@ -3436,31 +3436,31 @@
         <v>1.05</v>
       </c>
       <c r="X19">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y19">
         <v>1.33</v>
       </c>
       <c r="Z19">
-        <v>3.27</v>
+        <v>2.83</v>
       </c>
       <c r="AA19">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AB19">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC19">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="AD19">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AE19">
         <v>1.05</v>
       </c>
       <c r="AF19">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG19">
         <v>1.85</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AK19">
         <v>1.36</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="O20">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="P20">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Q20">
         <v>1.55</v>
@@ -3593,7 +3593,7 @@
         <v>2</v>
       </c>
       <c r="V20">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="W20">
         <v>1.2</v>
@@ -3608,10 +3608,10 @@
         <v>7</v>
       </c>
       <c r="AA20">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AB20">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AC20">
         <v>1.96</v>
@@ -3732,7 +3732,7 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="O21">
         <v>3.5</v>
@@ -3747,16 +3747,16 @@
         <v>2.38</v>
       </c>
       <c r="S21">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T21">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="U21">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="V21">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="W21">
         <v>1.14</v>
@@ -3765,31 +3765,31 @@
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z21">
-        <v>4.3</v>
+        <v>4.72</v>
       </c>
       <c r="AA21">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AB21">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AC21">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AD21">
+        <v>1.43</v>
+      </c>
+      <c r="AE21">
+        <v>1.18</v>
+      </c>
+      <c r="AF21">
         <v>1.46</v>
       </c>
-      <c r="AE21">
-        <v>1.16</v>
-      </c>
-      <c r="AF21">
-        <v>1.49</v>
-      </c>
       <c r="AG21">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK21">
         <v>1.36</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="O22">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="P22">
-        <v>5</v>
+        <v>2.62</v>
       </c>
       <c r="Q22">
-        <v>1.97</v>
+        <v>2.91</v>
       </c>
       <c r="R22">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="S22">
         <v>1.2</v>
       </c>
       <c r="T22">
-        <v>3.76</v>
+        <v>4.5</v>
       </c>
       <c r="U22">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="V22">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="W22">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="X22">
         <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="Z22">
-        <v>5.4</v>
+        <v>6.55</v>
       </c>
       <c r="AA22">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="AB22">
-        <v>2.52</v>
+        <v>3.25</v>
       </c>
       <c r="AC22">
-        <v>2.12</v>
+        <v>1.87</v>
       </c>
       <c r="AD22">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AE22">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="AF22">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="AG22">
-        <v>2.34</v>
+        <v>3.11</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AK22">
-        <v>2.4</v>
+        <v>1.42</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.3</v>
+        <v>1.48</v>
       </c>
       <c r="O23">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="P23">
-        <v>2.62</v>
+        <v>4.8</v>
       </c>
       <c r="Q23">
+        <v>1.93</v>
+      </c>
+      <c r="R23">
+        <v>2.45</v>
+      </c>
+      <c r="S23">
+        <v>1.22</v>
+      </c>
+      <c r="T23">
+        <v>3.75</v>
+      </c>
+      <c r="U23">
+        <v>1.89</v>
+      </c>
+      <c r="V23">
+        <v>1.49</v>
+      </c>
+      <c r="W23">
+        <v>1.1</v>
+      </c>
+      <c r="X23">
+        <v>1.02</v>
+      </c>
+      <c r="Y23">
+        <v>1.1</v>
+      </c>
+      <c r="Z23">
+        <v>5.05</v>
+      </c>
+      <c r="AA23">
+        <v>1.47</v>
+      </c>
+      <c r="AB23">
         <v>2.63</v>
       </c>
-      <c r="R23">
-        <v>2.49</v>
-      </c>
-      <c r="S23">
-        <v>1.17</v>
-      </c>
-      <c r="T23">
-        <v>4.5</v>
-      </c>
-      <c r="U23">
-        <v>1.88</v>
-      </c>
-      <c r="V23">
-        <v>1.79</v>
-      </c>
-      <c r="W23">
-        <v>1.22</v>
-      </c>
-      <c r="X23">
-        <v>0</v>
-      </c>
-      <c r="Y23">
-        <v>1.05</v>
-      </c>
-      <c r="Z23">
-        <v>6.65</v>
-      </c>
-      <c r="AA23">
-        <v>1.3</v>
-      </c>
-      <c r="AB23">
-        <v>2.97</v>
-      </c>
       <c r="AC23">
-        <v>1.85</v>
+        <v>2.34</v>
       </c>
       <c r="AD23">
-        <v>1.82</v>
+        <v>1.55</v>
       </c>
       <c r="AE23">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AF23">
-        <v>1.31</v>
+        <v>1.59</v>
       </c>
       <c r="AG23">
-        <v>3.11</v>
+        <v>2.19</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AK23">
-        <v>1.52</v>
+        <v>2.39</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="O24">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="P24">
-        <v>4.8</v>
+        <v>2.55</v>
       </c>
       <c r="Q24">
-        <v>1.94</v>
+        <v>3.02</v>
       </c>
       <c r="R24">
-        <v>2.48</v>
+        <v>2.24</v>
       </c>
       <c r="S24">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T24">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="U24">
-        <v>2.06</v>
+        <v>2.38</v>
       </c>
       <c r="V24">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="W24">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X24">
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="Z24">
-        <v>5.35</v>
+        <v>4.33</v>
       </c>
       <c r="AA24">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="AB24">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="AC24">
-        <v>2.13</v>
+        <v>2.51</v>
       </c>
       <c r="AD24">
-        <v>1.61</v>
+        <v>1.46</v>
       </c>
       <c r="AE24">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AF24">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG24">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AK24">
-        <v>2.36</v>
+        <v>1.41</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,61 +4384,61 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.65</v>
+        <v>1.5</v>
       </c>
       <c r="O25">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="P25">
-        <v>2.3</v>
+        <v>4.8</v>
       </c>
       <c r="Q25">
-        <v>3.1</v>
+        <v>1.92</v>
       </c>
       <c r="R25">
-        <v>2.31</v>
+        <v>2.62</v>
       </c>
       <c r="S25">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="T25">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="U25">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="V25">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="W25">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="X25">
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="Z25">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="AA25">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AB25">
-        <v>2.3</v>
+        <v>2.92</v>
       </c>
       <c r="AC25">
-        <v>2.29</v>
+        <v>1.86</v>
       </c>
       <c r="AD25">
-        <v>1.53</v>
+        <v>1.81</v>
       </c>
       <c r="AE25">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="AF25">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AG25">
         <v>2.5</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AK25">
-        <v>1.36</v>
+        <v>2.38</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4598,7 +4598,7 @@
         <v>1.31</v>
       </c>
       <c r="AE26">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF26">
         <v>1.8</v>
@@ -5525,80 +5525,80 @@
         </is>
       </c>
       <c r="N32">
-        <v>5.36</v>
+        <v>4.29</v>
       </c>
       <c r="O32">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P32">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="Q32">
-        <v>6.02</v>
+        <v>4.6</v>
       </c>
       <c r="R32">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="S32">
         <v>1.36</v>
       </c>
       <c r="T32">
-        <v>2.72</v>
+        <v>2.85</v>
       </c>
       <c r="U32">
         <v>2.72</v>
       </c>
       <c r="V32">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W32">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X32">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
+        <v>1.26</v>
+      </c>
+      <c r="Z32">
+        <v>3.2</v>
+      </c>
+      <c r="AA32">
+        <v>1.87</v>
+      </c>
+      <c r="AB32">
+        <v>1.8</v>
+      </c>
+      <c r="AC32">
+        <v>3.2</v>
+      </c>
+      <c r="AD32">
+        <v>1.26</v>
+      </c>
+      <c r="AE32">
+        <v>1.06</v>
+      </c>
+      <c r="AF32">
+        <v>1.85</v>
+      </c>
+      <c r="AG32">
+        <v>1.85</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ32">
         <v>1.25</v>
       </c>
-      <c r="Z32">
-        <v>3.28</v>
-      </c>
-      <c r="AA32">
-        <v>1.95</v>
-      </c>
-      <c r="AB32">
-        <v>1.85</v>
-      </c>
-      <c r="AC32">
-        <v>3.08</v>
-      </c>
-      <c r="AD32">
-        <v>1.28</v>
-      </c>
-      <c r="AE32">
-        <v>1.07</v>
-      </c>
-      <c r="AF32">
-        <v>1.87</v>
-      </c>
-      <c r="AG32">
-        <v>1.82</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ32">
-        <v>2.4</v>
-      </c>
       <c r="AK32">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="O33">
-        <v>3.75</v>
+        <v>3.94</v>
       </c>
       <c r="P33">
-        <v>4.56</v>
+        <v>5.03</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="O34">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="P34">
-        <v>2.87</v>
+        <v>3.05</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.38</v>
+        <v>1.38</v>
       </c>
       <c r="O35">
-        <v>3.25</v>
+        <v>4.85</v>
       </c>
       <c r="P35">
-        <v>2.87</v>
+        <v>7.19</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.38</v>
+        <v>1.88</v>
       </c>
       <c r="O36">
-        <v>4.7</v>
+        <v>3.64</v>
       </c>
       <c r="P36">
-        <v>7.24</v>
+        <v>3.79</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="O37">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="P37">
-        <v>3.61</v>
+        <v>4.4</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.78</v>
+        <v>2.52</v>
       </c>
       <c r="O38">
-        <v>3.95</v>
+        <v>3.44</v>
       </c>
       <c r="P38">
-        <v>3.88</v>
+        <v>2.58</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.65</v>
+        <v>3.5</v>
       </c>
       <c r="O47">
-        <v>3.85</v>
+        <v>3.68</v>
       </c>
       <c r="P47">
-        <v>4.85</v>
+        <v>1.95</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>3.55</v>
+        <v>1.61</v>
       </c>
       <c r="O48">
+        <v>4.05</v>
+      </c>
+      <c r="P48">
+        <v>4.98</v>
+      </c>
+      <c r="Q48">
+        <v>2.1</v>
+      </c>
+      <c r="R48">
+        <v>2.3</v>
+      </c>
+      <c r="S48">
+        <v>1.3</v>
+      </c>
+      <c r="T48">
+        <v>3.25</v>
+      </c>
+      <c r="U48">
+        <v>2.45</v>
+      </c>
+      <c r="V48">
+        <v>1.5</v>
+      </c>
+      <c r="W48">
+        <v>1.11</v>
+      </c>
+      <c r="X48">
+        <v>1.03</v>
+      </c>
+      <c r="Y48">
+        <v>1.23</v>
+      </c>
+      <c r="Z48">
         <v>3.6</v>
       </c>
-      <c r="P48">
-        <v>1.94</v>
-      </c>
-      <c r="Q48">
-        <v>0</v>
-      </c>
-      <c r="R48">
-        <v>0</v>
-      </c>
-      <c r="S48">
-        <v>0</v>
-      </c>
-      <c r="T48">
-        <v>0</v>
-      </c>
-      <c r="U48">
-        <v>0</v>
-      </c>
-      <c r="V48">
-        <v>0</v>
-      </c>
-      <c r="W48">
-        <v>0</v>
-      </c>
-      <c r="X48">
-        <v>0</v>
-      </c>
-      <c r="Y48">
-        <v>0</v>
-      </c>
-      <c r="Z48">
-        <v>0</v>
-      </c>
       <c r="AA48">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK48">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL48">
         <v>0</v>

--- a/jogos_2026-10-13.xlsx
+++ b/jogos_2026-10-13.xlsx
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,65 +1124,65 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.99</v>
+        <v>2.52</v>
       </c>
       <c r="O5">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="P5">
-        <v>3.72</v>
+        <v>2.63</v>
       </c>
       <c r="Q5">
-        <v>2.79</v>
+        <v>3.38</v>
       </c>
       <c r="R5">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="S5">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="T5">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="U5">
-        <v>3.87</v>
+        <v>3.52</v>
       </c>
       <c r="V5">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W5">
         <v>0</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y5">
+        <v>1.59</v>
+      </c>
+      <c r="Z5">
+        <v>2.17</v>
+      </c>
+      <c r="AA5">
+        <v>2.74</v>
+      </c>
+      <c r="AB5">
+        <v>1.35</v>
+      </c>
+      <c r="AC5">
+        <v>5.55</v>
+      </c>
+      <c r="AD5">
+        <v>1.08</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>2.23</v>
+      </c>
+      <c r="AG5">
         <v>1.55</v>
       </c>
-      <c r="Z5">
-        <v>2.23</v>
-      </c>
-      <c r="AA5">
-        <v>2.87</v>
-      </c>
-      <c r="AB5">
-        <v>1.34</v>
-      </c>
-      <c r="AC5">
-        <v>0</v>
-      </c>
-      <c r="AD5">
-        <v>0</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>2.39</v>
-      </c>
-      <c r="AG5">
-        <v>1.48</v>
-      </c>
       <c r="AH5" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AK5">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,31 +1287,31 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.52</v>
+        <v>1.99</v>
       </c>
       <c r="O6">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="P6">
-        <v>2.63</v>
+        <v>3.72</v>
       </c>
       <c r="Q6">
-        <v>3.38</v>
+        <v>2.79</v>
       </c>
       <c r="R6">
         <v>1.84</v>
       </c>
       <c r="S6">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="T6">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="U6">
-        <v>3.79</v>
+        <v>3.87</v>
       </c>
       <c r="V6">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W6">
         <v>0</v>
@@ -1320,16 +1320,16 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="Z6">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="AA6">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="AB6">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AC6">
         <v>0</v>
@@ -1341,10 +1341,10 @@
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>2.26</v>
+        <v>2.39</v>
       </c>
       <c r="AG6">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK6">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>3.5</v>
+        <v>2.45</v>
       </c>
       <c r="O15">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P15">
-        <v>2</v>
+        <v>2.53</v>
       </c>
       <c r="Q15">
-        <v>3.66</v>
+        <v>2.97</v>
       </c>
       <c r="R15">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="S15">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T15">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="U15">
         <v>2.25</v>
       </c>
       <c r="V15">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="W15">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X15">
         <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="Z15">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="AA15">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AB15">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AC15">
-        <v>2.44</v>
+        <v>2.27</v>
       </c>
       <c r="AD15">
+        <v>1.54</v>
+      </c>
+      <c r="AE15">
+        <v>1.18</v>
+      </c>
+      <c r="AF15">
         <v>1.47</v>
       </c>
-      <c r="AE15">
-        <v>1.13</v>
-      </c>
-      <c r="AF15">
-        <v>1.55</v>
-      </c>
       <c r="AG15">
-        <v>2.32</v>
+        <v>2.49</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.85</v>
+        <v>1.45</v>
       </c>
       <c r="AK15">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.45</v>
+        <v>3.5</v>
       </c>
       <c r="O16">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P16">
-        <v>2.52</v>
+        <v>1.98</v>
       </c>
       <c r="Q16">
-        <v>2.8</v>
+        <v>3.64</v>
       </c>
       <c r="R16">
         <v>2.27</v>
       </c>
       <c r="S16">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T16">
         <v>3.5</v>
       </c>
       <c r="U16">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="V16">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W16">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X16">
         <v>1.01</v>
       </c>
       <c r="Y16">
+        <v>1.18</v>
+      </c>
+      <c r="Z16">
+        <v>4.4</v>
+      </c>
+      <c r="AA16">
+        <v>1.66</v>
+      </c>
+      <c r="AB16">
+        <v>2.2</v>
+      </c>
+      <c r="AC16">
+        <v>2.63</v>
+      </c>
+      <c r="AD16">
+        <v>1.47</v>
+      </c>
+      <c r="AE16">
         <v>1.15</v>
       </c>
-      <c r="Z16">
-        <v>4.6</v>
-      </c>
-      <c r="AA16">
-        <v>1.57</v>
-      </c>
-      <c r="AB16">
-        <v>2.37</v>
-      </c>
-      <c r="AC16">
-        <v>2.27</v>
-      </c>
-      <c r="AD16">
-        <v>1.54</v>
-      </c>
-      <c r="AE16">
-        <v>1.18</v>
-      </c>
       <c r="AF16">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AG16">
-        <v>2.55</v>
+        <v>2.32</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.45</v>
+        <v>1.85</v>
       </c>
       <c r="AK16">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3910,7 +3910,7 @@
         <v>2.48</v>
       </c>
       <c r="S22">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="T22">
         <v>4.5</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="O23">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="P23">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="Q23">
         <v>1.93</v>
@@ -4230,7 +4230,7 @@
         <v>2.55</v>
       </c>
       <c r="Q24">
-        <v>3.02</v>
+        <v>2.7</v>
       </c>
       <c r="R24">
         <v>2.24</v>
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="O25">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="P25">
         <v>4.8</v>
@@ -4411,7 +4411,7 @@
         <v>1.73</v>
       </c>
       <c r="W25">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="X25">
         <v>1.01</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="O33">
-        <v>3.94</v>
+        <v>3.58</v>
       </c>
       <c r="P33">
-        <v>5.03</v>
+        <v>3.59</v>
       </c>
       <c r="Q33">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="R33">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S33">
         <v>1.33</v>
       </c>
       <c r="T33">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="U33">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="V33">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W33">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X33">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
         <v>1.27</v>
       </c>
       <c r="Z33">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="AA33">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AB33">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC33">
-        <v>3.07</v>
+        <v>3.14</v>
       </c>
       <c r="AD33">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE33">
         <v>1.08</v>
       </c>
       <c r="AF33">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG33">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK33">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.26</v>
+        <v>1.65</v>
       </c>
       <c r="O34">
-        <v>3.34</v>
+        <v>4.25</v>
       </c>
       <c r="P34">
-        <v>3.05</v>
+        <v>4.4</v>
       </c>
       <c r="Q34">
-        <v>2.75</v>
+        <v>2.14</v>
       </c>
       <c r="R34">
+        <v>2.44</v>
+      </c>
+      <c r="S34">
+        <v>1.25</v>
+      </c>
+      <c r="T34">
+        <v>3.8</v>
+      </c>
+      <c r="U34">
         <v>2.15</v>
       </c>
-      <c r="S34">
-        <v>1.36</v>
-      </c>
-      <c r="T34">
-        <v>2.9</v>
-      </c>
-      <c r="U34">
-        <v>2.8</v>
-      </c>
       <c r="V34">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="W34">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X34">
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.32</v>
+        <v>1.13</v>
       </c>
       <c r="Z34">
-        <v>3.37</v>
+        <v>5.2</v>
       </c>
       <c r="AA34">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="AB34">
+        <v>2.43</v>
+      </c>
+      <c r="AC34">
+        <v>2.13</v>
+      </c>
+      <c r="AD34">
         <v>1.66</v>
       </c>
-      <c r="AC34">
-        <v>3.2</v>
-      </c>
-      <c r="AD34">
-        <v>1.29</v>
-      </c>
       <c r="AE34">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AF34">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AG34">
-        <v>1.91</v>
+        <v>2.42</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AK34">
-        <v>1.57</v>
+        <v>2.17</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,80 +6014,80 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="O35">
-        <v>4.85</v>
+        <v>3.94</v>
       </c>
       <c r="P35">
-        <v>7.19</v>
+        <v>5.03</v>
       </c>
       <c r="Q35">
+        <v>2.1</v>
+      </c>
+      <c r="R35">
+        <v>2.3</v>
+      </c>
+      <c r="S35">
+        <v>1.33</v>
+      </c>
+      <c r="T35">
+        <v>3.1</v>
+      </c>
+      <c r="U35">
+        <v>2.5</v>
+      </c>
+      <c r="V35">
+        <v>1.44</v>
+      </c>
+      <c r="W35">
+        <v>1.11</v>
+      </c>
+      <c r="X35">
+        <v>1.02</v>
+      </c>
+      <c r="Y35">
+        <v>1.27</v>
+      </c>
+      <c r="Z35">
+        <v>3.3</v>
+      </c>
+      <c r="AA35">
         <v>1.8</v>
       </c>
-      <c r="R35">
-        <v>2.5</v>
-      </c>
-      <c r="S35">
+      <c r="AB35">
+        <v>2</v>
+      </c>
+      <c r="AC35">
+        <v>3.07</v>
+      </c>
+      <c r="AD35">
+        <v>1.37</v>
+      </c>
+      <c r="AE35">
+        <v>1.08</v>
+      </c>
+      <c r="AF35">
+        <v>1.8</v>
+      </c>
+      <c r="AG35">
+        <v>1.95</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35">
         <v>1.25</v>
       </c>
-      <c r="T35">
-        <v>3.5</v>
-      </c>
-      <c r="U35">
-        <v>2.25</v>
-      </c>
-      <c r="V35">
-        <v>1.57</v>
-      </c>
-      <c r="W35">
-        <v>1.14</v>
-      </c>
-      <c r="X35">
-        <v>1.01</v>
-      </c>
-      <c r="Y35">
-        <v>1.19</v>
-      </c>
-      <c r="Z35">
-        <v>4.74</v>
-      </c>
-      <c r="AA35">
-        <v>1.53</v>
-      </c>
-      <c r="AB35">
-        <v>2.45</v>
-      </c>
-      <c r="AC35">
-        <v>2.53</v>
-      </c>
-      <c r="AD35">
-        <v>1.53</v>
-      </c>
-      <c r="AE35">
-        <v>1.2</v>
-      </c>
-      <c r="AF35">
-        <v>1.75</v>
-      </c>
-      <c r="AG35">
-        <v>2</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ35">
-        <v>1.18</v>
-      </c>
       <c r="AK35">
-        <v>2.9</v>
+        <v>2.15</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.88</v>
+        <v>2.26</v>
       </c>
       <c r="O36">
-        <v>3.64</v>
+        <v>3.34</v>
       </c>
       <c r="P36">
-        <v>3.79</v>
+        <v>3.05</v>
       </c>
       <c r="Q36">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="R36">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S36">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T36">
+        <v>2.9</v>
+      </c>
+      <c r="U36">
         <v>2.8</v>
       </c>
-      <c r="U36">
-        <v>2.5</v>
-      </c>
       <c r="V36">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W36">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X36">
         <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="Z36">
-        <v>3.5</v>
+        <v>3.37</v>
       </c>
       <c r="AA36">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AB36">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AC36">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="AD36">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AE36">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF36">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG36">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK36">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.65</v>
+        <v>2.52</v>
       </c>
       <c r="O37">
-        <v>4.25</v>
+        <v>3.44</v>
       </c>
       <c r="P37">
-        <v>4.4</v>
+        <v>2.58</v>
       </c>
       <c r="Q37">
-        <v>2.14</v>
+        <v>2.9</v>
       </c>
       <c r="R37">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="S37">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T37">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="U37">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="V37">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="W37">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X37">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y37">
+        <v>1.21</v>
+      </c>
+      <c r="Z37">
+        <v>3.58</v>
+      </c>
+      <c r="AA37">
+        <v>1.87</v>
+      </c>
+      <c r="AB37">
+        <v>1.9</v>
+      </c>
+      <c r="AC37">
+        <v>3.14</v>
+      </c>
+      <c r="AD37">
+        <v>1.36</v>
+      </c>
+      <c r="AE37">
         <v>1.13</v>
       </c>
-      <c r="Z37">
-        <v>5.2</v>
-      </c>
-      <c r="AA37">
-        <v>1.5</v>
-      </c>
-      <c r="AB37">
-        <v>2.43</v>
-      </c>
-      <c r="AC37">
-        <v>2.13</v>
-      </c>
-      <c r="AD37">
-        <v>1.66</v>
-      </c>
-      <c r="AE37">
-        <v>1.2</v>
-      </c>
       <c r="AF37">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AG37">
-        <v>2.42</v>
+        <v>2.05</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AK37">
-        <v>2.17</v>
+        <v>1.53</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.52</v>
+        <v>1.38</v>
       </c>
       <c r="O38">
-        <v>3.44</v>
+        <v>4.85</v>
       </c>
       <c r="P38">
-        <v>2.58</v>
+        <v>7.19</v>
       </c>
       <c r="Q38">
-        <v>2.9</v>
+        <v>1.73</v>
       </c>
       <c r="R38">
-        <v>2.28</v>
+        <v>2.6</v>
       </c>
       <c r="S38">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T38">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="U38">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="V38">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="W38">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X38">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z38">
-        <v>3.58</v>
+        <v>4.74</v>
       </c>
       <c r="AA38">
-        <v>1.87</v>
+        <v>1.57</v>
       </c>
       <c r="AB38">
-        <v>1.9</v>
+        <v>2.38</v>
       </c>
       <c r="AC38">
-        <v>3.14</v>
+        <v>2.53</v>
       </c>
       <c r="AD38">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AE38">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AF38">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG38">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AK38">
-        <v>1.53</v>
+        <v>3</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.2</v>
+        <v>6.5</v>
       </c>
       <c r="O39">
-        <v>3.6</v>
+        <v>6.5</v>
       </c>
       <c r="P39">
-        <v>3</v>
+        <v>1.28</v>
       </c>
       <c r="Q39">
-        <v>2.63</v>
+        <v>5.03</v>
       </c>
       <c r="R39">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="S39">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="T39">
-        <v>3.34</v>
+        <v>5.75</v>
       </c>
       <c r="U39">
-        <v>2.4</v>
+        <v>1.65</v>
       </c>
       <c r="V39">
+        <v>2.11</v>
+      </c>
+      <c r="W39">
+        <v>1.3</v>
+      </c>
+      <c r="X39">
+        <v>1</v>
+      </c>
+      <c r="Y39">
+        <v>1.03</v>
+      </c>
+      <c r="Z39">
+        <v>10</v>
+      </c>
+      <c r="AA39">
+        <v>1.2</v>
+      </c>
+      <c r="AB39">
+        <v>4.5</v>
+      </c>
+      <c r="AC39">
         <v>1.5</v>
       </c>
-      <c r="W39">
-        <v>1.1</v>
-      </c>
-      <c r="X39">
-        <v>1.03</v>
-      </c>
-      <c r="Y39">
-        <v>1.16</v>
-      </c>
-      <c r="Z39">
-        <v>4.45</v>
-      </c>
-      <c r="AA39">
-        <v>1.66</v>
-      </c>
-      <c r="AB39">
-        <v>2.17</v>
-      </c>
-      <c r="AC39">
-        <v>2.39</v>
-      </c>
       <c r="AD39">
-        <v>1.52</v>
+        <v>2.5</v>
       </c>
       <c r="AE39">
-        <v>1.17</v>
+        <v>1.62</v>
       </c>
       <c r="AF39">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="AG39">
-        <v>2.38</v>
+        <v>2.77</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="AK39">
-        <v>1.62</v>
+        <v>1.05</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>7.75</v>
+        <v>1.85</v>
       </c>
       <c r="O40">
-        <v>6.5</v>
+        <v>4.2</v>
       </c>
       <c r="P40">
-        <v>1.28</v>
+        <v>3.68</v>
       </c>
       <c r="Q40">
-        <v>5.03</v>
+        <v>2.26</v>
       </c>
       <c r="R40">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="S40">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="T40">
-        <v>6.5</v>
+        <v>4.2</v>
       </c>
       <c r="U40">
-        <v>1.76</v>
+        <v>2.02</v>
       </c>
       <c r="V40">
-        <v>2.11</v>
+        <v>1.75</v>
       </c>
       <c r="W40">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="X40">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Z40">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="AA40">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AB40">
-        <v>4.5</v>
+        <v>3.04</v>
       </c>
       <c r="AC40">
-        <v>1.51</v>
+        <v>1.87</v>
       </c>
       <c r="AD40">
-        <v>2.48</v>
+        <v>1.87</v>
       </c>
       <c r="AE40">
-        <v>1.64</v>
+        <v>1.33</v>
       </c>
       <c r="AF40">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AG40">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="AK40">
-        <v>1.05</v>
+        <v>2</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,31 +6992,31 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.27</v>
+        <v>2</v>
       </c>
       <c r="O41">
-        <v>5.6</v>
+        <v>3.8</v>
       </c>
       <c r="P41">
-        <v>9.5</v>
+        <v>3.38</v>
       </c>
       <c r="Q41">
-        <v>1.69</v>
+        <v>2.5</v>
       </c>
       <c r="R41">
-        <v>2.67</v>
+        <v>2.36</v>
       </c>
       <c r="S41">
         <v>1.25</v>
       </c>
       <c r="T41">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="U41">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="V41">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="W41">
         <v>1.17</v>
@@ -7028,28 +7028,28 @@
         <v>1.11</v>
       </c>
       <c r="Z41">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AA41">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AB41">
-        <v>2.75</v>
+        <v>2.46</v>
       </c>
       <c r="AC41">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AD41">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AE41">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AF41">
-        <v>1.8</v>
+        <v>1.43</v>
       </c>
       <c r="AG41">
-        <v>1.81</v>
+        <v>2.66</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="AK41">
-        <v>3.6</v>
+        <v>1.84</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.95</v>
+        <v>16</v>
       </c>
       <c r="O42">
-        <v>4.05</v>
+        <v>10.5</v>
       </c>
       <c r="P42">
-        <v>3.52</v>
+        <v>1.1</v>
       </c>
       <c r="Q42">
-        <v>2.26</v>
+        <v>11.91</v>
       </c>
       <c r="R42">
-        <v>2.57</v>
+        <v>4.19</v>
       </c>
       <c r="S42">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="T42">
-        <v>4.2</v>
+        <v>6.5</v>
       </c>
       <c r="U42">
-        <v>2.01</v>
+        <v>1.6</v>
       </c>
       <c r="V42">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="W42">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="X42">
+        <v>1</v>
+      </c>
+      <c r="Y42">
         <v>1.01</v>
       </c>
-      <c r="Y42">
-        <v>1.07</v>
-      </c>
       <c r="Z42">
-        <v>6.1</v>
+        <v>13</v>
       </c>
       <c r="AA42">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="AB42">
-        <v>2.88</v>
+        <v>4.95</v>
       </c>
       <c r="AC42">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AD42">
-        <v>1.79</v>
+        <v>2.8</v>
       </c>
       <c r="AE42">
-        <v>1.32</v>
+        <v>1.9</v>
       </c>
       <c r="AF42">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="AG42">
-        <v>3</v>
+        <v>1.99</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.24</v>
+        <v>1.03</v>
       </c>
       <c r="AK42">
-        <v>1.85</v>
+        <v>1</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.08</v>
+        <v>1.26</v>
       </c>
       <c r="O43">
-        <v>3.8</v>
+        <v>5.8</v>
       </c>
       <c r="P43">
-        <v>3.2</v>
+        <v>13</v>
       </c>
       <c r="Q43">
-        <v>2.48</v>
+        <v>1.63</v>
       </c>
       <c r="R43">
-        <v>2.33</v>
+        <v>2.56</v>
       </c>
       <c r="S43">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T43">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="U43">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="V43">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="W43">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X43">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z43">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="AA43">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AB43">
-        <v>2.44</v>
+        <v>2.37</v>
       </c>
       <c r="AC43">
-        <v>2.21</v>
+        <v>2.31</v>
       </c>
       <c r="AD43">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AE43">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AF43">
-        <v>1.43</v>
+        <v>2.14</v>
       </c>
       <c r="AG43">
-        <v>2.66</v>
+        <v>1.64</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK43">
-        <v>1.73</v>
+        <v>4.2</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>16</v>
+        <v>1.26</v>
       </c>
       <c r="O44">
-        <v>10.5</v>
+        <v>5.9</v>
       </c>
       <c r="P44">
-        <v>1.1</v>
+        <v>9.5</v>
       </c>
       <c r="Q44">
-        <v>11.18</v>
+        <v>1.67</v>
       </c>
       <c r="R44">
-        <v>4.09</v>
+        <v>2.73</v>
       </c>
       <c r="S44">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="T44">
-        <v>6.5</v>
+        <v>3.9</v>
       </c>
       <c r="U44">
-        <v>1.58</v>
+        <v>2.1</v>
       </c>
       <c r="V44">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="W44">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="X44">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="Z44">
-        <v>11.5</v>
+        <v>6</v>
       </c>
       <c r="AA44">
-        <v>1.16</v>
+        <v>1.44</v>
       </c>
       <c r="AB44">
-        <v>4.95</v>
+        <v>2.75</v>
       </c>
       <c r="AC44">
-        <v>1.41</v>
+        <v>2.05</v>
       </c>
       <c r="AD44">
-        <v>2.64</v>
+        <v>1.73</v>
       </c>
       <c r="AE44">
-        <v>1.84</v>
+        <v>1.29</v>
       </c>
       <c r="AF44">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG44">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>1.03</v>
       </c>
       <c r="AK44">
-        <v>1</v>
+        <v>3.82</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.26</v>
+        <v>2.2</v>
       </c>
       <c r="O45">
-        <v>6.5</v>
+        <v>3.7</v>
       </c>
       <c r="P45">
-        <v>13</v>
+        <v>2.88</v>
       </c>
       <c r="Q45">
-        <v>1.63</v>
+        <v>2.73</v>
       </c>
       <c r="R45">
-        <v>2.56</v>
+        <v>2.2</v>
       </c>
       <c r="S45">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T45">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="U45">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="V45">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W45">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X45">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y45">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z45">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AA45">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="AB45">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="AC45">
-        <v>2.32</v>
+        <v>2.63</v>
       </c>
       <c r="AD45">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AE45">
         <v>1.18</v>
       </c>
       <c r="AF45">
-        <v>2.11</v>
+        <v>1.52</v>
       </c>
       <c r="AG45">
-        <v>1.65</v>
+        <v>2.38</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AK45">
-        <v>3.92</v>
+        <v>1.62</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -8009,10 +8009,10 @@
         <v>4.33</v>
       </c>
       <c r="AA47">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AB47">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AC47">
         <v>2.88</v>
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="O48">
         <v>4.05</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="O50">
         <v>3.1</v>

--- a/jogos_2026-10-13.xlsx
+++ b/jogos_2026-10-13.xlsx
@@ -653,7 +653,7 @@
         <v>1.33</v>
       </c>
       <c r="T2">
-        <v>2.86</v>
+        <v>2.7</v>
       </c>
       <c r="U2">
         <v>2.59</v>
@@ -674,10 +674,10 @@
         <v>3.71</v>
       </c>
       <c r="AA2">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AB2">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AC2">
         <v>3.3</v>
@@ -1954,16 +1954,16 @@
         <v>2.1</v>
       </c>
       <c r="S10">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="T10">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="U10">
         <v>2.77</v>
       </c>
       <c r="V10">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="W10">
         <v>1.05</v>
@@ -1978,10 +1978,10 @@
         <v>2.92</v>
       </c>
       <c r="AA10">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="AB10">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AC10">
         <v>3.8</v>
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="O20">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="P20">
         <v>10.5</v>
@@ -3590,7 +3590,7 @@
         <v>4</v>
       </c>
       <c r="U20">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="V20">
         <v>1.75</v>
@@ -3611,7 +3611,7 @@
         <v>1.4</v>
       </c>
       <c r="AB20">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="AC20">
         <v>1.96</v>
@@ -3623,7 +3623,7 @@
         <v>1.28</v>
       </c>
       <c r="AF20">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AG20">
         <v>1.85</v>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="O21">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P21">
         <v>2.2</v>
@@ -3771,16 +3771,16 @@
         <v>4.72</v>
       </c>
       <c r="AA21">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AB21">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="AC21">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AD21">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AE21">
         <v>1.18</v>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK21">
         <v>1.36</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.3</v>
+        <v>2.47</v>
       </c>
       <c r="O22">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P22">
-        <v>2.62</v>
+        <v>2.32</v>
       </c>
       <c r="Q22">
         <v>2.91</v>
@@ -3913,13 +3913,13 @@
         <v>1.13</v>
       </c>
       <c r="T22">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="U22">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="V22">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="W22">
         <v>1.22</v>
@@ -3934,10 +3934,10 @@
         <v>6.55</v>
       </c>
       <c r="AA22">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AB22">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AC22">
         <v>1.87</v>
@@ -3952,7 +3952,7 @@
         <v>1.35</v>
       </c>
       <c r="AG22">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         <v>1.5</v>
       </c>
       <c r="O23">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="P23">
         <v>5</v>
@@ -4070,7 +4070,7 @@
         <v>1.93</v>
       </c>
       <c r="R23">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S23">
         <v>1.22</v>
@@ -4082,10 +4082,10 @@
         <v>1.89</v>
       </c>
       <c r="V23">
-        <v>1.49</v>
+        <v>1.65</v>
       </c>
       <c r="W23">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X23">
         <v>1.02</v>
@@ -4097,10 +4097,10 @@
         <v>5.05</v>
       </c>
       <c r="AA23">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AB23">
-        <v>2.63</v>
+        <v>2.35</v>
       </c>
       <c r="AC23">
         <v>2.34</v>
@@ -4112,10 +4112,10 @@
         <v>1.18</v>
       </c>
       <c r="AF23">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AG23">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>1.13</v>
       </c>
       <c r="AK23">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,19 +4221,19 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="O24">
         <v>3.4</v>
       </c>
       <c r="P24">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="Q24">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="R24">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="S24">
         <v>1.29</v>
@@ -4242,40 +4242,40 @@
         <v>3.4</v>
       </c>
       <c r="U24">
-        <v>2.38</v>
+        <v>1.99</v>
       </c>
       <c r="V24">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="W24">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X24">
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z24">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="AA24">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AB24">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AC24">
-        <v>2.51</v>
+        <v>2.2</v>
       </c>
       <c r="AD24">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AE24">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF24">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AG24">
         <v>2.34</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK24">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4411,7 +4411,7 @@
         <v>1.73</v>
       </c>
       <c r="W25">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="X25">
         <v>1.01</v>
@@ -4423,10 +4423,10 @@
         <v>6.6</v>
       </c>
       <c r="AA25">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AB25">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="AC25">
         <v>1.86</v>
@@ -4565,7 +4565,7 @@
         <v>1.31</v>
       </c>
       <c r="T26">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="U26">
         <v>2.61</v>
@@ -4577,7 +4577,7 @@
         <v>1.1</v>
       </c>
       <c r="X26">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y26">
         <v>1.21</v>
@@ -4586,10 +4586,10 @@
         <v>3.6</v>
       </c>
       <c r="AA26">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AB26">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC26">
         <v>2.92</v>
@@ -5564,10 +5564,10 @@
         <v>3.2</v>
       </c>
       <c r="AA32">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AB32">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC32">
         <v>3.2</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,65 +5688,65 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.95</v>
+        <v>2.23</v>
       </c>
       <c r="O33">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="P33">
-        <v>3.59</v>
+        <v>2.94</v>
       </c>
       <c r="Q33">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="R33">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S33">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T33">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="U33">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="V33">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W33">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X33">
         <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="Z33">
-        <v>3.48</v>
+        <v>3.37</v>
       </c>
       <c r="AA33">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AB33">
+        <v>1.75</v>
+      </c>
+      <c r="AC33">
+        <v>3.2</v>
+      </c>
+      <c r="AD33">
+        <v>1.29</v>
+      </c>
+      <c r="AE33">
+        <v>1.1</v>
+      </c>
+      <c r="AF33">
+        <v>1.8</v>
+      </c>
+      <c r="AG33">
         <v>1.91</v>
       </c>
-      <c r="AC33">
-        <v>3.14</v>
-      </c>
-      <c r="AD33">
-        <v>1.36</v>
-      </c>
-      <c r="AE33">
-        <v>1.08</v>
-      </c>
-      <c r="AF33">
-        <v>1.75</v>
-      </c>
-      <c r="AG33">
-        <v>2</v>
-      </c>
       <c r="AH33" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK33">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.65</v>
+        <v>2.49</v>
       </c>
       <c r="O34">
-        <v>4.25</v>
+        <v>3.4</v>
       </c>
       <c r="P34">
-        <v>4.4</v>
+        <v>2.62</v>
       </c>
       <c r="Q34">
-        <v>2.14</v>
+        <v>2.9</v>
       </c>
       <c r="R34">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="S34">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T34">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="U34">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="V34">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="W34">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X34">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
+        <v>1.21</v>
+      </c>
+      <c r="Z34">
+        <v>3.58</v>
+      </c>
+      <c r="AA34">
+        <v>1.9</v>
+      </c>
+      <c r="AB34">
+        <v>1.9</v>
+      </c>
+      <c r="AC34">
+        <v>3.14</v>
+      </c>
+      <c r="AD34">
+        <v>1.36</v>
+      </c>
+      <c r="AE34">
         <v>1.13</v>
       </c>
-      <c r="Z34">
-        <v>5.2</v>
-      </c>
-      <c r="AA34">
-        <v>1.5</v>
-      </c>
-      <c r="AB34">
-        <v>2.43</v>
-      </c>
-      <c r="AC34">
-        <v>2.13</v>
-      </c>
-      <c r="AD34">
-        <v>1.66</v>
-      </c>
-      <c r="AE34">
-        <v>1.2</v>
-      </c>
       <c r="AF34">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AG34">
-        <v>2.42</v>
+        <v>2.05</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AK34">
-        <v>2.17</v>
+        <v>1.53</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="O35">
-        <v>3.94</v>
+        <v>4.05</v>
       </c>
       <c r="P35">
-        <v>5.03</v>
+        <v>4.15</v>
       </c>
       <c r="Q35">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="R35">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="S35">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T35">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="U35">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="V35">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="W35">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X35">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="Z35">
-        <v>3.3</v>
+        <v>5.2</v>
       </c>
       <c r="AA35">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AB35">
-        <v>2</v>
+        <v>2.62</v>
       </c>
       <c r="AC35">
-        <v>3.07</v>
+        <v>2.13</v>
       </c>
       <c r="AD35">
-        <v>1.37</v>
+        <v>1.66</v>
       </c>
       <c r="AE35">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AF35">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AG35">
-        <v>1.95</v>
+        <v>2.42</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK35">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.26</v>
+        <v>1.63</v>
       </c>
       <c r="O36">
-        <v>3.34</v>
+        <v>3.85</v>
       </c>
       <c r="P36">
-        <v>3.05</v>
+        <v>4.8</v>
       </c>
       <c r="Q36">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="R36">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S36">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T36">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="U36">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="V36">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W36">
+        <v>1.11</v>
+      </c>
+      <c r="X36">
+        <v>1.02</v>
+      </c>
+      <c r="Y36">
+        <v>1.27</v>
+      </c>
+      <c r="Z36">
+        <v>3.3</v>
+      </c>
+      <c r="AA36">
+        <v>1.8</v>
+      </c>
+      <c r="AB36">
+        <v>2</v>
+      </c>
+      <c r="AC36">
+        <v>3.07</v>
+      </c>
+      <c r="AD36">
+        <v>1.37</v>
+      </c>
+      <c r="AE36">
         <v>1.08</v>
-      </c>
-      <c r="X36">
-        <v>1.01</v>
-      </c>
-      <c r="Y36">
-        <v>1.32</v>
-      </c>
-      <c r="Z36">
-        <v>3.37</v>
-      </c>
-      <c r="AA36">
-        <v>2.05</v>
-      </c>
-      <c r="AB36">
-        <v>1.75</v>
-      </c>
-      <c r="AC36">
-        <v>3.2</v>
-      </c>
-      <c r="AD36">
-        <v>1.29</v>
-      </c>
-      <c r="AE36">
-        <v>1.1</v>
       </c>
       <c r="AF36">
         <v>1.8</v>
       </c>
       <c r="AG36">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK36">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.52</v>
+        <v>1.4</v>
       </c>
       <c r="O37">
-        <v>3.44</v>
+        <v>4.5</v>
       </c>
       <c r="P37">
-        <v>2.58</v>
+        <v>7</v>
       </c>
       <c r="Q37">
-        <v>2.9</v>
+        <v>1.73</v>
       </c>
       <c r="R37">
-        <v>2.28</v>
+        <v>2.6</v>
       </c>
       <c r="S37">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T37">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="U37">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="V37">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="W37">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X37">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z37">
-        <v>3.58</v>
+        <v>4.74</v>
       </c>
       <c r="AA37">
-        <v>1.87</v>
+        <v>1.61</v>
       </c>
       <c r="AB37">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AC37">
-        <v>3.14</v>
+        <v>2.53</v>
       </c>
       <c r="AD37">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AE37">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AF37">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG37">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AK37">
-        <v>1.53</v>
+        <v>3</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,58 +6503,58 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.38</v>
+        <v>2.02</v>
       </c>
       <c r="O38">
-        <v>4.85</v>
+        <v>3.58</v>
       </c>
       <c r="P38">
-        <v>7.19</v>
+        <v>3.59</v>
       </c>
       <c r="Q38">
-        <v>1.73</v>
+        <v>2.45</v>
       </c>
       <c r="R38">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="S38">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T38">
-        <v>3.5</v>
+        <v>3.02</v>
       </c>
       <c r="U38">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="V38">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="W38">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X38">
         <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="Z38">
-        <v>4.74</v>
+        <v>3.48</v>
       </c>
       <c r="AA38">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="AB38">
-        <v>2.38</v>
+        <v>1.91</v>
       </c>
       <c r="AC38">
-        <v>2.53</v>
+        <v>3.14</v>
       </c>
       <c r="AD38">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AE38">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AF38">
         <v>1.75</v>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AK38">
-        <v>3</v>
+        <v>1.73</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,80 +6666,80 @@
         </is>
       </c>
       <c r="N39">
-        <v>6.5</v>
+        <v>2.2</v>
       </c>
       <c r="O39">
-        <v>6.5</v>
+        <v>3.7</v>
       </c>
       <c r="P39">
-        <v>1.28</v>
+        <v>2.88</v>
       </c>
       <c r="Q39">
-        <v>5.03</v>
+        <v>2.73</v>
       </c>
       <c r="R39">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="S39">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="T39">
-        <v>5.75</v>
+        <v>3.34</v>
       </c>
       <c r="U39">
-        <v>1.65</v>
+        <v>2.4</v>
       </c>
       <c r="V39">
-        <v>2.11</v>
+        <v>1.5</v>
       </c>
       <c r="W39">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="X39">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y39">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="Z39">
-        <v>10</v>
+        <v>4.5</v>
       </c>
       <c r="AA39">
-        <v>1.2</v>
+        <v>1.71</v>
       </c>
       <c r="AB39">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="AC39">
-        <v>1.5</v>
+        <v>2.63</v>
       </c>
       <c r="AD39">
-        <v>2.5</v>
+        <v>1.44</v>
       </c>
       <c r="AE39">
+        <v>1.18</v>
+      </c>
+      <c r="AF39">
+        <v>1.52</v>
+      </c>
+      <c r="AG39">
+        <v>2.38</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39">
+        <v>1.24</v>
+      </c>
+      <c r="AK39">
         <v>1.62</v>
-      </c>
-      <c r="AF39">
-        <v>1.4</v>
-      </c>
-      <c r="AG39">
-        <v>2.77</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39">
-        <v>1.08</v>
-      </c>
-      <c r="AK39">
-        <v>1.05</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.85</v>
+        <v>16</v>
       </c>
       <c r="O40">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="P40">
-        <v>3.68</v>
+        <v>1.1</v>
       </c>
       <c r="Q40">
-        <v>2.26</v>
+        <v>11.91</v>
       </c>
       <c r="R40">
-        <v>2.63</v>
+        <v>4.19</v>
       </c>
       <c r="S40">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="T40">
-        <v>4.2</v>
+        <v>6.5</v>
       </c>
       <c r="U40">
-        <v>2.02</v>
+        <v>1.6</v>
       </c>
       <c r="V40">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="W40">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="X40">
+        <v>1</v>
+      </c>
+      <c r="Y40">
         <v>1.01</v>
       </c>
-      <c r="Y40">
-        <v>1.07</v>
-      </c>
       <c r="Z40">
-        <v>7.5</v>
+        <v>13</v>
       </c>
       <c r="AA40">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="AB40">
-        <v>3.04</v>
+        <v>4.95</v>
       </c>
       <c r="AC40">
-        <v>1.87</v>
+        <v>1.4</v>
       </c>
       <c r="AD40">
-        <v>1.87</v>
+        <v>2.8</v>
       </c>
       <c r="AE40">
-        <v>1.33</v>
+        <v>1.9</v>
       </c>
       <c r="AF40">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="AG40">
-        <v>3</v>
+        <v>1.99</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.24</v>
+        <v>1.03</v>
       </c>
       <c r="AK40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2</v>
+        <v>6.5</v>
       </c>
       <c r="O41">
-        <v>3.8</v>
+        <v>6.5</v>
       </c>
       <c r="P41">
-        <v>3.38</v>
+        <v>1.28</v>
       </c>
       <c r="Q41">
+        <v>5.03</v>
+      </c>
+      <c r="R41">
+        <v>2.9</v>
+      </c>
+      <c r="S41">
+        <v>1.15</v>
+      </c>
+      <c r="T41">
+        <v>5.75</v>
+      </c>
+      <c r="U41">
+        <v>1.65</v>
+      </c>
+      <c r="V41">
+        <v>2.11</v>
+      </c>
+      <c r="W41">
+        <v>1.3</v>
+      </c>
+      <c r="X41">
+        <v>1</v>
+      </c>
+      <c r="Y41">
+        <v>1.03</v>
+      </c>
+      <c r="Z41">
+        <v>10</v>
+      </c>
+      <c r="AA41">
+        <v>1.2</v>
+      </c>
+      <c r="AB41">
+        <v>4.5</v>
+      </c>
+      <c r="AC41">
+        <v>1.5</v>
+      </c>
+      <c r="AD41">
         <v>2.5</v>
       </c>
-      <c r="R41">
-        <v>2.36</v>
-      </c>
-      <c r="S41">
-        <v>1.25</v>
-      </c>
-      <c r="T41">
-        <v>3.35</v>
-      </c>
-      <c r="U41">
-        <v>2.16</v>
-      </c>
-      <c r="V41">
-        <v>1.7</v>
-      </c>
-      <c r="W41">
-        <v>1.17</v>
-      </c>
-      <c r="X41">
-        <v>1.01</v>
-      </c>
-      <c r="Y41">
-        <v>1.11</v>
-      </c>
-      <c r="Z41">
-        <v>5.5</v>
-      </c>
-      <c r="AA41">
-        <v>1.5</v>
-      </c>
-      <c r="AB41">
-        <v>2.46</v>
-      </c>
-      <c r="AC41">
-        <v>2.2</v>
-      </c>
-      <c r="AD41">
-        <v>1.63</v>
-      </c>
       <c r="AE41">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AF41">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AG41">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AK41">
-        <v>1.84</v>
+        <v>1.05</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>16</v>
+        <v>1.85</v>
       </c>
       <c r="O42">
-        <v>10.5</v>
+        <v>4.2</v>
       </c>
       <c r="P42">
-        <v>1.1</v>
+        <v>3.68</v>
       </c>
       <c r="Q42">
-        <v>11.91</v>
+        <v>2.26</v>
       </c>
       <c r="R42">
-        <v>4.19</v>
+        <v>2.63</v>
       </c>
       <c r="S42">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="T42">
-        <v>6.5</v>
+        <v>4.2</v>
       </c>
       <c r="U42">
-        <v>1.6</v>
+        <v>2.02</v>
       </c>
       <c r="V42">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="W42">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="X42">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Z42">
-        <v>13</v>
+        <v>7.5</v>
       </c>
       <c r="AA42">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="AB42">
-        <v>4.95</v>
+        <v>3.04</v>
       </c>
       <c r="AC42">
-        <v>1.4</v>
+        <v>1.87</v>
       </c>
       <c r="AD42">
-        <v>2.8</v>
+        <v>1.87</v>
       </c>
       <c r="AE42">
-        <v>1.9</v>
+        <v>1.33</v>
       </c>
       <c r="AF42">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="AG42">
-        <v>1.99</v>
+        <v>3</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.03</v>
+        <v>1.24</v>
       </c>
       <c r="AK42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.26</v>
+        <v>2</v>
       </c>
       <c r="O43">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="P43">
-        <v>13</v>
+        <v>3.38</v>
       </c>
       <c r="Q43">
+        <v>2.5</v>
+      </c>
+      <c r="R43">
+        <v>2.36</v>
+      </c>
+      <c r="S43">
+        <v>1.25</v>
+      </c>
+      <c r="T43">
+        <v>3.35</v>
+      </c>
+      <c r="U43">
+        <v>2.16</v>
+      </c>
+      <c r="V43">
+        <v>1.7</v>
+      </c>
+      <c r="W43">
+        <v>1.17</v>
+      </c>
+      <c r="X43">
+        <v>1.01</v>
+      </c>
+      <c r="Y43">
+        <v>1.11</v>
+      </c>
+      <c r="Z43">
+        <v>5.5</v>
+      </c>
+      <c r="AA43">
+        <v>1.5</v>
+      </c>
+      <c r="AB43">
+        <v>2.46</v>
+      </c>
+      <c r="AC43">
+        <v>2.2</v>
+      </c>
+      <c r="AD43">
         <v>1.63</v>
       </c>
-      <c r="R43">
-        <v>2.56</v>
-      </c>
-      <c r="S43">
-        <v>1.29</v>
-      </c>
-      <c r="T43">
-        <v>3.34</v>
-      </c>
-      <c r="U43">
-        <v>2.25</v>
-      </c>
-      <c r="V43">
-        <v>1.57</v>
-      </c>
-      <c r="W43">
-        <v>1.11</v>
-      </c>
-      <c r="X43">
-        <v>1.02</v>
-      </c>
-      <c r="Y43">
-        <v>1.14</v>
-      </c>
-      <c r="Z43">
-        <v>5</v>
-      </c>
-      <c r="AA43">
-        <v>1.57</v>
-      </c>
-      <c r="AB43">
-        <v>2.37</v>
-      </c>
-      <c r="AC43">
-        <v>2.31</v>
-      </c>
-      <c r="AD43">
-        <v>1.55</v>
-      </c>
       <c r="AE43">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AF43">
-        <v>2.14</v>
+        <v>1.43</v>
       </c>
       <c r="AG43">
-        <v>1.64</v>
+        <v>2.66</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AK43">
-        <v>4.2</v>
+        <v>1.84</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.2</v>
+        <v>1.26</v>
       </c>
       <c r="O45">
-        <v>3.7</v>
+        <v>5.8</v>
       </c>
       <c r="P45">
-        <v>2.88</v>
+        <v>13</v>
       </c>
       <c r="Q45">
-        <v>2.73</v>
+        <v>1.63</v>
       </c>
       <c r="R45">
-        <v>2.2</v>
+        <v>2.56</v>
       </c>
       <c r="S45">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T45">
         <v>3.34</v>
       </c>
       <c r="U45">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="V45">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W45">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X45">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y45">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z45">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AA45">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AB45">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AC45">
-        <v>2.63</v>
+        <v>2.31</v>
       </c>
       <c r="AD45">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AE45">
         <v>1.18</v>
       </c>
       <c r="AF45">
-        <v>1.52</v>
+        <v>2.14</v>
       </c>
       <c r="AG45">
-        <v>2.38</v>
+        <v>1.64</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AK45">
-        <v>1.62</v>
+        <v>4.2</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,80 +7970,80 @@
         </is>
       </c>
       <c r="N47">
-        <v>3.5</v>
+        <v>1.65</v>
       </c>
       <c r="O47">
-        <v>3.68</v>
+        <v>3.95</v>
       </c>
       <c r="P47">
-        <v>1.95</v>
+        <v>4.5</v>
       </c>
       <c r="Q47">
-        <v>3.9</v>
+        <v>2.1</v>
       </c>
       <c r="R47">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S47">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T47">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U47">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="V47">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W47">
+        <v>1.11</v>
+      </c>
+      <c r="X47">
+        <v>1.03</v>
+      </c>
+      <c r="Y47">
+        <v>1.23</v>
+      </c>
+      <c r="Z47">
+        <v>3.6</v>
+      </c>
+      <c r="AA47">
+        <v>1.73</v>
+      </c>
+      <c r="AB47">
+        <v>2.1</v>
+      </c>
+      <c r="AC47">
+        <v>2.62</v>
+      </c>
+      <c r="AD47">
+        <v>1.43</v>
+      </c>
+      <c r="AE47">
         <v>1.12</v>
       </c>
-      <c r="X47">
-        <v>1.02</v>
-      </c>
-      <c r="Y47">
-        <v>1.2</v>
-      </c>
-      <c r="Z47">
-        <v>4.33</v>
-      </c>
-      <c r="AA47">
-        <v>1.66</v>
-      </c>
-      <c r="AB47">
+      <c r="AF47">
+        <v>1.7</v>
+      </c>
+      <c r="AG47">
+        <v>2.05</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ47">
+        <v>1.25</v>
+      </c>
+      <c r="AK47">
         <v>2.2</v>
-      </c>
-      <c r="AC47">
-        <v>2.88</v>
-      </c>
-      <c r="AD47">
-        <v>1.44</v>
-      </c>
-      <c r="AE47">
-        <v>1.14</v>
-      </c>
-      <c r="AF47">
-        <v>1.62</v>
-      </c>
-      <c r="AG47">
-        <v>2.3</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ47">
-        <v>1.22</v>
-      </c>
-      <c r="AK47">
-        <v>1.3</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,80 +8133,80 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.63</v>
+        <v>3.25</v>
       </c>
       <c r="O48">
-        <v>4.05</v>
+        <v>3.7</v>
       </c>
       <c r="P48">
-        <v>4.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q48">
-        <v>2.1</v>
+        <v>3.9</v>
       </c>
       <c r="R48">
+        <v>2.38</v>
+      </c>
+      <c r="S48">
+        <v>1.29</v>
+      </c>
+      <c r="T48">
+        <v>3.4</v>
+      </c>
+      <c r="U48">
+        <v>2.4</v>
+      </c>
+      <c r="V48">
+        <v>1.53</v>
+      </c>
+      <c r="W48">
+        <v>1.12</v>
+      </c>
+      <c r="X48">
+        <v>1.02</v>
+      </c>
+      <c r="Y48">
+        <v>1.2</v>
+      </c>
+      <c r="Z48">
+        <v>4.33</v>
+      </c>
+      <c r="AA48">
+        <v>1.66</v>
+      </c>
+      <c r="AB48">
+        <v>2.2</v>
+      </c>
+      <c r="AC48">
+        <v>2.88</v>
+      </c>
+      <c r="AD48">
+        <v>1.44</v>
+      </c>
+      <c r="AE48">
+        <v>1.14</v>
+      </c>
+      <c r="AF48">
+        <v>1.62</v>
+      </c>
+      <c r="AG48">
         <v>2.3</v>
       </c>
-      <c r="S48">
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ48">
+        <v>1.22</v>
+      </c>
+      <c r="AK48">
         <v>1.3</v>
-      </c>
-      <c r="T48">
-        <v>3.25</v>
-      </c>
-      <c r="U48">
-        <v>2.45</v>
-      </c>
-      <c r="V48">
-        <v>1.5</v>
-      </c>
-      <c r="W48">
-        <v>1.11</v>
-      </c>
-      <c r="X48">
-        <v>1.03</v>
-      </c>
-      <c r="Y48">
-        <v>1.23</v>
-      </c>
-      <c r="Z48">
-        <v>3.6</v>
-      </c>
-      <c r="AA48">
-        <v>1.73</v>
-      </c>
-      <c r="AB48">
-        <v>2.1</v>
-      </c>
-      <c r="AC48">
-        <v>2.62</v>
-      </c>
-      <c r="AD48">
-        <v>1.43</v>
-      </c>
-      <c r="AE48">
-        <v>1.12</v>
-      </c>
-      <c r="AF48">
-        <v>1.7</v>
-      </c>
-      <c r="AG48">
-        <v>2.05</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ48">
-        <v>1.25</v>
-      </c>
-      <c r="AK48">
-        <v>2.2</v>
       </c>
       <c r="AL48">
         <v>0</v>

--- a/jogos_2026-10-13.xlsx
+++ b/jogos_2026-10-13.xlsx
@@ -653,7 +653,7 @@
         <v>1.33</v>
       </c>
       <c r="T2">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="U2">
         <v>2.59</v>
@@ -674,10 +674,10 @@
         <v>3.71</v>
       </c>
       <c r="AA2">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AB2">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AC2">
         <v>3.3</v>
@@ -1948,46 +1948,46 @@
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="R10">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S10">
         <v>1.36</v>
       </c>
       <c r="T10">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="U10">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="V10">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W10">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X10">
         <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z10">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AA10">
-        <v>2.07</v>
+        <v>1.99</v>
       </c>
       <c r="AB10">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC10">
-        <v>3.8</v>
+        <v>3.42</v>
       </c>
       <c r="AD10">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE10">
         <v>1.05</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AK10">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.45</v>
+        <v>3.5</v>
       </c>
       <c r="O15">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P15">
-        <v>2.53</v>
+        <v>1.98</v>
       </c>
       <c r="Q15">
-        <v>2.97</v>
+        <v>3.64</v>
       </c>
       <c r="R15">
         <v>2.27</v>
       </c>
       <c r="S15">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T15">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="U15">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="V15">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="W15">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X15">
         <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z15">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="AA15">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AB15">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="AC15">
-        <v>2.27</v>
+        <v>2.63</v>
       </c>
       <c r="AD15">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="AE15">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF15">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AG15">
-        <v>2.49</v>
+        <v>2.32</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.45</v>
+        <v>1.85</v>
       </c>
       <c r="AK15">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>3.5</v>
+        <v>2.45</v>
       </c>
       <c r="O16">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P16">
-        <v>1.98</v>
+        <v>2.53</v>
       </c>
       <c r="Q16">
-        <v>3.64</v>
+        <v>2.97</v>
       </c>
       <c r="R16">
         <v>2.27</v>
       </c>
       <c r="S16">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T16">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="U16">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="V16">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="W16">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X16">
         <v>1.01</v>
       </c>
       <c r="Y16">
+        <v>1.13</v>
+      </c>
+      <c r="Z16">
+        <v>5.5</v>
+      </c>
+      <c r="AA16">
+        <v>1.57</v>
+      </c>
+      <c r="AB16">
+        <v>2.27</v>
+      </c>
+      <c r="AC16">
+        <v>2.27</v>
+      </c>
+      <c r="AD16">
+        <v>1.54</v>
+      </c>
+      <c r="AE16">
         <v>1.18</v>
       </c>
-      <c r="Z16">
-        <v>4.4</v>
-      </c>
-      <c r="AA16">
-        <v>1.66</v>
-      </c>
-      <c r="AB16">
-        <v>2.2</v>
-      </c>
-      <c r="AC16">
-        <v>2.63</v>
-      </c>
-      <c r="AD16">
+      <c r="AF16">
         <v>1.47</v>
       </c>
-      <c r="AE16">
-        <v>1.15</v>
-      </c>
-      <c r="AF16">
-        <v>1.55</v>
-      </c>
       <c r="AG16">
-        <v>2.32</v>
+        <v>2.49</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.85</v>
+        <v>1.45</v>
       </c>
       <c r="AK16">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3611,7 +3611,7 @@
         <v>1.4</v>
       </c>
       <c r="AB20">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="AC20">
         <v>1.96</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="O21">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P21">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="Q21">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="R21">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="S21">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T21">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U21">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="V21">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="W21">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X21">
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z21">
-        <v>4.72</v>
+        <v>3.1</v>
       </c>
       <c r="AA21">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AB21">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AC21">
-        <v>2.01</v>
+        <v>2.2</v>
       </c>
       <c r="AD21">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AE21">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AF21">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AG21">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK21">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,80 +3895,80 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.47</v>
+        <v>2.75</v>
       </c>
       <c r="O22">
+        <v>3.6</v>
+      </c>
+      <c r="P22">
+        <v>2.2</v>
+      </c>
+      <c r="Q22">
+        <v>3.3</v>
+      </c>
+      <c r="R22">
+        <v>2.38</v>
+      </c>
+      <c r="S22">
+        <v>1.25</v>
+      </c>
+      <c r="T22">
         <v>3.5</v>
       </c>
-      <c r="P22">
-        <v>2.32</v>
-      </c>
-      <c r="Q22">
-        <v>2.91</v>
-      </c>
-      <c r="R22">
-        <v>2.48</v>
-      </c>
-      <c r="S22">
-        <v>1.13</v>
-      </c>
-      <c r="T22">
-        <v>4.2</v>
-      </c>
       <c r="U22">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="V22">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="W22">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="X22">
         <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="Z22">
-        <v>6.55</v>
+        <v>4.72</v>
       </c>
       <c r="AA22">
+        <v>1.5</v>
+      </c>
+      <c r="AB22">
+        <v>2.28</v>
+      </c>
+      <c r="AC22">
+        <v>2.01</v>
+      </c>
+      <c r="AD22">
+        <v>1.42</v>
+      </c>
+      <c r="AE22">
+        <v>1.18</v>
+      </c>
+      <c r="AF22">
+        <v>1.44</v>
+      </c>
+      <c r="AG22">
+        <v>2.5</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22">
+        <v>1.25</v>
+      </c>
+      <c r="AK22">
         <v>1.36</v>
-      </c>
-      <c r="AB22">
-        <v>3.1</v>
-      </c>
-      <c r="AC22">
-        <v>1.87</v>
-      </c>
-      <c r="AD22">
-        <v>1.8</v>
-      </c>
-      <c r="AE22">
-        <v>1.37</v>
-      </c>
-      <c r="AF22">
-        <v>1.35</v>
-      </c>
-      <c r="AG22">
-        <v>3</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22">
-        <v>1.17</v>
-      </c>
-      <c r="AK22">
-        <v>1.42</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.5</v>
+        <v>2.85</v>
       </c>
       <c r="O23">
-        <v>4.05</v>
+        <v>3.55</v>
       </c>
       <c r="P23">
-        <v>5</v>
+        <v>2.05</v>
       </c>
       <c r="Q23">
-        <v>1.93</v>
+        <v>2.88</v>
       </c>
       <c r="R23">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="S23">
+        <v>1.13</v>
+      </c>
+      <c r="T23">
+        <v>4.2</v>
+      </c>
+      <c r="U23">
+        <v>1.95</v>
+      </c>
+      <c r="V23">
+        <v>1.75</v>
+      </c>
+      <c r="W23">
         <v>1.22</v>
       </c>
-      <c r="T23">
-        <v>3.75</v>
-      </c>
-      <c r="U23">
-        <v>1.89</v>
-      </c>
-      <c r="V23">
-        <v>1.65</v>
-      </c>
-      <c r="W23">
-        <v>1.14</v>
-      </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Z23">
-        <v>5.05</v>
+        <v>6.55</v>
       </c>
       <c r="AA23">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AB23">
-        <v>2.35</v>
+        <v>3.1</v>
       </c>
       <c r="AC23">
-        <v>2.34</v>
+        <v>1.86</v>
       </c>
       <c r="AD23">
-        <v>1.55</v>
+        <v>1.81</v>
       </c>
       <c r="AE23">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="AF23">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="AG23">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AK23">
-        <v>2.4</v>
+        <v>1.35</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,80 +4221,80 @@
         </is>
       </c>
       <c r="N24">
+        <v>1.5</v>
+      </c>
+      <c r="O24">
+        <v>4.05</v>
+      </c>
+      <c r="P24">
+        <v>5</v>
+      </c>
+      <c r="Q24">
+        <v>1.93</v>
+      </c>
+      <c r="R24">
+        <v>2.5</v>
+      </c>
+      <c r="S24">
+        <v>1.22</v>
+      </c>
+      <c r="T24">
+        <v>3.75</v>
+      </c>
+      <c r="U24">
+        <v>1.9</v>
+      </c>
+      <c r="V24">
+        <v>1.65</v>
+      </c>
+      <c r="W24">
+        <v>1.14</v>
+      </c>
+      <c r="X24">
+        <v>1.02</v>
+      </c>
+      <c r="Y24">
+        <v>1.1</v>
+      </c>
+      <c r="Z24">
+        <v>5.05</v>
+      </c>
+      <c r="AA24">
+        <v>1.57</v>
+      </c>
+      <c r="AB24">
+        <v>2.55</v>
+      </c>
+      <c r="AC24">
+        <v>2.34</v>
+      </c>
+      <c r="AD24">
+        <v>1.55</v>
+      </c>
+      <c r="AE24">
+        <v>1.18</v>
+      </c>
+      <c r="AF24">
+        <v>1.62</v>
+      </c>
+      <c r="AG24">
+        <v>2.15</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24">
+        <v>1.13</v>
+      </c>
+      <c r="AK24">
         <v>2.4</v>
-      </c>
-      <c r="O24">
-        <v>3.4</v>
-      </c>
-      <c r="P24">
-        <v>2.45</v>
-      </c>
-      <c r="Q24">
-        <v>2.75</v>
-      </c>
-      <c r="R24">
-        <v>2.1</v>
-      </c>
-      <c r="S24">
-        <v>1.29</v>
-      </c>
-      <c r="T24">
-        <v>3.4</v>
-      </c>
-      <c r="U24">
-        <v>1.99</v>
-      </c>
-      <c r="V24">
-        <v>1.43</v>
-      </c>
-      <c r="W24">
-        <v>1.12</v>
-      </c>
-      <c r="X24">
-        <v>1.01</v>
-      </c>
-      <c r="Y24">
-        <v>1.14</v>
-      </c>
-      <c r="Z24">
-        <v>3.1</v>
-      </c>
-      <c r="AA24">
-        <v>1.66</v>
-      </c>
-      <c r="AB24">
-        <v>2.15</v>
-      </c>
-      <c r="AC24">
-        <v>2.2</v>
-      </c>
-      <c r="AD24">
-        <v>1.33</v>
-      </c>
-      <c r="AE24">
-        <v>1.11</v>
-      </c>
-      <c r="AF24">
-        <v>1.55</v>
-      </c>
-      <c r="AG24">
-        <v>2.34</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ24">
-        <v>1.29</v>
-      </c>
-      <c r="AK24">
-        <v>1.44</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4423,10 +4423,10 @@
         <v>6.6</v>
       </c>
       <c r="AA25">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB25">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="AC25">
         <v>1.86</v>
@@ -5528,7 +5528,7 @@
         <v>4.29</v>
       </c>
       <c r="O32">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P32">
         <v>1.67</v>
@@ -5564,10 +5564,10 @@
         <v>3.2</v>
       </c>
       <c r="AA32">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AB32">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC32">
         <v>3.2</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.23</v>
+        <v>2.52</v>
       </c>
       <c r="O33">
-        <v>3.34</v>
+        <v>3.44</v>
       </c>
       <c r="P33">
-        <v>2.94</v>
+        <v>2.62</v>
       </c>
       <c r="Q33">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="R33">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="S33">
+        <v>1.33</v>
+      </c>
+      <c r="T33">
+        <v>3.1</v>
+      </c>
+      <c r="U33">
+        <v>2.6</v>
+      </c>
+      <c r="V33">
+        <v>1.44</v>
+      </c>
+      <c r="W33">
+        <v>1.11</v>
+      </c>
+      <c r="X33">
+        <v>1.03</v>
+      </c>
+      <c r="Y33">
+        <v>1.21</v>
+      </c>
+      <c r="Z33">
+        <v>3.58</v>
+      </c>
+      <c r="AA33">
+        <v>1.87</v>
+      </c>
+      <c r="AB33">
+        <v>1.9</v>
+      </c>
+      <c r="AC33">
+        <v>3.14</v>
+      </c>
+      <c r="AD33">
         <v>1.36</v>
       </c>
-      <c r="T33">
-        <v>2.9</v>
-      </c>
-      <c r="U33">
-        <v>2.8</v>
-      </c>
-      <c r="V33">
-        <v>1.4</v>
-      </c>
-      <c r="W33">
-        <v>1.08</v>
-      </c>
-      <c r="X33">
-        <v>1.01</v>
-      </c>
-      <c r="Y33">
-        <v>1.32</v>
-      </c>
-      <c r="Z33">
-        <v>3.37</v>
-      </c>
-      <c r="AA33">
+      <c r="AE33">
+        <v>1.13</v>
+      </c>
+      <c r="AF33">
+        <v>1.7</v>
+      </c>
+      <c r="AG33">
         <v>2.05</v>
-      </c>
-      <c r="AB33">
-        <v>1.75</v>
-      </c>
-      <c r="AC33">
-        <v>3.2</v>
-      </c>
-      <c r="AD33">
-        <v>1.29</v>
-      </c>
-      <c r="AE33">
-        <v>1.1</v>
-      </c>
-      <c r="AF33">
-        <v>1.8</v>
-      </c>
-      <c r="AG33">
-        <v>1.91</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>1.33</v>
       </c>
       <c r="AK33">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,49 +5851,49 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.49</v>
+        <v>1.95</v>
       </c>
       <c r="O34">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="P34">
-        <v>2.62</v>
+        <v>3.59</v>
       </c>
       <c r="Q34">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="R34">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="S34">
         <v>1.33</v>
       </c>
       <c r="T34">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="U34">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="V34">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W34">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="Z34">
-        <v>3.58</v>
+        <v>3.48</v>
       </c>
       <c r="AA34">
         <v>1.9</v>
       </c>
       <c r="AB34">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC34">
         <v>3.14</v>
@@ -5902,13 +5902,13 @@
         <v>1.36</v>
       </c>
       <c r="AE34">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF34">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG34">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK34">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.71</v>
+        <v>2.23</v>
       </c>
       <c r="O35">
-        <v>4.05</v>
+        <v>3.34</v>
       </c>
       <c r="P35">
-        <v>4.15</v>
+        <v>2.94</v>
       </c>
       <c r="Q35">
-        <v>2.14</v>
+        <v>2.75</v>
       </c>
       <c r="R35">
-        <v>2.44</v>
+        <v>2.15</v>
       </c>
       <c r="S35">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="T35">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="U35">
-        <v>2.15</v>
+        <v>2.8</v>
       </c>
       <c r="V35">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="W35">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X35">
         <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.13</v>
+        <v>1.32</v>
       </c>
       <c r="Z35">
-        <v>5.2</v>
+        <v>3.37</v>
       </c>
       <c r="AA35">
-        <v>1.5</v>
+        <v>2.05</v>
       </c>
       <c r="AB35">
-        <v>2.62</v>
+        <v>1.75</v>
       </c>
       <c r="AC35">
-        <v>2.13</v>
+        <v>3.2</v>
       </c>
       <c r="AD35">
-        <v>1.66</v>
+        <v>1.29</v>
       </c>
       <c r="AE35">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AF35">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AG35">
-        <v>2.42</v>
+        <v>1.91</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AK35">
-        <v>2.17</v>
+        <v>1.57</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="O36">
-        <v>3.85</v>
+        <v>4.05</v>
       </c>
       <c r="P36">
-        <v>4.8</v>
+        <v>4.15</v>
       </c>
       <c r="Q36">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="R36">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="S36">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T36">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="U36">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="V36">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="W36">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X36">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="Z36">
-        <v>3.3</v>
+        <v>5.2</v>
       </c>
       <c r="AA36">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AB36">
-        <v>2</v>
+        <v>2.43</v>
       </c>
       <c r="AC36">
-        <v>3.07</v>
+        <v>2.13</v>
       </c>
       <c r="AD36">
-        <v>1.37</v>
+        <v>1.66</v>
       </c>
       <c r="AE36">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AF36">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AG36">
-        <v>1.95</v>
+        <v>2.42</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK36">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,80 +6340,80 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="O37">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="P37">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="Q37">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="R37">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="S37">
+        <v>1.33</v>
+      </c>
+      <c r="T37">
+        <v>3.1</v>
+      </c>
+      <c r="U37">
+        <v>2.5</v>
+      </c>
+      <c r="V37">
+        <v>1.44</v>
+      </c>
+      <c r="W37">
+        <v>1.11</v>
+      </c>
+      <c r="X37">
+        <v>1.02</v>
+      </c>
+      <c r="Y37">
+        <v>1.27</v>
+      </c>
+      <c r="Z37">
+        <v>3.3</v>
+      </c>
+      <c r="AA37">
+        <v>1.8</v>
+      </c>
+      <c r="AB37">
+        <v>2</v>
+      </c>
+      <c r="AC37">
+        <v>3.07</v>
+      </c>
+      <c r="AD37">
+        <v>1.37</v>
+      </c>
+      <c r="AE37">
+        <v>1.08</v>
+      </c>
+      <c r="AF37">
+        <v>1.8</v>
+      </c>
+      <c r="AG37">
+        <v>1.95</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ37">
         <v>1.25</v>
       </c>
-      <c r="T37">
-        <v>3.5</v>
-      </c>
-      <c r="U37">
-        <v>2.25</v>
-      </c>
-      <c r="V37">
-        <v>1.57</v>
-      </c>
-      <c r="W37">
-        <v>1.14</v>
-      </c>
-      <c r="X37">
-        <v>1.01</v>
-      </c>
-      <c r="Y37">
-        <v>1.19</v>
-      </c>
-      <c r="Z37">
-        <v>4.74</v>
-      </c>
-      <c r="AA37">
-        <v>1.61</v>
-      </c>
-      <c r="AB37">
-        <v>2.3</v>
-      </c>
-      <c r="AC37">
-        <v>2.53</v>
-      </c>
-      <c r="AD37">
-        <v>1.53</v>
-      </c>
-      <c r="AE37">
-        <v>1.2</v>
-      </c>
-      <c r="AF37">
-        <v>1.75</v>
-      </c>
-      <c r="AG37">
-        <v>2</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ37">
-        <v>1.18</v>
-      </c>
       <c r="AK37">
-        <v>3</v>
+        <v>2.15</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,58 +6503,58 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.02</v>
+        <v>1.4</v>
       </c>
       <c r="O38">
-        <v>3.58</v>
+        <v>4.5</v>
       </c>
       <c r="P38">
-        <v>3.59</v>
+        <v>7</v>
       </c>
       <c r="Q38">
-        <v>2.45</v>
+        <v>1.73</v>
       </c>
       <c r="R38">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="S38">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T38">
-        <v>3.02</v>
+        <v>3.5</v>
       </c>
       <c r="U38">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="V38">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="W38">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X38">
         <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="Z38">
-        <v>3.48</v>
+        <v>4.74</v>
       </c>
       <c r="AA38">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="AB38">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="AC38">
-        <v>3.14</v>
+        <v>2.53</v>
       </c>
       <c r="AD38">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AE38">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AF38">
         <v>1.75</v>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK38">
-        <v>1.73</v>
+        <v>3</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.2</v>
+        <v>1.26</v>
       </c>
       <c r="O39">
-        <v>3.7</v>
+        <v>5.8</v>
       </c>
       <c r="P39">
-        <v>2.88</v>
+        <v>13</v>
       </c>
       <c r="Q39">
-        <v>2.73</v>
+        <v>1.63</v>
       </c>
       <c r="R39">
-        <v>2.2</v>
+        <v>2.56</v>
       </c>
       <c r="S39">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T39">
         <v>3.34</v>
       </c>
       <c r="U39">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="V39">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W39">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X39">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z39">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AA39">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AB39">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AC39">
-        <v>2.63</v>
+        <v>2.31</v>
       </c>
       <c r="AD39">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AE39">
         <v>1.18</v>
       </c>
       <c r="AF39">
-        <v>1.52</v>
+        <v>2.14</v>
       </c>
       <c r="AG39">
-        <v>2.38</v>
+        <v>1.64</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AK39">
-        <v>1.62</v>
+        <v>4.2</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>16</v>
+        <v>2.2</v>
       </c>
       <c r="O40">
-        <v>10.5</v>
+        <v>3.7</v>
       </c>
       <c r="P40">
+        <v>2.88</v>
+      </c>
+      <c r="Q40">
+        <v>2.73</v>
+      </c>
+      <c r="R40">
+        <v>2.2</v>
+      </c>
+      <c r="S40">
+        <v>1.31</v>
+      </c>
+      <c r="T40">
+        <v>3.34</v>
+      </c>
+      <c r="U40">
+        <v>2.4</v>
+      </c>
+      <c r="V40">
+        <v>1.5</v>
+      </c>
+      <c r="W40">
         <v>1.1</v>
       </c>
-      <c r="Q40">
-        <v>11.91</v>
-      </c>
-      <c r="R40">
-        <v>4.19</v>
-      </c>
-      <c r="S40">
-        <v>1.1</v>
-      </c>
-      <c r="T40">
-        <v>6.5</v>
-      </c>
-      <c r="U40">
-        <v>1.6</v>
-      </c>
-      <c r="V40">
-        <v>2.2</v>
-      </c>
-      <c r="W40">
-        <v>1.41</v>
-      </c>
       <c r="X40">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y40">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="Z40">
-        <v>13</v>
+        <v>4.5</v>
       </c>
       <c r="AA40">
-        <v>1.16</v>
+        <v>1.71</v>
       </c>
       <c r="AB40">
-        <v>4.95</v>
+        <v>2.3</v>
       </c>
       <c r="AC40">
-        <v>1.4</v>
+        <v>2.63</v>
       </c>
       <c r="AD40">
-        <v>2.8</v>
+        <v>1.44</v>
       </c>
       <c r="AE40">
-        <v>1.9</v>
+        <v>1.18</v>
       </c>
       <c r="AF40">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="AG40">
-        <v>1.99</v>
+        <v>2.38</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.03</v>
+        <v>1.24</v>
       </c>
       <c r="AK40">
-        <v>1</v>
+        <v>1.62</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,80 +6992,80 @@
         </is>
       </c>
       <c r="N41">
+        <v>16</v>
+      </c>
+      <c r="O41">
+        <v>10.5</v>
+      </c>
+      <c r="P41">
+        <v>1.1</v>
+      </c>
+      <c r="Q41">
+        <v>11.91</v>
+      </c>
+      <c r="R41">
+        <v>4.19</v>
+      </c>
+      <c r="S41">
+        <v>1.1</v>
+      </c>
+      <c r="T41">
         <v>6.5</v>
       </c>
-      <c r="O41">
-        <v>6.5</v>
-      </c>
-      <c r="P41">
-        <v>1.28</v>
-      </c>
-      <c r="Q41">
-        <v>5.03</v>
-      </c>
-      <c r="R41">
-        <v>2.9</v>
-      </c>
-      <c r="S41">
-        <v>1.15</v>
-      </c>
-      <c r="T41">
-        <v>5.75</v>
-      </c>
       <c r="U41">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="V41">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="W41">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="X41">
         <v>1</v>
       </c>
       <c r="Y41">
+        <v>1.01</v>
+      </c>
+      <c r="Z41">
+        <v>13</v>
+      </c>
+      <c r="AA41">
+        <v>1.16</v>
+      </c>
+      <c r="AB41">
+        <v>4.95</v>
+      </c>
+      <c r="AC41">
+        <v>1.4</v>
+      </c>
+      <c r="AD41">
+        <v>2.8</v>
+      </c>
+      <c r="AE41">
+        <v>1.9</v>
+      </c>
+      <c r="AF41">
+        <v>1.73</v>
+      </c>
+      <c r="AG41">
+        <v>1.99</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ41">
         <v>1.03</v>
       </c>
-      <c r="Z41">
-        <v>10</v>
-      </c>
-      <c r="AA41">
-        <v>1.2</v>
-      </c>
-      <c r="AB41">
-        <v>4.5</v>
-      </c>
-      <c r="AC41">
-        <v>1.5</v>
-      </c>
-      <c r="AD41">
-        <v>2.5</v>
-      </c>
-      <c r="AE41">
-        <v>1.62</v>
-      </c>
-      <c r="AF41">
-        <v>1.4</v>
-      </c>
-      <c r="AG41">
-        <v>2.77</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ41">
-        <v>1.08</v>
-      </c>
       <c r="AK41">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.85</v>
+        <v>6.5</v>
       </c>
       <c r="O42">
-        <v>4.2</v>
+        <v>6.5</v>
       </c>
       <c r="P42">
-        <v>3.68</v>
+        <v>1.28</v>
       </c>
       <c r="Q42">
-        <v>2.26</v>
+        <v>5.03</v>
       </c>
       <c r="R42">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="S42">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="T42">
-        <v>4.2</v>
+        <v>5.75</v>
       </c>
       <c r="U42">
-        <v>2.02</v>
+        <v>1.65</v>
       </c>
       <c r="V42">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="W42">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="X42">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y42">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Z42">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="AA42">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AB42">
-        <v>3.04</v>
+        <v>4.5</v>
       </c>
       <c r="AC42">
-        <v>1.87</v>
+        <v>1.5</v>
       </c>
       <c r="AD42">
-        <v>1.87</v>
+        <v>2.5</v>
       </c>
       <c r="AE42">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="AF42">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AG42">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="AK42">
-        <v>2</v>
+        <v>1.05</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="O43">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="P43">
-        <v>3.38</v>
+        <v>3.68</v>
       </c>
       <c r="Q43">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="R43">
-        <v>2.36</v>
+        <v>2.63</v>
       </c>
       <c r="S43">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="T43">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="U43">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="V43">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="W43">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="X43">
         <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z43">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA43">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AB43">
-        <v>2.46</v>
+        <v>3.04</v>
       </c>
       <c r="AC43">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="AD43">
-        <v>1.63</v>
+        <v>1.87</v>
       </c>
       <c r="AE43">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AF43">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AG43">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK43">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,31 +7481,31 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.26</v>
+        <v>2</v>
       </c>
       <c r="O44">
-        <v>5.9</v>
+        <v>3.8</v>
       </c>
       <c r="P44">
-        <v>9.5</v>
+        <v>3.38</v>
       </c>
       <c r="Q44">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="R44">
-        <v>2.73</v>
+        <v>2.36</v>
       </c>
       <c r="S44">
         <v>1.25</v>
       </c>
       <c r="T44">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="U44">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="V44">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="W44">
         <v>1.17</v>
@@ -7517,28 +7517,28 @@
         <v>1.11</v>
       </c>
       <c r="Z44">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AA44">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AB44">
-        <v>2.75</v>
+        <v>2.46</v>
       </c>
       <c r="AC44">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AD44">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AE44">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF44">
-        <v>1.8</v>
+        <v>1.43</v>
       </c>
       <c r="AG44">
-        <v>1.86</v>
+        <v>2.66</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.03</v>
+        <v>1.25</v>
       </c>
       <c r="AK44">
-        <v>3.82</v>
+        <v>1.84</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G45">
@@ -7647,61 +7647,61 @@
         <v>1.26</v>
       </c>
       <c r="O45">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="P45">
-        <v>13</v>
+        <v>9.5</v>
       </c>
       <c r="Q45">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="R45">
-        <v>2.56</v>
+        <v>2.73</v>
       </c>
       <c r="S45">
+        <v>1.25</v>
+      </c>
+      <c r="T45">
+        <v>3.9</v>
+      </c>
+      <c r="U45">
+        <v>2.1</v>
+      </c>
+      <c r="V45">
+        <v>1.67</v>
+      </c>
+      <c r="W45">
+        <v>1.17</v>
+      </c>
+      <c r="X45">
+        <v>1.01</v>
+      </c>
+      <c r="Y45">
+        <v>1.11</v>
+      </c>
+      <c r="Z45">
+        <v>6</v>
+      </c>
+      <c r="AA45">
+        <v>1.44</v>
+      </c>
+      <c r="AB45">
+        <v>2.75</v>
+      </c>
+      <c r="AC45">
+        <v>2.05</v>
+      </c>
+      <c r="AD45">
+        <v>1.73</v>
+      </c>
+      <c r="AE45">
         <v>1.29</v>
       </c>
-      <c r="T45">
-        <v>3.34</v>
-      </c>
-      <c r="U45">
-        <v>2.25</v>
-      </c>
-      <c r="V45">
-        <v>1.57</v>
-      </c>
-      <c r="W45">
-        <v>1.11</v>
-      </c>
-      <c r="X45">
-        <v>1.02</v>
-      </c>
-      <c r="Y45">
-        <v>1.14</v>
-      </c>
-      <c r="Z45">
-        <v>5</v>
-      </c>
-      <c r="AA45">
-        <v>1.57</v>
-      </c>
-      <c r="AB45">
-        <v>2.37</v>
-      </c>
-      <c r="AC45">
-        <v>2.31</v>
-      </c>
-      <c r="AD45">
-        <v>1.55</v>
-      </c>
-      <c r="AE45">
-        <v>1.18</v>
-      </c>
       <c r="AF45">
-        <v>2.14</v>
+        <v>1.8</v>
       </c>
       <c r="AG45">
-        <v>1.64</v>
+        <v>1.86</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="AK45">
-        <v>4.2</v>
+        <v>3.82</v>
       </c>
       <c r="AL45">
         <v>0</v>

--- a/jogos_2026-10-13.xlsx
+++ b/jogos_2026-10-13.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O2">
         <v>3.2</v>
       </c>
       <c r="P2">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="Q2">
         <v>2.5</v>
@@ -650,19 +650,19 @@
         <v>2.2</v>
       </c>
       <c r="S2">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T2">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="U2">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="V2">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W2">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X2">
         <v>1.03</v>
@@ -671,13 +671,13 @@
         <v>1.25</v>
       </c>
       <c r="Z2">
-        <v>3.71</v>
+        <v>3.61</v>
       </c>
       <c r="AA2">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AB2">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AC2">
         <v>3.3</v>
@@ -686,7 +686,7 @@
         <v>1.27</v>
       </c>
       <c r="AE2">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF2">
         <v>1.7</v>
@@ -807,7 +807,7 @@
         <v>1.82</v>
       </c>
       <c r="Q3">
-        <v>5.09</v>
+        <v>5.26</v>
       </c>
       <c r="R3">
         <v>1.93</v>
@@ -852,10 +852,10 @@
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AG3">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>1.24</v>
       </c>
       <c r="AK3">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -970,55 +970,55 @@
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R4">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W4">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y4">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z4">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA4">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC4">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AD4">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE4">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK4">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Abu Qair Semad</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Asyut Petroleum</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
+        <v>1.89</v>
+      </c>
+      <c r="O8">
+        <v>3</v>
+      </c>
+      <c r="P8">
+        <v>4.27</v>
+      </c>
+      <c r="Q8">
+        <v>2.63</v>
+      </c>
+      <c r="R8">
         <v>2</v>
       </c>
-      <c r="O8">
-        <v>2.77</v>
-      </c>
-      <c r="P8">
+      <c r="S8">
+        <v>1.44</v>
+      </c>
+      <c r="T8">
+        <v>2.26</v>
+      </c>
+      <c r="U8">
         <v>3.6</v>
       </c>
-      <c r="Q8">
-        <v>2.7</v>
-      </c>
-      <c r="R8">
-        <v>1.95</v>
-      </c>
-      <c r="S8">
-        <v>1.61</v>
-      </c>
-      <c r="T8">
-        <v>2.4</v>
-      </c>
-      <c r="U8">
-        <v>3.5</v>
-      </c>
       <c r="V8">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="W8">
         <v>1.02</v>
       </c>
       <c r="X8">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Y8">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="Z8">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="AA8">
-        <v>2.64</v>
+        <v>2.41</v>
       </c>
       <c r="AB8">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AC8">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="AD8">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AE8">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AF8">
         <v>2.15</v>
       </c>
       <c r="AG8">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK8">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Abu Qair Semad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Asyut Petroleum</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.89</v>
+        <v>2.03</v>
       </c>
       <c r="O9">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="P9">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="Q9">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="R9">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S9">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="T9">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="U9">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="V9">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="W9">
         <v>1.02</v>
       </c>
       <c r="X9">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Y9">
+        <v>1.52</v>
+      </c>
+      <c r="Z9">
+        <v>2.5</v>
+      </c>
+      <c r="AA9">
+        <v>2.64</v>
+      </c>
+      <c r="AB9">
         <v>1.47</v>
       </c>
-      <c r="Z9">
-        <v>2.44</v>
-      </c>
-      <c r="AA9">
-        <v>2.41</v>
-      </c>
-      <c r="AB9">
-        <v>1.48</v>
-      </c>
       <c r="AC9">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AD9">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AE9">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AF9">
         <v>2.15</v>
       </c>
       <c r="AG9">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AK9">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1957,7 +1957,7 @@
         <v>1.36</v>
       </c>
       <c r="T10">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="U10">
         <v>2.73</v>
@@ -1966,7 +1966,7 @@
         <v>1.38</v>
       </c>
       <c r="W10">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X10">
         <v>1.02</v>
@@ -2111,55 +2111,55 @@
         <v>3.36</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2274,55 +2274,55 @@
         <v>0</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X12">
         <v>0</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2437,55 +2437,55 @@
         <v>0</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X13">
         <v>0</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="O18">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="P18">
-        <v>3.7</v>
+        <v>3.94</v>
       </c>
       <c r="Q18">
         <v>2.88</v>
@@ -3258,10 +3258,10 @@
         <v>1.83</v>
       </c>
       <c r="S18">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="T18">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="U18">
         <v>4</v>
@@ -3270,7 +3270,7 @@
         <v>1.2</v>
       </c>
       <c r="W18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X18">
         <v>1.11</v>
@@ -3282,7 +3282,7 @@
         <v>2.08</v>
       </c>
       <c r="AA18">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AB18">
         <v>1.33</v>
@@ -3297,7 +3297,7 @@
         <v>1.02</v>
       </c>
       <c r="AF18">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AG18">
         <v>1.5</v>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.99</v>
+        <v>2.87</v>
       </c>
       <c r="O19">
         <v>2.7</v>
@@ -3415,25 +3415,25 @@
         <v>2.49</v>
       </c>
       <c r="Q19">
-        <v>3.5</v>
+        <v>3.61</v>
       </c>
       <c r="R19">
         <v>1.95</v>
       </c>
       <c r="S19">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T19">
-        <v>2.47</v>
+        <v>2.75</v>
       </c>
       <c r="U19">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="V19">
         <v>1.36</v>
       </c>
       <c r="W19">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X19">
         <v>1.04</v>
@@ -3741,10 +3741,10 @@
         <v>2.45</v>
       </c>
       <c r="Q21">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="R21">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S21">
         <v>1.29</v>
@@ -3771,10 +3771,10 @@
         <v>3.1</v>
       </c>
       <c r="AA21">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AB21">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AC21">
         <v>2.2</v>
@@ -3925,7 +3925,7 @@
         <v>1.14</v>
       </c>
       <c r="X22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
         <v>1.13</v>
@@ -4067,7 +4067,7 @@
         <v>2.05</v>
       </c>
       <c r="Q23">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="R23">
         <v>2.49</v>
@@ -4393,16 +4393,16 @@
         <v>4.8</v>
       </c>
       <c r="Q25">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="R25">
         <v>2.62</v>
       </c>
       <c r="S25">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="T25">
-        <v>4.25</v>
+        <v>4.05</v>
       </c>
       <c r="U25">
         <v>2</v>
@@ -4417,28 +4417,28 @@
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z25">
-        <v>6.6</v>
+        <v>6.15</v>
       </c>
       <c r="AA25">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB25">
-        <v>2.92</v>
+        <v>2.81</v>
       </c>
       <c r="AC25">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="AD25">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="AE25">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AF25">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AG25">
         <v>2.5</v>
@@ -4457,7 +4457,7 @@
         <v>1.1</v>
       </c>
       <c r="AK25">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4589,7 +4589,7 @@
         <v>1.85</v>
       </c>
       <c r="AB26">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC26">
         <v>2.92</v>
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="O27">
         <v>4.6</v>
       </c>
       <c r="P27">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5564,10 +5564,10 @@
         <v>3.2</v>
       </c>
       <c r="AA32">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AB32">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AC32">
         <v>3.2</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,49 +5688,49 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.52</v>
+        <v>1.95</v>
       </c>
       <c r="O33">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="P33">
+        <v>3.59</v>
+      </c>
+      <c r="Q33">
+        <v>2.45</v>
+      </c>
+      <c r="R33">
+        <v>2.2</v>
+      </c>
+      <c r="S33">
+        <v>1.35</v>
+      </c>
+      <c r="T33">
+        <v>2.77</v>
+      </c>
+      <c r="U33">
         <v>2.62</v>
       </c>
-      <c r="Q33">
-        <v>2.9</v>
-      </c>
-      <c r="R33">
-        <v>2.28</v>
-      </c>
-      <c r="S33">
-        <v>1.33</v>
-      </c>
-      <c r="T33">
-        <v>3.1</v>
-      </c>
-      <c r="U33">
-        <v>2.6</v>
-      </c>
       <c r="V33">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W33">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X33">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="Z33">
-        <v>3.58</v>
+        <v>3.48</v>
       </c>
       <c r="AA33">
         <v>1.87</v>
       </c>
       <c r="AB33">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC33">
         <v>3.14</v>
@@ -5739,13 +5739,13 @@
         <v>1.36</v>
       </c>
       <c r="AE33">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF33">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG33">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK33">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,65 +5851,65 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="O34">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="P34">
-        <v>3.59</v>
+        <v>2.97</v>
       </c>
       <c r="Q34">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="R34">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S34">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T34">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="U34">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="V34">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W34">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X34">
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="Z34">
-        <v>3.48</v>
+        <v>3.37</v>
       </c>
       <c r="AA34">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AB34">
+        <v>1.75</v>
+      </c>
+      <c r="AC34">
+        <v>3.2</v>
+      </c>
+      <c r="AD34">
+        <v>1.29</v>
+      </c>
+      <c r="AE34">
+        <v>1.1</v>
+      </c>
+      <c r="AF34">
+        <v>1.8</v>
+      </c>
+      <c r="AG34">
         <v>1.91</v>
       </c>
-      <c r="AC34">
-        <v>3.14</v>
-      </c>
-      <c r="AD34">
-        <v>1.36</v>
-      </c>
-      <c r="AE34">
-        <v>1.08</v>
-      </c>
-      <c r="AF34">
-        <v>1.75</v>
-      </c>
-      <c r="AG34">
-        <v>2</v>
-      </c>
       <c r="AH34" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK34">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.23</v>
+        <v>2.52</v>
       </c>
       <c r="O35">
-        <v>3.34</v>
+        <v>3.44</v>
       </c>
       <c r="P35">
-        <v>2.94</v>
+        <v>2.61</v>
       </c>
       <c r="Q35">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="R35">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="S35">
+        <v>1.33</v>
+      </c>
+      <c r="T35">
+        <v>3.1</v>
+      </c>
+      <c r="U35">
+        <v>2.6</v>
+      </c>
+      <c r="V35">
+        <v>1.44</v>
+      </c>
+      <c r="W35">
+        <v>1.11</v>
+      </c>
+      <c r="X35">
+        <v>1.03</v>
+      </c>
+      <c r="Y35">
+        <v>1.21</v>
+      </c>
+      <c r="Z35">
+        <v>3.58</v>
+      </c>
+      <c r="AA35">
+        <v>1.87</v>
+      </c>
+      <c r="AB35">
+        <v>1.9</v>
+      </c>
+      <c r="AC35">
+        <v>3.14</v>
+      </c>
+      <c r="AD35">
         <v>1.36</v>
       </c>
-      <c r="T35">
-        <v>2.9</v>
-      </c>
-      <c r="U35">
-        <v>2.8</v>
-      </c>
-      <c r="V35">
-        <v>1.4</v>
-      </c>
-      <c r="W35">
-        <v>1.08</v>
-      </c>
-      <c r="X35">
-        <v>1.01</v>
-      </c>
-      <c r="Y35">
-        <v>1.32</v>
-      </c>
-      <c r="Z35">
-        <v>3.37</v>
-      </c>
-      <c r="AA35">
+      <c r="AE35">
+        <v>1.13</v>
+      </c>
+      <c r="AF35">
+        <v>1.7</v>
+      </c>
+      <c r="AG35">
         <v>2.05</v>
-      </c>
-      <c r="AB35">
-        <v>1.75</v>
-      </c>
-      <c r="AC35">
-        <v>3.2</v>
-      </c>
-      <c r="AD35">
-        <v>1.29</v>
-      </c>
-      <c r="AE35">
-        <v>1.1</v>
-      </c>
-      <c r="AF35">
-        <v>1.8</v>
-      </c>
-      <c r="AG35">
-        <v>1.91</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>1.33</v>
       </c>
       <c r="AK35">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,31 +6177,31 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.71</v>
+        <v>1.4</v>
       </c>
       <c r="O36">
-        <v>4.05</v>
+        <v>4.5</v>
       </c>
       <c r="P36">
-        <v>4.15</v>
+        <v>7</v>
       </c>
       <c r="Q36">
-        <v>2.14</v>
+        <v>1.8</v>
       </c>
       <c r="R36">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="S36">
         <v>1.25</v>
       </c>
       <c r="T36">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="U36">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="V36">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="W36">
         <v>1.14</v>
@@ -6210,31 +6210,31 @@
         <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="Z36">
-        <v>5.2</v>
+        <v>4.74</v>
       </c>
       <c r="AA36">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AB36">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="AC36">
-        <v>2.13</v>
+        <v>2.53</v>
       </c>
       <c r="AD36">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AE36">
         <v>1.2</v>
       </c>
       <c r="AF36">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AG36">
-        <v>2.42</v>
+        <v>2</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK36">
-        <v>2.17</v>
+        <v>2.88</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="O37">
         <v>3.85</v>
       </c>
       <c r="P37">
-        <v>4.8</v>
+        <v>4.25</v>
       </c>
       <c r="Q37">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="R37">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S37">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="T37">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="U37">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="V37">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="W37">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X37">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="Z37">
-        <v>3.3</v>
+        <v>5.2</v>
       </c>
       <c r="AA37">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AB37">
-        <v>2</v>
+        <v>2.63</v>
       </c>
       <c r="AC37">
-        <v>3.07</v>
+        <v>2.13</v>
       </c>
       <c r="AD37">
-        <v>1.37</v>
+        <v>1.66</v>
       </c>
       <c r="AE37">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AF37">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AG37">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK37">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,80 +6503,80 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="O38">
-        <v>4.5</v>
+        <v>3.94</v>
       </c>
       <c r="P38">
-        <v>7</v>
+        <v>4.92</v>
       </c>
       <c r="Q38">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="R38">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="S38">
+        <v>1.33</v>
+      </c>
+      <c r="T38">
+        <v>3.1</v>
+      </c>
+      <c r="U38">
+        <v>2.5</v>
+      </c>
+      <c r="V38">
+        <v>1.44</v>
+      </c>
+      <c r="W38">
+        <v>1.07</v>
+      </c>
+      <c r="X38">
+        <v>1.02</v>
+      </c>
+      <c r="Y38">
+        <v>1.27</v>
+      </c>
+      <c r="Z38">
+        <v>3.3</v>
+      </c>
+      <c r="AA38">
+        <v>1.8</v>
+      </c>
+      <c r="AB38">
+        <v>2</v>
+      </c>
+      <c r="AC38">
+        <v>3.05</v>
+      </c>
+      <c r="AD38">
+        <v>1.37</v>
+      </c>
+      <c r="AE38">
+        <v>1.08</v>
+      </c>
+      <c r="AF38">
+        <v>1.8</v>
+      </c>
+      <c r="AG38">
+        <v>1.95</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38">
         <v>1.25</v>
       </c>
-      <c r="T38">
-        <v>3.5</v>
-      </c>
-      <c r="U38">
-        <v>2.25</v>
-      </c>
-      <c r="V38">
-        <v>1.57</v>
-      </c>
-      <c r="W38">
-        <v>1.14</v>
-      </c>
-      <c r="X38">
-        <v>1.01</v>
-      </c>
-      <c r="Y38">
-        <v>1.19</v>
-      </c>
-      <c r="Z38">
-        <v>4.74</v>
-      </c>
-      <c r="AA38">
-        <v>1.61</v>
-      </c>
-      <c r="AB38">
-        <v>2.38</v>
-      </c>
-      <c r="AC38">
-        <v>2.53</v>
-      </c>
-      <c r="AD38">
-        <v>1.53</v>
-      </c>
-      <c r="AE38">
-        <v>1.2</v>
-      </c>
-      <c r="AF38">
-        <v>1.75</v>
-      </c>
-      <c r="AG38">
-        <v>2</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ38">
-        <v>1.2</v>
-      </c>
       <c r="AK38">
-        <v>3</v>
+        <v>2.15</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.26</v>
+        <v>2.2</v>
       </c>
       <c r="O39">
-        <v>5.8</v>
+        <v>3.7</v>
       </c>
       <c r="P39">
-        <v>13</v>
+        <v>2.88</v>
       </c>
       <c r="Q39">
-        <v>1.63</v>
+        <v>2.73</v>
       </c>
       <c r="R39">
-        <v>2.56</v>
+        <v>2.2</v>
       </c>
       <c r="S39">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T39">
         <v>3.34</v>
       </c>
       <c r="U39">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="V39">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W39">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X39">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y39">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z39">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AA39">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="AB39">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="AC39">
-        <v>2.31</v>
+        <v>2.63</v>
       </c>
       <c r="AD39">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AE39">
         <v>1.18</v>
       </c>
       <c r="AF39">
-        <v>2.14</v>
+        <v>1.52</v>
       </c>
       <c r="AG39">
-        <v>1.64</v>
+        <v>2.38</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AK39">
-        <v>4.2</v>
+        <v>1.62</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,80 +6829,80 @@
         </is>
       </c>
       <c r="N40">
+        <v>16</v>
+      </c>
+      <c r="O40">
+        <v>10.5</v>
+      </c>
+      <c r="P40">
+        <v>1.1</v>
+      </c>
+      <c r="Q40">
+        <v>11.91</v>
+      </c>
+      <c r="R40">
+        <v>4.19</v>
+      </c>
+      <c r="S40">
+        <v>1.1</v>
+      </c>
+      <c r="T40">
+        <v>6.5</v>
+      </c>
+      <c r="U40">
+        <v>1.6</v>
+      </c>
+      <c r="V40">
         <v>2.2</v>
       </c>
-      <c r="O40">
-        <v>3.7</v>
-      </c>
-      <c r="P40">
-        <v>2.88</v>
-      </c>
-      <c r="Q40">
-        <v>2.73</v>
-      </c>
-      <c r="R40">
-        <v>2.2</v>
-      </c>
-      <c r="S40">
-        <v>1.31</v>
-      </c>
-      <c r="T40">
-        <v>3.34</v>
-      </c>
-      <c r="U40">
-        <v>2.4</v>
-      </c>
-      <c r="V40">
-        <v>1.5</v>
-      </c>
       <c r="W40">
-        <v>1.1</v>
+        <v>1.41</v>
       </c>
       <c r="X40">
+        <v>1</v>
+      </c>
+      <c r="Y40">
+        <v>1.01</v>
+      </c>
+      <c r="Z40">
+        <v>13</v>
+      </c>
+      <c r="AA40">
+        <v>1.16</v>
+      </c>
+      <c r="AB40">
+        <v>4.95</v>
+      </c>
+      <c r="AC40">
+        <v>1.4</v>
+      </c>
+      <c r="AD40">
+        <v>2.8</v>
+      </c>
+      <c r="AE40">
+        <v>1.9</v>
+      </c>
+      <c r="AF40">
+        <v>1.73</v>
+      </c>
+      <c r="AG40">
+        <v>1.99</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ40">
         <v>1.03</v>
       </c>
-      <c r="Y40">
-        <v>1.18</v>
-      </c>
-      <c r="Z40">
-        <v>4.5</v>
-      </c>
-      <c r="AA40">
-        <v>1.71</v>
-      </c>
-      <c r="AB40">
-        <v>2.3</v>
-      </c>
-      <c r="AC40">
-        <v>2.63</v>
-      </c>
-      <c r="AD40">
-        <v>1.44</v>
-      </c>
-      <c r="AE40">
-        <v>1.18</v>
-      </c>
-      <c r="AF40">
-        <v>1.52</v>
-      </c>
-      <c r="AG40">
-        <v>2.38</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ40">
-        <v>1.24</v>
-      </c>
       <c r="AK40">
-        <v>1.62</v>
+        <v>1</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>16</v>
+        <v>1.26</v>
       </c>
       <c r="O41">
-        <v>10.5</v>
+        <v>5.8</v>
       </c>
       <c r="P41">
-        <v>1.1</v>
+        <v>13</v>
       </c>
       <c r="Q41">
-        <v>11.91</v>
+        <v>1.63</v>
       </c>
       <c r="R41">
-        <v>4.19</v>
+        <v>2.56</v>
       </c>
       <c r="S41">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="T41">
-        <v>6.5</v>
+        <v>3.34</v>
       </c>
       <c r="U41">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="V41">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="W41">
-        <v>1.41</v>
+        <v>1.11</v>
       </c>
       <c r="X41">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="Z41">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AA41">
-        <v>1.16</v>
+        <v>1.57</v>
       </c>
       <c r="AB41">
-        <v>4.95</v>
+        <v>2.37</v>
       </c>
       <c r="AC41">
-        <v>1.4</v>
+        <v>2.31</v>
       </c>
       <c r="AD41">
-        <v>2.8</v>
+        <v>1.55</v>
       </c>
       <c r="AE41">
-        <v>1.9</v>
+        <v>1.18</v>
       </c>
       <c r="AF41">
-        <v>1.73</v>
+        <v>2.14</v>
       </c>
       <c r="AG41">
-        <v>1.99</v>
+        <v>1.64</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="AK41">
-        <v>1</v>
+        <v>4.2</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,65 +7970,65 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.65</v>
+        <v>3.3</v>
       </c>
       <c r="O47">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="P47">
-        <v>4.5</v>
+        <v>1.98</v>
       </c>
       <c r="Q47">
-        <v>2.1</v>
+        <v>3.9</v>
       </c>
       <c r="R47">
+        <v>2.38</v>
+      </c>
+      <c r="S47">
+        <v>1.29</v>
+      </c>
+      <c r="T47">
+        <v>3.4</v>
+      </c>
+      <c r="U47">
+        <v>2.4</v>
+      </c>
+      <c r="V47">
+        <v>1.53</v>
+      </c>
+      <c r="W47">
+        <v>1.12</v>
+      </c>
+      <c r="X47">
+        <v>1.02</v>
+      </c>
+      <c r="Y47">
+        <v>1.2</v>
+      </c>
+      <c r="Z47">
+        <v>3.65</v>
+      </c>
+      <c r="AA47">
+        <v>1.66</v>
+      </c>
+      <c r="AB47">
+        <v>2.2</v>
+      </c>
+      <c r="AC47">
+        <v>2.54</v>
+      </c>
+      <c r="AD47">
+        <v>1.44</v>
+      </c>
+      <c r="AE47">
+        <v>1.13</v>
+      </c>
+      <c r="AF47">
+        <v>1.62</v>
+      </c>
+      <c r="AG47">
         <v>2.3</v>
       </c>
-      <c r="S47">
-        <v>1.3</v>
-      </c>
-      <c r="T47">
-        <v>3.25</v>
-      </c>
-      <c r="U47">
-        <v>2.45</v>
-      </c>
-      <c r="V47">
-        <v>1.5</v>
-      </c>
-      <c r="W47">
-        <v>1.11</v>
-      </c>
-      <c r="X47">
-        <v>1.03</v>
-      </c>
-      <c r="Y47">
-        <v>1.23</v>
-      </c>
-      <c r="Z47">
-        <v>3.6</v>
-      </c>
-      <c r="AA47">
-        <v>1.73</v>
-      </c>
-      <c r="AB47">
-        <v>2.1</v>
-      </c>
-      <c r="AC47">
-        <v>2.62</v>
-      </c>
-      <c r="AD47">
-        <v>1.43</v>
-      </c>
-      <c r="AE47">
-        <v>1.12</v>
-      </c>
-      <c r="AF47">
-        <v>1.7</v>
-      </c>
-      <c r="AG47">
-        <v>2.05</v>
-      </c>
       <c r="AH47" t="inlineStr">
         <is>
           <t>[]</t>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
+        <v>1.22</v>
+      </c>
+      <c r="AK47">
         <v>1.25</v>
-      </c>
-      <c r="AK47">
-        <v>2.2</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,80 +8133,80 @@
         </is>
       </c>
       <c r="N48">
-        <v>3.25</v>
+        <v>1.64</v>
       </c>
       <c r="O48">
         <v>3.7</v>
       </c>
       <c r="P48">
-        <v>1.99</v>
+        <v>4.98</v>
       </c>
       <c r="Q48">
-        <v>3.9</v>
+        <v>2.1</v>
       </c>
       <c r="R48">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S48">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T48">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U48">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="V48">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W48">
+        <v>1.11</v>
+      </c>
+      <c r="X48">
+        <v>1.03</v>
+      </c>
+      <c r="Y48">
+        <v>1.23</v>
+      </c>
+      <c r="Z48">
+        <v>3.6</v>
+      </c>
+      <c r="AA48">
+        <v>1.73</v>
+      </c>
+      <c r="AB48">
+        <v>2.1</v>
+      </c>
+      <c r="AC48">
+        <v>2.62</v>
+      </c>
+      <c r="AD48">
+        <v>1.43</v>
+      </c>
+      <c r="AE48">
         <v>1.12</v>
       </c>
-      <c r="X48">
-        <v>1.02</v>
-      </c>
-      <c r="Y48">
-        <v>1.2</v>
-      </c>
-      <c r="Z48">
-        <v>4.33</v>
-      </c>
-      <c r="AA48">
-        <v>1.66</v>
-      </c>
-      <c r="AB48">
+      <c r="AF48">
+        <v>1.7</v>
+      </c>
+      <c r="AG48">
+        <v>2.05</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ48">
+        <v>1.25</v>
+      </c>
+      <c r="AK48">
         <v>2.2</v>
-      </c>
-      <c r="AC48">
-        <v>2.88</v>
-      </c>
-      <c r="AD48">
-        <v>1.44</v>
-      </c>
-      <c r="AE48">
-        <v>1.14</v>
-      </c>
-      <c r="AF48">
-        <v>1.62</v>
-      </c>
-      <c r="AG48">
-        <v>2.3</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ48">
-        <v>1.22</v>
-      </c>
-      <c r="AK48">
-        <v>1.3</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q49">
         <v>0</v>

--- a/jogos_2026-10-13.xlsx
+++ b/jogos_2026-10-13.xlsx
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="O5">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="P5">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="Q5">
         <v>3.38</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="O11">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="P11">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="Q11">
         <v>2.59</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q12">
         <v>4.78</v>
@@ -2295,7 +2295,7 @@
         <v>1.2</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
         <v>1.13</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q13">
         <v>2.63</v>
@@ -2757,10 +2757,10 @@
         <v>3.5</v>
       </c>
       <c r="O15">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P15">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="Q15">
         <v>3.64</v>
@@ -2799,7 +2799,7 @@
         <v>2.2</v>
       </c>
       <c r="AC15">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="AD15">
         <v>1.47</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AK15">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2923,10 +2923,10 @@
         <v>3.7</v>
       </c>
       <c r="P16">
-        <v>2.53</v>
+        <v>2.38</v>
       </c>
       <c r="Q16">
-        <v>2.97</v>
+        <v>2.8</v>
       </c>
       <c r="R16">
         <v>2.27</v>
@@ -2956,7 +2956,7 @@
         <v>5.5</v>
       </c>
       <c r="AA16">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB16">
         <v>2.27</v>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.45</v>
+        <v>1.24</v>
       </c>
       <c r="AK16">
         <v>1.5</v>
@@ -3741,7 +3741,7 @@
         <v>2.45</v>
       </c>
       <c r="Q21">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="R21">
         <v>2.3</v>
@@ -3753,7 +3753,7 @@
         <v>3.4</v>
       </c>
       <c r="U21">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="V21">
         <v>1.42</v>
@@ -4058,16 +4058,16 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.85</v>
+        <v>2.62</v>
       </c>
       <c r="O23">
         <v>3.55</v>
       </c>
       <c r="P23">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="Q23">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="R23">
         <v>2.49</v>
@@ -4085,7 +4085,7 @@
         <v>1.75</v>
       </c>
       <c r="W23">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X23">
         <v>1.01</v>
@@ -4242,7 +4242,7 @@
         <v>3.75</v>
       </c>
       <c r="U24">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V24">
         <v>1.65</v>
@@ -4384,34 +4384,34 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="O25">
+        <v>3.9</v>
+      </c>
+      <c r="P25">
         <v>4.2</v>
       </c>
-      <c r="P25">
-        <v>4.8</v>
-      </c>
       <c r="Q25">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="R25">
-        <v>2.62</v>
+        <v>2.51</v>
       </c>
       <c r="S25">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="T25">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="U25">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="V25">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="W25">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X25">
         <v>1.01</v>
@@ -4420,28 +4420,28 @@
         <v>1.06</v>
       </c>
       <c r="Z25">
-        <v>6.15</v>
+        <v>6.05</v>
       </c>
       <c r="AA25">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AB25">
-        <v>2.81</v>
+        <v>2.74</v>
       </c>
       <c r="AC25">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="AD25">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AE25">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AF25">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AG25">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AK25">
-        <v>2.32</v>
+        <v>2.12</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -5579,10 +5579,10 @@
         <v>1.06</v>
       </c>
       <c r="AF32">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG32">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,58 +5688,58 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="O33">
+        <v>4.5</v>
+      </c>
+      <c r="P33">
+        <v>7</v>
+      </c>
+      <c r="Q33">
+        <v>1.8</v>
+      </c>
+      <c r="R33">
+        <v>2.5</v>
+      </c>
+      <c r="S33">
+        <v>1.25</v>
+      </c>
+      <c r="T33">
         <v>3.5</v>
       </c>
-      <c r="P33">
-        <v>3.59</v>
-      </c>
-      <c r="Q33">
-        <v>2.45</v>
-      </c>
-      <c r="R33">
-        <v>2.2</v>
-      </c>
-      <c r="S33">
-        <v>1.35</v>
-      </c>
-      <c r="T33">
-        <v>2.77</v>
-      </c>
       <c r="U33">
-        <v>2.62</v>
+        <v>2.23</v>
       </c>
       <c r="V33">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="W33">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X33">
         <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="Z33">
-        <v>3.48</v>
+        <v>4.74</v>
       </c>
       <c r="AA33">
-        <v>1.87</v>
+        <v>1.61</v>
       </c>
       <c r="AB33">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="AC33">
-        <v>3.14</v>
+        <v>2.53</v>
       </c>
       <c r="AD33">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AE33">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AF33">
         <v>1.75</v>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK33">
-        <v>1.8</v>
+        <v>2.88</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,80 +5851,80 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="O34">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P34">
-        <v>2.97</v>
+        <v>3.59</v>
       </c>
       <c r="Q34">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="R34">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S34">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T34">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="U34">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="V34">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W34">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X34">
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="Z34">
-        <v>3.37</v>
+        <v>3.48</v>
       </c>
       <c r="AA34">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AB34">
+        <v>1.91</v>
+      </c>
+      <c r="AC34">
+        <v>3.14</v>
+      </c>
+      <c r="AD34">
+        <v>1.36</v>
+      </c>
+      <c r="AE34">
+        <v>1.08</v>
+      </c>
+      <c r="AF34">
         <v>1.75</v>
       </c>
-      <c r="AC34">
-        <v>3.2</v>
-      </c>
-      <c r="AD34">
-        <v>1.29</v>
-      </c>
-      <c r="AE34">
-        <v>1.1</v>
-      </c>
-      <c r="AF34">
+      <c r="AG34">
+        <v>2</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ34">
+        <v>1.3</v>
+      </c>
+      <c r="AK34">
         <v>1.8</v>
-      </c>
-      <c r="AG34">
-        <v>1.91</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ34">
-        <v>1.33</v>
-      </c>
-      <c r="AK34">
-        <v>1.57</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.52</v>
+        <v>2.18</v>
       </c>
       <c r="O35">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="P35">
-        <v>2.61</v>
+        <v>2.97</v>
       </c>
       <c r="Q35">
+        <v>2.75</v>
+      </c>
+      <c r="R35">
+        <v>2.15</v>
+      </c>
+      <c r="S35">
+        <v>1.36</v>
+      </c>
+      <c r="T35">
         <v>2.9</v>
       </c>
-      <c r="R35">
-        <v>2.28</v>
-      </c>
-      <c r="S35">
-        <v>1.33</v>
-      </c>
-      <c r="T35">
-        <v>3.1</v>
-      </c>
       <c r="U35">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="V35">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W35">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="Z35">
-        <v>3.58</v>
+        <v>3.37</v>
       </c>
       <c r="AA35">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AB35">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AC35">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AD35">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AE35">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF35">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AG35">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>1.33</v>
       </c>
       <c r="AK35">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,80 +6177,80 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.4</v>
+        <v>2.52</v>
       </c>
       <c r="O36">
-        <v>4.5</v>
+        <v>3.44</v>
       </c>
       <c r="P36">
-        <v>7</v>
+        <v>2.61</v>
       </c>
       <c r="Q36">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="R36">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="S36">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T36">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="U36">
-        <v>2.23</v>
+        <v>2.6</v>
       </c>
       <c r="V36">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="W36">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X36">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y36">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="Z36">
-        <v>4.74</v>
+        <v>3.58</v>
       </c>
       <c r="AA36">
-        <v>1.61</v>
+        <v>1.87</v>
       </c>
       <c r="AB36">
-        <v>2.38</v>
+        <v>1.9</v>
       </c>
       <c r="AC36">
-        <v>2.53</v>
+        <v>3.14</v>
       </c>
       <c r="AD36">
+        <v>1.36</v>
+      </c>
+      <c r="AE36">
+        <v>1.13</v>
+      </c>
+      <c r="AF36">
+        <v>1.7</v>
+      </c>
+      <c r="AG36">
+        <v>2.05</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ36">
+        <v>1.33</v>
+      </c>
+      <c r="AK36">
         <v>1.53</v>
-      </c>
-      <c r="AE36">
-        <v>1.2</v>
-      </c>
-      <c r="AF36">
-        <v>1.75</v>
-      </c>
-      <c r="AG36">
-        <v>2</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ36">
-        <v>1.2</v>
-      </c>
-      <c r="AK36">
-        <v>2.88</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6672,7 +6672,7 @@
         <v>3.7</v>
       </c>
       <c r="P39">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="Q39">
         <v>2.73</v>
@@ -6690,7 +6690,7 @@
         <v>2.4</v>
       </c>
       <c r="V39">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W39">
         <v>1.1</v>
@@ -6708,7 +6708,7 @@
         <v>1.71</v>
       </c>
       <c r="AB39">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AC39">
         <v>2.63</v>
@@ -6829,16 +6829,16 @@
         </is>
       </c>
       <c r="N40">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O40">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="P40">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Q40">
-        <v>11.91</v>
+        <v>11.89</v>
       </c>
       <c r="R40">
         <v>4.19</v>
@@ -6847,7 +6847,7 @@
         <v>1.1</v>
       </c>
       <c r="T40">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="U40">
         <v>1.6</v>
@@ -6868,16 +6868,16 @@
         <v>13</v>
       </c>
       <c r="AA40">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AB40">
-        <v>4.95</v>
+        <v>5.5</v>
       </c>
       <c r="AC40">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AD40">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AE40">
         <v>1.9</v>
@@ -6899,7 +6899,7 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.03</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AK40">
         <v>1</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="O41">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="P41">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q41">
         <v>1.63</v>
@@ -7031,7 +7031,7 @@
         <v>5</v>
       </c>
       <c r="AA41">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB41">
         <v>2.37</v>
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AK41">
         <v>4.2</v>
@@ -7158,7 +7158,7 @@
         <v>6.5</v>
       </c>
       <c r="O42">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="P42">
         <v>1.28</v>
@@ -7206,7 +7206,7 @@
         <v>2.5</v>
       </c>
       <c r="AE42">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AF42">
         <v>1.4</v>
@@ -7228,7 +7228,7 @@
         <v>1.08</v>
       </c>
       <c r="AK42">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,19 +7318,19 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="O43">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="P43">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="Q43">
         <v>2.26</v>
       </c>
       <c r="R43">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="S43">
         <v>1.14</v>
@@ -7351,7 +7351,7 @@
         <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z43">
         <v>7.5</v>
@@ -7484,13 +7484,13 @@
         <v>2</v>
       </c>
       <c r="O44">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P44">
-        <v>3.38</v>
+        <v>2.75</v>
       </c>
       <c r="Q44">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="R44">
         <v>2.36</v>
@@ -7517,19 +7517,19 @@
         <v>1.11</v>
       </c>
       <c r="Z44">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AA44">
         <v>1.5</v>
       </c>
       <c r="AB44">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="AC44">
         <v>2.2</v>
       </c>
       <c r="AD44">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AE44">
         <v>1.25</v>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK44">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7647,19 +7647,19 @@
         <v>1.26</v>
       </c>
       <c r="O45">
-        <v>5.9</v>
+        <v>5.75</v>
       </c>
       <c r="P45">
         <v>9.5</v>
       </c>
       <c r="Q45">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="R45">
-        <v>2.73</v>
+        <v>2.61</v>
       </c>
       <c r="S45">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T45">
         <v>3.9</v>
@@ -7671,7 +7671,7 @@
         <v>1.67</v>
       </c>
       <c r="W45">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X45">
         <v>1.01</v>
@@ -7717,7 +7717,7 @@
         <v>1.03</v>
       </c>
       <c r="AK45">
-        <v>3.82</v>
+        <v>3.6</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O50">
-        <v>3.1</v>
+        <v>3.01</v>
       </c>
       <c r="P50">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="Q50">
         <v>2.75</v>
@@ -8498,7 +8498,7 @@
         <v>2.74</v>
       </c>
       <c r="AA50">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AB50">
         <v>1.61</v>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AK50">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AL50">
         <v>0</v>

--- a/jogos_2026-10-13.xlsx
+++ b/jogos_2026-10-13.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O2">
         <v>3.2</v>
       </c>
       <c r="P2">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q2">
         <v>2.5</v>
@@ -650,19 +650,19 @@
         <v>2.2</v>
       </c>
       <c r="S2">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T2">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="U2">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="V2">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W2">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X2">
         <v>1.03</v>
@@ -671,22 +671,22 @@
         <v>1.25</v>
       </c>
       <c r="Z2">
-        <v>3.61</v>
+        <v>3.5</v>
       </c>
       <c r="AA2">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AB2">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AC2">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AD2">
         <v>1.27</v>
       </c>
       <c r="AE2">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF2">
         <v>1.7</v>
@@ -807,10 +807,10 @@
         <v>1.82</v>
       </c>
       <c r="Q3">
-        <v>5.26</v>
+        <v>5.72</v>
       </c>
       <c r="R3">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="S3">
         <v>1.44</v>
@@ -831,16 +831,16 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="Z3">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="AA3">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="AB3">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AC3">
         <v>0</v>
@@ -852,10 +852,10 @@
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2.27</v>
+        <v>2.35</v>
       </c>
       <c r="AG3">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK3">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1622,7 +1622,7 @@
         <v>4.27</v>
       </c>
       <c r="Q8">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="R8">
         <v>2</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="O9">
         <v>2.85</v>
       </c>
       <c r="P9">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="Q9">
         <v>2.7</v>
@@ -1821,7 +1821,7 @@
         <v>1.47</v>
       </c>
       <c r="AC9">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="AD9">
         <v>1.15</v>
@@ -1993,7 +1993,7 @@
         <v>1.05</v>
       </c>
       <c r="AF10">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG10">
         <v>1.95</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>4.33</v>
+        <v>2.2</v>
       </c>
       <c r="O12">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="P12">
-        <v>1.57</v>
+        <v>2.5</v>
       </c>
       <c r="Q12">
-        <v>4.78</v>
+        <v>2.6</v>
       </c>
       <c r="R12">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="S12">
+        <v>1.13</v>
+      </c>
+      <c r="T12">
+        <v>4.6</v>
+      </c>
+      <c r="U12">
+        <v>1.8</v>
+      </c>
+      <c r="V12">
+        <v>1.82</v>
+      </c>
+      <c r="W12">
         <v>1.22</v>
       </c>
-      <c r="T12">
-        <v>4.33</v>
-      </c>
-      <c r="U12">
-        <v>2.1</v>
-      </c>
-      <c r="V12">
-        <v>1.75</v>
-      </c>
-      <c r="W12">
-        <v>1.2</v>
-      </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y12">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="Z12">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AA12">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="AB12">
-        <v>2.8</v>
+        <v>3.04</v>
       </c>
       <c r="AC12">
-        <v>2.15</v>
+        <v>1.81</v>
       </c>
       <c r="AD12">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="AE12">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AF12">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AG12">
-        <v>2.44</v>
+        <v>3.08</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK12">
-        <v>1.13</v>
+        <v>1.62</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
+        <v>4.33</v>
+      </c>
+      <c r="O13">
+        <v>4</v>
+      </c>
+      <c r="P13">
+        <v>1.55</v>
+      </c>
+      <c r="Q13">
+        <v>4.76</v>
+      </c>
+      <c r="R13">
+        <v>2.44</v>
+      </c>
+      <c r="S13">
+        <v>1.2</v>
+      </c>
+      <c r="T13">
+        <v>4</v>
+      </c>
+      <c r="U13">
+        <v>2.15</v>
+      </c>
+      <c r="V13">
+        <v>1.67</v>
+      </c>
+      <c r="W13">
+        <v>1.17</v>
+      </c>
+      <c r="X13">
+        <v>1.01</v>
+      </c>
+      <c r="Y13">
+        <v>1.12</v>
+      </c>
+      <c r="Z13">
+        <v>6</v>
+      </c>
+      <c r="AA13">
+        <v>1.44</v>
+      </c>
+      <c r="AB13">
+        <v>2.7</v>
+      </c>
+      <c r="AC13">
         <v>2.2</v>
       </c>
-      <c r="O13">
-        <v>3.8</v>
-      </c>
-      <c r="P13">
-        <v>2.5</v>
-      </c>
-      <c r="Q13">
-        <v>2.63</v>
-      </c>
-      <c r="R13">
-        <v>2.63</v>
-      </c>
-      <c r="S13">
-        <v>1.18</v>
-      </c>
-      <c r="T13">
-        <v>5</v>
-      </c>
-      <c r="U13">
-        <v>1.91</v>
-      </c>
-      <c r="V13">
-        <v>1.91</v>
-      </c>
-      <c r="W13">
-        <v>1.29</v>
-      </c>
-      <c r="X13">
-        <v>0</v>
-      </c>
-      <c r="Y13">
-        <v>1.09</v>
-      </c>
-      <c r="Z13">
-        <v>7.5</v>
-      </c>
-      <c r="AA13">
-        <v>1.3</v>
-      </c>
-      <c r="AB13">
-        <v>3.5</v>
-      </c>
-      <c r="AC13">
-        <v>1.83</v>
-      </c>
       <c r="AD13">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AE13">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AF13">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="AG13">
-        <v>3.34</v>
+        <v>2.38</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK13">
-        <v>1.57</v>
+        <v>1.12</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AK18">
         <v>1.62</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="O21">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P21">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="Q21">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="R21">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S21">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T21">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U21">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="V21">
+        <v>1.57</v>
+      </c>
+      <c r="W21">
+        <v>1.14</v>
+      </c>
+      <c r="X21">
+        <v>1.02</v>
+      </c>
+      <c r="Y21">
+        <v>1.13</v>
+      </c>
+      <c r="Z21">
+        <v>4.72</v>
+      </c>
+      <c r="AA21">
+        <v>1.5</v>
+      </c>
+      <c r="AB21">
+        <v>2.28</v>
+      </c>
+      <c r="AC21">
+        <v>2.01</v>
+      </c>
+      <c r="AD21">
         <v>1.42</v>
       </c>
-      <c r="W21">
-        <v>1.12</v>
-      </c>
-      <c r="X21">
-        <v>1.01</v>
-      </c>
-      <c r="Y21">
-        <v>1.14</v>
-      </c>
-      <c r="Z21">
-        <v>3.1</v>
-      </c>
-      <c r="AA21">
-        <v>1.62</v>
-      </c>
-      <c r="AB21">
-        <v>2.25</v>
-      </c>
-      <c r="AC21">
-        <v>2.2</v>
-      </c>
-      <c r="AD21">
-        <v>1.33</v>
-      </c>
       <c r="AE21">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AF21">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AG21">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK21">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,80 +3895,80 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="O22">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P22">
+        <v>2.45</v>
+      </c>
+      <c r="Q22">
+        <v>2.9</v>
+      </c>
+      <c r="R22">
+        <v>2.3</v>
+      </c>
+      <c r="S22">
+        <v>1.29</v>
+      </c>
+      <c r="T22">
+        <v>3.4</v>
+      </c>
+      <c r="U22">
+        <v>2.02</v>
+      </c>
+      <c r="V22">
+        <v>1.42</v>
+      </c>
+      <c r="W22">
+        <v>1.12</v>
+      </c>
+      <c r="X22">
+        <v>1.01</v>
+      </c>
+      <c r="Y22">
+        <v>1.14</v>
+      </c>
+      <c r="Z22">
+        <v>3.1</v>
+      </c>
+      <c r="AA22">
+        <v>1.62</v>
+      </c>
+      <c r="AB22">
+        <v>2.25</v>
+      </c>
+      <c r="AC22">
         <v>2.2</v>
       </c>
-      <c r="Q22">
-        <v>3.3</v>
-      </c>
-      <c r="R22">
-        <v>2.38</v>
-      </c>
-      <c r="S22">
-        <v>1.25</v>
-      </c>
-      <c r="T22">
-        <v>3.5</v>
-      </c>
-      <c r="U22">
-        <v>2.15</v>
-      </c>
-      <c r="V22">
-        <v>1.57</v>
-      </c>
-      <c r="W22">
-        <v>1.14</v>
-      </c>
-      <c r="X22">
-        <v>1.02</v>
-      </c>
-      <c r="Y22">
-        <v>1.13</v>
-      </c>
-      <c r="Z22">
-        <v>4.72</v>
-      </c>
-      <c r="AA22">
-        <v>1.5</v>
-      </c>
-      <c r="AB22">
-        <v>2.28</v>
-      </c>
-      <c r="AC22">
-        <v>2.01</v>
-      </c>
       <c r="AD22">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AE22">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AF22">
+        <v>1.55</v>
+      </c>
+      <c r="AG22">
+        <v>2.34</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22">
+        <v>1.29</v>
+      </c>
+      <c r="AK22">
         <v>1.44</v>
-      </c>
-      <c r="AG22">
-        <v>2.5</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22">
-        <v>1.25</v>
-      </c>
-      <c r="AK22">
-        <v>1.36</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4577,7 +4577,7 @@
         <v>1.1</v>
       </c>
       <c r="X26">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y26">
         <v>1.21</v>
@@ -5371,22 +5371,22 @@
         <v>5.28</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W31">
         <v>0</v>
@@ -5395,16 +5395,16 @@
         <v>0</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC31">
         <v>0</v>
@@ -5416,10 +5416,10 @@
         <v>0</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,58 +5688,58 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="O33">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="P33">
-        <v>7</v>
+        <v>3.59</v>
       </c>
       <c r="Q33">
-        <v>1.8</v>
+        <v>2.45</v>
       </c>
       <c r="R33">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="S33">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="T33">
-        <v>3.5</v>
+        <v>2.77</v>
       </c>
       <c r="U33">
-        <v>2.23</v>
+        <v>2.62</v>
       </c>
       <c r="V33">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="W33">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X33">
         <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="Z33">
-        <v>4.74</v>
+        <v>3.48</v>
       </c>
       <c r="AA33">
-        <v>1.61</v>
+        <v>1.87</v>
       </c>
       <c r="AB33">
-        <v>2.38</v>
+        <v>1.91</v>
       </c>
       <c r="AC33">
-        <v>2.53</v>
+        <v>3.14</v>
       </c>
       <c r="AD33">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AE33">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AF33">
         <v>1.75</v>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK33">
-        <v>2.88</v>
+        <v>1.8</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,49 +5851,49 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.95</v>
+        <v>2.52</v>
       </c>
       <c r="O34">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="P34">
-        <v>3.59</v>
+        <v>2.61</v>
       </c>
       <c r="Q34">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="R34">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="S34">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T34">
-        <v>2.77</v>
+        <v>3.1</v>
       </c>
       <c r="U34">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V34">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W34">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X34">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="Z34">
-        <v>3.48</v>
+        <v>3.58</v>
       </c>
       <c r="AA34">
         <v>1.87</v>
       </c>
       <c r="AB34">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AC34">
         <v>3.14</v>
@@ -5902,13 +5902,13 @@
         <v>1.36</v>
       </c>
       <c r="AE34">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF34">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG34">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK34">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,7 +6014,7 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="O35">
         <v>3.3</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.52</v>
+        <v>1.4</v>
       </c>
       <c r="O36">
-        <v>3.44</v>
+        <v>4.5</v>
       </c>
       <c r="P36">
-        <v>2.61</v>
+        <v>7</v>
       </c>
       <c r="Q36">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="R36">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="S36">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T36">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="U36">
-        <v>2.6</v>
+        <v>2.23</v>
       </c>
       <c r="V36">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="W36">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X36">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z36">
-        <v>3.58</v>
+        <v>4.74</v>
       </c>
       <c r="AA36">
-        <v>1.87</v>
+        <v>1.61</v>
       </c>
       <c r="AB36">
-        <v>1.9</v>
+        <v>2.38</v>
       </c>
       <c r="AC36">
-        <v>3.14</v>
+        <v>2.53</v>
       </c>
       <c r="AD36">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AE36">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AF36">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG36">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AK36">
-        <v>1.53</v>
+        <v>2.88</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,10 +6340,10 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="O37">
-        <v>3.85</v>
+        <v>4.05</v>
       </c>
       <c r="P37">
         <v>4.25</v>
@@ -6379,7 +6379,7 @@
         <v>5.2</v>
       </c>
       <c r="AA37">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB37">
         <v>2.63</v>
@@ -6509,7 +6509,7 @@
         <v>3.94</v>
       </c>
       <c r="P38">
-        <v>4.92</v>
+        <v>5.05</v>
       </c>
       <c r="Q38">
         <v>2.1</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK38">
         <v>2.15</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,80 +6829,80 @@
         </is>
       </c>
       <c r="N40">
-        <v>14</v>
+        <v>1.24</v>
       </c>
       <c r="O40">
+        <v>5.9</v>
+      </c>
+      <c r="P40">
         <v>11</v>
       </c>
-      <c r="P40">
-        <v>1.07</v>
-      </c>
       <c r="Q40">
-        <v>11.89</v>
+        <v>1.63</v>
       </c>
       <c r="R40">
-        <v>4.19</v>
+        <v>2.56</v>
       </c>
       <c r="S40">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="T40">
-        <v>7</v>
+        <v>3.34</v>
       </c>
       <c r="U40">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="V40">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="W40">
-        <v>1.41</v>
+        <v>1.11</v>
       </c>
       <c r="X40">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="Z40">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AA40">
+        <v>1.53</v>
+      </c>
+      <c r="AB40">
+        <v>2.37</v>
+      </c>
+      <c r="AC40">
+        <v>2.31</v>
+      </c>
+      <c r="AD40">
+        <v>1.55</v>
+      </c>
+      <c r="AE40">
+        <v>1.18</v>
+      </c>
+      <c r="AF40">
+        <v>2.14</v>
+      </c>
+      <c r="AG40">
+        <v>1.64</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ40">
         <v>1.14</v>
       </c>
-      <c r="AB40">
-        <v>5.5</v>
-      </c>
-      <c r="AC40">
-        <v>1.36</v>
-      </c>
-      <c r="AD40">
-        <v>3</v>
-      </c>
-      <c r="AE40">
-        <v>1.9</v>
-      </c>
-      <c r="AF40">
-        <v>1.73</v>
-      </c>
-      <c r="AG40">
-        <v>1.99</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ40">
-        <v>8.699999999999999</v>
-      </c>
       <c r="AK40">
-        <v>1</v>
+        <v>4.2</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.24</v>
+        <v>14</v>
       </c>
       <c r="O41">
-        <v>5.9</v>
+        <v>11</v>
       </c>
       <c r="P41">
-        <v>11</v>
+        <v>1.07</v>
       </c>
       <c r="Q41">
-        <v>1.63</v>
+        <v>11.89</v>
       </c>
       <c r="R41">
-        <v>2.56</v>
+        <v>4.19</v>
       </c>
       <c r="S41">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="T41">
-        <v>3.34</v>
+        <v>7</v>
       </c>
       <c r="U41">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="V41">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="W41">
-        <v>1.11</v>
+        <v>1.41</v>
       </c>
       <c r="X41">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y41">
+        <v>1.01</v>
+      </c>
+      <c r="Z41">
+        <v>13</v>
+      </c>
+      <c r="AA41">
         <v>1.14</v>
       </c>
-      <c r="Z41">
-        <v>5</v>
-      </c>
-      <c r="AA41">
-        <v>1.53</v>
-      </c>
       <c r="AB41">
-        <v>2.37</v>
+        <v>5.5</v>
       </c>
       <c r="AC41">
-        <v>2.31</v>
+        <v>1.36</v>
       </c>
       <c r="AD41">
-        <v>1.55</v>
+        <v>3</v>
       </c>
       <c r="AE41">
-        <v>1.18</v>
+        <v>1.9</v>
       </c>
       <c r="AF41">
-        <v>2.14</v>
+        <v>1.73</v>
       </c>
       <c r="AG41">
-        <v>1.64</v>
+        <v>1.99</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.14</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AK41">
-        <v>4.2</v>
+        <v>1</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,80 +7970,80 @@
         </is>
       </c>
       <c r="N47">
-        <v>3.3</v>
+        <v>1.64</v>
       </c>
       <c r="O47">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="P47">
+        <v>4.98</v>
+      </c>
+      <c r="Q47">
         <v>1.98</v>
       </c>
-      <c r="Q47">
-        <v>3.9</v>
-      </c>
       <c r="R47">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="S47">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T47">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U47">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="V47">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W47">
+        <v>1.11</v>
+      </c>
+      <c r="X47">
+        <v>1.03</v>
+      </c>
+      <c r="Y47">
+        <v>1.23</v>
+      </c>
+      <c r="Z47">
+        <v>3.6</v>
+      </c>
+      <c r="AA47">
+        <v>1.73</v>
+      </c>
+      <c r="AB47">
+        <v>2.1</v>
+      </c>
+      <c r="AC47">
+        <v>2.62</v>
+      </c>
+      <c r="AD47">
+        <v>1.43</v>
+      </c>
+      <c r="AE47">
         <v>1.12</v>
       </c>
-      <c r="X47">
-        <v>1.02</v>
-      </c>
-      <c r="Y47">
-        <v>1.2</v>
-      </c>
-      <c r="Z47">
-        <v>3.65</v>
-      </c>
-      <c r="AA47">
-        <v>1.66</v>
-      </c>
-      <c r="AB47">
+      <c r="AF47">
+        <v>1.7</v>
+      </c>
+      <c r="AG47">
+        <v>2.05</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ47">
+        <v>1.25</v>
+      </c>
+      <c r="AK47">
         <v>2.2</v>
-      </c>
-      <c r="AC47">
-        <v>2.54</v>
-      </c>
-      <c r="AD47">
-        <v>1.44</v>
-      </c>
-      <c r="AE47">
-        <v>1.13</v>
-      </c>
-      <c r="AF47">
-        <v>1.62</v>
-      </c>
-      <c r="AG47">
-        <v>2.3</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ47">
-        <v>1.22</v>
-      </c>
-      <c r="AK47">
-        <v>1.25</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,65 +8133,65 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.64</v>
+        <v>3.3</v>
       </c>
       <c r="O48">
         <v>3.7</v>
       </c>
       <c r="P48">
-        <v>4.98</v>
+        <v>1.98</v>
       </c>
       <c r="Q48">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="R48">
+        <v>2.2</v>
+      </c>
+      <c r="S48">
+        <v>1.29</v>
+      </c>
+      <c r="T48">
+        <v>3.4</v>
+      </c>
+      <c r="U48">
+        <v>2.4</v>
+      </c>
+      <c r="V48">
+        <v>1.53</v>
+      </c>
+      <c r="W48">
+        <v>1.12</v>
+      </c>
+      <c r="X48">
+        <v>1.02</v>
+      </c>
+      <c r="Y48">
+        <v>1.2</v>
+      </c>
+      <c r="Z48">
+        <v>3.65</v>
+      </c>
+      <c r="AA48">
+        <v>1.66</v>
+      </c>
+      <c r="AB48">
+        <v>2.2</v>
+      </c>
+      <c r="AC48">
+        <v>2.54</v>
+      </c>
+      <c r="AD48">
+        <v>1.44</v>
+      </c>
+      <c r="AE48">
+        <v>1.13</v>
+      </c>
+      <c r="AF48">
+        <v>1.62</v>
+      </c>
+      <c r="AG48">
         <v>2.3</v>
       </c>
-      <c r="S48">
-        <v>1.3</v>
-      </c>
-      <c r="T48">
-        <v>3.25</v>
-      </c>
-      <c r="U48">
-        <v>2.45</v>
-      </c>
-      <c r="V48">
-        <v>1.5</v>
-      </c>
-      <c r="W48">
-        <v>1.11</v>
-      </c>
-      <c r="X48">
-        <v>1.03</v>
-      </c>
-      <c r="Y48">
-        <v>1.23</v>
-      </c>
-      <c r="Z48">
-        <v>3.6</v>
-      </c>
-      <c r="AA48">
-        <v>1.73</v>
-      </c>
-      <c r="AB48">
-        <v>2.1</v>
-      </c>
-      <c r="AC48">
-        <v>2.62</v>
-      </c>
-      <c r="AD48">
-        <v>1.43</v>
-      </c>
-      <c r="AE48">
-        <v>1.12</v>
-      </c>
-      <c r="AF48">
-        <v>1.7</v>
-      </c>
-      <c r="AG48">
-        <v>2.05</v>
-      </c>
       <c r="AH48" t="inlineStr">
         <is>
           <t>[]</t>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK48">
-        <v>2.2</v>
+        <v>1.21</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8305,22 +8305,22 @@
         <v>1.6</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W49">
         <v>0</v>
@@ -8329,31 +8329,31 @@
         <v>0</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE49">
         <v>0</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AL49">
         <v>0</v>

--- a/jogos_2026-10-13.xlsx
+++ b/jogos_2026-10-13.xlsx
@@ -1981,7 +1981,7 @@
         <v>1.99</v>
       </c>
       <c r="AB10">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC10">
         <v>3.42</v>
@@ -2108,7 +2108,7 @@
         <v>3.3</v>
       </c>
       <c r="P11">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="Q11">
         <v>2.59</v>
@@ -2313,16 +2313,16 @@
         <v>1.81</v>
       </c>
       <c r="AD12">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AE12">
         <v>1.34</v>
       </c>
       <c r="AF12">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AG12">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -3602,10 +3602,10 @@
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z20">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AA20">
         <v>1.4</v>
@@ -3614,13 +3614,13 @@
         <v>2.88</v>
       </c>
       <c r="AC20">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="AD20">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AE20">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AF20">
         <v>1.85</v>
@@ -3732,7 +3732,7 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="O21">
         <v>3.6</v>
@@ -3741,10 +3741,10 @@
         <v>2.2</v>
       </c>
       <c r="Q21">
-        <v>3.3</v>
+        <v>3.02</v>
       </c>
       <c r="R21">
-        <v>2.38</v>
+        <v>2.21</v>
       </c>
       <c r="S21">
         <v>1.25</v>
@@ -3805,7 +3805,7 @@
         <v>1.25</v>
       </c>
       <c r="AK21">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="O22">
         <v>3.4</v>
@@ -3907,7 +3907,7 @@
         <v>2.9</v>
       </c>
       <c r="R22">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="S22">
         <v>1.29</v>
@@ -3916,10 +3916,10 @@
         <v>3.4</v>
       </c>
       <c r="U22">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="V22">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W22">
         <v>1.12</v>
@@ -3952,7 +3952,7 @@
         <v>1.55</v>
       </c>
       <c r="AG22">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -4058,19 +4058,19 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="O23">
         <v>3.55</v>
       </c>
       <c r="P23">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="Q23">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="R23">
-        <v>2.49</v>
+        <v>2.42</v>
       </c>
       <c r="S23">
         <v>1.13</v>
@@ -4091,10 +4091,10 @@
         <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Z23">
-        <v>6.55</v>
+        <v>6.5</v>
       </c>
       <c r="AA23">
         <v>1.36</v>
@@ -4103,16 +4103,16 @@
         <v>3.1</v>
       </c>
       <c r="AC23">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AD23">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="AE23">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AF23">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AG23">
         <v>3</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK23">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4251,28 +4251,28 @@
         <v>1.14</v>
       </c>
       <c r="X24">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
         <v>1.1</v>
       </c>
       <c r="Z24">
-        <v>5.05</v>
+        <v>4.8</v>
       </c>
       <c r="AA24">
         <v>1.57</v>
       </c>
       <c r="AB24">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="AC24">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="AD24">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AE24">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF24">
         <v>1.62</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AK24">
         <v>2.4</v>
@@ -4393,10 +4393,10 @@
         <v>4.2</v>
       </c>
       <c r="Q25">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="R25">
-        <v>2.51</v>
+        <v>2.44</v>
       </c>
       <c r="S25">
         <v>1.2</v>
@@ -4408,7 +4408,7 @@
         <v>2.05</v>
       </c>
       <c r="V25">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="W25">
         <v>1.18</v>
@@ -4420,7 +4420,7 @@
         <v>1.06</v>
       </c>
       <c r="Z25">
-        <v>6.05</v>
+        <v>6.5</v>
       </c>
       <c r="AA25">
         <v>1.4</v>
@@ -4429,19 +4429,19 @@
         <v>2.74</v>
       </c>
       <c r="AC25">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="AD25">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AE25">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AF25">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AG25">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AK25">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -5555,13 +5555,13 @@
         <v>1.08</v>
       </c>
       <c r="X32">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y32">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z32">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA32">
         <v>1.88</v>
@@ -5570,13 +5570,13 @@
         <v>1.79</v>
       </c>
       <c r="AC32">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD32">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE32">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF32">
         <v>1.87</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.95</v>
+        <v>2.52</v>
       </c>
       <c r="O33">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P33">
-        <v>3.59</v>
+        <v>2.61</v>
       </c>
       <c r="Q33">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="R33">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="S33">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T33">
-        <v>2.77</v>
+        <v>3.1</v>
       </c>
       <c r="U33">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V33">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W33">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y33">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z33">
-        <v>3.48</v>
+        <v>3.8</v>
       </c>
       <c r="AA33">
         <v>1.87</v>
       </c>
       <c r="AB33">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AC33">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="AD33">
         <v>1.36</v>
       </c>
       <c r="AE33">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF33">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG33">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK33">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.52</v>
+        <v>2.26</v>
       </c>
       <c r="O34">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="P34">
-        <v>2.61</v>
+        <v>2.97</v>
       </c>
       <c r="Q34">
+        <v>2.75</v>
+      </c>
+      <c r="R34">
+        <v>2.15</v>
+      </c>
+      <c r="S34">
+        <v>1.36</v>
+      </c>
+      <c r="T34">
         <v>2.9</v>
       </c>
-      <c r="R34">
-        <v>2.28</v>
-      </c>
-      <c r="S34">
+      <c r="U34">
+        <v>2.8</v>
+      </c>
+      <c r="V34">
+        <v>1.4</v>
+      </c>
+      <c r="W34">
+        <v>1.08</v>
+      </c>
+      <c r="X34">
+        <v>1.05</v>
+      </c>
+      <c r="Y34">
         <v>1.33</v>
       </c>
-      <c r="T34">
-        <v>3.1</v>
-      </c>
-      <c r="U34">
-        <v>2.6</v>
-      </c>
-      <c r="V34">
-        <v>1.44</v>
-      </c>
-      <c r="W34">
-        <v>1.11</v>
-      </c>
-      <c r="X34">
-        <v>1.03</v>
-      </c>
-      <c r="Y34">
-        <v>1.21</v>
-      </c>
       <c r="Z34">
-        <v>3.58</v>
+        <v>3.25</v>
       </c>
       <c r="AA34">
+        <v>2.04</v>
+      </c>
+      <c r="AB34">
+        <v>1.75</v>
+      </c>
+      <c r="AC34">
+        <v>3.5</v>
+      </c>
+      <c r="AD34">
+        <v>1.29</v>
+      </c>
+      <c r="AE34">
+        <v>1.07</v>
+      </c>
+      <c r="AF34">
         <v>1.87</v>
       </c>
-      <c r="AB34">
+      <c r="AG34">
         <v>1.9</v>
-      </c>
-      <c r="AC34">
-        <v>3.14</v>
-      </c>
-      <c r="AD34">
-        <v>1.36</v>
-      </c>
-      <c r="AE34">
-        <v>1.13</v>
-      </c>
-      <c r="AF34">
-        <v>1.7</v>
-      </c>
-      <c r="AG34">
-        <v>2.05</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>1.33</v>
       </c>
       <c r="AK34">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.28</v>
+        <v>1.4</v>
       </c>
       <c r="O35">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="P35">
-        <v>2.97</v>
+        <v>7</v>
       </c>
       <c r="Q35">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="R35">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="S35">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T35">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="U35">
-        <v>2.8</v>
+        <v>2.23</v>
       </c>
       <c r="V35">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="W35">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X35">
         <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="Z35">
-        <v>3.37</v>
+        <v>5</v>
       </c>
       <c r="AA35">
-        <v>2.05</v>
+        <v>1.61</v>
       </c>
       <c r="AB35">
+        <v>2.38</v>
+      </c>
+      <c r="AC35">
+        <v>2.55</v>
+      </c>
+      <c r="AD35">
+        <v>1.5</v>
+      </c>
+      <c r="AE35">
+        <v>1.2</v>
+      </c>
+      <c r="AF35">
         <v>1.75</v>
       </c>
-      <c r="AC35">
-        <v>3.2</v>
-      </c>
-      <c r="AD35">
-        <v>1.29</v>
-      </c>
-      <c r="AE35">
-        <v>1.1</v>
-      </c>
-      <c r="AF35">
-        <v>1.8</v>
-      </c>
       <c r="AG35">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AK35">
-        <v>1.57</v>
+        <v>2.88</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,58 +6177,58 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="O36">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="P36">
-        <v>7</v>
+        <v>3.6</v>
       </c>
       <c r="Q36">
-        <v>1.8</v>
+        <v>2.45</v>
       </c>
       <c r="R36">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="S36">
+        <v>1.33</v>
+      </c>
+      <c r="T36">
+        <v>2.77</v>
+      </c>
+      <c r="U36">
+        <v>2.62</v>
+      </c>
+      <c r="V36">
+        <v>1.43</v>
+      </c>
+      <c r="W36">
+        <v>1.07</v>
+      </c>
+      <c r="X36">
+        <v>1.04</v>
+      </c>
+      <c r="Y36">
         <v>1.25</v>
       </c>
-      <c r="T36">
-        <v>3.5</v>
-      </c>
-      <c r="U36">
-        <v>2.23</v>
-      </c>
-      <c r="V36">
-        <v>1.57</v>
-      </c>
-      <c r="W36">
-        <v>1.14</v>
-      </c>
-      <c r="X36">
-        <v>1.01</v>
-      </c>
-      <c r="Y36">
-        <v>1.19</v>
-      </c>
       <c r="Z36">
-        <v>4.74</v>
+        <v>3.8</v>
       </c>
       <c r="AA36">
-        <v>1.61</v>
+        <v>1.87</v>
       </c>
       <c r="AB36">
-        <v>2.38</v>
+        <v>1.9</v>
       </c>
       <c r="AC36">
-        <v>2.53</v>
+        <v>3.1</v>
       </c>
       <c r="AD36">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AE36">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AF36">
         <v>1.75</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AK36">
-        <v>2.88</v>
+        <v>1.8</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6376,7 +6376,7 @@
         <v>1.13</v>
       </c>
       <c r="Z37">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AA37">
         <v>1.53</v>
@@ -6385,13 +6385,13 @@
         <v>2.63</v>
       </c>
       <c r="AC37">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AD37">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AE37">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF37">
         <v>1.5</v>
@@ -6509,7 +6509,7 @@
         <v>3.94</v>
       </c>
       <c r="P38">
-        <v>5.05</v>
+        <v>4.95</v>
       </c>
       <c r="Q38">
         <v>2.1</v>
@@ -6533,13 +6533,13 @@
         <v>1.07</v>
       </c>
       <c r="X38">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y38">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z38">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="AA38">
         <v>1.8</v>
@@ -6548,19 +6548,19 @@
         <v>2</v>
       </c>
       <c r="AC38">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AD38">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE38">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF38">
         <v>1.8</v>
       </c>
       <c r="AG38">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -7982,13 +7982,13 @@
         <v>1.98</v>
       </c>
       <c r="R47">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="S47">
         <v>1.3</v>
       </c>
       <c r="T47">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U47">
         <v>2.45</v>
@@ -8000,28 +8000,28 @@
         <v>1.11</v>
       </c>
       <c r="X47">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z47">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="AA47">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AB47">
         <v>2.1</v>
       </c>
       <c r="AC47">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AD47">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE47">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF47">
         <v>1.7</v>
@@ -8043,7 +8043,7 @@
         <v>1.25</v>
       </c>
       <c r="AK47">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AL47">
         <v>0</v>

--- a/jogos_2026-10-13.xlsx
+++ b/jogos_2026-10-13.xlsx
@@ -650,7 +650,7 @@
         <v>2.2</v>
       </c>
       <c r="S2">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T2">
         <v>2.73</v>
@@ -674,13 +674,13 @@
         <v>3.5</v>
       </c>
       <c r="AA2">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AB2">
         <v>1.83</v>
       </c>
       <c r="AC2">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="AD2">
         <v>1.27</v>
@@ -970,55 +970,55 @@
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1616,16 +1616,16 @@
         <v>1.89</v>
       </c>
       <c r="O8">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="P8">
-        <v>4.27</v>
+        <v>3.75</v>
       </c>
       <c r="Q8">
         <v>2.6</v>
       </c>
       <c r="R8">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="S8">
         <v>1.44</v>
@@ -1652,7 +1652,7 @@
         <v>2.44</v>
       </c>
       <c r="AA8">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="AB8">
         <v>1.5</v>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="O9">
         <v>2.85</v>
@@ -1815,7 +1815,7 @@
         <v>2.5</v>
       </c>
       <c r="AA9">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="AB9">
         <v>1.47</v>
@@ -1981,7 +1981,7 @@
         <v>1.99</v>
       </c>
       <c r="AB10">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC10">
         <v>3.42</v>
@@ -1993,7 +1993,7 @@
         <v>1.05</v>
       </c>
       <c r="AF10">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG10">
         <v>1.95</v>
@@ -2757,28 +2757,28 @@
         <v>3.5</v>
       </c>
       <c r="O15">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P15">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="Q15">
-        <v>3.64</v>
+        <v>3.44</v>
       </c>
       <c r="R15">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="S15">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T15">
         <v>3.5</v>
       </c>
       <c r="U15">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="V15">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W15">
         <v>1.15</v>
@@ -2796,7 +2796,7 @@
         <v>1.66</v>
       </c>
       <c r="AB15">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="AC15">
         <v>2.45</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AK15">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2947,13 +2947,13 @@
         <v>1.13</v>
       </c>
       <c r="X16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z16">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AA16">
         <v>1.53</v>
@@ -2968,7 +2968,7 @@
         <v>1.54</v>
       </c>
       <c r="AE16">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF16">
         <v>1.47</v>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK16">
         <v>1.5</v>
@@ -3243,10 +3243,10 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="O18">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="P18">
         <v>3.94</v>
@@ -3273,28 +3273,28 @@
         <v>1.03</v>
       </c>
       <c r="X18">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y18">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="Z18">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="AA18">
         <v>3</v>
       </c>
       <c r="AB18">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AC18">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AD18">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AE18">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF18">
         <v>2.45</v>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.87</v>
+        <v>2.93</v>
       </c>
       <c r="O19">
         <v>2.7</v>
@@ -3421,10 +3421,10 @@
         <v>1.95</v>
       </c>
       <c r="S19">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T19">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="U19">
         <v>2.9</v>
@@ -3436,13 +3436,13 @@
         <v>1.07</v>
       </c>
       <c r="X19">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y19">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z19">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="AA19">
         <v>2.15</v>
@@ -3451,13 +3451,13 @@
         <v>1.7</v>
       </c>
       <c r="AC19">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AD19">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE19">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF19">
         <v>1.8</v>
@@ -3581,7 +3581,7 @@
         <v>1.55</v>
       </c>
       <c r="R20">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="S20">
         <v>1.2</v>
@@ -3735,7 +3735,7 @@
         <v>2.8</v>
       </c>
       <c r="O21">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P21">
         <v>2.2</v>
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="O22">
         <v>3.4</v>
@@ -3916,10 +3916,10 @@
         <v>3.4</v>
       </c>
       <c r="U22">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="V22">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W22">
         <v>1.12</v>
@@ -4058,19 +4058,19 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="O23">
         <v>3.55</v>
       </c>
       <c r="P23">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="Q23">
         <v>2.96</v>
       </c>
       <c r="R23">
-        <v>2.42</v>
+        <v>2.49</v>
       </c>
       <c r="S23">
         <v>1.13</v>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK23">
         <v>1.39</v>
@@ -4550,7 +4550,7 @@
         <v>1.61</v>
       </c>
       <c r="O26">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P26">
         <v>4.33</v>
@@ -4586,7 +4586,7 @@
         <v>3.6</v>
       </c>
       <c r="AA26">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB26">
         <v>1.9</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="O27">
         <v>4.6</v>
       </c>
       <c r="P27">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="Q27">
         <v>1.75</v>
@@ -4740,34 +4740,34 @@
         <v>1.06</v>
       </c>
       <c r="X27">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y27">
         <v>1.3</v>
       </c>
       <c r="Z27">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA27">
         <v>2</v>
       </c>
       <c r="AB27">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AC27">
         <v>3.5</v>
       </c>
       <c r="AD27">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE27">
         <v>1.08</v>
       </c>
       <c r="AF27">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AG27">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -5534,10 +5534,10 @@
         <v>1.67</v>
       </c>
       <c r="Q32">
-        <v>4.6</v>
+        <v>4.24</v>
       </c>
       <c r="R32">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="S32">
         <v>1.36</v>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.25</v>
+        <v>1.92</v>
       </c>
       <c r="AK32">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5691,10 +5691,10 @@
         <v>2.52</v>
       </c>
       <c r="O33">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
       <c r="P33">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="Q33">
         <v>2.9</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.26</v>
+        <v>1.4</v>
       </c>
       <c r="O34">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="P34">
-        <v>2.97</v>
+        <v>7</v>
       </c>
       <c r="Q34">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="R34">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="S34">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T34">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="U34">
-        <v>2.8</v>
+        <v>2.23</v>
       </c>
       <c r="V34">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="W34">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X34">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="Z34">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="AA34">
-        <v>2.04</v>
+        <v>1.61</v>
       </c>
       <c r="AB34">
+        <v>2.38</v>
+      </c>
+      <c r="AC34">
+        <v>2.55</v>
+      </c>
+      <c r="AD34">
+        <v>1.5</v>
+      </c>
+      <c r="AE34">
+        <v>1.2</v>
+      </c>
+      <c r="AF34">
         <v>1.75</v>
       </c>
-      <c r="AC34">
-        <v>3.5</v>
-      </c>
-      <c r="AD34">
-        <v>1.29</v>
-      </c>
-      <c r="AE34">
-        <v>1.07</v>
-      </c>
-      <c r="AF34">
-        <v>1.87</v>
-      </c>
       <c r="AG34">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AK34">
-        <v>1.57</v>
+        <v>2.88</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,58 +6014,58 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="O35">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="P35">
-        <v>7</v>
+        <v>3.6</v>
       </c>
       <c r="Q35">
-        <v>1.8</v>
+        <v>2.45</v>
       </c>
       <c r="R35">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="S35">
+        <v>1.33</v>
+      </c>
+      <c r="T35">
+        <v>2.77</v>
+      </c>
+      <c r="U35">
+        <v>2.62</v>
+      </c>
+      <c r="V35">
+        <v>1.43</v>
+      </c>
+      <c r="W35">
+        <v>1.07</v>
+      </c>
+      <c r="X35">
+        <v>1.04</v>
+      </c>
+      <c r="Y35">
         <v>1.25</v>
       </c>
-      <c r="T35">
-        <v>3.5</v>
-      </c>
-      <c r="U35">
-        <v>2.23</v>
-      </c>
-      <c r="V35">
-        <v>1.57</v>
-      </c>
-      <c r="W35">
-        <v>1.14</v>
-      </c>
-      <c r="X35">
-        <v>1.01</v>
-      </c>
-      <c r="Y35">
-        <v>1.17</v>
-      </c>
       <c r="Z35">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="AA35">
-        <v>1.61</v>
+        <v>1.87</v>
       </c>
       <c r="AB35">
-        <v>2.38</v>
+        <v>1.9</v>
       </c>
       <c r="AC35">
-        <v>2.55</v>
+        <v>3.25</v>
       </c>
       <c r="AD35">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AE35">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AF35">
         <v>1.75</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK35">
-        <v>2.88</v>
+        <v>1.73</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,80 +6177,80 @@
         </is>
       </c>
       <c r="N36">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="O36">
+        <v>3.35</v>
+      </c>
+      <c r="P36">
+        <v>2.97</v>
+      </c>
+      <c r="Q36">
+        <v>2.75</v>
+      </c>
+      <c r="R36">
+        <v>2.15</v>
+      </c>
+      <c r="S36">
+        <v>1.36</v>
+      </c>
+      <c r="T36">
+        <v>2.9</v>
+      </c>
+      <c r="U36">
+        <v>2.8</v>
+      </c>
+      <c r="V36">
+        <v>1.4</v>
+      </c>
+      <c r="W36">
+        <v>1.08</v>
+      </c>
+      <c r="X36">
+        <v>1.05</v>
+      </c>
+      <c r="Y36">
+        <v>1.33</v>
+      </c>
+      <c r="Z36">
+        <v>3.25</v>
+      </c>
+      <c r="AA36">
+        <v>2.04</v>
+      </c>
+      <c r="AB36">
+        <v>1.75</v>
+      </c>
+      <c r="AC36">
         <v>3.5</v>
       </c>
-      <c r="P36">
-        <v>3.6</v>
-      </c>
-      <c r="Q36">
-        <v>2.45</v>
-      </c>
-      <c r="R36">
-        <v>2.2</v>
-      </c>
-      <c r="S36">
+      <c r="AD36">
+        <v>1.29</v>
+      </c>
+      <c r="AE36">
+        <v>1.07</v>
+      </c>
+      <c r="AF36">
+        <v>1.87</v>
+      </c>
+      <c r="AG36">
+        <v>1.9</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ36">
         <v>1.33</v>
       </c>
-      <c r="T36">
-        <v>2.77</v>
-      </c>
-      <c r="U36">
-        <v>2.62</v>
-      </c>
-      <c r="V36">
-        <v>1.43</v>
-      </c>
-      <c r="W36">
-        <v>1.07</v>
-      </c>
-      <c r="X36">
-        <v>1.04</v>
-      </c>
-      <c r="Y36">
-        <v>1.25</v>
-      </c>
-      <c r="Z36">
-        <v>3.8</v>
-      </c>
-      <c r="AA36">
-        <v>1.87</v>
-      </c>
-      <c r="AB36">
-        <v>1.9</v>
-      </c>
-      <c r="AC36">
-        <v>3.1</v>
-      </c>
-      <c r="AD36">
-        <v>1.36</v>
-      </c>
-      <c r="AE36">
-        <v>1.1</v>
-      </c>
-      <c r="AF36">
-        <v>1.75</v>
-      </c>
-      <c r="AG36">
-        <v>2</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ36">
-        <v>1.23</v>
-      </c>
       <c r="AK36">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="O38">
-        <v>3.94</v>
+        <v>3.98</v>
       </c>
       <c r="P38">
         <v>4.95</v>
@@ -6666,10 +6666,10 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="O39">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P39">
         <v>2.7</v>
@@ -6678,7 +6678,7 @@
         <v>2.73</v>
       </c>
       <c r="R39">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="S39">
         <v>1.31</v>
@@ -6705,10 +6705,10 @@
         <v>4.5</v>
       </c>
       <c r="AA39">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="AB39">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC39">
         <v>2.63</v>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK39">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6832,7 +6832,7 @@
         <v>1.24</v>
       </c>
       <c r="O40">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="P40">
         <v>11</v>
@@ -6841,7 +6841,7 @@
         <v>1.63</v>
       </c>
       <c r="R40">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="S40">
         <v>1.29</v>
@@ -6886,7 +6886,7 @@
         <v>2.14</v>
       </c>
       <c r="AG40">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>1.14</v>
       </c>
       <c r="AK40">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>14</v>
+        <v>1.93</v>
       </c>
       <c r="O41">
-        <v>11</v>
+        <v>3.85</v>
       </c>
       <c r="P41">
-        <v>1.07</v>
+        <v>3.5</v>
       </c>
       <c r="Q41">
-        <v>11.89</v>
+        <v>2.38</v>
       </c>
       <c r="R41">
-        <v>4.19</v>
+        <v>2.36</v>
       </c>
       <c r="S41">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="T41">
-        <v>7</v>
+        <v>3.35</v>
       </c>
       <c r="U41">
-        <v>1.6</v>
+        <v>2.16</v>
       </c>
       <c r="V41">
-        <v>2.2</v>
+        <v>1.66</v>
       </c>
       <c r="W41">
-        <v>1.41</v>
+        <v>1.17</v>
       </c>
       <c r="X41">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="Z41">
-        <v>13</v>
+        <v>5.5</v>
       </c>
       <c r="AA41">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="AB41">
-        <v>5.5</v>
+        <v>2.62</v>
       </c>
       <c r="AC41">
-        <v>1.36</v>
+        <v>2.15</v>
       </c>
       <c r="AD41">
-        <v>3</v>
+        <v>1.63</v>
       </c>
       <c r="AE41">
-        <v>1.9</v>
+        <v>1.25</v>
       </c>
       <c r="AF41">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="AG41">
-        <v>1.99</v>
+        <v>2.62</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>8.699999999999999</v>
+        <v>1.19</v>
       </c>
       <c r="AK41">
-        <v>1</v>
+        <v>1.92</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,80 +7155,80 @@
         </is>
       </c>
       <c r="N42">
-        <v>6.5</v>
+        <v>14</v>
       </c>
       <c r="O42">
-        <v>6.7</v>
+        <v>11</v>
       </c>
       <c r="P42">
-        <v>1.28</v>
+        <v>1.07</v>
       </c>
       <c r="Q42">
-        <v>5.03</v>
+        <v>11.95</v>
       </c>
       <c r="R42">
-        <v>2.9</v>
+        <v>4.37</v>
       </c>
       <c r="S42">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="T42">
-        <v>5.75</v>
+        <v>7</v>
       </c>
       <c r="U42">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="V42">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="W42">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="X42">
         <v>1</v>
       </c>
       <c r="Y42">
+        <v>1.01</v>
+      </c>
+      <c r="Z42">
+        <v>13</v>
+      </c>
+      <c r="AA42">
+        <v>1.11</v>
+      </c>
+      <c r="AB42">
+        <v>4.95</v>
+      </c>
+      <c r="AC42">
+        <v>1.36</v>
+      </c>
+      <c r="AD42">
+        <v>3</v>
+      </c>
+      <c r="AE42">
+        <v>1.9</v>
+      </c>
+      <c r="AF42">
+        <v>1.73</v>
+      </c>
+      <c r="AG42">
+        <v>1.99</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ42">
         <v>1.03</v>
       </c>
-      <c r="Z42">
-        <v>10</v>
-      </c>
-      <c r="AA42">
-        <v>1.2</v>
-      </c>
-      <c r="AB42">
-        <v>4.5</v>
-      </c>
-      <c r="AC42">
-        <v>1.5</v>
-      </c>
-      <c r="AD42">
-        <v>2.5</v>
-      </c>
-      <c r="AE42">
-        <v>1.67</v>
-      </c>
-      <c r="AF42">
-        <v>1.4</v>
-      </c>
-      <c r="AG42">
-        <v>2.77</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ42">
-        <v>1.08</v>
-      </c>
       <c r="AK42">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.83</v>
+        <v>6.5</v>
       </c>
       <c r="O43">
-        <v>4.25</v>
+        <v>6.7</v>
       </c>
       <c r="P43">
-        <v>3.8</v>
+        <v>1.27</v>
       </c>
       <c r="Q43">
-        <v>2.26</v>
+        <v>6.66</v>
       </c>
       <c r="R43">
-        <v>2.5</v>
+        <v>3.26</v>
       </c>
       <c r="S43">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="T43">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="U43">
-        <v>2.02</v>
+        <v>1.67</v>
       </c>
       <c r="V43">
-        <v>1.75</v>
+        <v>2.22</v>
       </c>
       <c r="W43">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="X43">
+        <v>1</v>
+      </c>
+      <c r="Y43">
         <v>1.01</v>
       </c>
-      <c r="Y43">
-        <v>1.06</v>
-      </c>
       <c r="Z43">
-        <v>7.5</v>
+        <v>8.6</v>
       </c>
       <c r="AA43">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AB43">
-        <v>3.04</v>
+        <v>4.5</v>
       </c>
       <c r="AC43">
-        <v>1.87</v>
+        <v>1.44</v>
       </c>
       <c r="AD43">
-        <v>1.87</v>
+        <v>2.46</v>
       </c>
       <c r="AE43">
-        <v>1.33</v>
+        <v>1.78</v>
       </c>
       <c r="AF43">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AG43">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.24</v>
+        <v>3.92</v>
       </c>
       <c r="AK43">
-        <v>2</v>
+        <v>1.07</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="O44">
-        <v>3.7</v>
+        <v>4.35</v>
       </c>
       <c r="P44">
-        <v>2.75</v>
+        <v>3.8</v>
       </c>
       <c r="Q44">
-        <v>2.45</v>
+        <v>2.21</v>
       </c>
       <c r="R44">
-        <v>2.36</v>
+        <v>2.54</v>
       </c>
       <c r="S44">
+        <v>1.17</v>
+      </c>
+      <c r="T44">
+        <v>5</v>
+      </c>
+      <c r="U44">
+        <v>1.9</v>
+      </c>
+      <c r="V44">
+        <v>1.83</v>
+      </c>
+      <c r="W44">
         <v>1.25</v>
-      </c>
-      <c r="T44">
-        <v>3.35</v>
-      </c>
-      <c r="U44">
-        <v>2.16</v>
-      </c>
-      <c r="V44">
-        <v>1.7</v>
-      </c>
-      <c r="W44">
-        <v>1.17</v>
       </c>
       <c r="X44">
         <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="Z44">
-        <v>5.75</v>
+        <v>7.5</v>
       </c>
       <c r="AA44">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AB44">
-        <v>2.47</v>
+        <v>3.26</v>
       </c>
       <c r="AC44">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AD44">
-        <v>1.64</v>
+        <v>1.91</v>
       </c>
       <c r="AE44">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AF44">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AG44">
-        <v>2.66</v>
+        <v>3.1</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AK44">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7650,16 +7650,16 @@
         <v>5.75</v>
       </c>
       <c r="P45">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="Q45">
         <v>1.63</v>
       </c>
       <c r="R45">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="S45">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T45">
         <v>3.9</v>
@@ -7695,7 +7695,7 @@
         <v>1.73</v>
       </c>
       <c r="AE45">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AF45">
         <v>1.8</v>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK45">
         <v>3.6</v>
@@ -7976,13 +7976,13 @@
         <v>3.95</v>
       </c>
       <c r="P47">
-        <v>4.98</v>
+        <v>5.25</v>
       </c>
       <c r="Q47">
         <v>1.98</v>
       </c>
       <c r="R47">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S47">
         <v>1.3</v>
@@ -7991,7 +7991,7 @@
         <v>3.3</v>
       </c>
       <c r="U47">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="V47">
         <v>1.5</v>
@@ -8015,13 +8015,13 @@
         <v>2.1</v>
       </c>
       <c r="AC47">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AD47">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE47">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF47">
         <v>1.7</v>
@@ -8169,7 +8169,7 @@
         <v>1.2</v>
       </c>
       <c r="Z48">
-        <v>3.65</v>
+        <v>4.33</v>
       </c>
       <c r="AA48">
         <v>1.66</v>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.2</v>
+        <v>1.73</v>
       </c>
       <c r="AK48">
         <v>1.21</v>
@@ -8489,13 +8489,13 @@
         <v>1.05</v>
       </c>
       <c r="X50">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y50">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z50">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="AA50">
         <v>2.25</v>
@@ -8504,19 +8504,19 @@
         <v>1.61</v>
       </c>
       <c r="AC50">
-        <v>3.95</v>
+        <v>4.33</v>
       </c>
       <c r="AD50">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE50">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF50">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AG50">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>

--- a/jogos_2026-10-13.xlsx
+++ b/jogos_2026-10-13.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="O2">
         <v>3.2</v>
@@ -674,10 +674,10 @@
         <v>3.5</v>
       </c>
       <c r="AA2">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AB2">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AC2">
         <v>3.27</v>
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O5">
         <v>2.8</v>
@@ -1963,10 +1963,10 @@
         <v>2.73</v>
       </c>
       <c r="V10">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W10">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X10">
         <v>1.02</v>
@@ -1987,7 +1987,7 @@
         <v>3.42</v>
       </c>
       <c r="AD10">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AE10">
         <v>1.05</v>
@@ -1996,7 +1996,7 @@
         <v>1.8</v>
       </c>
       <c r="AG10">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>3.3</v>
       </c>
       <c r="P11">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q11">
         <v>2.59</v>
@@ -2120,7 +2120,7 @@
         <v>1.33</v>
       </c>
       <c r="T11">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="U11">
         <v>2.72</v>
@@ -2274,10 +2274,10 @@
         <v>2.5</v>
       </c>
       <c r="Q12">
+        <v>2.63</v>
+      </c>
+      <c r="R12">
         <v>2.6</v>
-      </c>
-      <c r="R12">
-        <v>2.63</v>
       </c>
       <c r="S12">
         <v>1.13</v>
@@ -2286,7 +2286,7 @@
         <v>4.6</v>
       </c>
       <c r="U12">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="V12">
         <v>1.82</v>
@@ -2295,7 +2295,7 @@
         <v>1.22</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
         <v>1.05</v>
@@ -2319,10 +2319,10 @@
         <v>1.34</v>
       </c>
       <c r="AF12">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AG12">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>1.17</v>
       </c>
       <c r="AK12">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -3587,7 +3587,7 @@
         <v>1.2</v>
       </c>
       <c r="T20">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="U20">
         <v>1.95</v>
@@ -3611,10 +3611,10 @@
         <v>1.4</v>
       </c>
       <c r="AB20">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AC20">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AD20">
         <v>1.75</v>
@@ -3623,10 +3623,10 @@
         <v>1.3</v>
       </c>
       <c r="AF20">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG20">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,34 +4058,34 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.72</v>
+        <v>1.5</v>
       </c>
       <c r="O23">
-        <v>3.55</v>
+        <v>4.05</v>
       </c>
       <c r="P23">
-        <v>2.08</v>
+        <v>5</v>
       </c>
       <c r="Q23">
-        <v>2.96</v>
+        <v>1.93</v>
       </c>
       <c r="R23">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="S23">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="T23">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="U23">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="V23">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="W23">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="X23">
         <v>1.01</v>
@@ -4094,28 +4094,28 @@
         <v>1.1</v>
       </c>
       <c r="Z23">
-        <v>6.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA23">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AB23">
-        <v>3.1</v>
+        <v>2.35</v>
       </c>
       <c r="AC23">
-        <v>1.9</v>
+        <v>2.33</v>
       </c>
       <c r="AD23">
-        <v>1.87</v>
+        <v>1.57</v>
       </c>
       <c r="AE23">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AF23">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="AG23">
-        <v>3</v>
+        <v>2.15</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK23">
-        <v>1.39</v>
+        <v>2.4</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,34 +4221,34 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.5</v>
+        <v>2.72</v>
       </c>
       <c r="O24">
-        <v>4.05</v>
+        <v>3.55</v>
       </c>
       <c r="P24">
-        <v>5</v>
+        <v>2.08</v>
       </c>
       <c r="Q24">
-        <v>1.93</v>
+        <v>2.96</v>
       </c>
       <c r="R24">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="S24">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="T24">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="U24">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="V24">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="W24">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="X24">
         <v>1.01</v>
@@ -4257,28 +4257,28 @@
         <v>1.1</v>
       </c>
       <c r="Z24">
-        <v>4.8</v>
+        <v>6.5</v>
       </c>
       <c r="AA24">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AB24">
-        <v>2.35</v>
+        <v>3.1</v>
       </c>
       <c r="AC24">
-        <v>2.33</v>
+        <v>1.9</v>
       </c>
       <c r="AD24">
-        <v>1.57</v>
+        <v>1.87</v>
       </c>
       <c r="AE24">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AF24">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AG24">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK24">
-        <v>2.4</v>
+        <v>1.39</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -5531,7 +5531,7 @@
         <v>3.5</v>
       </c>
       <c r="P32">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="Q32">
         <v>4.24</v>
@@ -5570,10 +5570,10 @@
         <v>1.79</v>
       </c>
       <c r="AC32">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AD32">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE32">
         <v>1.1</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.52</v>
+        <v>1.52</v>
       </c>
       <c r="O33">
-        <v>3.44</v>
+        <v>4.05</v>
       </c>
       <c r="P33">
+        <v>4.25</v>
+      </c>
+      <c r="Q33">
+        <v>2.14</v>
+      </c>
+      <c r="R33">
+        <v>2.5</v>
+      </c>
+      <c r="S33">
+        <v>1.22</v>
+      </c>
+      <c r="T33">
+        <v>3.8</v>
+      </c>
+      <c r="U33">
+        <v>2.15</v>
+      </c>
+      <c r="V33">
+        <v>1.65</v>
+      </c>
+      <c r="W33">
+        <v>1.14</v>
+      </c>
+      <c r="X33">
+        <v>1.01</v>
+      </c>
+      <c r="Y33">
+        <v>1.13</v>
+      </c>
+      <c r="Z33">
+        <v>6</v>
+      </c>
+      <c r="AA33">
+        <v>1.53</v>
+      </c>
+      <c r="AB33">
         <v>2.63</v>
       </c>
-      <c r="Q33">
-        <v>2.9</v>
-      </c>
-      <c r="R33">
-        <v>2.28</v>
-      </c>
-      <c r="S33">
-        <v>1.33</v>
-      </c>
-      <c r="T33">
-        <v>3.1</v>
-      </c>
-      <c r="U33">
-        <v>2.6</v>
-      </c>
-      <c r="V33">
-        <v>1.44</v>
-      </c>
-      <c r="W33">
-        <v>1.11</v>
-      </c>
-      <c r="X33">
-        <v>1.04</v>
-      </c>
-      <c r="Y33">
+      <c r="AC33">
+        <v>2.2</v>
+      </c>
+      <c r="AD33">
+        <v>1.65</v>
+      </c>
+      <c r="AE33">
         <v>1.25</v>
       </c>
-      <c r="Z33">
-        <v>3.8</v>
-      </c>
-      <c r="AA33">
-        <v>1.87</v>
-      </c>
-      <c r="AB33">
-        <v>1.9</v>
-      </c>
-      <c r="AC33">
-        <v>3.1</v>
-      </c>
-      <c r="AD33">
-        <v>1.36</v>
-      </c>
-      <c r="AE33">
-        <v>1.1</v>
-      </c>
       <c r="AF33">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AG33">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AK33">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,80 +5851,80 @@
         </is>
       </c>
       <c r="N34">
+        <v>2.26</v>
+      </c>
+      <c r="O34">
+        <v>3.35</v>
+      </c>
+      <c r="P34">
+        <v>2.97</v>
+      </c>
+      <c r="Q34">
+        <v>2.75</v>
+      </c>
+      <c r="R34">
+        <v>2.15</v>
+      </c>
+      <c r="S34">
+        <v>1.36</v>
+      </c>
+      <c r="T34">
+        <v>2.9</v>
+      </c>
+      <c r="U34">
+        <v>2.8</v>
+      </c>
+      <c r="V34">
         <v>1.4</v>
       </c>
-      <c r="O34">
-        <v>4.5</v>
-      </c>
-      <c r="P34">
-        <v>7</v>
-      </c>
-      <c r="Q34">
-        <v>1.8</v>
-      </c>
-      <c r="R34">
-        <v>2.5</v>
-      </c>
-      <c r="S34">
-        <v>1.25</v>
-      </c>
-      <c r="T34">
+      <c r="W34">
+        <v>1.08</v>
+      </c>
+      <c r="X34">
+        <v>1.05</v>
+      </c>
+      <c r="Y34">
+        <v>1.33</v>
+      </c>
+      <c r="Z34">
+        <v>3.25</v>
+      </c>
+      <c r="AA34">
+        <v>2.04</v>
+      </c>
+      <c r="AB34">
+        <v>1.75</v>
+      </c>
+      <c r="AC34">
         <v>3.5</v>
       </c>
-      <c r="U34">
-        <v>2.23</v>
-      </c>
-      <c r="V34">
+      <c r="AD34">
+        <v>1.29</v>
+      </c>
+      <c r="AE34">
+        <v>1.07</v>
+      </c>
+      <c r="AF34">
+        <v>1.87</v>
+      </c>
+      <c r="AG34">
+        <v>1.9</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ34">
+        <v>1.33</v>
+      </c>
+      <c r="AK34">
         <v>1.57</v>
-      </c>
-      <c r="W34">
-        <v>1.14</v>
-      </c>
-      <c r="X34">
-        <v>1.01</v>
-      </c>
-      <c r="Y34">
-        <v>1.17</v>
-      </c>
-      <c r="Z34">
-        <v>5</v>
-      </c>
-      <c r="AA34">
-        <v>1.61</v>
-      </c>
-      <c r="AB34">
-        <v>2.38</v>
-      </c>
-      <c r="AC34">
-        <v>2.55</v>
-      </c>
-      <c r="AD34">
-        <v>1.5</v>
-      </c>
-      <c r="AE34">
-        <v>1.2</v>
-      </c>
-      <c r="AF34">
-        <v>1.75</v>
-      </c>
-      <c r="AG34">
-        <v>2</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ34">
-        <v>1.2</v>
-      </c>
-      <c r="AK34">
-        <v>2.88</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.26</v>
+        <v>2.52</v>
       </c>
       <c r="O36">
-        <v>3.35</v>
+        <v>3.44</v>
       </c>
       <c r="P36">
-        <v>2.97</v>
+        <v>2.63</v>
       </c>
       <c r="Q36">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="R36">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="S36">
+        <v>1.33</v>
+      </c>
+      <c r="T36">
+        <v>3.1</v>
+      </c>
+      <c r="U36">
+        <v>2.6</v>
+      </c>
+      <c r="V36">
+        <v>1.44</v>
+      </c>
+      <c r="W36">
+        <v>1.11</v>
+      </c>
+      <c r="X36">
+        <v>1.04</v>
+      </c>
+      <c r="Y36">
+        <v>1.25</v>
+      </c>
+      <c r="Z36">
+        <v>3.8</v>
+      </c>
+      <c r="AA36">
+        <v>1.87</v>
+      </c>
+      <c r="AB36">
+        <v>1.9</v>
+      </c>
+      <c r="AC36">
+        <v>3.1</v>
+      </c>
+      <c r="AD36">
         <v>1.36</v>
       </c>
-      <c r="T36">
-        <v>2.9</v>
-      </c>
-      <c r="U36">
-        <v>2.8</v>
-      </c>
-      <c r="V36">
-        <v>1.4</v>
-      </c>
-      <c r="W36">
-        <v>1.08</v>
-      </c>
-      <c r="X36">
-        <v>1.05</v>
-      </c>
-      <c r="Y36">
-        <v>1.33</v>
-      </c>
-      <c r="Z36">
-        <v>3.25</v>
-      </c>
-      <c r="AA36">
-        <v>2.04</v>
-      </c>
-      <c r="AB36">
-        <v>1.75</v>
-      </c>
-      <c r="AC36">
-        <v>3.5</v>
-      </c>
-      <c r="AD36">
-        <v>1.29</v>
-      </c>
       <c r="AE36">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF36">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AG36">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>1.33</v>
       </c>
       <c r="AK36">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,31 +6340,31 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="O37">
-        <v>4.05</v>
+        <v>4.5</v>
       </c>
       <c r="P37">
-        <v>4.25</v>
+        <v>7</v>
       </c>
       <c r="Q37">
-        <v>2.14</v>
+        <v>1.8</v>
       </c>
       <c r="R37">
         <v>2.5</v>
       </c>
       <c r="S37">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T37">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="U37">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="V37">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="W37">
         <v>1.14</v>
@@ -6373,31 +6373,31 @@
         <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA37">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AB37">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="AC37">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="AD37">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AE37">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AF37">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AG37">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK37">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="O39">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="P39">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="Q39">
-        <v>2.73</v>
+        <v>2.38</v>
       </c>
       <c r="R39">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="S39">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T39">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="U39">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="V39">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="W39">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X39">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="Z39">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AA39">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AB39">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="AC39">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="AD39">
+        <v>1.63</v>
+      </c>
+      <c r="AE39">
+        <v>1.25</v>
+      </c>
+      <c r="AF39">
         <v>1.44</v>
       </c>
-      <c r="AE39">
-        <v>1.18</v>
-      </c>
-      <c r="AF39">
-        <v>1.52</v>
-      </c>
       <c r="AG39">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK39">
-        <v>1.71</v>
+        <v>1.92</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,34 +6992,34 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.93</v>
+        <v>1.26</v>
       </c>
       <c r="O41">
-        <v>3.85</v>
+        <v>5.75</v>
       </c>
       <c r="P41">
-        <v>3.5</v>
+        <v>10</v>
       </c>
       <c r="Q41">
-        <v>2.38</v>
+        <v>1.63</v>
       </c>
       <c r="R41">
-        <v>2.36</v>
+        <v>2.64</v>
       </c>
       <c r="S41">
         <v>1.25</v>
       </c>
       <c r="T41">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="U41">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="V41">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W41">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X41">
         <v>1.01</v>
@@ -7028,28 +7028,28 @@
         <v>1.11</v>
       </c>
       <c r="Z41">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AA41">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB41">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AC41">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AD41">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AE41">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF41">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AG41">
-        <v>2.62</v>
+        <v>1.86</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.19</v>
+        <v>1.02</v>
       </c>
       <c r="AK41">
-        <v>1.92</v>
+        <v>3.6</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>14</v>
+        <v>2.1</v>
       </c>
       <c r="O42">
-        <v>11</v>
+        <v>3.75</v>
       </c>
       <c r="P42">
-        <v>1.07</v>
+        <v>2.7</v>
       </c>
       <c r="Q42">
-        <v>11.95</v>
+        <v>2.73</v>
       </c>
       <c r="R42">
-        <v>4.37</v>
+        <v>2.24</v>
       </c>
       <c r="S42">
+        <v>1.31</v>
+      </c>
+      <c r="T42">
+        <v>3.34</v>
+      </c>
+      <c r="U42">
+        <v>2.4</v>
+      </c>
+      <c r="V42">
+        <v>1.53</v>
+      </c>
+      <c r="W42">
         <v>1.1</v>
       </c>
-      <c r="T42">
-        <v>7</v>
-      </c>
-      <c r="U42">
+      <c r="X42">
+        <v>1.03</v>
+      </c>
+      <c r="Y42">
+        <v>1.18</v>
+      </c>
+      <c r="Z42">
+        <v>4.5</v>
+      </c>
+      <c r="AA42">
+        <v>1.61</v>
+      </c>
+      <c r="AB42">
+        <v>2.3</v>
+      </c>
+      <c r="AC42">
+        <v>2.63</v>
+      </c>
+      <c r="AD42">
+        <v>1.44</v>
+      </c>
+      <c r="AE42">
+        <v>1.18</v>
+      </c>
+      <c r="AF42">
         <v>1.52</v>
       </c>
-      <c r="V42">
-        <v>2.3</v>
-      </c>
-      <c r="W42">
-        <v>1.43</v>
-      </c>
-      <c r="X42">
-        <v>1</v>
-      </c>
-      <c r="Y42">
-        <v>1.01</v>
-      </c>
-      <c r="Z42">
-        <v>13</v>
-      </c>
-      <c r="AA42">
-        <v>1.11</v>
-      </c>
-      <c r="AB42">
-        <v>4.95</v>
-      </c>
-      <c r="AC42">
-        <v>1.36</v>
-      </c>
-      <c r="AD42">
-        <v>3</v>
-      </c>
-      <c r="AE42">
-        <v>1.9</v>
-      </c>
-      <c r="AF42">
-        <v>1.73</v>
-      </c>
       <c r="AG42">
-        <v>1.99</v>
+        <v>2.38</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="AK42">
-        <v>1</v>
+        <v>1.71</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,34 +7318,34 @@
         </is>
       </c>
       <c r="N43">
-        <v>6.5</v>
+        <v>14</v>
       </c>
       <c r="O43">
-        <v>6.7</v>
+        <v>11</v>
       </c>
       <c r="P43">
-        <v>1.27</v>
+        <v>1.07</v>
       </c>
       <c r="Q43">
-        <v>6.66</v>
+        <v>11.95</v>
       </c>
       <c r="R43">
-        <v>3.26</v>
+        <v>4.37</v>
       </c>
       <c r="S43">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="T43">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="U43">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="V43">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="W43">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="X43">
         <v>1</v>
@@ -7354,28 +7354,28 @@
         <v>1.01</v>
       </c>
       <c r="Z43">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="AA43">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AB43">
-        <v>4.5</v>
+        <v>4.95</v>
       </c>
       <c r="AC43">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AD43">
-        <v>2.46</v>
+        <v>3</v>
       </c>
       <c r="AE43">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AF43">
-        <v>1.41</v>
+        <v>1.73</v>
       </c>
       <c r="AG43">
-        <v>2.73</v>
+        <v>1.99</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>3.92</v>
+        <v>1.03</v>
       </c>
       <c r="AK43">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.75</v>
+        <v>6.5</v>
       </c>
       <c r="O44">
-        <v>4.35</v>
+        <v>6.7</v>
       </c>
       <c r="P44">
-        <v>3.8</v>
+        <v>1.27</v>
       </c>
       <c r="Q44">
-        <v>2.21</v>
+        <v>6.66</v>
       </c>
       <c r="R44">
-        <v>2.54</v>
+        <v>3.26</v>
       </c>
       <c r="S44">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="T44">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="U44">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="V44">
-        <v>1.83</v>
+        <v>2.22</v>
       </c>
       <c r="W44">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="X44">
+        <v>1</v>
+      </c>
+      <c r="Y44">
         <v>1.01</v>
       </c>
-      <c r="Y44">
-        <v>1.06</v>
-      </c>
       <c r="Z44">
-        <v>7.5</v>
+        <v>8.6</v>
       </c>
       <c r="AA44">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AB44">
-        <v>3.26</v>
+        <v>4.5</v>
       </c>
       <c r="AC44">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="AD44">
-        <v>1.91</v>
+        <v>2.46</v>
       </c>
       <c r="AE44">
-        <v>1.4</v>
+        <v>1.78</v>
       </c>
       <c r="AF44">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AG44">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.16</v>
+        <v>3.92</v>
       </c>
       <c r="AK44">
-        <v>1.95</v>
+        <v>1.07</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.26</v>
+        <v>1.75</v>
       </c>
       <c r="O45">
-        <v>5.75</v>
+        <v>4.35</v>
       </c>
       <c r="P45">
-        <v>10</v>
+        <v>3.8</v>
       </c>
       <c r="Q45">
-        <v>1.63</v>
+        <v>2.21</v>
       </c>
       <c r="R45">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="S45">
+        <v>1.17</v>
+      </c>
+      <c r="T45">
+        <v>5</v>
+      </c>
+      <c r="U45">
+        <v>1.9</v>
+      </c>
+      <c r="V45">
+        <v>1.83</v>
+      </c>
+      <c r="W45">
         <v>1.25</v>
-      </c>
-      <c r="T45">
-        <v>3.9</v>
-      </c>
-      <c r="U45">
-        <v>2.1</v>
-      </c>
-      <c r="V45">
-        <v>1.67</v>
-      </c>
-      <c r="W45">
-        <v>1.18</v>
       </c>
       <c r="X45">
         <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="Z45">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="AA45">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AB45">
-        <v>2.75</v>
+        <v>3.26</v>
       </c>
       <c r="AC45">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AD45">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AE45">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AF45">
-        <v>1.8</v>
+        <v>1.33</v>
       </c>
       <c r="AG45">
-        <v>1.86</v>
+        <v>3.1</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="AK45">
-        <v>3.6</v>
+        <v>1.95</v>
       </c>
       <c r="AL45">
         <v>0</v>

--- a/jogos_2026-10-13.xlsx
+++ b/jogos_2026-10-13.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="O2">
         <v>3.2</v>
@@ -650,7 +650,7 @@
         <v>2.2</v>
       </c>
       <c r="S2">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T2">
         <v>2.73</v>
@@ -671,13 +671,13 @@
         <v>1.25</v>
       </c>
       <c r="Z2">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AA2">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AB2">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AC2">
         <v>3.27</v>
@@ -689,7 +689,7 @@
         <v>1.06</v>
       </c>
       <c r="AF2">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG2">
         <v>1.95</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK2">
         <v>1.62</v>
@@ -3762,7 +3762,7 @@
         <v>1.14</v>
       </c>
       <c r="X21">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
         <v>1.13</v>
@@ -3771,7 +3771,7 @@
         <v>4.72</v>
       </c>
       <c r="AA21">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AB21">
         <v>2.28</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O22">
         <v>3.4</v>
       </c>
       <c r="P22">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="Q22">
         <v>2.9</v>
@@ -3910,28 +3910,28 @@
         <v>2.18</v>
       </c>
       <c r="S22">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T22">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U22">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="V22">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W22">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X22">
         <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z22">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA22">
         <v>1.62</v>
@@ -3940,16 +3940,16 @@
         <v>2.25</v>
       </c>
       <c r="AC22">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="AD22">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="AE22">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AF22">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG22">
         <v>2.38</v>
@@ -4061,13 +4061,13 @@
         <v>1.5</v>
       </c>
       <c r="O23">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="P23">
         <v>5</v>
       </c>
       <c r="Q23">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="R23">
         <v>2.5</v>
@@ -4076,10 +4076,10 @@
         <v>1.22</v>
       </c>
       <c r="T23">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="U23">
-        <v>1.91</v>
+        <v>2.12</v>
       </c>
       <c r="V23">
         <v>1.65</v>
@@ -4088,10 +4088,10 @@
         <v>1.14</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z23">
         <v>4.8</v>
@@ -4100,7 +4100,7 @@
         <v>1.57</v>
       </c>
       <c r="AB23">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AC23">
         <v>2.33</v>
@@ -4109,13 +4109,13 @@
         <v>1.57</v>
       </c>
       <c r="AE23">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AF23">
         <v>1.62</v>
       </c>
       <c r="AG23">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AK23">
         <v>2.4</v>
@@ -4221,16 +4221,16 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.72</v>
+        <v>2.91</v>
       </c>
       <c r="O24">
         <v>3.55</v>
       </c>
       <c r="P24">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q24">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="R24">
         <v>2.49</v>
@@ -4239,7 +4239,7 @@
         <v>1.13</v>
       </c>
       <c r="T24">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="U24">
         <v>1.95</v>
@@ -4248,7 +4248,7 @@
         <v>1.75</v>
       </c>
       <c r="W24">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X24">
         <v>1.01</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="AK24">
         <v>1.39</v>
@@ -4393,10 +4393,10 @@
         <v>4.2</v>
       </c>
       <c r="Q25">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="R25">
-        <v>2.44</v>
+        <v>2.51</v>
       </c>
       <c r="S25">
         <v>1.2</v>
@@ -4405,13 +4405,13 @@
         <v>4</v>
       </c>
       <c r="U25">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="V25">
-        <v>1.74</v>
+        <v>1.86</v>
       </c>
       <c r="W25">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X25">
         <v>1.01</v>
@@ -4441,7 +4441,7 @@
         <v>1.4</v>
       </c>
       <c r="AG25">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4547,28 +4547,28 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="O26">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P26">
-        <v>4.33</v>
+        <v>4.81</v>
       </c>
       <c r="Q26">
         <v>2.19</v>
       </c>
       <c r="R26">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S26">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T26">
         <v>2.94</v>
       </c>
       <c r="U26">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="V26">
         <v>1.44</v>
@@ -4583,7 +4583,7 @@
         <v>1.21</v>
       </c>
       <c r="Z26">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AA26">
         <v>1.8</v>
@@ -4598,13 +4598,13 @@
         <v>1.31</v>
       </c>
       <c r="AE26">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF26">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG26">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>1.18</v>
       </c>
       <c r="AK26">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5371,55 +5371,55 @@
         <v>5.28</v>
       </c>
       <c r="Q31">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="R31">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="S31">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="T31">
-        <v>2.71</v>
+        <v>2.4</v>
       </c>
       <c r="U31">
-        <v>3.03</v>
+        <v>3.8</v>
       </c>
       <c r="V31">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y31">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="Z31">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="AA31">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="AB31">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF31">
-        <v>2.34</v>
+        <v>2.75</v>
       </c>
       <c r="AG31">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.21</v>
+        <v>1.06</v>
       </c>
       <c r="AK31">
-        <v>2.04</v>
+        <v>2.7</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.52</v>
+        <v>2</v>
       </c>
       <c r="O33">
-        <v>4.05</v>
+        <v>3.5</v>
       </c>
       <c r="P33">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="Q33">
-        <v>2.14</v>
+        <v>2.45</v>
       </c>
       <c r="R33">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="S33">
+        <v>1.3</v>
+      </c>
+      <c r="T33">
+        <v>2.77</v>
+      </c>
+      <c r="U33">
+        <v>2.62</v>
+      </c>
+      <c r="V33">
+        <v>1.4</v>
+      </c>
+      <c r="W33">
+        <v>1.06</v>
+      </c>
+      <c r="X33">
+        <v>1.04</v>
+      </c>
+      <c r="Y33">
         <v>1.22</v>
       </c>
-      <c r="T33">
+      <c r="Z33">
         <v>3.8</v>
       </c>
-      <c r="U33">
-        <v>2.15</v>
-      </c>
-      <c r="V33">
-        <v>1.65</v>
-      </c>
-      <c r="W33">
-        <v>1.14</v>
-      </c>
-      <c r="X33">
-        <v>1.01</v>
-      </c>
-      <c r="Y33">
-        <v>1.13</v>
-      </c>
-      <c r="Z33">
-        <v>6</v>
-      </c>
       <c r="AA33">
-        <v>1.53</v>
+        <v>1.87</v>
       </c>
       <c r="AB33">
-        <v>2.63</v>
+        <v>1.9</v>
       </c>
       <c r="AC33">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="AD33">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="AE33">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AF33">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AG33">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AK33">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.26</v>
+        <v>2.47</v>
       </c>
       <c r="O34">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P34">
-        <v>2.97</v>
+        <v>2.45</v>
       </c>
       <c r="Q34">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="R34">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="S34">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T34">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="U34">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="V34">
         <v>1.4</v>
       </c>
       <c r="W34">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X34">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y34">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="Z34">
-        <v>3.25</v>
+        <v>3.58</v>
       </c>
       <c r="AA34">
-        <v>2.04</v>
+        <v>1.82</v>
       </c>
       <c r="AB34">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AC34">
-        <v>3.5</v>
+        <v>2.97</v>
       </c>
       <c r="AD34">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AE34">
         <v>1.07</v>
       </c>
       <c r="AF34">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AG34">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AK34">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="O35">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="P35">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="Q35">
-        <v>2.45</v>
+        <v>2.14</v>
       </c>
       <c r="R35">
-        <v>2.1</v>
+        <v>2.44</v>
       </c>
       <c r="S35">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="T35">
-        <v>2.77</v>
+        <v>3.8</v>
       </c>
       <c r="U35">
-        <v>2.62</v>
+        <v>2.15</v>
       </c>
       <c r="V35">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="W35">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X35">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="Z35">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="AA35">
-        <v>1.87</v>
+        <v>1.44</v>
       </c>
       <c r="AB35">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="AC35">
-        <v>3.25</v>
+        <v>2.2</v>
       </c>
       <c r="AD35">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="AE35">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AF35">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AG35">
-        <v>2</v>
+        <v>2.42</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AK35">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.52</v>
+        <v>2.25</v>
       </c>
       <c r="O36">
-        <v>3.44</v>
+        <v>3.35</v>
       </c>
       <c r="P36">
-        <v>2.63</v>
+        <v>3.1</v>
       </c>
       <c r="Q36">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="R36">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="S36">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T36">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="U36">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="V36">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="W36">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X36">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y36">
+        <v>1.28</v>
+      </c>
+      <c r="Z36">
+        <v>3.08</v>
+      </c>
+      <c r="AA36">
+        <v>1.97</v>
+      </c>
+      <c r="AB36">
+        <v>1.78</v>
+      </c>
+      <c r="AC36">
+        <v>3.28</v>
+      </c>
+      <c r="AD36">
         <v>1.25</v>
       </c>
-      <c r="Z36">
-        <v>3.8</v>
-      </c>
-      <c r="AA36">
+      <c r="AE36">
+        <v>1.07</v>
+      </c>
+      <c r="AF36">
         <v>1.87</v>
       </c>
-      <c r="AB36">
+      <c r="AG36">
         <v>1.9</v>
-      </c>
-      <c r="AC36">
-        <v>3.1</v>
-      </c>
-      <c r="AD36">
-        <v>1.36</v>
-      </c>
-      <c r="AE36">
-        <v>1.1</v>
-      </c>
-      <c r="AF36">
-        <v>1.7</v>
-      </c>
-      <c r="AG36">
-        <v>2.05</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>1.33</v>
       </c>
       <c r="AK36">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,7 +6340,7 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="O37">
         <v>4.5</v>
@@ -6379,13 +6379,13 @@
         <v>5</v>
       </c>
       <c r="AA37">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="AB37">
-        <v>2.38</v>
+        <v>2.21</v>
       </c>
       <c r="AC37">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AD37">
         <v>1.5</v>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AK37">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,34 +6503,34 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="O38">
-        <v>3.98</v>
+        <v>3.9</v>
       </c>
       <c r="P38">
-        <v>4.95</v>
+        <v>5.03</v>
       </c>
       <c r="Q38">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="R38">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S38">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T38">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="U38">
         <v>2.5</v>
       </c>
       <c r="V38">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W38">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X38">
         <v>1.04</v>
@@ -6539,22 +6539,22 @@
         <v>1.25</v>
       </c>
       <c r="Z38">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AA38">
         <v>1.8</v>
       </c>
       <c r="AB38">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AC38">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AD38">
         <v>1.36</v>
       </c>
       <c r="AE38">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF38">
         <v>1.8</v>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK38">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.93</v>
+        <v>1.24</v>
       </c>
       <c r="O39">
-        <v>3.85</v>
+        <v>6.5</v>
       </c>
       <c r="P39">
-        <v>3.5</v>
+        <v>11</v>
       </c>
       <c r="Q39">
-        <v>2.38</v>
+        <v>1.63</v>
       </c>
       <c r="R39">
-        <v>2.36</v>
+        <v>2.54</v>
       </c>
       <c r="S39">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T39">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="U39">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="V39">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="W39">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X39">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z39">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AA39">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB39">
-        <v>2.62</v>
+        <v>2.37</v>
       </c>
       <c r="AC39">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="AD39">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AE39">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AF39">
-        <v>1.44</v>
+        <v>2.14</v>
       </c>
       <c r="AG39">
-        <v>2.62</v>
+        <v>1.8</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AK39">
-        <v>1.92</v>
+        <v>4</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.24</v>
+        <v>14</v>
       </c>
       <c r="O40">
-        <v>6.5</v>
+        <v>11</v>
       </c>
       <c r="P40">
-        <v>11</v>
+        <v>1.07</v>
       </c>
       <c r="Q40">
-        <v>1.63</v>
+        <v>11.95</v>
       </c>
       <c r="R40">
-        <v>2.54</v>
+        <v>4.37</v>
       </c>
       <c r="S40">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="T40">
-        <v>3.34</v>
+        <v>7</v>
       </c>
       <c r="U40">
-        <v>2.25</v>
+        <v>1.52</v>
       </c>
       <c r="V40">
-        <v>1.57</v>
+        <v>2.3</v>
       </c>
       <c r="W40">
+        <v>1.43</v>
+      </c>
+      <c r="X40">
+        <v>1</v>
+      </c>
+      <c r="Y40">
+        <v>1.01</v>
+      </c>
+      <c r="Z40">
+        <v>13</v>
+      </c>
+      <c r="AA40">
         <v>1.11</v>
       </c>
-      <c r="X40">
-        <v>1.02</v>
-      </c>
-      <c r="Y40">
-        <v>1.14</v>
-      </c>
-      <c r="Z40">
-        <v>5</v>
-      </c>
-      <c r="AA40">
-        <v>1.53</v>
-      </c>
       <c r="AB40">
-        <v>2.37</v>
+        <v>4.95</v>
       </c>
       <c r="AC40">
-        <v>2.31</v>
+        <v>1.36</v>
       </c>
       <c r="AD40">
-        <v>1.55</v>
+        <v>3</v>
       </c>
       <c r="AE40">
-        <v>1.18</v>
+        <v>1.9</v>
       </c>
       <c r="AF40">
-        <v>2.14</v>
+        <v>1.73</v>
       </c>
       <c r="AG40">
-        <v>1.8</v>
+        <v>1.99</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="AK40">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>14</v>
+        <v>1.93</v>
       </c>
       <c r="O43">
-        <v>11</v>
+        <v>3.85</v>
       </c>
       <c r="P43">
-        <v>1.07</v>
+        <v>3.5</v>
       </c>
       <c r="Q43">
-        <v>11.95</v>
+        <v>2.38</v>
       </c>
       <c r="R43">
-        <v>4.37</v>
+        <v>2.36</v>
       </c>
       <c r="S43">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="T43">
-        <v>7</v>
+        <v>3.35</v>
       </c>
       <c r="U43">
-        <v>1.52</v>
+        <v>2.16</v>
       </c>
       <c r="V43">
-        <v>2.3</v>
+        <v>1.66</v>
       </c>
       <c r="W43">
-        <v>1.43</v>
+        <v>1.17</v>
       </c>
       <c r="X43">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="Z43">
-        <v>13</v>
+        <v>5.5</v>
       </c>
       <c r="AA43">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="AB43">
-        <v>4.95</v>
+        <v>2.62</v>
       </c>
       <c r="AC43">
-        <v>1.36</v>
+        <v>2.15</v>
       </c>
       <c r="AD43">
-        <v>3</v>
+        <v>1.63</v>
       </c>
       <c r="AE43">
-        <v>1.9</v>
+        <v>1.25</v>
       </c>
       <c r="AF43">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="AG43">
-        <v>1.99</v>
+        <v>2.62</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="AK43">
-        <v>1</v>
+        <v>1.92</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.64</v>
+        <v>3.3</v>
       </c>
       <c r="O47">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="P47">
-        <v>5.25</v>
+        <v>1.95</v>
       </c>
       <c r="Q47">
-        <v>1.98</v>
+        <v>3.5</v>
       </c>
       <c r="R47">
+        <v>2.2</v>
+      </c>
+      <c r="S47">
+        <v>1.28</v>
+      </c>
+      <c r="T47">
+        <v>3.26</v>
+      </c>
+      <c r="U47">
         <v>2.4</v>
       </c>
-      <c r="S47">
-        <v>1.3</v>
-      </c>
-      <c r="T47">
-        <v>3.3</v>
-      </c>
-      <c r="U47">
-        <v>2.38</v>
-      </c>
       <c r="V47">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W47">
         <v>1.11</v>
       </c>
       <c r="X47">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y47">
         <v>1.2</v>
       </c>
       <c r="Z47">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AA47">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AB47">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AC47">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AD47">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE47">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF47">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AG47">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="AK47">
-        <v>2.4</v>
+        <v>1.27</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="O48">
-        <v>3.7</v>
+        <v>4.05</v>
       </c>
       <c r="P48">
+        <v>5.25</v>
+      </c>
+      <c r="Q48">
         <v>1.98</v>
       </c>
-      <c r="Q48">
-        <v>3.5</v>
-      </c>
       <c r="R48">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="S48">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T48">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="U48">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="V48">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="W48">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X48">
         <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z48">
         <v>4.33</v>
       </c>
       <c r="AA48">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AB48">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC48">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="AD48">
         <v>1.44</v>
       </c>
       <c r="AE48">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF48">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AG48">
-        <v>2.3</v>
+        <v>1.99</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.73</v>
+        <v>1.17</v>
       </c>
       <c r="AK48">
-        <v>1.21</v>
+        <v>2.25</v>
       </c>
       <c r="AL48">
         <v>0</v>

--- a/jogos_2026-10-13.xlsx
+++ b/jogos_2026-10-13.xlsx
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.62</v>
+        <v>1.99</v>
       </c>
       <c r="O5">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="P5">
-        <v>2.7</v>
+        <v>3.72</v>
       </c>
       <c r="Q5">
-        <v>3.38</v>
+        <v>2.79</v>
       </c>
       <c r="R5">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="S5">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="T5">
+        <v>2.27</v>
+      </c>
+      <c r="U5">
+        <v>3.87</v>
+      </c>
+      <c r="V5">
+        <v>1.2</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>1.55</v>
+      </c>
+      <c r="Z5">
         <v>2.23</v>
       </c>
-      <c r="U5">
-        <v>3.52</v>
-      </c>
-      <c r="V5">
-        <v>1.22</v>
-      </c>
-      <c r="W5">
-        <v>0</v>
-      </c>
-      <c r="X5">
-        <v>1.08</v>
-      </c>
-      <c r="Y5">
-        <v>1.59</v>
-      </c>
-      <c r="Z5">
-        <v>2.17</v>
-      </c>
       <c r="AA5">
-        <v>2.74</v>
+        <v>2.87</v>
       </c>
       <c r="AB5">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AC5">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="AD5">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>2.23</v>
+        <v>2.39</v>
       </c>
       <c r="AG5">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AK5">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,65 +1287,65 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.99</v>
+        <v>2.62</v>
       </c>
       <c r="O6">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="P6">
-        <v>3.72</v>
+        <v>2.7</v>
       </c>
       <c r="Q6">
-        <v>2.79</v>
+        <v>3.38</v>
       </c>
       <c r="R6">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="S6">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="T6">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="U6">
-        <v>3.87</v>
+        <v>3.52</v>
       </c>
       <c r="V6">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W6">
         <v>0</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y6">
+        <v>1.59</v>
+      </c>
+      <c r="Z6">
+        <v>2.17</v>
+      </c>
+      <c r="AA6">
+        <v>2.74</v>
+      </c>
+      <c r="AB6">
+        <v>1.35</v>
+      </c>
+      <c r="AC6">
+        <v>5.55</v>
+      </c>
+      <c r="AD6">
+        <v>1.08</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>2.23</v>
+      </c>
+      <c r="AG6">
         <v>1.55</v>
       </c>
-      <c r="Z6">
-        <v>2.23</v>
-      </c>
-      <c r="AA6">
-        <v>2.87</v>
-      </c>
-      <c r="AB6">
-        <v>1.34</v>
-      </c>
-      <c r="AC6">
-        <v>0</v>
-      </c>
-      <c r="AD6">
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>2.39</v>
-      </c>
-      <c r="AG6">
-        <v>1.48</v>
-      </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AK6">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -2102,19 +2102,19 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="O11">
         <v>3.3</v>
       </c>
       <c r="P11">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="Q11">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="R11">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="S11">
         <v>1.33</v>
@@ -2123,43 +2123,43 @@
         <v>3</v>
       </c>
       <c r="U11">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="V11">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W11">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X11">
         <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z11">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="AA11">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AB11">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AC11">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AD11">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AE11">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF11">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AG11">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK11">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2274,22 +2274,22 @@
         <v>2.5</v>
       </c>
       <c r="Q12">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="R12">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="S12">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="T12">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="U12">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="V12">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="W12">
         <v>1.22</v>
@@ -2313,7 +2313,7 @@
         <v>1.81</v>
       </c>
       <c r="AD12">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AE12">
         <v>1.34</v>
@@ -2322,7 +2322,7 @@
         <v>1.3</v>
       </c>
       <c r="AG12">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK12">
         <v>1.57</v>
@@ -2428,37 +2428,37 @@
         </is>
       </c>
       <c r="N13">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="O13">
         <v>4</v>
       </c>
       <c r="P13">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="Q13">
-        <v>4.76</v>
+        <v>4.75</v>
       </c>
       <c r="R13">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="S13">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T13">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="U13">
         <v>2.15</v>
       </c>
       <c r="V13">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="W13">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
         <v>1.12</v>
@@ -2470,7 +2470,7 @@
         <v>1.44</v>
       </c>
       <c r="AB13">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="AC13">
         <v>2.2</v>
@@ -2479,13 +2479,13 @@
         <v>1.65</v>
       </c>
       <c r="AE13">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AF13">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AG13">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AK13">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -3768,16 +3768,16 @@
         <v>1.13</v>
       </c>
       <c r="Z21">
-        <v>4.72</v>
+        <v>4.78</v>
       </c>
       <c r="AA21">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AB21">
         <v>2.28</v>
       </c>
       <c r="AC21">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AD21">
         <v>1.42</v>
@@ -3786,7 +3786,7 @@
         <v>1.18</v>
       </c>
       <c r="AF21">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AG21">
         <v>2.5</v>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK21">
         <v>1.38</v>
@@ -3916,7 +3916,7 @@
         <v>3.5</v>
       </c>
       <c r="U22">
-        <v>1.98</v>
+        <v>2.46</v>
       </c>
       <c r="V22">
         <v>1.44</v>
@@ -3934,10 +3934,10 @@
         <v>4.5</v>
       </c>
       <c r="AA22">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AB22">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AC22">
         <v>2.63</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK22">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4094,7 +4094,7 @@
         <v>1.14</v>
       </c>
       <c r="Z23">
-        <v>4.8</v>
+        <v>4.86</v>
       </c>
       <c r="AA23">
         <v>1.57</v>
@@ -4103,7 +4103,7 @@
         <v>2.38</v>
       </c>
       <c r="AC23">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="AD23">
         <v>1.57</v>
@@ -4224,10 +4224,10 @@
         <v>2.91</v>
       </c>
       <c r="O24">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="P24">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q24">
         <v>2.94</v>
@@ -5362,34 +5362,34 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="O31">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="P31">
-        <v>5.28</v>
+        <v>7</v>
       </c>
       <c r="Q31">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="R31">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S31">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="T31">
         <v>2.4</v>
       </c>
       <c r="U31">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="V31">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="W31">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X31">
         <v>1.06</v>
@@ -5407,19 +5407,19 @@
         <v>1.45</v>
       </c>
       <c r="AC31">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="AD31">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AE31">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF31">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AG31">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="AK31">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5531,7 +5531,7 @@
         <v>3.5</v>
       </c>
       <c r="P32">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="Q32">
         <v>4.24</v>
@@ -5546,10 +5546,10 @@
         <v>2.85</v>
       </c>
       <c r="U32">
-        <v>2.72</v>
+        <v>2.92</v>
       </c>
       <c r="V32">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W32">
         <v>1.08</v>
@@ -5564,10 +5564,10 @@
         <v>3.5</v>
       </c>
       <c r="AA32">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="AB32">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC32">
         <v>3.25</v>
@@ -5579,7 +5579,7 @@
         <v>1.1</v>
       </c>
       <c r="AF32">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AG32">
         <v>1.86</v>
@@ -5598,7 +5598,7 @@
         <v>1.92</v>
       </c>
       <c r="AK32">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="O33">
-        <v>3.5</v>
+        <v>3.98</v>
       </c>
       <c r="P33">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="Q33">
-        <v>2.45</v>
+        <v>2.14</v>
       </c>
       <c r="R33">
-        <v>2.1</v>
+        <v>2.44</v>
       </c>
       <c r="S33">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T33">
-        <v>2.77</v>
+        <v>3.8</v>
       </c>
       <c r="U33">
-        <v>2.62</v>
+        <v>2.15</v>
       </c>
       <c r="V33">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="W33">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="X33">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="Z33">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="AA33">
-        <v>1.87</v>
+        <v>1.44</v>
       </c>
       <c r="AB33">
-        <v>1.9</v>
+        <v>2.43</v>
       </c>
       <c r="AC33">
-        <v>3.25</v>
+        <v>2.2</v>
       </c>
       <c r="AD33">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="AE33">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AF33">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AG33">
-        <v>2</v>
+        <v>2.42</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AK33">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.47</v>
+        <v>2</v>
       </c>
       <c r="O34">
         <v>3.5</v>
       </c>
       <c r="P34">
-        <v>2.45</v>
+        <v>3.6</v>
       </c>
       <c r="Q34">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="R34">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="S34">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T34">
-        <v>3.1</v>
+        <v>2.77</v>
       </c>
       <c r="U34">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="V34">
         <v>1.4</v>
       </c>
       <c r="W34">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X34">
         <v>1.04</v>
       </c>
       <c r="Y34">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z34">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="AA34">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AB34">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AC34">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="AD34">
         <v>1.36</v>
       </c>
       <c r="AE34">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF34">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG34">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.46</v>
+        <v>1.22</v>
       </c>
       <c r="AK34">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.65</v>
+        <v>2.25</v>
       </c>
       <c r="O35">
-        <v>3.95</v>
+        <v>3.35</v>
       </c>
       <c r="P35">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="Q35">
-        <v>2.14</v>
+        <v>2.88</v>
       </c>
       <c r="R35">
-        <v>2.44</v>
+        <v>2.1</v>
       </c>
       <c r="S35">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="T35">
-        <v>3.8</v>
+        <v>2.82</v>
       </c>
       <c r="U35">
-        <v>2.15</v>
+        <v>2.99</v>
       </c>
       <c r="V35">
-        <v>1.65</v>
+        <v>1.39</v>
       </c>
       <c r="W35">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X35">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y35">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="Z35">
-        <v>6</v>
+        <v>3.08</v>
       </c>
       <c r="AA35">
-        <v>1.44</v>
+        <v>1.97</v>
       </c>
       <c r="AB35">
-        <v>2.5</v>
+        <v>1.78</v>
       </c>
       <c r="AC35">
-        <v>2.2</v>
+        <v>3.28</v>
       </c>
       <c r="AD35">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="AE35">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AF35">
-        <v>1.5</v>
+        <v>1.87</v>
       </c>
       <c r="AG35">
-        <v>2.42</v>
+        <v>1.9</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AK35">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.25</v>
+        <v>2.46</v>
       </c>
       <c r="O36">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P36">
+        <v>2.58</v>
+      </c>
+      <c r="Q36">
         <v>3.1</v>
       </c>
-      <c r="Q36">
-        <v>2.88</v>
-      </c>
       <c r="R36">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="S36">
+        <v>1.35</v>
+      </c>
+      <c r="T36">
+        <v>2.77</v>
+      </c>
+      <c r="U36">
+        <v>2.76</v>
+      </c>
+      <c r="V36">
+        <v>1.4</v>
+      </c>
+      <c r="W36">
+        <v>1.11</v>
+      </c>
+      <c r="X36">
+        <v>1.04</v>
+      </c>
+      <c r="Y36">
+        <v>1.21</v>
+      </c>
+      <c r="Z36">
+        <v>3.58</v>
+      </c>
+      <c r="AA36">
+        <v>1.82</v>
+      </c>
+      <c r="AB36">
+        <v>1.92</v>
+      </c>
+      <c r="AC36">
+        <v>2.97</v>
+      </c>
+      <c r="AD36">
         <v>1.36</v>
-      </c>
-      <c r="T36">
-        <v>2.82</v>
-      </c>
-      <c r="U36">
-        <v>2.8</v>
-      </c>
-      <c r="V36">
-        <v>1.39</v>
-      </c>
-      <c r="W36">
-        <v>1.08</v>
-      </c>
-      <c r="X36">
-        <v>1.05</v>
-      </c>
-      <c r="Y36">
-        <v>1.28</v>
-      </c>
-      <c r="Z36">
-        <v>3.08</v>
-      </c>
-      <c r="AA36">
-        <v>1.97</v>
-      </c>
-      <c r="AB36">
-        <v>1.78</v>
-      </c>
-      <c r="AC36">
-        <v>3.28</v>
-      </c>
-      <c r="AD36">
-        <v>1.25</v>
       </c>
       <c r="AE36">
         <v>1.07</v>
       </c>
       <c r="AF36">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AG36">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AK36">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,7 +6340,7 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="O37">
         <v>4.5</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="O38">
         <v>3.9</v>
       </c>
       <c r="P38">
-        <v>5.03</v>
+        <v>5</v>
       </c>
       <c r="Q38">
         <v>2.16</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.24</v>
+        <v>1.93</v>
       </c>
       <c r="O39">
-        <v>6.5</v>
+        <v>3.85</v>
       </c>
       <c r="P39">
-        <v>11</v>
+        <v>3.5</v>
       </c>
       <c r="Q39">
+        <v>2.38</v>
+      </c>
+      <c r="R39">
+        <v>2.36</v>
+      </c>
+      <c r="S39">
+        <v>1.25</v>
+      </c>
+      <c r="T39">
+        <v>3.35</v>
+      </c>
+      <c r="U39">
+        <v>2.16</v>
+      </c>
+      <c r="V39">
+        <v>1.66</v>
+      </c>
+      <c r="W39">
+        <v>1.17</v>
+      </c>
+      <c r="X39">
+        <v>1.01</v>
+      </c>
+      <c r="Y39">
+        <v>1.11</v>
+      </c>
+      <c r="Z39">
+        <v>5.5</v>
+      </c>
+      <c r="AA39">
+        <v>1.5</v>
+      </c>
+      <c r="AB39">
+        <v>2.62</v>
+      </c>
+      <c r="AC39">
+        <v>2.15</v>
+      </c>
+      <c r="AD39">
         <v>1.63</v>
       </c>
-      <c r="R39">
-        <v>2.54</v>
-      </c>
-      <c r="S39">
-        <v>1.29</v>
-      </c>
-      <c r="T39">
-        <v>3.34</v>
-      </c>
-      <c r="U39">
-        <v>2.25</v>
-      </c>
-      <c r="V39">
-        <v>1.57</v>
-      </c>
-      <c r="W39">
-        <v>1.11</v>
-      </c>
-      <c r="X39">
-        <v>1.02</v>
-      </c>
-      <c r="Y39">
-        <v>1.14</v>
-      </c>
-      <c r="Z39">
-        <v>5</v>
-      </c>
-      <c r="AA39">
-        <v>1.53</v>
-      </c>
-      <c r="AB39">
-        <v>2.37</v>
-      </c>
-      <c r="AC39">
-        <v>2.31</v>
-      </c>
-      <c r="AD39">
-        <v>1.55</v>
-      </c>
       <c r="AE39">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AF39">
-        <v>2.14</v>
+        <v>1.44</v>
       </c>
       <c r="AG39">
-        <v>1.8</v>
+        <v>2.62</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AK39">
-        <v>4</v>
+        <v>1.92</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>14</v>
+        <v>1.24</v>
       </c>
       <c r="O40">
+        <v>6.5</v>
+      </c>
+      <c r="P40">
         <v>11</v>
       </c>
-      <c r="P40">
-        <v>1.07</v>
-      </c>
       <c r="Q40">
-        <v>11.95</v>
+        <v>1.63</v>
       </c>
       <c r="R40">
-        <v>4.37</v>
+        <v>2.54</v>
       </c>
       <c r="S40">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="T40">
-        <v>7</v>
+        <v>3.34</v>
       </c>
       <c r="U40">
-        <v>1.52</v>
+        <v>2.25</v>
       </c>
       <c r="V40">
-        <v>2.3</v>
+        <v>1.57</v>
       </c>
       <c r="W40">
-        <v>1.43</v>
+        <v>1.11</v>
       </c>
       <c r="X40">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="Z40">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AA40">
-        <v>1.11</v>
+        <v>1.53</v>
       </c>
       <c r="AB40">
-        <v>4.95</v>
+        <v>2.37</v>
       </c>
       <c r="AC40">
-        <v>1.36</v>
+        <v>2.31</v>
       </c>
       <c r="AD40">
-        <v>3</v>
+        <v>1.55</v>
       </c>
       <c r="AE40">
-        <v>1.9</v>
+        <v>1.18</v>
       </c>
       <c r="AF40">
-        <v>1.73</v>
+        <v>2.14</v>
       </c>
       <c r="AG40">
-        <v>1.99</v>
+        <v>1.8</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AK40">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.93</v>
+        <v>14</v>
       </c>
       <c r="O43">
-        <v>3.85</v>
+        <v>11</v>
       </c>
       <c r="P43">
-        <v>3.5</v>
+        <v>1.07</v>
       </c>
       <c r="Q43">
-        <v>2.38</v>
+        <v>11.95</v>
       </c>
       <c r="R43">
-        <v>2.36</v>
+        <v>4.37</v>
       </c>
       <c r="S43">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="T43">
-        <v>3.35</v>
+        <v>7</v>
       </c>
       <c r="U43">
-        <v>2.16</v>
+        <v>1.52</v>
       </c>
       <c r="V43">
-        <v>1.66</v>
+        <v>2.3</v>
       </c>
       <c r="W43">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="X43">
+        <v>1</v>
+      </c>
+      <c r="Y43">
         <v>1.01</v>
       </c>
-      <c r="Y43">
+      <c r="Z43">
+        <v>13</v>
+      </c>
+      <c r="AA43">
         <v>1.11</v>
       </c>
-      <c r="Z43">
-        <v>5.5</v>
-      </c>
-      <c r="AA43">
-        <v>1.5</v>
-      </c>
       <c r="AB43">
-        <v>2.62</v>
+        <v>4.95</v>
       </c>
       <c r="AC43">
-        <v>2.15</v>
+        <v>1.36</v>
       </c>
       <c r="AD43">
-        <v>1.63</v>
+        <v>3</v>
       </c>
       <c r="AE43">
-        <v>1.25</v>
+        <v>1.9</v>
       </c>
       <c r="AF43">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AG43">
-        <v>2.62</v>
+        <v>1.99</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.19</v>
+        <v>1.03</v>
       </c>
       <c r="AK43">
-        <v>1.92</v>
+        <v>1</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7970,10 +7970,10 @@
         </is>
       </c>
       <c r="N47">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O47">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P47">
         <v>1.95</v>
@@ -8139,7 +8139,7 @@
         <v>4.05</v>
       </c>
       <c r="P48">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="Q48">
         <v>1.98</v>
@@ -8154,7 +8154,7 @@
         <v>3.12</v>
       </c>
       <c r="U48">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="V48">
         <v>1.49</v>
@@ -8166,7 +8166,7 @@
         <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z48">
         <v>4.33</v>
@@ -8296,80 +8296,80 @@
         </is>
       </c>
       <c r="N49">
-        <v>4.64</v>
+        <v>4.5</v>
       </c>
       <c r="O49">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P49">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="Q49">
-        <v>5.05</v>
+        <v>4.6</v>
       </c>
       <c r="R49">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S49">
+        <v>1.36</v>
+      </c>
+      <c r="T49">
+        <v>2.88</v>
+      </c>
+      <c r="U49">
+        <v>2.7</v>
+      </c>
+      <c r="V49">
+        <v>1.36</v>
+      </c>
+      <c r="W49">
+        <v>1.05</v>
+      </c>
+      <c r="X49">
+        <v>1.03</v>
+      </c>
+      <c r="Y49">
+        <v>1.29</v>
+      </c>
+      <c r="Z49">
+        <v>3.3</v>
+      </c>
+      <c r="AA49">
+        <v>2</v>
+      </c>
+      <c r="AB49">
+        <v>1.73</v>
+      </c>
+      <c r="AC49">
+        <v>3.6</v>
+      </c>
+      <c r="AD49">
         <v>1.25</v>
       </c>
-      <c r="T49">
-        <v>3.3</v>
-      </c>
-      <c r="U49">
-        <v>2.45</v>
-      </c>
-      <c r="V49">
-        <v>1.46</v>
-      </c>
-      <c r="W49">
-        <v>0</v>
-      </c>
-      <c r="X49">
-        <v>0</v>
-      </c>
-      <c r="Y49">
+      <c r="AE49">
+        <v>1.06</v>
+      </c>
+      <c r="AF49">
+        <v>1.95</v>
+      </c>
+      <c r="AG49">
+        <v>1.75</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ49">
         <v>1.25</v>
       </c>
-      <c r="Z49">
-        <v>3.38</v>
-      </c>
-      <c r="AA49">
-        <v>1.91</v>
-      </c>
-      <c r="AB49">
-        <v>1.75</v>
-      </c>
-      <c r="AC49">
-        <v>3.51</v>
-      </c>
-      <c r="AD49">
-        <v>1.24</v>
-      </c>
-      <c r="AE49">
-        <v>0</v>
-      </c>
-      <c r="AF49">
-        <v>1.89</v>
-      </c>
-      <c r="AG49">
-        <v>1.77</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ49">
-        <v>1.17</v>
-      </c>
       <c r="AK49">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AL49">
         <v>0</v>

--- a/jogos_2026-10-13.xlsx
+++ b/jogos_2026-10-13.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O2">
         <v>3.2</v>
@@ -680,7 +680,7 @@
         <v>1.8</v>
       </c>
       <c r="AC2">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="AD2">
         <v>1.27</v>
@@ -689,7 +689,7 @@
         <v>1.06</v>
       </c>
       <c r="AF2">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG2">
         <v>1.95</v>
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q4">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R4">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="S4">
+        <v>1.31</v>
+      </c>
+      <c r="T4">
+        <v>2.95</v>
+      </c>
+      <c r="U4">
+        <v>2.45</v>
+      </c>
+      <c r="V4">
+        <v>1.44</v>
+      </c>
+      <c r="W4">
+        <v>1.1</v>
+      </c>
+      <c r="X4">
+        <v>1</v>
+      </c>
+      <c r="Y4">
+        <v>1.21</v>
+      </c>
+      <c r="Z4">
+        <v>3.58</v>
+      </c>
+      <c r="AA4">
+        <v>1.76</v>
+      </c>
+      <c r="AB4">
+        <v>1.92</v>
+      </c>
+      <c r="AC4">
+        <v>2.83</v>
+      </c>
+      <c r="AD4">
         <v>1.33</v>
       </c>
-      <c r="T4">
-        <v>2.86</v>
-      </c>
-      <c r="U4">
-        <v>2.69</v>
-      </c>
-      <c r="V4">
-        <v>1.37</v>
-      </c>
-      <c r="W4">
-        <v>1.05</v>
-      </c>
-      <c r="X4">
-        <v>1.01</v>
-      </c>
-      <c r="Y4">
-        <v>1.25</v>
-      </c>
-      <c r="Z4">
-        <v>3.28</v>
-      </c>
-      <c r="AA4">
-        <v>1.89</v>
-      </c>
-      <c r="AB4">
-        <v>1.78</v>
-      </c>
-      <c r="AC4">
-        <v>3.28</v>
-      </c>
-      <c r="AD4">
-        <v>1.25</v>
-      </c>
       <c r="AE4">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF4">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AG4">
-        <v>1.99</v>
+        <v>2.11</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.24</v>
       </c>
       <c r="AK4">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1616,10 +1616,10 @@
         <v>1.89</v>
       </c>
       <c r="O8">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="P8">
-        <v>3.75</v>
+        <v>4.09</v>
       </c>
       <c r="Q8">
         <v>2.6</v>
@@ -1631,7 +1631,7 @@
         <v>1.44</v>
       </c>
       <c r="T8">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="U8">
         <v>3.6</v>
@@ -1643,28 +1643,28 @@
         <v>1.02</v>
       </c>
       <c r="X8">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Y8">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="Z8">
-        <v>2.44</v>
+        <v>2.49</v>
       </c>
       <c r="AA8">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="AB8">
         <v>1.5</v>
       </c>
       <c r="AC8">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AD8">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AE8">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF8">
         <v>2.15</v>
@@ -1686,7 +1686,7 @@
         <v>1.33</v>
       </c>
       <c r="AK8">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="O9">
-        <v>2.85</v>
+        <v>2.91</v>
       </c>
       <c r="P9">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="Q9">
         <v>2.7</v>
@@ -1806,7 +1806,7 @@
         <v>1.02</v>
       </c>
       <c r="X9">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Y9">
         <v>1.52</v>
@@ -1818,13 +1818,13 @@
         <v>2.62</v>
       </c>
       <c r="AB9">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AC9">
         <v>5.5</v>
       </c>
       <c r="AD9">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AE9">
         <v>1</v>
@@ -2102,19 +2102,19 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O11">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P11">
         <v>3</v>
       </c>
       <c r="Q11">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="R11">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S11">
         <v>1.33</v>
@@ -2123,43 +2123,43 @@
         <v>3</v>
       </c>
       <c r="U11">
-        <v>2.76</v>
+        <v>2.71</v>
       </c>
       <c r="V11">
         <v>1.4</v>
       </c>
       <c r="W11">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X11">
         <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z11">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="AA11">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AB11">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AC11">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AD11">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AE11">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF11">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AG11">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2265,31 +2265,31 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="O12">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P12">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="Q12">
         <v>2.45</v>
       </c>
       <c r="R12">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="S12">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T12">
-        <v>4.33</v>
+        <v>4.45</v>
       </c>
       <c r="U12">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="V12">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="W12">
         <v>1.22</v>
@@ -2298,28 +2298,28 @@
         <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Z12">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="AA12">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AB12">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="AC12">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AD12">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AE12">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AF12">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AG12">
         <v>3</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK12">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,19 +2428,19 @@
         </is>
       </c>
       <c r="N13">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="O13">
+        <v>4.05</v>
+      </c>
+      <c r="P13">
+        <v>1.52</v>
+      </c>
+      <c r="Q13">
         <v>4</v>
       </c>
-      <c r="P13">
-        <v>1.53</v>
-      </c>
-      <c r="Q13">
-        <v>4.75</v>
-      </c>
       <c r="R13">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S13">
         <v>1.25</v>
@@ -2455,38 +2455,38 @@
         <v>1.62</v>
       </c>
       <c r="W13">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X13">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
         <v>1.12</v>
       </c>
       <c r="Z13">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="AA13">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AB13">
+        <v>2.55</v>
+      </c>
+      <c r="AC13">
+        <v>2.25</v>
+      </c>
+      <c r="AD13">
+        <v>1.62</v>
+      </c>
+      <c r="AE13">
+        <v>1.25</v>
+      </c>
+      <c r="AF13">
+        <v>1.49</v>
+      </c>
+      <c r="AG13">
         <v>2.38</v>
       </c>
-      <c r="AC13">
-        <v>2.2</v>
-      </c>
-      <c r="AD13">
-        <v>1.65</v>
-      </c>
-      <c r="AE13">
-        <v>1.21</v>
-      </c>
-      <c r="AF13">
-        <v>1.6</v>
-      </c>
-      <c r="AG13">
-        <v>2.2</v>
-      </c>
       <c r="AH13" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
+        <v>1.25</v>
+      </c>
+      <c r="AK13">
         <v>1.22</v>
-      </c>
-      <c r="AK13">
-        <v>1.18</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2754,16 +2754,16 @@
         </is>
       </c>
       <c r="N15">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="O15">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P15">
         <v>2.06</v>
       </c>
       <c r="Q15">
-        <v>3.44</v>
+        <v>3.99</v>
       </c>
       <c r="R15">
         <v>2.29</v>
@@ -2772,40 +2772,40 @@
         <v>1.29</v>
       </c>
       <c r="T15">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="U15">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="V15">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W15">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X15">
         <v>1.01</v>
       </c>
       <c r="Y15">
+        <v>1.17</v>
+      </c>
+      <c r="Z15">
+        <v>4.5</v>
+      </c>
+      <c r="AA15">
+        <v>1.6</v>
+      </c>
+      <c r="AB15">
+        <v>2.12</v>
+      </c>
+      <c r="AC15">
+        <v>2.5</v>
+      </c>
+      <c r="AD15">
+        <v>1.46</v>
+      </c>
+      <c r="AE15">
         <v>1.18</v>
-      </c>
-      <c r="Z15">
-        <v>4.4</v>
-      </c>
-      <c r="AA15">
-        <v>1.66</v>
-      </c>
-      <c r="AB15">
-        <v>2.31</v>
-      </c>
-      <c r="AC15">
-        <v>2.45</v>
-      </c>
-      <c r="AD15">
-        <v>1.47</v>
-      </c>
-      <c r="AE15">
-        <v>1.15</v>
       </c>
       <c r="AF15">
         <v>1.55</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="AK15">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,16 +2917,16 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="O16">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P16">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
       <c r="Q16">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="R16">
         <v>2.27</v>
@@ -2941,13 +2941,13 @@
         <v>2.25</v>
       </c>
       <c r="V16">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="W16">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
         <v>1.14</v>
@@ -2959,19 +2959,19 @@
         <v>1.53</v>
       </c>
       <c r="AB16">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="AC16">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="AD16">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AE16">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF16">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AG16">
         <v>2.49</v>
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="O18">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="P18">
-        <v>3.94</v>
+        <v>3.7</v>
       </c>
       <c r="Q18">
         <v>2.88</v>
@@ -3258,10 +3258,10 @@
         <v>1.83</v>
       </c>
       <c r="S18">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="T18">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="U18">
         <v>4</v>
@@ -3273,7 +3273,7 @@
         <v>1.03</v>
       </c>
       <c r="X18">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Y18">
         <v>1.62</v>
@@ -3288,13 +3288,13 @@
         <v>1.36</v>
       </c>
       <c r="AC18">
-        <v>6.5</v>
+        <v>6.54</v>
       </c>
       <c r="AD18">
         <v>1.1</v>
       </c>
       <c r="AE18">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF18">
         <v>2.45</v>
@@ -3406,25 +3406,25 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.93</v>
+        <v>2.99</v>
       </c>
       <c r="O19">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="P19">
-        <v>2.49</v>
+        <v>2.28</v>
       </c>
       <c r="Q19">
-        <v>3.61</v>
+        <v>3.5</v>
       </c>
       <c r="R19">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="S19">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T19">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U19">
         <v>2.9</v>
@@ -3442,22 +3442,22 @@
         <v>1.36</v>
       </c>
       <c r="Z19">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="AA19">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB19">
         <v>1.7</v>
       </c>
       <c r="AC19">
-        <v>4.1</v>
+        <v>3.34</v>
       </c>
       <c r="AD19">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AE19">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF19">
         <v>1.8</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="O20">
         <v>6.5</v>
       </c>
       <c r="P20">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Q20">
         <v>1.55</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,19 +3732,19 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="O21">
         <v>3.4</v>
       </c>
       <c r="P21">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="Q21">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="R21">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="S21">
         <v>1.25</v>
@@ -3753,10 +3753,10 @@
         <v>3.5</v>
       </c>
       <c r="U21">
-        <v>2.15</v>
+        <v>2.46</v>
       </c>
       <c r="V21">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="W21">
         <v>1.14</v>
@@ -3765,31 +3765,31 @@
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="Z21">
-        <v>4.78</v>
+        <v>4.5</v>
       </c>
       <c r="AA21">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AB21">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="AC21">
-        <v>2.02</v>
+        <v>2.63</v>
       </c>
       <c r="AD21">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AE21">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF21">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AG21">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK21">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.45</v>
+        <v>1.5</v>
       </c>
       <c r="O22">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="P22">
-        <v>2.37</v>
+        <v>5</v>
       </c>
       <c r="Q22">
-        <v>2.9</v>
+        <v>1.91</v>
       </c>
       <c r="R22">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="S22">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T22">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="U22">
-        <v>2.46</v>
+        <v>2.12</v>
       </c>
       <c r="V22">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="W22">
         <v>1.14</v>
       </c>
       <c r="X22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z22">
-        <v>4.5</v>
+        <v>4.86</v>
       </c>
       <c r="AA22">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AB22">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="AC22">
-        <v>2.63</v>
+        <v>2.34</v>
       </c>
       <c r="AD22">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AE22">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF22">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AG22">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK22">
-        <v>1.43</v>
+        <v>2.4</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="O23">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="P23">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="Q23">
-        <v>1.91</v>
+        <v>3.02</v>
       </c>
       <c r="R23">
-        <v>2.5</v>
+        <v>2.21</v>
       </c>
       <c r="S23">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T23">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="U23">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="V23">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="W23">
         <v>1.14</v>
       </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z23">
-        <v>4.86</v>
+        <v>4.78</v>
       </c>
       <c r="AA23">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AB23">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AC23">
-        <v>2.34</v>
+        <v>2.02</v>
       </c>
       <c r="AD23">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="AE23">
         <v>1.18</v>
       </c>
       <c r="AF23">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AG23">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AK23">
-        <v>2.4</v>
+        <v>1.38</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4224,10 +4224,10 @@
         <v>2.91</v>
       </c>
       <c r="O24">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="P24">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q24">
         <v>2.94</v>
@@ -4242,10 +4242,10 @@
         <v>4.5</v>
       </c>
       <c r="U24">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="V24">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="W24">
         <v>1.15</v>
@@ -4260,7 +4260,7 @@
         <v>6.5</v>
       </c>
       <c r="AA24">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AB24">
         <v>3.1</v>
@@ -4384,40 +4384,40 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="O25">
         <v>3.9</v>
       </c>
       <c r="P25">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="Q25">
         <v>2.03</v>
       </c>
       <c r="R25">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="S25">
         <v>1.2</v>
       </c>
       <c r="T25">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="U25">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="V25">
         <v>1.86</v>
       </c>
       <c r="W25">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X25">
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Z25">
         <v>6.5</v>
@@ -4426,22 +4426,22 @@
         <v>1.4</v>
       </c>
       <c r="AB25">
-        <v>2.74</v>
+        <v>2.56</v>
       </c>
       <c r="AC25">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AD25">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AE25">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AF25">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG25">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4713,61 +4713,61 @@
         <v>1.3</v>
       </c>
       <c r="O27">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="P27">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="Q27">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="R27">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="S27">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T27">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="U27">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="V27">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W27">
+        <v>1.04</v>
+      </c>
+      <c r="X27">
+        <v>1</v>
+      </c>
+      <c r="Y27">
+        <v>1.27</v>
+      </c>
+      <c r="Z27">
+        <v>3.14</v>
+      </c>
+      <c r="AA27">
+        <v>1.9</v>
+      </c>
+      <c r="AB27">
+        <v>1.77</v>
+      </c>
+      <c r="AC27">
+        <v>3.28</v>
+      </c>
+      <c r="AD27">
+        <v>1.25</v>
+      </c>
+      <c r="AE27">
         <v>1.06</v>
       </c>
-      <c r="X27">
-        <v>1.04</v>
-      </c>
-      <c r="Y27">
-        <v>1.3</v>
-      </c>
-      <c r="Z27">
-        <v>3.4</v>
-      </c>
-      <c r="AA27">
-        <v>2</v>
-      </c>
-      <c r="AB27">
-        <v>1.8</v>
-      </c>
-      <c r="AC27">
-        <v>3.5</v>
-      </c>
-      <c r="AD27">
-        <v>1.29</v>
-      </c>
-      <c r="AE27">
-        <v>1.08</v>
-      </c>
       <c r="AF27">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AG27">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AK27">
-        <v>3.4</v>
+        <v>3.04</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="O28">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="P28">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="O29">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P29">
-        <v>4.7</v>
+        <v>4.33</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="O30">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P30">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,80 +5362,80 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="O31">
         <v>3.4</v>
       </c>
       <c r="P31">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="Q31">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="R31">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="S31">
         <v>1.44</v>
       </c>
       <c r="T31">
-        <v>2.4</v>
+        <v>2.59</v>
       </c>
       <c r="U31">
-        <v>3.2</v>
+        <v>3.11</v>
       </c>
       <c r="V31">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="W31">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X31">
+        <v>1.03</v>
+      </c>
+      <c r="Y31">
+        <v>1.37</v>
+      </c>
+      <c r="Z31">
+        <v>2.88</v>
+      </c>
+      <c r="AA31">
+        <v>2.18</v>
+      </c>
+      <c r="AB31">
+        <v>1.65</v>
+      </c>
+      <c r="AC31">
+        <v>3.84</v>
+      </c>
+      <c r="AD31">
+        <v>1.18</v>
+      </c>
+      <c r="AE31">
+        <v>1.03</v>
+      </c>
+      <c r="AF31">
+        <v>2.15</v>
+      </c>
+      <c r="AG31">
+        <v>1.59</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31">
         <v>1.06</v>
       </c>
-      <c r="Y31">
-        <v>1.45</v>
-      </c>
-      <c r="Z31">
-        <v>2.55</v>
-      </c>
-      <c r="AA31">
-        <v>2.55</v>
-      </c>
-      <c r="AB31">
-        <v>1.45</v>
-      </c>
-      <c r="AC31">
-        <v>5.2</v>
-      </c>
-      <c r="AD31">
-        <v>1.13</v>
-      </c>
-      <c r="AE31">
-        <v>1.02</v>
-      </c>
-      <c r="AF31">
-        <v>2.5</v>
-      </c>
-      <c r="AG31">
-        <v>1.44</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ31">
-        <v>1.25</v>
-      </c>
       <c r="AK31">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5531,7 +5531,7 @@
         <v>3.5</v>
       </c>
       <c r="P32">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="Q32">
         <v>4.24</v>
@@ -5691,10 +5691,10 @@
         <v>1.65</v>
       </c>
       <c r="O33">
-        <v>3.98</v>
+        <v>4.3</v>
       </c>
       <c r="P33">
-        <v>4.33</v>
+        <v>4.54</v>
       </c>
       <c r="Q33">
         <v>2.14</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,58 +5851,58 @@
         </is>
       </c>
       <c r="N34">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="O34">
+        <v>4.6</v>
+      </c>
+      <c r="P34">
+        <v>7</v>
+      </c>
+      <c r="Q34">
+        <v>1.8</v>
+      </c>
+      <c r="R34">
+        <v>2.5</v>
+      </c>
+      <c r="S34">
+        <v>1.25</v>
+      </c>
+      <c r="T34">
         <v>3.5</v>
       </c>
-      <c r="P34">
-        <v>3.6</v>
-      </c>
-      <c r="Q34">
-        <v>2.5</v>
-      </c>
-      <c r="R34">
-        <v>2.2</v>
-      </c>
-      <c r="S34">
-        <v>1.3</v>
-      </c>
-      <c r="T34">
-        <v>2.77</v>
-      </c>
       <c r="U34">
-        <v>2.62</v>
+        <v>2.23</v>
       </c>
       <c r="V34">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="W34">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X34">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z34">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="AA34">
-        <v>1.9</v>
+        <v>1.52</v>
       </c>
       <c r="AB34">
-        <v>1.9</v>
+        <v>2.21</v>
       </c>
       <c r="AC34">
-        <v>3.1</v>
+        <v>2.42</v>
       </c>
       <c r="AD34">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AE34">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AF34">
         <v>1.75</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AK34">
-        <v>1.73</v>
+        <v>2.91</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,7 +6014,7 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="O35">
         <v>3.35</v>
@@ -6029,7 +6029,7 @@
         <v>2.1</v>
       </c>
       <c r="S35">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T35">
         <v>2.82</v>
@@ -6041,7 +6041,7 @@
         <v>1.39</v>
       </c>
       <c r="W35">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X35">
         <v>1.05</v>
@@ -6065,13 +6065,13 @@
         <v>1.25</v>
       </c>
       <c r="AE35">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF35">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AG35">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.46</v>
+        <v>2</v>
       </c>
       <c r="O36">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P36">
-        <v>2.58</v>
+        <v>3.66</v>
       </c>
       <c r="Q36">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="R36">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="S36">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T36">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="U36">
-        <v>2.76</v>
+        <v>2.62</v>
       </c>
       <c r="V36">
         <v>1.4</v>
       </c>
       <c r="W36">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X36">
         <v>1.04</v>
       </c>
       <c r="Y36">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z36">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="AA36">
-        <v>1.82</v>
+        <v>1.96</v>
       </c>
       <c r="AB36">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="AC36">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="AD36">
         <v>1.36</v>
       </c>
       <c r="AE36">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF36">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG36">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="AK36">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
+        <v>2.42</v>
+      </c>
+      <c r="O37">
+        <v>3.4</v>
+      </c>
+      <c r="P37">
+        <v>2.7</v>
+      </c>
+      <c r="Q37">
+        <v>3.07</v>
+      </c>
+      <c r="R37">
+        <v>2.14</v>
+      </c>
+      <c r="S37">
+        <v>1.35</v>
+      </c>
+      <c r="T37">
+        <v>2.77</v>
+      </c>
+      <c r="U37">
+        <v>2.76</v>
+      </c>
+      <c r="V37">
         <v>1.4</v>
       </c>
-      <c r="O37">
-        <v>4.5</v>
-      </c>
-      <c r="P37">
-        <v>7</v>
-      </c>
-      <c r="Q37">
-        <v>1.8</v>
-      </c>
-      <c r="R37">
-        <v>2.5</v>
-      </c>
-      <c r="S37">
+      <c r="W37">
+        <v>1.11</v>
+      </c>
+      <c r="X37">
+        <v>1.04</v>
+      </c>
+      <c r="Y37">
         <v>1.25</v>
       </c>
-      <c r="T37">
-        <v>3.5</v>
-      </c>
-      <c r="U37">
-        <v>2.23</v>
-      </c>
-      <c r="V37">
-        <v>1.57</v>
-      </c>
-      <c r="W37">
-        <v>1.14</v>
-      </c>
-      <c r="X37">
-        <v>1.01</v>
-      </c>
-      <c r="Y37">
-        <v>1.17</v>
-      </c>
       <c r="Z37">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="AA37">
-        <v>1.52</v>
+        <v>1.87</v>
       </c>
       <c r="AB37">
-        <v>2.21</v>
+        <v>1.98</v>
       </c>
       <c r="AC37">
-        <v>2.42</v>
+        <v>3.1</v>
       </c>
       <c r="AD37">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AE37">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AF37">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AG37">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>2.91</v>
+        <v>1.44</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="O38">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P38">
         <v>5</v>
@@ -6560,7 +6560,7 @@
         <v>1.8</v>
       </c>
       <c r="AG38">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.93</v>
+        <v>20</v>
       </c>
       <c r="O39">
-        <v>3.85</v>
+        <v>13.5</v>
       </c>
       <c r="P39">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="Q39">
-        <v>2.38</v>
+        <v>12.17</v>
       </c>
       <c r="R39">
-        <v>2.36</v>
+        <v>4.47</v>
       </c>
       <c r="S39">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="T39">
-        <v>3.35</v>
+        <v>7</v>
       </c>
       <c r="U39">
-        <v>2.16</v>
+        <v>1.49</v>
       </c>
       <c r="V39">
-        <v>1.66</v>
+        <v>2.29</v>
       </c>
       <c r="W39">
-        <v>1.17</v>
+        <v>1.44</v>
       </c>
       <c r="X39">
+        <v>1</v>
+      </c>
+      <c r="Y39">
         <v>1.01</v>
       </c>
-      <c r="Y39">
+      <c r="Z39">
+        <v>13</v>
+      </c>
+      <c r="AA39">
         <v>1.11</v>
       </c>
-      <c r="Z39">
-        <v>5.5</v>
-      </c>
-      <c r="AA39">
-        <v>1.5</v>
-      </c>
       <c r="AB39">
-        <v>2.62</v>
+        <v>4.95</v>
       </c>
       <c r="AC39">
-        <v>2.15</v>
+        <v>1.36</v>
       </c>
       <c r="AD39">
-        <v>1.63</v>
+        <v>3</v>
       </c>
       <c r="AE39">
-        <v>1.25</v>
+        <v>1.9</v>
       </c>
       <c r="AF39">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AG39">
-        <v>2.62</v>
+        <v>2.1</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.19</v>
+        <v>1.03</v>
       </c>
       <c r="AK39">
-        <v>1.92</v>
+        <v>1</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,80 +6829,80 @@
         </is>
       </c>
       <c r="N40">
+        <v>1.23</v>
+      </c>
+      <c r="O40">
+        <v>5.75</v>
+      </c>
+      <c r="P40">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="Q40">
+        <v>1.6</v>
+      </c>
+      <c r="R40">
+        <v>2.7</v>
+      </c>
+      <c r="S40">
         <v>1.24</v>
       </c>
-      <c r="O40">
-        <v>6.5</v>
-      </c>
-      <c r="P40">
-        <v>11</v>
-      </c>
-      <c r="Q40">
-        <v>1.63</v>
-      </c>
-      <c r="R40">
-        <v>2.54</v>
-      </c>
-      <c r="S40">
-        <v>1.29</v>
-      </c>
       <c r="T40">
-        <v>3.34</v>
+        <v>3.9</v>
       </c>
       <c r="U40">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="V40">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="W40">
+        <v>1.18</v>
+      </c>
+      <c r="X40">
+        <v>1.01</v>
+      </c>
+      <c r="Y40">
         <v>1.11</v>
       </c>
-      <c r="X40">
+      <c r="Z40">
+        <v>6</v>
+      </c>
+      <c r="AA40">
+        <v>1.44</v>
+      </c>
+      <c r="AB40">
+        <v>2.75</v>
+      </c>
+      <c r="AC40">
+        <v>1.97</v>
+      </c>
+      <c r="AD40">
+        <v>1.81</v>
+      </c>
+      <c r="AE40">
+        <v>1.28</v>
+      </c>
+      <c r="AF40">
+        <v>1.83</v>
+      </c>
+      <c r="AG40">
+        <v>1.87</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ40">
         <v>1.02</v>
       </c>
-      <c r="Y40">
-        <v>1.14</v>
-      </c>
-      <c r="Z40">
-        <v>5</v>
-      </c>
-      <c r="AA40">
-        <v>1.53</v>
-      </c>
-      <c r="AB40">
-        <v>2.37</v>
-      </c>
-      <c r="AC40">
-        <v>2.31</v>
-      </c>
-      <c r="AD40">
-        <v>1.55</v>
-      </c>
-      <c r="AE40">
-        <v>1.18</v>
-      </c>
-      <c r="AF40">
-        <v>2.14</v>
-      </c>
-      <c r="AG40">
-        <v>1.8</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ40">
-        <v>1.14</v>
-      </c>
       <c r="AK40">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="O41">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="P41">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q41">
         <v>1.63</v>
       </c>
       <c r="R41">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="S41">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T41">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="U41">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="V41">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="W41">
+        <v>1.11</v>
+      </c>
+      <c r="X41">
+        <v>1.03</v>
+      </c>
+      <c r="Y41">
+        <v>1.14</v>
+      </c>
+      <c r="Z41">
+        <v>5</v>
+      </c>
+      <c r="AA41">
+        <v>1.64</v>
+      </c>
+      <c r="AB41">
+        <v>2.37</v>
+      </c>
+      <c r="AC41">
+        <v>2.44</v>
+      </c>
+      <c r="AD41">
+        <v>1.56</v>
+      </c>
+      <c r="AE41">
         <v>1.18</v>
       </c>
-      <c r="X41">
-        <v>1.01</v>
-      </c>
-      <c r="Y41">
-        <v>1.11</v>
-      </c>
-      <c r="Z41">
-        <v>6</v>
-      </c>
-      <c r="AA41">
-        <v>1.44</v>
-      </c>
-      <c r="AB41">
-        <v>2.75</v>
-      </c>
-      <c r="AC41">
-        <v>2.05</v>
-      </c>
-      <c r="AD41">
-        <v>1.73</v>
-      </c>
-      <c r="AE41">
-        <v>1.26</v>
-      </c>
       <c r="AF41">
-        <v>1.8</v>
+        <v>2.17</v>
       </c>
       <c r="AG41">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="AK41">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7158,52 +7158,52 @@
         <v>2.1</v>
       </c>
       <c r="O42">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="P42">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="Q42">
         <v>2.73</v>
       </c>
       <c r="R42">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="S42">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T42">
-        <v>3.34</v>
+        <v>3.36</v>
       </c>
       <c r="U42">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V42">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="W42">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X42">
         <v>1.03</v>
       </c>
       <c r="Y42">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z42">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AA42">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="AB42">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AC42">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AD42">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AE42">
         <v>1.18</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AK42">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>14</v>
+        <v>1.92</v>
       </c>
       <c r="O43">
-        <v>11</v>
+        <v>3.9</v>
       </c>
       <c r="P43">
-        <v>1.07</v>
+        <v>3.5</v>
       </c>
       <c r="Q43">
-        <v>11.95</v>
+        <v>2.38</v>
       </c>
       <c r="R43">
-        <v>4.37</v>
+        <v>2.36</v>
       </c>
       <c r="S43">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="T43">
-        <v>7</v>
+        <v>3.35</v>
       </c>
       <c r="U43">
-        <v>1.52</v>
+        <v>2.18</v>
       </c>
       <c r="V43">
-        <v>2.3</v>
+        <v>1.65</v>
       </c>
       <c r="W43">
-        <v>1.43</v>
+        <v>1.18</v>
       </c>
       <c r="X43">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="Z43">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="AA43">
-        <v>1.11</v>
+        <v>1.46</v>
       </c>
       <c r="AB43">
-        <v>4.95</v>
+        <v>2.53</v>
       </c>
       <c r="AC43">
-        <v>1.36</v>
+        <v>2.15</v>
       </c>
       <c r="AD43">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="AE43">
-        <v>1.9</v>
+        <v>1.25</v>
       </c>
       <c r="AF43">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="AG43">
-        <v>1.99</v>
+        <v>2.88</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="AK43">
-        <v>1</v>
+        <v>1.93</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,34 +7481,34 @@
         </is>
       </c>
       <c r="N44">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="O44">
         <v>6.7</v>
       </c>
       <c r="P44">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Q44">
-        <v>6.66</v>
+        <v>6.63</v>
       </c>
       <c r="R44">
-        <v>3.26</v>
+        <v>3.01</v>
       </c>
       <c r="S44">
         <v>1.12</v>
       </c>
       <c r="T44">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="U44">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="V44">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="W44">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X44">
         <v>1</v>
@@ -7523,22 +7523,22 @@
         <v>1.2</v>
       </c>
       <c r="AB44">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AC44">
+        <v>1.49</v>
+      </c>
+      <c r="AD44">
+        <v>2.47</v>
+      </c>
+      <c r="AE44">
+        <v>1.66</v>
+      </c>
+      <c r="AF44">
         <v>1.44</v>
       </c>
-      <c r="AD44">
-        <v>2.46</v>
-      </c>
-      <c r="AE44">
-        <v>1.78</v>
-      </c>
-      <c r="AF44">
-        <v>1.41</v>
-      </c>
       <c r="AG44">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7647,16 +7647,16 @@
         <v>1.75</v>
       </c>
       <c r="O45">
-        <v>4.35</v>
+        <v>4.3</v>
       </c>
       <c r="P45">
-        <v>3.8</v>
+        <v>3.63</v>
       </c>
       <c r="Q45">
-        <v>2.21</v>
+        <v>2.32</v>
       </c>
       <c r="R45">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="S45">
         <v>1.17</v>
@@ -7671,16 +7671,16 @@
         <v>1.83</v>
       </c>
       <c r="W45">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X45">
         <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z45">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AA45">
         <v>1.33</v>
@@ -7689,10 +7689,10 @@
         <v>3.26</v>
       </c>
       <c r="AC45">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AD45">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AE45">
         <v>1.4</v>
@@ -7701,7 +7701,7 @@
         <v>1.33</v>
       </c>
       <c r="AG45">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AK45">
         <v>1.95</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,80 +7970,80 @@
         </is>
       </c>
       <c r="N47">
-        <v>3.25</v>
+        <v>1.6</v>
       </c>
       <c r="O47">
-        <v>3.7</v>
+        <v>4.05</v>
       </c>
       <c r="P47">
-        <v>1.95</v>
+        <v>5.56</v>
       </c>
       <c r="Q47">
-        <v>3.5</v>
+        <v>1.98</v>
       </c>
       <c r="R47">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="S47">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T47">
-        <v>3.26</v>
+        <v>3.12</v>
       </c>
       <c r="U47">
-        <v>2.4</v>
+        <v>2.59</v>
       </c>
       <c r="V47">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="W47">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X47">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z47">
         <v>4.5</v>
       </c>
       <c r="AA47">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AB47">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AC47">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AD47">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AE47">
+        <v>1.12</v>
+      </c>
+      <c r="AF47">
+        <v>1.71</v>
+      </c>
+      <c r="AG47">
+        <v>1.99</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ47">
         <v>1.17</v>
       </c>
-      <c r="AF47">
-        <v>1.6</v>
-      </c>
-      <c r="AG47">
-        <v>2.18</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ47">
-        <v>1.8</v>
-      </c>
       <c r="AK47">
-        <v>1.27</v>
+        <v>2.25</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="O48">
-        <v>4.05</v>
+        <v>3.65</v>
       </c>
       <c r="P48">
-        <v>5</v>
+        <v>1.95</v>
       </c>
       <c r="Q48">
-        <v>1.98</v>
+        <v>3.5</v>
       </c>
       <c r="R48">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="S48">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T48">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="U48">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="V48">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="W48">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X48">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z48">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AA48">
         <v>1.69</v>
       </c>
       <c r="AB48">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AC48">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AD48">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AE48">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF48">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AG48">
-        <v>1.99</v>
+        <v>2.18</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.17</v>
+        <v>1.8</v>
       </c>
       <c r="AK48">
-        <v>2.25</v>
+        <v>1.27</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,80 +8296,80 @@
         </is>
       </c>
       <c r="N49">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O49">
+        <v>3.25</v>
+      </c>
+      <c r="P49">
+        <v>1.73</v>
+      </c>
+      <c r="Q49">
+        <v>4</v>
+      </c>
+      <c r="R49">
+        <v>1.95</v>
+      </c>
+      <c r="S49">
+        <v>1.48</v>
+      </c>
+      <c r="T49">
+        <v>2.34</v>
+      </c>
+      <c r="U49">
         <v>3.4</v>
       </c>
-      <c r="P49">
-        <v>1.65</v>
-      </c>
-      <c r="Q49">
-        <v>4.6</v>
-      </c>
-      <c r="R49">
-        <v>2.15</v>
-      </c>
-      <c r="S49">
-        <v>1.36</v>
-      </c>
-      <c r="T49">
-        <v>2.88</v>
-      </c>
-      <c r="U49">
-        <v>2.7</v>
-      </c>
       <c r="V49">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="W49">
+        <v>1.04</v>
+      </c>
+      <c r="X49">
         <v>1.05</v>
       </c>
-      <c r="X49">
-        <v>1.03</v>
-      </c>
       <c r="Y49">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="Z49">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="AA49">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AB49">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AC49">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="AD49">
+        <v>1.14</v>
+      </c>
+      <c r="AE49">
+        <v>1.01</v>
+      </c>
+      <c r="AF49">
+        <v>2.1</v>
+      </c>
+      <c r="AG49">
+        <v>1.62</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ49">
+        <v>1.35</v>
+      </c>
+      <c r="AK49">
         <v>1.25</v>
-      </c>
-      <c r="AE49">
-        <v>1.06</v>
-      </c>
-      <c r="AF49">
-        <v>1.95</v>
-      </c>
-      <c r="AG49">
-        <v>1.75</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ49">
-        <v>1.25</v>
-      </c>
-      <c r="AK49">
-        <v>1.14</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O50">
-        <v>3.01</v>
+        <v>3.1</v>
       </c>
       <c r="P50">
-        <v>3.25</v>
+        <v>3.43</v>
       </c>
       <c r="Q50">
         <v>2.75</v>
@@ -8474,49 +8474,49 @@
         <v>1.93</v>
       </c>
       <c r="S50">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="T50">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="U50">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="V50">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W50">
         <v>1.05</v>
       </c>
       <c r="X50">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y50">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z50">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="AA50">
         <v>2.25</v>
       </c>
       <c r="AB50">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AC50">
-        <v>4.33</v>
+        <v>3.95</v>
       </c>
       <c r="AD50">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE50">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF50">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AG50">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>

--- a/jogos_2026-10-13.xlsx
+++ b/jogos_2026-10-13.xlsx
@@ -644,10 +644,10 @@
         <v>3.1</v>
       </c>
       <c r="Q2">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="R2">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="S2">
         <v>1.33</v>
@@ -656,7 +656,7 @@
         <v>2.73</v>
       </c>
       <c r="U2">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="V2">
         <v>1.42</v>
@@ -680,7 +680,7 @@
         <v>1.8</v>
       </c>
       <c r="AC2">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AD2">
         <v>1.27</v>
@@ -689,7 +689,7 @@
         <v>1.06</v>
       </c>
       <c r="AF2">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG2">
         <v>1.95</v>
@@ -708,7 +708,7 @@
         <v>1.25</v>
       </c>
       <c r="AK2">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>4.13</v>
+        <v>4.9</v>
       </c>
       <c r="O3">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P3">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="Q3">
         <v>5.72</v>
@@ -1649,7 +1649,7 @@
         <v>1.42</v>
       </c>
       <c r="Z8">
-        <v>2.49</v>
+        <v>2.65</v>
       </c>
       <c r="AA8">
         <v>2.41</v>
@@ -1779,19 +1779,19 @@
         <v>2.05</v>
       </c>
       <c r="O9">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="P9">
         <v>3.6</v>
       </c>
       <c r="Q9">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="R9">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="S9">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="T9">
         <v>2.4</v>
@@ -1809,10 +1809,10 @@
         <v>1.12</v>
       </c>
       <c r="Y9">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Z9">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="AA9">
         <v>2.62</v>
@@ -1948,10 +1948,10 @@
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="R10">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="S10">
         <v>1.36</v>
@@ -1966,7 +1966,7 @@
         <v>1.39</v>
       </c>
       <c r="W10">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X10">
         <v>1.02</v>
@@ -1978,13 +1978,13 @@
         <v>2.97</v>
       </c>
       <c r="AA10">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AB10">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AC10">
-        <v>3.42</v>
+        <v>3.66</v>
       </c>
       <c r="AD10">
         <v>1.27</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AK10">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2108,13 +2108,13 @@
         <v>3.2</v>
       </c>
       <c r="P11">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Q11">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="R11">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S11">
         <v>1.33</v>
@@ -2123,43 +2123,43 @@
         <v>3</v>
       </c>
       <c r="U11">
-        <v>2.71</v>
+        <v>2.56</v>
       </c>
       <c r="V11">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W11">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X11">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z11">
-        <v>3.42</v>
+        <v>3.8</v>
       </c>
       <c r="AA11">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AB11">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="AC11">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AD11">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AE11">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF11">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AG11">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>1.3</v>
       </c>
       <c r="AK11">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,19 +2265,19 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="O12">
         <v>3.7</v>
       </c>
       <c r="P12">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="Q12">
         <v>2.45</v>
       </c>
       <c r="R12">
-        <v>2.49</v>
+        <v>2.59</v>
       </c>
       <c r="S12">
         <v>1.2</v>
@@ -2286,13 +2286,13 @@
         <v>4.45</v>
       </c>
       <c r="U12">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V12">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="W12">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X12">
         <v>1.01</v>
@@ -2304,10 +2304,10 @@
         <v>6.5</v>
       </c>
       <c r="AA12">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB12">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AC12">
         <v>1.9</v>
@@ -2600,55 +2600,55 @@
         <v>5.25</v>
       </c>
       <c r="Q14">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="R14">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S14">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="T14">
-        <v>2.92</v>
+        <v>2.39</v>
       </c>
       <c r="U14">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="V14">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="W14">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X14">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z14">
-        <v>3.58</v>
+        <v>3.82</v>
       </c>
       <c r="AA14">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AB14">
         <v>2</v>
       </c>
       <c r="AC14">
-        <v>2.46</v>
+        <v>2.81</v>
       </c>
       <c r="AD14">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AE14">
         <v>1.09</v>
       </c>
       <c r="AF14">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AG14">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK14">
-        <v>2.25</v>
+        <v>1.94</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O17">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="P17">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="Q17">
         <v>5.8</v>
@@ -3095,10 +3095,10 @@
         <v>1.91</v>
       </c>
       <c r="S17">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="T17">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="U17">
         <v>3.76</v>
@@ -3131,7 +3131,7 @@
         <v>1.13</v>
       </c>
       <c r="AE17">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF17">
         <v>2.25</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK17">
         <v>1.14</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="O18">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="P18">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="Q18">
         <v>2.88</v>
@@ -3412,7 +3412,7 @@
         <v>2.82</v>
       </c>
       <c r="P19">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="Q19">
         <v>3.5</v>
@@ -3572,7 +3572,7 @@
         <v>1.2</v>
       </c>
       <c r="O20">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="P20">
         <v>11</v>
@@ -3747,10 +3747,10 @@
         <v>2.18</v>
       </c>
       <c r="S21">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T21">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U21">
         <v>2.46</v>
@@ -3759,7 +3759,7 @@
         <v>1.44</v>
       </c>
       <c r="W21">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X21">
         <v>1.01</v>
@@ -4254,22 +4254,22 @@
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z24">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA24">
         <v>1.31</v>
       </c>
       <c r="AB24">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AC24">
+        <v>1.87</v>
+      </c>
+      <c r="AD24">
         <v>1.9</v>
-      </c>
-      <c r="AD24">
-        <v>1.87</v>
       </c>
       <c r="AE24">
         <v>1.36</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AK24">
         <v>1.39</v>
@@ -4399,10 +4399,10 @@
         <v>2.53</v>
       </c>
       <c r="S25">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T25">
-        <v>3.82</v>
+        <v>2.9</v>
       </c>
       <c r="U25">
         <v>2.05</v>
@@ -4417,31 +4417,31 @@
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z25">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AA25">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AB25">
-        <v>2.56</v>
+        <v>2.2</v>
       </c>
       <c r="AC25">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AD25">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="AE25">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AF25">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG25">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4547,16 +4547,16 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="O26">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="P26">
-        <v>4.81</v>
+        <v>4.5</v>
       </c>
       <c r="Q26">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="R26">
         <v>2.2</v>
@@ -4589,7 +4589,7 @@
         <v>1.8</v>
       </c>
       <c r="AB26">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AC26">
         <v>2.92</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,19 +4873,19 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="O28">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="P28">
-        <v>2.7</v>
+        <v>4.33</v>
       </c>
       <c r="Q28">
-        <v>3.22</v>
+        <v>2.43</v>
       </c>
       <c r="R28">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="S28">
         <v>1.44</v>
@@ -4906,13 +4906,13 @@
         <v>1.07</v>
       </c>
       <c r="Y28">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="Z28">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AA28">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AB28">
         <v>1.5</v>
@@ -4927,10 +4927,10 @@
         <v>1.04</v>
       </c>
       <c r="AF28">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AG28">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK28">
-        <v>1.43</v>
+        <v>1.88</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,19 +5036,19 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="O29">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P29">
-        <v>4.33</v>
+        <v>2.7</v>
       </c>
       <c r="Q29">
-        <v>2.43</v>
+        <v>3.22</v>
       </c>
       <c r="R29">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="S29">
         <v>1.44</v>
@@ -5069,13 +5069,13 @@
         <v>1.07</v>
       </c>
       <c r="Y29">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="Z29">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AA29">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AB29">
         <v>1.5</v>
@@ -5090,10 +5090,10 @@
         <v>1.04</v>
       </c>
       <c r="AF29">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AG29">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK29">
-        <v>1.88</v>
+        <v>1.43</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5365,10 +5365,10 @@
         <v>1.55</v>
       </c>
       <c r="O31">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P31">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="Q31">
         <v>2.11</v>
@@ -5854,7 +5854,7 @@
         <v>1.4</v>
       </c>
       <c r="O34">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="P34">
         <v>7</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,61 +6014,61 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="O35">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P35">
-        <v>3</v>
+        <v>3.66</v>
       </c>
       <c r="Q35">
-        <v>2.88</v>
+        <v>2.59</v>
       </c>
       <c r="R35">
         <v>2.1</v>
       </c>
       <c r="S35">
+        <v>1.33</v>
+      </c>
+      <c r="T35">
+        <v>2.75</v>
+      </c>
+      <c r="U35">
+        <v>2.62</v>
+      </c>
+      <c r="V35">
         <v>1.36</v>
       </c>
-      <c r="T35">
-        <v>2.82</v>
-      </c>
-      <c r="U35">
-        <v>2.99</v>
-      </c>
-      <c r="V35">
-        <v>1.39</v>
-      </c>
       <c r="W35">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X35">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y35">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="Z35">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="AA35">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AB35">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="AC35">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="AD35">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AE35">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF35">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG35">
         <v>2</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK35">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,61 +6177,61 @@
         </is>
       </c>
       <c r="N36">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="O36">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P36">
-        <v>3.66</v>
+        <v>3.1</v>
       </c>
       <c r="Q36">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="R36">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S36">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T36">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="U36">
-        <v>2.62</v>
+        <v>2.99</v>
       </c>
       <c r="V36">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W36">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X36">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y36">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="Z36">
-        <v>3.8</v>
+        <v>3.08</v>
       </c>
       <c r="AA36">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AB36">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="AC36">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="AD36">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AE36">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF36">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG36">
         <v>2</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK36">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6343,16 +6343,16 @@
         <v>2.42</v>
       </c>
       <c r="O37">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
       <c r="P37">
         <v>2.7</v>
       </c>
       <c r="Q37">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="R37">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="S37">
         <v>1.35</v>
@@ -6394,10 +6394,10 @@
         <v>1.1</v>
       </c>
       <c r="AF37">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AG37">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="O38">
         <v>4</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>20</v>
+        <v>1.23</v>
       </c>
       <c r="O39">
-        <v>13.5</v>
+        <v>5.75</v>
       </c>
       <c r="P39">
-        <v>1.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q39">
-        <v>12.17</v>
+        <v>1.6</v>
       </c>
       <c r="R39">
-        <v>4.47</v>
+        <v>2.7</v>
       </c>
       <c r="S39">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="T39">
-        <v>7</v>
+        <v>3.9</v>
       </c>
       <c r="U39">
-        <v>1.49</v>
+        <v>2.1</v>
       </c>
       <c r="V39">
-        <v>2.29</v>
+        <v>1.67</v>
       </c>
       <c r="W39">
+        <v>1.18</v>
+      </c>
+      <c r="X39">
+        <v>1.01</v>
+      </c>
+      <c r="Y39">
+        <v>1.11</v>
+      </c>
+      <c r="Z39">
+        <v>6</v>
+      </c>
+      <c r="AA39">
         <v>1.44</v>
       </c>
-      <c r="X39">
-        <v>1</v>
-      </c>
-      <c r="Y39">
-        <v>1.01</v>
-      </c>
-      <c r="Z39">
-        <v>13</v>
-      </c>
-      <c r="AA39">
-        <v>1.11</v>
-      </c>
       <c r="AB39">
-        <v>4.95</v>
+        <v>2.75</v>
       </c>
       <c r="AC39">
-        <v>1.36</v>
+        <v>1.97</v>
       </c>
       <c r="AD39">
-        <v>3</v>
+        <v>1.81</v>
       </c>
       <c r="AE39">
-        <v>1.9</v>
+        <v>1.28</v>
       </c>
       <c r="AF39">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AG39">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK39">
-        <v>1</v>
+        <v>4.15</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.23</v>
+        <v>2.1</v>
       </c>
       <c r="O40">
-        <v>5.75</v>
+        <v>3.58</v>
       </c>
       <c r="P40">
-        <v>9.699999999999999</v>
+        <v>2.73</v>
       </c>
       <c r="Q40">
-        <v>1.6</v>
+        <v>2.73</v>
       </c>
       <c r="R40">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="S40">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="T40">
-        <v>3.9</v>
+        <v>3.36</v>
       </c>
       <c r="U40">
-        <v>2.1</v>
+        <v>2.42</v>
       </c>
       <c r="V40">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="W40">
+        <v>1.11</v>
+      </c>
+      <c r="X40">
+        <v>1.03</v>
+      </c>
+      <c r="Y40">
+        <v>1.14</v>
+      </c>
+      <c r="Z40">
+        <v>5</v>
+      </c>
+      <c r="AA40">
+        <v>1.71</v>
+      </c>
+      <c r="AB40">
+        <v>2.32</v>
+      </c>
+      <c r="AC40">
+        <v>2.5</v>
+      </c>
+      <c r="AD40">
+        <v>1.5</v>
+      </c>
+      <c r="AE40">
         <v>1.18</v>
       </c>
-      <c r="X40">
-        <v>1.01</v>
-      </c>
-      <c r="Y40">
-        <v>1.11</v>
-      </c>
-      <c r="Z40">
-        <v>6</v>
-      </c>
-      <c r="AA40">
-        <v>1.44</v>
-      </c>
-      <c r="AB40">
-        <v>2.75</v>
-      </c>
-      <c r="AC40">
-        <v>1.97</v>
-      </c>
-      <c r="AD40">
-        <v>1.81</v>
-      </c>
-      <c r="AE40">
-        <v>1.28</v>
-      </c>
       <c r="AF40">
-        <v>1.83</v>
+        <v>1.52</v>
       </c>
       <c r="AG40">
-        <v>1.87</v>
+        <v>2.38</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.02</v>
+        <v>1.32</v>
       </c>
       <c r="AK40">
-        <v>4.15</v>
+        <v>1.7</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.23</v>
+        <v>1.92</v>
       </c>
       <c r="O41">
-        <v>6.5</v>
+        <v>3.9</v>
       </c>
       <c r="P41">
-        <v>11</v>
+        <v>3.5</v>
       </c>
       <c r="Q41">
-        <v>1.63</v>
+        <v>2.38</v>
       </c>
       <c r="R41">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="S41">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T41">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="U41">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="V41">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="W41">
+        <v>1.18</v>
+      </c>
+      <c r="X41">
+        <v>1.01</v>
+      </c>
+      <c r="Y41">
         <v>1.11</v>
       </c>
-      <c r="X41">
-        <v>1.03</v>
-      </c>
-      <c r="Y41">
-        <v>1.14</v>
-      </c>
       <c r="Z41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA41">
-        <v>1.64</v>
+        <v>1.46</v>
       </c>
       <c r="AB41">
-        <v>2.37</v>
+        <v>2.53</v>
       </c>
       <c r="AC41">
-        <v>2.44</v>
+        <v>2.15</v>
       </c>
       <c r="AD41">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AE41">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AF41">
-        <v>2.17</v>
+        <v>1.44</v>
       </c>
       <c r="AG41">
-        <v>1.63</v>
+        <v>2.88</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AK41">
-        <v>4</v>
+        <v>1.93</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,31 +7155,31 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.1</v>
+        <v>1.23</v>
       </c>
       <c r="O42">
-        <v>3.58</v>
+        <v>6.5</v>
       </c>
       <c r="P42">
-        <v>2.73</v>
+        <v>11</v>
       </c>
       <c r="Q42">
-        <v>2.73</v>
+        <v>1.63</v>
       </c>
       <c r="R42">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="S42">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="T42">
-        <v>3.36</v>
+        <v>3.6</v>
       </c>
       <c r="U42">
-        <v>2.42</v>
+        <v>2.25</v>
       </c>
       <c r="V42">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="W42">
         <v>1.11</v>
@@ -7194,25 +7194,25 @@
         <v>5</v>
       </c>
       <c r="AA42">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AB42">
-        <v>2.32</v>
+        <v>2.37</v>
       </c>
       <c r="AC42">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="AD42">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AE42">
         <v>1.18</v>
       </c>
       <c r="AF42">
-        <v>1.52</v>
+        <v>2.17</v>
       </c>
       <c r="AG42">
-        <v>2.38</v>
+        <v>1.63</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="AK42">
-        <v>1.7</v>
+        <v>4</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.92</v>
+        <v>20</v>
       </c>
       <c r="O43">
-        <v>3.9</v>
+        <v>13.5</v>
       </c>
       <c r="P43">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="Q43">
-        <v>2.38</v>
+        <v>12.17</v>
       </c>
       <c r="R43">
-        <v>2.36</v>
+        <v>4.47</v>
       </c>
       <c r="S43">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="T43">
-        <v>3.35</v>
+        <v>7</v>
       </c>
       <c r="U43">
-        <v>2.18</v>
+        <v>1.49</v>
       </c>
       <c r="V43">
+        <v>2.29</v>
+      </c>
+      <c r="W43">
+        <v>1.44</v>
+      </c>
+      <c r="X43">
+        <v>1</v>
+      </c>
+      <c r="Y43">
+        <v>1.01</v>
+      </c>
+      <c r="Z43">
+        <v>13</v>
+      </c>
+      <c r="AA43">
+        <v>1.11</v>
+      </c>
+      <c r="AB43">
+        <v>4.95</v>
+      </c>
+      <c r="AC43">
+        <v>1.36</v>
+      </c>
+      <c r="AD43">
+        <v>3</v>
+      </c>
+      <c r="AE43">
+        <v>1.9</v>
+      </c>
+      <c r="AF43">
         <v>1.65</v>
       </c>
-      <c r="W43">
-        <v>1.18</v>
-      </c>
-      <c r="X43">
-        <v>1.01</v>
-      </c>
-      <c r="Y43">
-        <v>1.11</v>
-      </c>
-      <c r="Z43">
-        <v>6</v>
-      </c>
-      <c r="AA43">
-        <v>1.46</v>
-      </c>
-      <c r="AB43">
-        <v>2.53</v>
-      </c>
-      <c r="AC43">
-        <v>2.15</v>
-      </c>
-      <c r="AD43">
-        <v>1.67</v>
-      </c>
-      <c r="AE43">
-        <v>1.25</v>
-      </c>
-      <c r="AF43">
-        <v>1.44</v>
-      </c>
       <c r="AG43">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.19</v>
+        <v>1.03</v>
       </c>
       <c r="AK43">
-        <v>1.93</v>
+        <v>1</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8086,12 +8086,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>3.2</v>
+        <v>1.95</v>
       </c>
       <c r="O48">
-        <v>3.65</v>
+        <v>2.9</v>
       </c>
       <c r="P48">
-        <v>1.95</v>
+        <v>3.99</v>
       </c>
       <c r="Q48">
-        <v>3.5</v>
+        <v>2.31</v>
       </c>
       <c r="R48">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="S48">
-        <v>1.29</v>
+        <v>1.54</v>
       </c>
       <c r="T48">
-        <v>3.4</v>
+        <v>2.27</v>
       </c>
       <c r="U48">
+        <v>3.58</v>
+      </c>
+      <c r="V48">
+        <v>1.21</v>
+      </c>
+      <c r="W48">
+        <v>1.03</v>
+      </c>
+      <c r="X48">
+        <v>1.08</v>
+      </c>
+      <c r="Y48">
+        <v>1.5</v>
+      </c>
+      <c r="Z48">
+        <v>2.55</v>
+      </c>
+      <c r="AA48">
+        <v>2.49</v>
+      </c>
+      <c r="AB48">
+        <v>1.47</v>
+      </c>
+      <c r="AC48">
+        <v>5.5</v>
+      </c>
+      <c r="AD48">
+        <v>1.14</v>
+      </c>
+      <c r="AE48">
+        <v>1.02</v>
+      </c>
+      <c r="AF48">
         <v>2.4</v>
       </c>
-      <c r="V48">
-        <v>1.51</v>
-      </c>
-      <c r="W48">
-        <v>1.11</v>
-      </c>
-      <c r="X48">
-        <v>1.01</v>
-      </c>
-      <c r="Y48">
-        <v>1.2</v>
-      </c>
-      <c r="Z48">
-        <v>4.5</v>
-      </c>
-      <c r="AA48">
-        <v>1.69</v>
-      </c>
-      <c r="AB48">
-        <v>2.09</v>
-      </c>
-      <c r="AC48">
-        <v>2.62</v>
-      </c>
-      <c r="AD48">
-        <v>1.38</v>
-      </c>
-      <c r="AE48">
-        <v>1.17</v>
-      </c>
-      <c r="AF48">
-        <v>1.6</v>
-      </c>
       <c r="AG48">
-        <v>2.18</v>
+        <v>1.5</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.8</v>
+        <v>1.24</v>
       </c>
       <c r="AK48">
-        <v>1.27</v>
+        <v>2.03</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>2026-10-13 16:00:00</t>
+          <t>2026-10-13 16:15:00</t>
         </is>
       </c>
     </row>
@@ -8332,7 +8332,7 @@
         <v>1.44</v>
       </c>
       <c r="Z49">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="AA49">
         <v>2.4</v>

--- a/jogos_2026-10-13.xlsx
+++ b/jogos_2026-10-13.xlsx
@@ -641,25 +641,25 @@
         <v>3.2</v>
       </c>
       <c r="P2">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q2">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="R2">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="S2">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T2">
         <v>2.73</v>
       </c>
       <c r="U2">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="V2">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W2">
         <v>1.1</v>
@@ -708,7 +708,7 @@
         <v>1.25</v>
       </c>
       <c r="AK2">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="O3">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P3">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="Q3">
         <v>5.72</v>
@@ -961,25 +961,25 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="O4">
         <v>3.2</v>
       </c>
       <c r="P4">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q4">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="R4">
-        <v>2.09</v>
+        <v>2.28</v>
       </c>
       <c r="S4">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T4">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="U4">
         <v>2.45</v>
@@ -988,37 +988,37 @@
         <v>1.44</v>
       </c>
       <c r="W4">
+        <v>1.11</v>
+      </c>
+      <c r="X4">
+        <v>1.02</v>
+      </c>
+      <c r="Y4">
+        <v>1.2</v>
+      </c>
+      <c r="Z4">
+        <v>3.72</v>
+      </c>
+      <c r="AA4">
+        <v>1.85</v>
+      </c>
+      <c r="AB4">
+        <v>2.04</v>
+      </c>
+      <c r="AC4">
+        <v>2.74</v>
+      </c>
+      <c r="AD4">
+        <v>1.39</v>
+      </c>
+      <c r="AE4">
         <v>1.1</v>
       </c>
-      <c r="X4">
-        <v>1</v>
-      </c>
-      <c r="Y4">
-        <v>1.21</v>
-      </c>
-      <c r="Z4">
-        <v>3.58</v>
-      </c>
-      <c r="AA4">
-        <v>1.76</v>
-      </c>
-      <c r="AB4">
-        <v>1.92</v>
-      </c>
-      <c r="AC4">
-        <v>2.83</v>
-      </c>
-      <c r="AD4">
-        <v>1.33</v>
-      </c>
-      <c r="AE4">
-        <v>1.09</v>
-      </c>
       <c r="AF4">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG4">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK4">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="O5">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="P5">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="Q5">
         <v>2.79</v>
@@ -1320,10 +1320,10 @@
         <v>1.08</v>
       </c>
       <c r="Y6">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="Z6">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="AA6">
         <v>2.74</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q10">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="R10">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="S10">
         <v>1.36</v>
@@ -2012,7 +2012,7 @@
         <v>1.21</v>
       </c>
       <c r="AK10">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,25 +2102,25 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="O11">
+        <v>3.25</v>
+      </c>
+      <c r="P11">
+        <v>3.1</v>
+      </c>
+      <c r="Q11">
+        <v>2.61</v>
+      </c>
+      <c r="R11">
+        <v>2.25</v>
+      </c>
+      <c r="S11">
+        <v>1.3</v>
+      </c>
+      <c r="T11">
         <v>3.2</v>
-      </c>
-      <c r="P11">
-        <v>2.9</v>
-      </c>
-      <c r="Q11">
-        <v>2.74</v>
-      </c>
-      <c r="R11">
-        <v>2.1</v>
-      </c>
-      <c r="S11">
-        <v>1.33</v>
-      </c>
-      <c r="T11">
-        <v>3</v>
       </c>
       <c r="U11">
         <v>2.56</v>
@@ -2135,19 +2135,19 @@
         <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z11">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AA11">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AB11">
         <v>1.98</v>
       </c>
       <c r="AC11">
-        <v>3.1</v>
+        <v>2.89</v>
       </c>
       <c r="AD11">
         <v>1.38</v>
@@ -2156,7 +2156,7 @@
         <v>1.09</v>
       </c>
       <c r="AF11">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG11">
         <v>2.2</v>
@@ -2175,7 +2175,7 @@
         <v>1.3</v>
       </c>
       <c r="AK11">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2594,16 +2594,16 @@
         <v>1.44</v>
       </c>
       <c r="O14">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="P14">
         <v>5.25</v>
       </c>
       <c r="Q14">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="R14">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="S14">
         <v>1.28</v>
@@ -2615,40 +2615,40 @@
         <v>2.55</v>
       </c>
       <c r="V14">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="W14">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z14">
-        <v>3.82</v>
+        <v>4.15</v>
       </c>
       <c r="AA14">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="AB14">
         <v>2</v>
       </c>
       <c r="AC14">
-        <v>2.81</v>
+        <v>2.59</v>
       </c>
       <c r="AD14">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="AE14">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF14">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AG14">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AK14">
-        <v>1.94</v>
+        <v>2.27</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3569,7 +3569,7 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="O20">
         <v>6.7</v>
@@ -4547,16 +4547,16 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="O26">
         <v>3.85</v>
       </c>
       <c r="P26">
-        <v>4.5</v>
+        <v>4.29</v>
       </c>
       <c r="Q26">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="R26">
         <v>2.2</v>
@@ -4589,7 +4589,7 @@
         <v>1.8</v>
       </c>
       <c r="AB26">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AC26">
         <v>2.92</v>
@@ -4601,10 +4601,10 @@
         <v>1.08</v>
       </c>
       <c r="AF26">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG26">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK26">
         <v>2.2</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,25 +4710,25 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.3</v>
+        <v>7</v>
       </c>
       <c r="O27">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="P27">
-        <v>8.5</v>
+        <v>1.36</v>
       </c>
       <c r="Q27">
-        <v>1.78</v>
+        <v>7.55</v>
       </c>
       <c r="R27">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="S27">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T27">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="U27">
         <v>2.76</v>
@@ -4740,34 +4740,34 @@
         <v>1.04</v>
       </c>
       <c r="X27">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y27">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z27">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AA27">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AB27">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AC27">
-        <v>3.28</v>
+        <v>3.8</v>
       </c>
       <c r="AD27">
         <v>1.25</v>
       </c>
       <c r="AE27">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF27">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AG27">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AK27">
-        <v>3.04</v>
+        <v>1.02</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,65 +4873,65 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.75</v>
+        <v>1.3</v>
       </c>
       <c r="O28">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="P28">
-        <v>4.33</v>
+        <v>8.5</v>
       </c>
       <c r="Q28">
-        <v>2.43</v>
+        <v>1.78</v>
       </c>
       <c r="R28">
-        <v>1.93</v>
+        <v>2.28</v>
       </c>
       <c r="S28">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="T28">
-        <v>2.45</v>
+        <v>2.76</v>
       </c>
       <c r="U28">
-        <v>3.18</v>
+        <v>2.76</v>
       </c>
       <c r="V28">
+        <v>1.35</v>
+      </c>
+      <c r="W28">
+        <v>1.04</v>
+      </c>
+      <c r="X28">
+        <v>1</v>
+      </c>
+      <c r="Y28">
         <v>1.27</v>
       </c>
-      <c r="W28">
-        <v>1.03</v>
-      </c>
-      <c r="X28">
-        <v>1.07</v>
-      </c>
-      <c r="Y28">
-        <v>1.47</v>
-      </c>
       <c r="Z28">
-        <v>2.63</v>
+        <v>3.14</v>
       </c>
       <c r="AA28">
-        <v>2.55</v>
+        <v>1.9</v>
       </c>
       <c r="AB28">
+        <v>1.77</v>
+      </c>
+      <c r="AC28">
+        <v>3.28</v>
+      </c>
+      <c r="AD28">
+        <v>1.25</v>
+      </c>
+      <c r="AE28">
+        <v>1.06</v>
+      </c>
+      <c r="AF28">
+        <v>2.4</v>
+      </c>
+      <c r="AG28">
         <v>1.5</v>
       </c>
-      <c r="AC28">
-        <v>5</v>
-      </c>
-      <c r="AD28">
-        <v>1.17</v>
-      </c>
-      <c r="AE28">
-        <v>1.04</v>
-      </c>
-      <c r="AF28">
-        <v>2.2</v>
-      </c>
-      <c r="AG28">
-        <v>1.62</v>
-      </c>
       <c r="AH28" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AK28">
-        <v>1.88</v>
+        <v>3.04</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,19 +5036,19 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="O29">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="P29">
-        <v>2.7</v>
+        <v>4.33</v>
       </c>
       <c r="Q29">
-        <v>3.22</v>
+        <v>2.43</v>
       </c>
       <c r="R29">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="S29">
         <v>1.44</v>
@@ -5069,13 +5069,13 @@
         <v>1.07</v>
       </c>
       <c r="Y29">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="Z29">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AA29">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AB29">
         <v>1.5</v>
@@ -5090,10 +5090,10 @@
         <v>1.04</v>
       </c>
       <c r="AF29">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AG29">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK29">
-        <v>1.43</v>
+        <v>1.88</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O30">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="P30">
-        <v>1.36</v>
+        <v>2.7</v>
       </c>
       <c r="Q30">
-        <v>7.55</v>
+        <v>3.22</v>
       </c>
       <c r="R30">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="S30">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="T30">
-        <v>2.64</v>
+        <v>2.45</v>
       </c>
       <c r="U30">
-        <v>2.76</v>
+        <v>3.18</v>
       </c>
       <c r="V30">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="W30">
+        <v>1.03</v>
+      </c>
+      <c r="X30">
+        <v>1.07</v>
+      </c>
+      <c r="Y30">
+        <v>1.44</v>
+      </c>
+      <c r="Z30">
+        <v>2.7</v>
+      </c>
+      <c r="AA30">
+        <v>2.45</v>
+      </c>
+      <c r="AB30">
+        <v>1.5</v>
+      </c>
+      <c r="AC30">
+        <v>5</v>
+      </c>
+      <c r="AD30">
+        <v>1.17</v>
+      </c>
+      <c r="AE30">
         <v>1.04</v>
       </c>
-      <c r="X30">
-        <v>1.05</v>
-      </c>
-      <c r="Y30">
-        <v>1.33</v>
-      </c>
-      <c r="Z30">
-        <v>3.25</v>
-      </c>
-      <c r="AA30">
+      <c r="AF30">
         <v>2.1</v>
       </c>
-      <c r="AB30">
-        <v>1.73</v>
-      </c>
-      <c r="AC30">
-        <v>3.8</v>
-      </c>
-      <c r="AD30">
-        <v>1.25</v>
-      </c>
-      <c r="AE30">
-        <v>1.07</v>
-      </c>
-      <c r="AF30">
-        <v>2.38</v>
-      </c>
       <c r="AG30">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AK30">
-        <v>1.02</v>
+        <v>1.43</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5365,10 +5365,10 @@
         <v>1.55</v>
       </c>
       <c r="O31">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P31">
-        <v>5.25</v>
+        <v>5.29</v>
       </c>
       <c r="Q31">
         <v>2.11</v>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="N32">
-        <v>4.29</v>
+        <v>4.3</v>
       </c>
       <c r="O32">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P32">
         <v>1.7</v>
@@ -5546,13 +5546,13 @@
         <v>2.85</v>
       </c>
       <c r="U32">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="V32">
         <v>1.39</v>
       </c>
       <c r="W32">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X32">
         <v>1.04</v>
@@ -5564,7 +5564,7 @@
         <v>3.5</v>
       </c>
       <c r="AA32">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AB32">
         <v>1.8</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,31 +5688,31 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="O33">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="P33">
-        <v>4.54</v>
+        <v>7</v>
       </c>
       <c r="Q33">
-        <v>2.14</v>
+        <v>1.8</v>
       </c>
       <c r="R33">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="S33">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T33">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="U33">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="V33">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="W33">
         <v>1.14</v>
@@ -5721,31 +5721,31 @@
         <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA33">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AB33">
-        <v>2.43</v>
+        <v>2.21</v>
       </c>
       <c r="AC33">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="AD33">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AE33">
         <v>1.2</v>
       </c>
       <c r="AF33">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AG33">
-        <v>2.42</v>
+        <v>2</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AK33">
-        <v>2.2</v>
+        <v>2.91</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,58 +5851,58 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="O34">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="P34">
-        <v>7</v>
+        <v>3.66</v>
       </c>
       <c r="Q34">
-        <v>1.8</v>
+        <v>2.59</v>
       </c>
       <c r="R34">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="S34">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T34">
+        <v>2.75</v>
+      </c>
+      <c r="U34">
+        <v>2.62</v>
+      </c>
+      <c r="V34">
+        <v>1.36</v>
+      </c>
+      <c r="W34">
+        <v>1.06</v>
+      </c>
+      <c r="X34">
+        <v>1.04</v>
+      </c>
+      <c r="Y34">
+        <v>1.22</v>
+      </c>
+      <c r="Z34">
         <v>3.5</v>
       </c>
-      <c r="U34">
-        <v>2.23</v>
-      </c>
-      <c r="V34">
-        <v>1.57</v>
-      </c>
-      <c r="W34">
-        <v>1.14</v>
-      </c>
-      <c r="X34">
-        <v>1.01</v>
-      </c>
-      <c r="Y34">
-        <v>1.17</v>
-      </c>
-      <c r="Z34">
-        <v>5</v>
-      </c>
       <c r="AA34">
-        <v>1.52</v>
+        <v>1.95</v>
       </c>
       <c r="AB34">
-        <v>2.21</v>
+        <v>1.84</v>
       </c>
       <c r="AC34">
-        <v>2.42</v>
+        <v>3.25</v>
       </c>
       <c r="AD34">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AE34">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AF34">
         <v>1.75</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AK34">
-        <v>2.91</v>
+        <v>1.73</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="O35">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P35">
-        <v>3.66</v>
+        <v>4.54</v>
       </c>
       <c r="Q35">
-        <v>2.59</v>
+        <v>2.14</v>
       </c>
       <c r="R35">
-        <v>2.1</v>
+        <v>2.44</v>
       </c>
       <c r="S35">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="T35">
-        <v>2.75</v>
+        <v>3.8</v>
       </c>
       <c r="U35">
-        <v>2.62</v>
+        <v>2.15</v>
       </c>
       <c r="V35">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="W35">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="X35">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="Z35">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="AA35">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="AB35">
-        <v>1.84</v>
+        <v>2.43</v>
       </c>
       <c r="AC35">
-        <v>3.25</v>
+        <v>2.2</v>
       </c>
       <c r="AD35">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="AE35">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AF35">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AG35">
-        <v>2</v>
+        <v>2.42</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AK35">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="O40">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="P40">
-        <v>2.73</v>
+        <v>3.5</v>
       </c>
       <c r="Q40">
-        <v>2.73</v>
+        <v>2.38</v>
       </c>
       <c r="R40">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="S40">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="T40">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="U40">
-        <v>2.42</v>
+        <v>2.18</v>
       </c>
       <c r="V40">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="W40">
+        <v>1.18</v>
+      </c>
+      <c r="X40">
+        <v>1.01</v>
+      </c>
+      <c r="Y40">
         <v>1.11</v>
       </c>
-      <c r="X40">
-        <v>1.03</v>
-      </c>
-      <c r="Y40">
-        <v>1.14</v>
-      </c>
       <c r="Z40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA40">
-        <v>1.71</v>
+        <v>1.46</v>
       </c>
       <c r="AB40">
-        <v>2.32</v>
+        <v>2.53</v>
       </c>
       <c r="AC40">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="AD40">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AE40">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AF40">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AG40">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AK40">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.92</v>
+        <v>20</v>
       </c>
       <c r="O41">
-        <v>3.9</v>
+        <v>13.5</v>
       </c>
       <c r="P41">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="Q41">
-        <v>2.38</v>
+        <v>12.17</v>
       </c>
       <c r="R41">
-        <v>2.36</v>
+        <v>4.47</v>
       </c>
       <c r="S41">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="T41">
-        <v>3.35</v>
+        <v>7</v>
       </c>
       <c r="U41">
-        <v>2.18</v>
+        <v>1.49</v>
       </c>
       <c r="V41">
+        <v>2.29</v>
+      </c>
+      <c r="W41">
+        <v>1.44</v>
+      </c>
+      <c r="X41">
+        <v>1</v>
+      </c>
+      <c r="Y41">
+        <v>1.01</v>
+      </c>
+      <c r="Z41">
+        <v>13</v>
+      </c>
+      <c r="AA41">
+        <v>1.11</v>
+      </c>
+      <c r="AB41">
+        <v>4.95</v>
+      </c>
+      <c r="AC41">
+        <v>1.36</v>
+      </c>
+      <c r="AD41">
+        <v>3</v>
+      </c>
+      <c r="AE41">
+        <v>1.9</v>
+      </c>
+      <c r="AF41">
         <v>1.65</v>
       </c>
-      <c r="W41">
-        <v>1.18</v>
-      </c>
-      <c r="X41">
-        <v>1.01</v>
-      </c>
-      <c r="Y41">
-        <v>1.11</v>
-      </c>
-      <c r="Z41">
-        <v>6</v>
-      </c>
-      <c r="AA41">
-        <v>1.46</v>
-      </c>
-      <c r="AB41">
-        <v>2.53</v>
-      </c>
-      <c r="AC41">
-        <v>2.15</v>
-      </c>
-      <c r="AD41">
-        <v>1.67</v>
-      </c>
-      <c r="AE41">
-        <v>1.25</v>
-      </c>
-      <c r="AF41">
-        <v>1.44</v>
-      </c>
       <c r="AG41">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.19</v>
+        <v>1.03</v>
       </c>
       <c r="AK41">
-        <v>1.93</v>
+        <v>1</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>20</v>
+        <v>2.1</v>
       </c>
       <c r="O43">
-        <v>13.5</v>
+        <v>3.58</v>
       </c>
       <c r="P43">
-        <v>1.1</v>
+        <v>2.73</v>
       </c>
       <c r="Q43">
-        <v>12.17</v>
+        <v>2.73</v>
       </c>
       <c r="R43">
-        <v>4.47</v>
+        <v>2.4</v>
       </c>
       <c r="S43">
-        <v>1.1</v>
+        <v>1.32</v>
       </c>
       <c r="T43">
-        <v>7</v>
+        <v>3.36</v>
       </c>
       <c r="U43">
-        <v>1.49</v>
+        <v>2.42</v>
       </c>
       <c r="V43">
-        <v>2.29</v>
+        <v>1.56</v>
       </c>
       <c r="W43">
-        <v>1.44</v>
+        <v>1.11</v>
       </c>
       <c r="X43">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="Z43">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AA43">
-        <v>1.11</v>
+        <v>1.71</v>
       </c>
       <c r="AB43">
-        <v>4.95</v>
+        <v>2.32</v>
       </c>
       <c r="AC43">
-        <v>1.36</v>
+        <v>2.5</v>
       </c>
       <c r="AD43">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AE43">
-        <v>1.9</v>
+        <v>1.18</v>
       </c>
       <c r="AF43">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AG43">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="AK43">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,80 +7807,80 @@
         </is>
       </c>
       <c r="N46">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="O46">
-        <v>3.65</v>
+        <v>4.05</v>
       </c>
       <c r="P46">
-        <v>2</v>
+        <v>5.56</v>
       </c>
       <c r="Q46">
-        <v>3.5</v>
+        <v>1.98</v>
       </c>
       <c r="R46">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="S46">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T46">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="U46">
-        <v>2.4</v>
+        <v>2.59</v>
       </c>
       <c r="V46">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="W46">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X46">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z46">
         <v>4.5</v>
       </c>
       <c r="AA46">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AB46">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AC46">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AD46">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AE46">
+        <v>1.12</v>
+      </c>
+      <c r="AF46">
+        <v>1.71</v>
+      </c>
+      <c r="AG46">
+        <v>1.99</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ46">
         <v>1.17</v>
       </c>
-      <c r="AF46">
-        <v>1.57</v>
-      </c>
-      <c r="AG46">
-        <v>2.18</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ46">
-        <v>1.8</v>
-      </c>
       <c r="AK46">
-        <v>1.27</v>
+        <v>2.25</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="O47">
-        <v>4.05</v>
+        <v>3.65</v>
       </c>
       <c r="P47">
-        <v>5.56</v>
+        <v>2</v>
       </c>
       <c r="Q47">
-        <v>1.98</v>
+        <v>3.5</v>
       </c>
       <c r="R47">
+        <v>2.2</v>
+      </c>
+      <c r="S47">
+        <v>1.29</v>
+      </c>
+      <c r="T47">
+        <v>3.4</v>
+      </c>
+      <c r="U47">
         <v>2.4</v>
       </c>
-      <c r="S47">
-        <v>1.3</v>
-      </c>
-      <c r="T47">
-        <v>3.12</v>
-      </c>
-      <c r="U47">
-        <v>2.59</v>
-      </c>
       <c r="V47">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="W47">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X47">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z47">
         <v>4.5</v>
       </c>
       <c r="AA47">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AB47">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AC47">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AD47">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AE47">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF47">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AG47">
-        <v>1.99</v>
+        <v>2.18</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.17</v>
+        <v>1.8</v>
       </c>
       <c r="AK47">
-        <v>2.25</v>
+        <v>1.27</v>
       </c>
       <c r="AL47">
         <v>0</v>

--- a/jogos_2026-10-13.xlsx
+++ b/jogos_2026-10-13.xlsx
@@ -647,7 +647,7 @@
         <v>2.5</v>
       </c>
       <c r="R2">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="S2">
         <v>1.36</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK2">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -794,68 +794,68 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N3">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O3">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P3">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="Q3">
-        <v>5.72</v>
+        <v>5.8</v>
       </c>
       <c r="R3">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="S3">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="T3">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="U3">
-        <v>3.5</v>
+        <v>3.18</v>
       </c>
       <c r="V3">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y3">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="Z3">
-        <v>2.46</v>
+        <v>2.41</v>
       </c>
       <c r="AA3">
-        <v>2.56</v>
+        <v>2.41</v>
       </c>
       <c r="AB3">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF3">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AG3">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK3">
         <v>1.1</v>
@@ -1120,69 +1120,69 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N5">
         <v>2</v>
       </c>
       <c r="O5">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P5">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Q5">
-        <v>2.79</v>
+        <v>2.82</v>
       </c>
       <c r="R5">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="S5">
+        <v>1.58</v>
+      </c>
+      <c r="T5">
+        <v>2.18</v>
+      </c>
+      <c r="U5">
+        <v>3.85</v>
+      </c>
+      <c r="V5">
+        <v>1.18</v>
+      </c>
+      <c r="W5">
+        <v>1.02</v>
+      </c>
+      <c r="X5">
+        <v>1.07</v>
+      </c>
+      <c r="Y5">
+        <v>1.58</v>
+      </c>
+      <c r="Z5">
+        <v>2.18</v>
+      </c>
+      <c r="AA5">
+        <v>2.74</v>
+      </c>
+      <c r="AB5">
+        <v>1.35</v>
+      </c>
+      <c r="AC5">
+        <v>5.75</v>
+      </c>
+      <c r="AD5">
+        <v>1.07</v>
+      </c>
+      <c r="AE5">
+        <v>1.01</v>
+      </c>
+      <c r="AF5">
+        <v>2.32</v>
+      </c>
+      <c r="AG5">
         <v>1.51</v>
       </c>
-      <c r="T5">
-        <v>2.27</v>
-      </c>
-      <c r="U5">
-        <v>3.87</v>
-      </c>
-      <c r="V5">
-        <v>1.2</v>
-      </c>
-      <c r="W5">
-        <v>0</v>
-      </c>
-      <c r="X5">
-        <v>0</v>
-      </c>
-      <c r="Y5">
-        <v>1.55</v>
-      </c>
-      <c r="Z5">
-        <v>2.23</v>
-      </c>
-      <c r="AA5">
-        <v>2.87</v>
-      </c>
-      <c r="AB5">
-        <v>1.34</v>
-      </c>
-      <c r="AC5">
-        <v>0</v>
-      </c>
-      <c r="AD5">
-        <v>0</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>2.39</v>
-      </c>
-      <c r="AG5">
-        <v>1.48</v>
-      </c>
       <c r="AH5" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK5">
         <v>1.62</v>
@@ -1283,11 +1283,11 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N6">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="O6">
         <v>2.8</v>
@@ -1314,16 +1314,16 @@
         <v>1.22</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X6">
         <v>1.08</v>
       </c>
       <c r="Y6">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="Z6">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="AA6">
         <v>2.74</v>
@@ -1338,7 +1338,7 @@
         <v>1.08</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF6">
         <v>2.23</v>
@@ -1616,10 +1616,10 @@
         <v>1.89</v>
       </c>
       <c r="O8">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="P8">
-        <v>4.09</v>
+        <v>3.7</v>
       </c>
       <c r="Q8">
         <v>2.6</v>
@@ -1649,13 +1649,13 @@
         <v>1.42</v>
       </c>
       <c r="Z8">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="AA8">
-        <v>2.41</v>
+        <v>2.37</v>
       </c>
       <c r="AB8">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AC8">
         <v>5</v>
@@ -1667,10 +1667,10 @@
         <v>1.05</v>
       </c>
       <c r="AF8">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AG8">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>2.05</v>
       </c>
       <c r="O9">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="P9">
         <v>3.6</v>
@@ -1803,13 +1803,13 @@
         <v>1.22</v>
       </c>
       <c r="W9">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X9">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Y9">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="Z9">
         <v>2.52</v>
@@ -1818,7 +1818,7 @@
         <v>2.62</v>
       </c>
       <c r="AB9">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AC9">
         <v>5.5</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="O10">
         <v>3.4</v>
       </c>
       <c r="P10">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="Q10">
         <v>2.4</v>
       </c>
       <c r="R10">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="S10">
         <v>1.36</v>
@@ -2012,7 +2012,7 @@
         <v>1.21</v>
       </c>
       <c r="AK10">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2105,7 +2105,7 @@
         <v>2.05</v>
       </c>
       <c r="O11">
-        <v>3.25</v>
+        <v>3.66</v>
       </c>
       <c r="P11">
         <v>3.1</v>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.91</v>
+        <v>2.12</v>
       </c>
       <c r="O12">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="P12">
         <v>3.1</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>4.9</v>
+        <v>4.25</v>
       </c>
       <c r="O13">
-        <v>4.05</v>
+        <v>3.85</v>
       </c>
       <c r="P13">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="Q13">
         <v>4</v>
@@ -3243,19 +3243,19 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O18">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="P18">
-        <v>3.9</v>
+        <v>3.94</v>
       </c>
       <c r="Q18">
         <v>2.88</v>
       </c>
       <c r="R18">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="S18">
         <v>1.7</v>
@@ -3276,10 +3276,10 @@
         <v>1.15</v>
       </c>
       <c r="Y18">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="Z18">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AA18">
         <v>3</v>
@@ -3288,7 +3288,7 @@
         <v>1.36</v>
       </c>
       <c r="AC18">
-        <v>6.54</v>
+        <v>6.35</v>
       </c>
       <c r="AD18">
         <v>1.1</v>
@@ -3297,10 +3297,10 @@
         <v>1.02</v>
       </c>
       <c r="AF18">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AG18">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3406,58 +3406,58 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="O19">
-        <v>2.82</v>
+        <v>2.85</v>
       </c>
       <c r="P19">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="Q19">
         <v>3.5</v>
       </c>
       <c r="R19">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="S19">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="T19">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U19">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="V19">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W19">
         <v>1.07</v>
       </c>
       <c r="X19">
+        <v>1.05</v>
+      </c>
+      <c r="Y19">
+        <v>1.32</v>
+      </c>
+      <c r="Z19">
+        <v>2.88</v>
+      </c>
+      <c r="AA19">
+        <v>2.12</v>
+      </c>
+      <c r="AB19">
+        <v>1.72</v>
+      </c>
+      <c r="AC19">
+        <v>3.65</v>
+      </c>
+      <c r="AD19">
+        <v>1.24</v>
+      </c>
+      <c r="AE19">
         <v>1.06</v>
-      </c>
-      <c r="Y19">
-        <v>1.36</v>
-      </c>
-      <c r="Z19">
-        <v>2.83</v>
-      </c>
-      <c r="AA19">
-        <v>2.1</v>
-      </c>
-      <c r="AB19">
-        <v>1.7</v>
-      </c>
-      <c r="AC19">
-        <v>3.34</v>
-      </c>
-      <c r="AD19">
-        <v>1.27</v>
-      </c>
-      <c r="AE19">
-        <v>1.05</v>
       </c>
       <c r="AF19">
         <v>1.8</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AK19">
         <v>1.36</v>
@@ -3732,7 +3732,7 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="O21">
         <v>3.4</v>
@@ -3744,22 +3744,22 @@
         <v>2.9</v>
       </c>
       <c r="R21">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="S21">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T21">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U21">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="V21">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="W21">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X21">
         <v>1.01</v>
@@ -3774,7 +3774,7 @@
         <v>1.66</v>
       </c>
       <c r="AB21">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="AC21">
         <v>2.63</v>
@@ -3805,7 +3805,7 @@
         <v>1.25</v>
       </c>
       <c r="AK21">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3913,10 +3913,10 @@
         <v>1.22</v>
       </c>
       <c r="T22">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="U22">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="V22">
         <v>1.65</v>
@@ -3931,7 +3931,7 @@
         <v>1.14</v>
       </c>
       <c r="Z22">
-        <v>4.86</v>
+        <v>4.92</v>
       </c>
       <c r="AA22">
         <v>1.57</v>
@@ -3940,7 +3940,7 @@
         <v>2.38</v>
       </c>
       <c r="AC22">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="AD22">
         <v>1.57</v>
@@ -3968,7 +3968,7 @@
         <v>1.14</v>
       </c>
       <c r="AK22">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,7 +4058,7 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="O23">
         <v>3.75</v>
@@ -4067,10 +4067,10 @@
         <v>2.2</v>
       </c>
       <c r="Q23">
-        <v>3.02</v>
+        <v>2.96</v>
       </c>
       <c r="R23">
-        <v>2.21</v>
+        <v>2.29</v>
       </c>
       <c r="S23">
         <v>1.25</v>
@@ -4131,7 +4131,7 @@
         <v>1.24</v>
       </c>
       <c r="AK23">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4230,7 +4230,7 @@
         <v>2.1</v>
       </c>
       <c r="Q24">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="R24">
         <v>2.49</v>
@@ -4263,7 +4263,7 @@
         <v>1.31</v>
       </c>
       <c r="AB24">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AC24">
         <v>1.87</v>
@@ -4294,7 +4294,7 @@
         <v>1.73</v>
       </c>
       <c r="AK24">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4393,13 +4393,13 @@
         <v>4.33</v>
       </c>
       <c r="Q25">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="R25">
-        <v>2.53</v>
+        <v>2.43</v>
       </c>
       <c r="S25">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="T25">
         <v>2.9</v>
@@ -4408,7 +4408,7 @@
         <v>2.05</v>
       </c>
       <c r="V25">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="W25">
         <v>1.18</v>
@@ -4432,7 +4432,7 @@
         <v>2.2</v>
       </c>
       <c r="AD25">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AE25">
         <v>1.25</v>
@@ -4457,7 +4457,7 @@
         <v>1.17</v>
       </c>
       <c r="AK25">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,16 +4547,16 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="O26">
         <v>3.85</v>
       </c>
       <c r="P26">
-        <v>4.29</v>
+        <v>4.5</v>
       </c>
       <c r="Q26">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="R26">
         <v>2.2</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK26">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,25 +4710,25 @@
         </is>
       </c>
       <c r="N27">
-        <v>7</v>
+        <v>1.3</v>
       </c>
       <c r="O27">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="P27">
-        <v>1.36</v>
+        <v>8.5</v>
       </c>
       <c r="Q27">
-        <v>7.55</v>
+        <v>1.78</v>
       </c>
       <c r="R27">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="S27">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T27">
-        <v>2.64</v>
+        <v>2.76</v>
       </c>
       <c r="U27">
         <v>2.76</v>
@@ -4740,34 +4740,34 @@
         <v>1.04</v>
       </c>
       <c r="X27">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y27">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Z27">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="AA27">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AB27">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AC27">
-        <v>3.8</v>
+        <v>3.28</v>
       </c>
       <c r="AD27">
         <v>1.25</v>
       </c>
       <c r="AE27">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF27">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AG27">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AK27">
-        <v>1.02</v>
+        <v>3.04</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,80 +4873,80 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.3</v>
+        <v>1.75</v>
       </c>
       <c r="O28">
+        <v>3.1</v>
+      </c>
+      <c r="P28">
         <v>4.33</v>
       </c>
-      <c r="P28">
-        <v>8.5</v>
-      </c>
       <c r="Q28">
-        <v>1.78</v>
+        <v>2.43</v>
       </c>
       <c r="R28">
-        <v>2.28</v>
+        <v>1.93</v>
       </c>
       <c r="S28">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="T28">
-        <v>2.76</v>
+        <v>2.45</v>
       </c>
       <c r="U28">
-        <v>2.76</v>
+        <v>3.18</v>
       </c>
       <c r="V28">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="W28">
+        <v>1.03</v>
+      </c>
+      <c r="X28">
+        <v>1.07</v>
+      </c>
+      <c r="Y28">
+        <v>1.47</v>
+      </c>
+      <c r="Z28">
+        <v>2.63</v>
+      </c>
+      <c r="AA28">
+        <v>2.55</v>
+      </c>
+      <c r="AB28">
+        <v>1.5</v>
+      </c>
+      <c r="AC28">
+        <v>5</v>
+      </c>
+      <c r="AD28">
+        <v>1.17</v>
+      </c>
+      <c r="AE28">
         <v>1.04</v>
       </c>
-      <c r="X28">
-        <v>1</v>
-      </c>
-      <c r="Y28">
-        <v>1.27</v>
-      </c>
-      <c r="Z28">
-        <v>3.14</v>
-      </c>
-      <c r="AA28">
-        <v>1.9</v>
-      </c>
-      <c r="AB28">
-        <v>1.77</v>
-      </c>
-      <c r="AC28">
-        <v>3.28</v>
-      </c>
-      <c r="AD28">
+      <c r="AF28">
+        <v>2.2</v>
+      </c>
+      <c r="AG28">
+        <v>1.62</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28">
         <v>1.25</v>
       </c>
-      <c r="AE28">
-        <v>1.06</v>
-      </c>
-      <c r="AF28">
-        <v>2.4</v>
-      </c>
-      <c r="AG28">
-        <v>1.5</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28">
-        <v>1.12</v>
-      </c>
       <c r="AK28">
-        <v>3.04</v>
+        <v>1.88</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.75</v>
+        <v>7</v>
       </c>
       <c r="O29">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="P29">
-        <v>4.33</v>
+        <v>1.36</v>
       </c>
       <c r="Q29">
-        <v>2.43</v>
+        <v>7.55</v>
       </c>
       <c r="R29">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="S29">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="T29">
-        <v>2.45</v>
+        <v>2.64</v>
       </c>
       <c r="U29">
-        <v>3.18</v>
+        <v>2.76</v>
       </c>
       <c r="V29">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="W29">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X29">
+        <v>1.05</v>
+      </c>
+      <c r="Y29">
+        <v>1.33</v>
+      </c>
+      <c r="Z29">
+        <v>3.25</v>
+      </c>
+      <c r="AA29">
+        <v>2.1</v>
+      </c>
+      <c r="AB29">
+        <v>1.73</v>
+      </c>
+      <c r="AC29">
+        <v>3.8</v>
+      </c>
+      <c r="AD29">
+        <v>1.25</v>
+      </c>
+      <c r="AE29">
         <v>1.07</v>
       </c>
-      <c r="Y29">
-        <v>1.47</v>
-      </c>
-      <c r="Z29">
-        <v>2.63</v>
-      </c>
-      <c r="AA29">
-        <v>2.55</v>
-      </c>
-      <c r="AB29">
-        <v>1.5</v>
-      </c>
-      <c r="AC29">
-        <v>5</v>
-      </c>
-      <c r="AD29">
-        <v>1.17</v>
-      </c>
-      <c r="AE29">
-        <v>1.04</v>
-      </c>
       <c r="AF29">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AG29">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK29">
-        <v>1.88</v>
+        <v>1.02</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5368,7 +5368,7 @@
         <v>3.5</v>
       </c>
       <c r="P31">
-        <v>5.29</v>
+        <v>4.75</v>
       </c>
       <c r="Q31">
         <v>2.11</v>
@@ -5401,7 +5401,7 @@
         <v>2.88</v>
       </c>
       <c r="AA31">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AB31">
         <v>1.65</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="O33">
-        <v>4.5</v>
+        <v>3.35</v>
       </c>
       <c r="P33">
-        <v>7</v>
+        <v>3.66</v>
       </c>
       <c r="Q33">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="R33">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="S33">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="T33">
+        <v>2.73</v>
+      </c>
+      <c r="U33">
+        <v>2.7</v>
+      </c>
+      <c r="V33">
+        <v>1.36</v>
+      </c>
+      <c r="W33">
+        <v>1.06</v>
+      </c>
+      <c r="X33">
+        <v>1.04</v>
+      </c>
+      <c r="Y33">
+        <v>1.29</v>
+      </c>
+      <c r="Z33">
         <v>3.5</v>
       </c>
-      <c r="U33">
-        <v>2.23</v>
-      </c>
-      <c r="V33">
-        <v>1.57</v>
-      </c>
-      <c r="W33">
-        <v>1.14</v>
-      </c>
-      <c r="X33">
-        <v>1.01</v>
-      </c>
-      <c r="Y33">
-        <v>1.17</v>
-      </c>
-      <c r="Z33">
-        <v>5</v>
-      </c>
       <c r="AA33">
-        <v>1.52</v>
+        <v>1.98</v>
       </c>
       <c r="AB33">
-        <v>2.21</v>
+        <v>1.82</v>
       </c>
       <c r="AC33">
-        <v>2.42</v>
+        <v>3.25</v>
       </c>
       <c r="AD33">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AE33">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AF33">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG33">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AK33">
-        <v>2.91</v>
+        <v>1.67</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,58 +5851,58 @@
         </is>
       </c>
       <c r="N34">
-        <v>2</v>
+        <v>1.44</v>
       </c>
       <c r="O34">
-        <v>3.4</v>
+        <v>4.55</v>
       </c>
       <c r="P34">
-        <v>3.66</v>
+        <v>7.19</v>
       </c>
       <c r="Q34">
-        <v>2.59</v>
+        <v>1.83</v>
       </c>
       <c r="R34">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="S34">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T34">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="U34">
-        <v>2.62</v>
+        <v>2.22</v>
       </c>
       <c r="V34">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="W34">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="X34">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z34">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="AA34">
-        <v>1.95</v>
+        <v>1.52</v>
       </c>
       <c r="AB34">
-        <v>1.84</v>
+        <v>2.22</v>
       </c>
       <c r="AC34">
-        <v>3.25</v>
+        <v>2.42</v>
       </c>
       <c r="AD34">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AE34">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AF34">
         <v>1.75</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AK34">
-        <v>1.73</v>
+        <v>2.91</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6017,10 +6017,10 @@
         <v>1.65</v>
       </c>
       <c r="O35">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="P35">
-        <v>4.54</v>
+        <v>4.09</v>
       </c>
       <c r="Q35">
         <v>2.14</v>
@@ -6035,13 +6035,13 @@
         <v>3.8</v>
       </c>
       <c r="U35">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="V35">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="W35">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X35">
         <v>1.01</v>
@@ -6087,7 +6087,7 @@
         <v>1.17</v>
       </c>
       <c r="AK35">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6198,10 +6198,10 @@
         <v>2.82</v>
       </c>
       <c r="U36">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="V36">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W36">
         <v>1.05</v>
@@ -6340,7 +6340,7 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="O37">
         <v>3.44</v>
@@ -6349,25 +6349,25 @@
         <v>2.7</v>
       </c>
       <c r="Q37">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R37">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="S37">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T37">
         <v>2.77</v>
       </c>
       <c r="U37">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="V37">
         <v>1.4</v>
       </c>
       <c r="W37">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X37">
         <v>1.04</v>
@@ -6394,10 +6394,10 @@
         <v>1.1</v>
       </c>
       <c r="AF37">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG37">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6521,16 +6521,16 @@
         <v>1.31</v>
       </c>
       <c r="T38">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="U38">
         <v>2.5</v>
       </c>
       <c r="V38">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W38">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X38">
         <v>1.04</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>20</v>
+        <v>1.23</v>
       </c>
       <c r="O41">
-        <v>13.5</v>
+        <v>6.5</v>
       </c>
       <c r="P41">
-        <v>1.1</v>
+        <v>11</v>
       </c>
       <c r="Q41">
-        <v>12.17</v>
+        <v>1.63</v>
       </c>
       <c r="R41">
-        <v>4.47</v>
+        <v>2.54</v>
       </c>
       <c r="S41">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="T41">
-        <v>7</v>
+        <v>3.6</v>
       </c>
       <c r="U41">
-        <v>1.49</v>
+        <v>2.25</v>
       </c>
       <c r="V41">
-        <v>2.29</v>
+        <v>1.6</v>
       </c>
       <c r="W41">
-        <v>1.44</v>
+        <v>1.11</v>
       </c>
       <c r="X41">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y41">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="Z41">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AA41">
-        <v>1.11</v>
+        <v>1.64</v>
       </c>
       <c r="AB41">
-        <v>4.95</v>
+        <v>2.37</v>
       </c>
       <c r="AC41">
-        <v>1.36</v>
+        <v>2.44</v>
       </c>
       <c r="AD41">
-        <v>3</v>
+        <v>1.56</v>
       </c>
       <c r="AE41">
-        <v>1.9</v>
+        <v>1.18</v>
       </c>
       <c r="AF41">
-        <v>1.65</v>
+        <v>2.17</v>
       </c>
       <c r="AG41">
-        <v>2.1</v>
+        <v>1.63</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AK41">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,31 +7155,31 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.23</v>
+        <v>2.1</v>
       </c>
       <c r="O42">
-        <v>6.5</v>
+        <v>3.58</v>
       </c>
       <c r="P42">
-        <v>11</v>
+        <v>2.73</v>
       </c>
       <c r="Q42">
-        <v>1.63</v>
+        <v>2.73</v>
       </c>
       <c r="R42">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="S42">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T42">
-        <v>3.6</v>
+        <v>3.36</v>
       </c>
       <c r="U42">
-        <v>2.25</v>
+        <v>2.42</v>
       </c>
       <c r="V42">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="W42">
         <v>1.11</v>
@@ -7194,25 +7194,25 @@
         <v>5</v>
       </c>
       <c r="AA42">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="AB42">
-        <v>2.37</v>
+        <v>2.32</v>
       </c>
       <c r="AC42">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AD42">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AE42">
         <v>1.18</v>
       </c>
       <c r="AF42">
-        <v>2.17</v>
+        <v>1.52</v>
       </c>
       <c r="AG42">
-        <v>1.63</v>
+        <v>2.38</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="AK42">
-        <v>4</v>
+        <v>1.7</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,80 +7318,80 @@
         </is>
       </c>
       <c r="N43">
+        <v>20</v>
+      </c>
+      <c r="O43">
+        <v>13.5</v>
+      </c>
+      <c r="P43">
+        <v>1.1</v>
+      </c>
+      <c r="Q43">
+        <v>12.17</v>
+      </c>
+      <c r="R43">
+        <v>4.47</v>
+      </c>
+      <c r="S43">
+        <v>1.1</v>
+      </c>
+      <c r="T43">
+        <v>7</v>
+      </c>
+      <c r="U43">
+        <v>1.49</v>
+      </c>
+      <c r="V43">
+        <v>2.29</v>
+      </c>
+      <c r="W43">
+        <v>1.44</v>
+      </c>
+      <c r="X43">
+        <v>1</v>
+      </c>
+      <c r="Y43">
+        <v>1.01</v>
+      </c>
+      <c r="Z43">
+        <v>13</v>
+      </c>
+      <c r="AA43">
+        <v>1.11</v>
+      </c>
+      <c r="AB43">
+        <v>4.95</v>
+      </c>
+      <c r="AC43">
+        <v>1.36</v>
+      </c>
+      <c r="AD43">
+        <v>3</v>
+      </c>
+      <c r="AE43">
+        <v>1.9</v>
+      </c>
+      <c r="AF43">
+        <v>1.65</v>
+      </c>
+      <c r="AG43">
         <v>2.1</v>
       </c>
-      <c r="O43">
-        <v>3.58</v>
-      </c>
-      <c r="P43">
-        <v>2.73</v>
-      </c>
-      <c r="Q43">
-        <v>2.73</v>
-      </c>
-      <c r="R43">
-        <v>2.4</v>
-      </c>
-      <c r="S43">
-        <v>1.32</v>
-      </c>
-      <c r="T43">
-        <v>3.36</v>
-      </c>
-      <c r="U43">
-        <v>2.42</v>
-      </c>
-      <c r="V43">
-        <v>1.56</v>
-      </c>
-      <c r="W43">
-        <v>1.11</v>
-      </c>
-      <c r="X43">
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ43">
         <v>1.03</v>
       </c>
-      <c r="Y43">
-        <v>1.14</v>
-      </c>
-      <c r="Z43">
-        <v>5</v>
-      </c>
-      <c r="AA43">
-        <v>1.71</v>
-      </c>
-      <c r="AB43">
-        <v>2.32</v>
-      </c>
-      <c r="AC43">
-        <v>2.5</v>
-      </c>
-      <c r="AD43">
-        <v>1.5</v>
-      </c>
-      <c r="AE43">
-        <v>1.18</v>
-      </c>
-      <c r="AF43">
-        <v>1.52</v>
-      </c>
-      <c r="AG43">
-        <v>2.38</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ43">
-        <v>1.32</v>
-      </c>
       <c r="AK43">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="O46">
-        <v>4.05</v>
+        <v>3.65</v>
       </c>
       <c r="P46">
-        <v>5.56</v>
+        <v>2</v>
       </c>
       <c r="Q46">
-        <v>1.98</v>
+        <v>3.61</v>
       </c>
       <c r="R46">
+        <v>2.2</v>
+      </c>
+      <c r="S46">
+        <v>1.29</v>
+      </c>
+      <c r="T46">
+        <v>3.4</v>
+      </c>
+      <c r="U46">
         <v>2.4</v>
       </c>
-      <c r="S46">
-        <v>1.3</v>
-      </c>
-      <c r="T46">
-        <v>3.12</v>
-      </c>
-      <c r="U46">
-        <v>2.59</v>
-      </c>
       <c r="V46">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="W46">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X46">
         <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z46">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA46">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AB46">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AC46">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AD46">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AE46">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF46">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AG46">
-        <v>1.99</v>
+        <v>2.18</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.17</v>
+        <v>1.8</v>
       </c>
       <c r="AK46">
-        <v>2.25</v>
+        <v>1.27</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="O47">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="P47">
-        <v>2</v>
+        <v>5.56</v>
       </c>
       <c r="Q47">
-        <v>3.5</v>
+        <v>2.12</v>
       </c>
       <c r="R47">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="S47">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T47">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U47">
-        <v>2.4</v>
+        <v>2.61</v>
       </c>
       <c r="V47">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="W47">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X47">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z47">
         <v>4.5</v>
       </c>
       <c r="AA47">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AB47">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AC47">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AD47">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AE47">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF47">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="AG47">
-        <v>2.18</v>
+        <v>1.99</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="AK47">
-        <v>1.27</v>
+        <v>2.25</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8308,52 +8308,52 @@
         <v>4</v>
       </c>
       <c r="R49">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="S49">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="T49">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="U49">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="V49">
         <v>1.25</v>
       </c>
       <c r="W49">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X49">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y49">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="Z49">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="AA49">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="AB49">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AC49">
-        <v>4.8</v>
+        <v>5.25</v>
       </c>
       <c r="AD49">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AE49">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF49">
         <v>2.1</v>
       </c>
       <c r="AG49">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AK49">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8492,28 +8492,28 @@
         <v>1.03</v>
       </c>
       <c r="Y50">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z50">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="AA50">
         <v>2.25</v>
       </c>
       <c r="AB50">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AC50">
-        <v>3.95</v>
+        <v>4.33</v>
       </c>
       <c r="AD50">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE50">
         <v>1.02</v>
       </c>
       <c r="AF50">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AG50">
         <v>1.8</v>

--- a/jogos_2026-10-13.xlsx
+++ b/jogos_2026-10-13.xlsx
@@ -976,7 +976,7 @@
         <v>2.28</v>
       </c>
       <c r="S4">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T4">
         <v>3.2</v>
@@ -988,7 +988,7 @@
         <v>1.44</v>
       </c>
       <c r="W4">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X4">
         <v>1.02</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,43 +1124,43 @@
         </is>
       </c>
       <c r="N5">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="O5">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="P5">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="Q5">
-        <v>2.82</v>
+        <v>3.38</v>
       </c>
       <c r="R5">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="S5">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="T5">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="U5">
-        <v>3.85</v>
+        <v>3.52</v>
       </c>
       <c r="V5">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="W5">
         <v>1.02</v>
       </c>
       <c r="X5">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y5">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Z5">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AA5">
         <v>2.74</v>
@@ -1169,19 +1169,19 @@
         <v>1.35</v>
       </c>
       <c r="AC5">
-        <v>5.75</v>
+        <v>5.55</v>
       </c>
       <c r="AD5">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AE5">
         <v>1.01</v>
       </c>
       <c r="AF5">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="AG5">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AK5">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,43 +1287,43 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="O6">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="P6">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="Q6">
-        <v>3.38</v>
+        <v>2.82</v>
       </c>
       <c r="R6">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="S6">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="T6">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="U6">
-        <v>3.52</v>
+        <v>3.85</v>
       </c>
       <c r="V6">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="W6">
         <v>1.02</v>
       </c>
       <c r="X6">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y6">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="Z6">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="AA6">
         <v>2.74</v>
@@ -1332,19 +1332,19 @@
         <v>1.35</v>
       </c>
       <c r="AC6">
-        <v>5.55</v>
+        <v>5.75</v>
       </c>
       <c r="AD6">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AE6">
         <v>1.01</v>
       </c>
       <c r="AF6">
-        <v>2.23</v>
+        <v>2.32</v>
       </c>
       <c r="AG6">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK6">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1453,7 +1453,7 @@
         <v>2.15</v>
       </c>
       <c r="O7">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="P7">
         <v>3.5</v>
@@ -1471,7 +1471,7 @@
         <v>2.12</v>
       </c>
       <c r="U7">
-        <v>3.98</v>
+        <v>4.5</v>
       </c>
       <c r="V7">
         <v>1.17</v>
@@ -1480,7 +1480,7 @@
         <v>1.03</v>
       </c>
       <c r="X7">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Y7">
         <v>1.65</v>
@@ -1489,19 +1489,19 @@
         <v>2.06</v>
       </c>
       <c r="AA7">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AB7">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AC7">
-        <v>6.55</v>
+        <v>6.5</v>
       </c>
       <c r="AD7">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AE7">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF7">
         <v>2.42</v>
@@ -2108,7 +2108,7 @@
         <v>3.66</v>
       </c>
       <c r="P11">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q11">
         <v>2.61</v>
@@ -2138,16 +2138,16 @@
         <v>1.22</v>
       </c>
       <c r="Z11">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA11">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AB11">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AC11">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="AD11">
         <v>1.38</v>
@@ -2156,10 +2156,10 @@
         <v>1.09</v>
       </c>
       <c r="AF11">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG11">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.12</v>
+        <v>1.91</v>
       </c>
       <c r="O12">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P12">
         <v>3.1</v>
@@ -2431,31 +2431,31 @@
         <v>4.25</v>
       </c>
       <c r="O13">
-        <v>3.85</v>
+        <v>4.05</v>
       </c>
       <c r="P13">
         <v>1.66</v>
       </c>
       <c r="Q13">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="R13">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="S13">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="T13">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="U13">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="V13">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="W13">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="X13">
         <v>1.01</v>
@@ -2467,13 +2467,13 @@
         <v>4.8</v>
       </c>
       <c r="AA13">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="AB13">
-        <v>2.55</v>
+        <v>2.07</v>
       </c>
       <c r="AC13">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AD13">
         <v>1.62</v>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="AK13">
         <v>1.22</v>
@@ -2597,7 +2597,7 @@
         <v>4.1</v>
       </c>
       <c r="P14">
-        <v>5.25</v>
+        <v>4.77</v>
       </c>
       <c r="Q14">
         <v>1.95</v>
@@ -2606,13 +2606,13 @@
         <v>2.28</v>
       </c>
       <c r="S14">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T14">
         <v>2.39</v>
       </c>
       <c r="U14">
-        <v>2.55</v>
+        <v>2.32</v>
       </c>
       <c r="V14">
         <v>1.49</v>
@@ -2633,7 +2633,7 @@
         <v>1.64</v>
       </c>
       <c r="AB14">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC14">
         <v>2.59</v>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AK14">
         <v>2.27</v>
@@ -2760,10 +2760,10 @@
         <v>3.75</v>
       </c>
       <c r="P15">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="Q15">
-        <v>3.99</v>
+        <v>3.97</v>
       </c>
       <c r="R15">
         <v>2.29</v>
@@ -2775,13 +2775,13 @@
         <v>3.42</v>
       </c>
       <c r="U15">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="V15">
         <v>1.55</v>
       </c>
       <c r="W15">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X15">
         <v>1.01</v>
@@ -2917,25 +2917,25 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.33</v>
+        <v>2.53</v>
       </c>
       <c r="O16">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="P16">
         <v>2.65</v>
       </c>
       <c r="Q16">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="R16">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="S16">
         <v>1.29</v>
       </c>
       <c r="T16">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="U16">
         <v>2.25</v>
@@ -2959,13 +2959,13 @@
         <v>1.53</v>
       </c>
       <c r="AB16">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="AC16">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AD16">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AE16">
         <v>1.18</v>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AK16">
         <v>1.5</v>
@@ -3080,19 +3080,19 @@
         </is>
       </c>
       <c r="N17">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="O17">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="P17">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="Q17">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="R17">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="S17">
         <v>1.57</v>
@@ -3101,7 +3101,7 @@
         <v>2.25</v>
       </c>
       <c r="U17">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="V17">
         <v>1.19</v>
@@ -3119,10 +3119,10 @@
         <v>2.45</v>
       </c>
       <c r="AA17">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AB17">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AC17">
         <v>6</v>
@@ -3134,7 +3134,7 @@
         <v>1.02</v>
       </c>
       <c r="AF17">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AG17">
         <v>1.57</v>
@@ -3575,13 +3575,13 @@
         <v>6.7</v>
       </c>
       <c r="P20">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q20">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="R20">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="S20">
         <v>1.2</v>
@@ -3590,13 +3590,13 @@
         <v>4.5</v>
       </c>
       <c r="U20">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="V20">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="W20">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X20">
         <v>1.01</v>
@@ -3617,7 +3617,7 @@
         <v>1.99</v>
       </c>
       <c r="AD20">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AE20">
         <v>1.3</v>
@@ -3732,7 +3732,7 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="O21">
         <v>3.4</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="O22">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="P22">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="Q22">
-        <v>1.91</v>
+        <v>2.96</v>
       </c>
       <c r="R22">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="S22">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T22">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U22">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="V22">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="W22">
         <v>1.14</v>
       </c>
       <c r="X22">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
+        <v>1.13</v>
+      </c>
+      <c r="Z22">
+        <v>4.78</v>
+      </c>
+      <c r="AA22">
+        <v>1.5</v>
+      </c>
+      <c r="AB22">
+        <v>2.28</v>
+      </c>
+      <c r="AC22">
+        <v>2</v>
+      </c>
+      <c r="AD22">
+        <v>1.43</v>
+      </c>
+      <c r="AE22">
         <v>1.14</v>
       </c>
-      <c r="Z22">
-        <v>4.92</v>
-      </c>
-      <c r="AA22">
-        <v>1.57</v>
-      </c>
-      <c r="AB22">
-        <v>2.38</v>
-      </c>
-      <c r="AC22">
-        <v>2.36</v>
-      </c>
-      <c r="AD22">
-        <v>1.57</v>
-      </c>
-      <c r="AE22">
-        <v>1.18</v>
-      </c>
       <c r="AF22">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AG22">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AK22">
-        <v>2.45</v>
+        <v>1.36</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="O23">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="P23">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q23">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="R23">
-        <v>2.29</v>
+        <v>2.49</v>
       </c>
       <c r="S23">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="T23">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="U23">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="V23">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="W23">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X23">
         <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z23">
-        <v>4.78</v>
+        <v>7.5</v>
       </c>
       <c r="AA23">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="AB23">
-        <v>2.28</v>
+        <v>3.1</v>
       </c>
       <c r="AC23">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="AD23">
-        <v>1.42</v>
+        <v>1.9</v>
       </c>
       <c r="AE23">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AF23">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AG23">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.24</v>
+        <v>1.73</v>
       </c>
       <c r="AK23">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.91</v>
+        <v>1.48</v>
       </c>
       <c r="O24">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="P24">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="Q24">
-        <v>2.9</v>
+        <v>1.91</v>
       </c>
       <c r="R24">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="S24">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="T24">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="U24">
-        <v>1.91</v>
+        <v>2.26</v>
       </c>
       <c r="V24">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="W24">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X24">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z24">
-        <v>7.5</v>
+        <v>4.92</v>
       </c>
       <c r="AA24">
-        <v>1.31</v>
+        <v>1.57</v>
       </c>
       <c r="AB24">
-        <v>3.2</v>
+        <v>2.38</v>
       </c>
       <c r="AC24">
-        <v>1.87</v>
+        <v>2.36</v>
       </c>
       <c r="AD24">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="AE24">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AF24">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="AG24">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.73</v>
+        <v>1.14</v>
       </c>
       <c r="AK24">
-        <v>1.31</v>
+        <v>2.45</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="O25">
         <v>3.9</v>
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="O27">
-        <v>4.33</v>
+        <v>5.55</v>
       </c>
       <c r="P27">
-        <v>8.5</v>
+        <v>13</v>
       </c>
       <c r="Q27">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="R27">
-        <v>2.28</v>
+        <v>2.6</v>
       </c>
       <c r="S27">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T27">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="U27">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="V27">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W27">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X27">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z27">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AA27">
         <v>1.9</v>
       </c>
       <c r="AB27">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AC27">
-        <v>3.28</v>
+        <v>3.08</v>
       </c>
       <c r="AD27">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE27">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF27">
-        <v>2.4</v>
+        <v>3.18</v>
       </c>
       <c r="AG27">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AK27">
-        <v>3.04</v>
+        <v>4.1</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,34 +4873,34 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="O28">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P28">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="Q28">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="R28">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="S28">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T28">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="U28">
         <v>3.18</v>
       </c>
       <c r="V28">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W28">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X28">
         <v>1.07</v>
@@ -4912,7 +4912,7 @@
         <v>2.63</v>
       </c>
       <c r="AA28">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AB28">
         <v>1.5</v>
@@ -4927,10 +4927,10 @@
         <v>1.04</v>
       </c>
       <c r="AF28">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AG28">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AK28">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="O29">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="P29">
+        <v>1.28</v>
+      </c>
+      <c r="Q29">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="R29">
+        <v>2.29</v>
+      </c>
+      <c r="S29">
         <v>1.36</v>
       </c>
-      <c r="Q29">
-        <v>7.55</v>
-      </c>
-      <c r="R29">
-        <v>2.2</v>
-      </c>
-      <c r="S29">
-        <v>1.38</v>
-      </c>
       <c r="T29">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="U29">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="V29">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W29">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X29">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z29">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="AA29">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AB29">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AC29">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="AD29">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE29">
         <v>1.07</v>
       </c>
       <c r="AF29">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AG29">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AK29">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,52 +5199,52 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.5</v>
+        <v>2.06</v>
       </c>
       <c r="O30">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="P30">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="Q30">
-        <v>3.22</v>
+        <v>2.88</v>
       </c>
       <c r="R30">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="S30">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="T30">
-        <v>2.45</v>
+        <v>2.31</v>
       </c>
       <c r="U30">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="V30">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W30">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X30">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y30">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="Z30">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AA30">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AB30">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AC30">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AD30">
         <v>1.17</v>
@@ -5253,10 +5253,10 @@
         <v>1.04</v>
       </c>
       <c r="AF30">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG30">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK30">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5546,13 +5546,13 @@
         <v>2.85</v>
       </c>
       <c r="U32">
-        <v>2.94</v>
+        <v>2.72</v>
       </c>
       <c r="V32">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W32">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X32">
         <v>1.04</v>
@@ -5564,7 +5564,7 @@
         <v>3.5</v>
       </c>
       <c r="AA32">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="AB32">
         <v>1.8</v>
@@ -5576,7 +5576,7 @@
         <v>1.33</v>
       </c>
       <c r="AE32">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF32">
         <v>1.83</v>
@@ -5598,7 +5598,7 @@
         <v>1.92</v>
       </c>
       <c r="AK32">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5691,13 +5691,13 @@
         <v>2</v>
       </c>
       <c r="O33">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P33">
         <v>3.66</v>
       </c>
       <c r="Q33">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="R33">
         <v>2.1</v>
@@ -5721,13 +5721,13 @@
         <v>1.04</v>
       </c>
       <c r="Y33">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z33">
         <v>3.5</v>
       </c>
       <c r="AA33">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AB33">
         <v>1.82</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="O34">
-        <v>4.55</v>
+        <v>4.3</v>
       </c>
       <c r="P34">
-        <v>7.19</v>
+        <v>4.09</v>
       </c>
       <c r="Q34">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="R34">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="S34">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T34">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U34">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="V34">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="W34">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X34">
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA34">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AB34">
-        <v>2.22</v>
+        <v>2.43</v>
       </c>
       <c r="AC34">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="AD34">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AE34">
         <v>1.2</v>
       </c>
       <c r="AF34">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AG34">
-        <v>2</v>
+        <v>2.42</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AK34">
-        <v>2.91</v>
+        <v>2.1</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="O35">
-        <v>4.2</v>
+        <v>3.38</v>
       </c>
       <c r="P35">
-        <v>4.09</v>
+        <v>3.1</v>
       </c>
       <c r="Q35">
-        <v>2.14</v>
+        <v>2.88</v>
       </c>
       <c r="R35">
-        <v>2.44</v>
+        <v>2.02</v>
       </c>
       <c r="S35">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="T35">
-        <v>3.8</v>
+        <v>2.82</v>
       </c>
       <c r="U35">
-        <v>2.23</v>
+        <v>3.01</v>
       </c>
       <c r="V35">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="W35">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="X35">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y35">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="Z35">
-        <v>6</v>
+        <v>3.08</v>
       </c>
       <c r="AA35">
-        <v>1.44</v>
+        <v>1.97</v>
       </c>
       <c r="AB35">
-        <v>2.43</v>
+        <v>1.78</v>
       </c>
       <c r="AC35">
-        <v>2.2</v>
+        <v>3.28</v>
       </c>
       <c r="AD35">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="AE35">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AF35">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AG35">
-        <v>2.42</v>
+        <v>2</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AK35">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,80 +6177,80 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="O36">
-        <v>3.35</v>
+        <v>3.44</v>
       </c>
       <c r="P36">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="Q36">
         <v>2.88</v>
       </c>
       <c r="R36">
+        <v>2.08</v>
+      </c>
+      <c r="S36">
+        <v>1.33</v>
+      </c>
+      <c r="T36">
+        <v>2.74</v>
+      </c>
+      <c r="U36">
+        <v>2.83</v>
+      </c>
+      <c r="V36">
+        <v>1.4</v>
+      </c>
+      <c r="W36">
+        <v>1.07</v>
+      </c>
+      <c r="X36">
+        <v>1.04</v>
+      </c>
+      <c r="Y36">
+        <v>1.25</v>
+      </c>
+      <c r="Z36">
+        <v>3.8</v>
+      </c>
+      <c r="AA36">
+        <v>1.93</v>
+      </c>
+      <c r="AB36">
+        <v>1.94</v>
+      </c>
+      <c r="AC36">
+        <v>3.1</v>
+      </c>
+      <c r="AD36">
+        <v>1.36</v>
+      </c>
+      <c r="AE36">
+        <v>1.1</v>
+      </c>
+      <c r="AF36">
+        <v>1.67</v>
+      </c>
+      <c r="AG36">
         <v>2.1</v>
       </c>
-      <c r="S36">
-        <v>1.36</v>
-      </c>
-      <c r="T36">
-        <v>2.82</v>
-      </c>
-      <c r="U36">
-        <v>3.01</v>
-      </c>
-      <c r="V36">
-        <v>1.36</v>
-      </c>
-      <c r="W36">
-        <v>1.05</v>
-      </c>
-      <c r="X36">
-        <v>1.05</v>
-      </c>
-      <c r="Y36">
-        <v>1.28</v>
-      </c>
-      <c r="Z36">
-        <v>3.08</v>
-      </c>
-      <c r="AA36">
-        <v>1.97</v>
-      </c>
-      <c r="AB36">
-        <v>1.78</v>
-      </c>
-      <c r="AC36">
-        <v>3.28</v>
-      </c>
-      <c r="AD36">
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ36">
         <v>1.25</v>
       </c>
-      <c r="AE36">
-        <v>1.08</v>
-      </c>
-      <c r="AF36">
-        <v>1.8</v>
-      </c>
-      <c r="AG36">
-        <v>2</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ36">
-        <v>1.33</v>
-      </c>
       <c r="AK36">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.45</v>
+        <v>1.44</v>
       </c>
       <c r="O37">
-        <v>3.44</v>
+        <v>4.85</v>
       </c>
       <c r="P37">
-        <v>2.7</v>
+        <v>7.19</v>
       </c>
       <c r="Q37">
-        <v>3.1</v>
+        <v>1.85</v>
       </c>
       <c r="R37">
-        <v>2.08</v>
+        <v>2.5</v>
       </c>
       <c r="S37">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T37">
-        <v>2.77</v>
+        <v>3.5</v>
       </c>
       <c r="U37">
-        <v>2.77</v>
+        <v>2.22</v>
       </c>
       <c r="V37">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="W37">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X37">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z37">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="AA37">
-        <v>1.87</v>
+        <v>1.52</v>
       </c>
       <c r="AB37">
-        <v>1.98</v>
+        <v>2.21</v>
       </c>
       <c r="AC37">
-        <v>3.1</v>
+        <v>2.42</v>
       </c>
       <c r="AD37">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AE37">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AF37">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG37">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK37">
-        <v>1.5</v>
+        <v>2.91</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6666,22 +6666,22 @@
         </is>
       </c>
       <c r="N39">
+        <v>1.26</v>
+      </c>
+      <c r="O39">
+        <v>6.4</v>
+      </c>
+      <c r="P39">
+        <v>10</v>
+      </c>
+      <c r="Q39">
+        <v>1.61</v>
+      </c>
+      <c r="R39">
+        <v>3.02</v>
+      </c>
+      <c r="S39">
         <v>1.23</v>
-      </c>
-      <c r="O39">
-        <v>5.75</v>
-      </c>
-      <c r="P39">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="Q39">
-        <v>1.6</v>
-      </c>
-      <c r="R39">
-        <v>2.7</v>
-      </c>
-      <c r="S39">
-        <v>1.24</v>
       </c>
       <c r="T39">
         <v>3.9</v>
@@ -6705,10 +6705,10 @@
         <v>6</v>
       </c>
       <c r="AA39">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB39">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="AC39">
         <v>1.97</v>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK39">
         <v>4.15</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.92</v>
+        <v>1.2</v>
       </c>
       <c r="O40">
-        <v>3.9</v>
+        <v>6.8</v>
       </c>
       <c r="P40">
+        <v>13</v>
+      </c>
+      <c r="Q40">
+        <v>1.63</v>
+      </c>
+      <c r="R40">
+        <v>2.56</v>
+      </c>
+      <c r="S40">
+        <v>1.27</v>
+      </c>
+      <c r="T40">
         <v>3.5</v>
       </c>
-      <c r="Q40">
+      <c r="U40">
+        <v>2.29</v>
+      </c>
+      <c r="V40">
+        <v>1.63</v>
+      </c>
+      <c r="W40">
+        <v>1.14</v>
+      </c>
+      <c r="X40">
+        <v>1.02</v>
+      </c>
+      <c r="Y40">
+        <v>1.14</v>
+      </c>
+      <c r="Z40">
+        <v>5</v>
+      </c>
+      <c r="AA40">
+        <v>1.5</v>
+      </c>
+      <c r="AB40">
         <v>2.38</v>
       </c>
-      <c r="R40">
-        <v>2.36</v>
-      </c>
-      <c r="S40">
-        <v>1.25</v>
-      </c>
-      <c r="T40">
-        <v>3.35</v>
-      </c>
-      <c r="U40">
-        <v>2.18</v>
-      </c>
-      <c r="V40">
-        <v>1.65</v>
-      </c>
-      <c r="W40">
-        <v>1.18</v>
-      </c>
-      <c r="X40">
-        <v>1.01</v>
-      </c>
-      <c r="Y40">
-        <v>1.11</v>
-      </c>
-      <c r="Z40">
-        <v>6</v>
-      </c>
-      <c r="AA40">
-        <v>1.46</v>
-      </c>
-      <c r="AB40">
-        <v>2.53</v>
-      </c>
       <c r="AC40">
-        <v>2.15</v>
+        <v>2.42</v>
       </c>
       <c r="AD40">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AE40">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AF40">
-        <v>1.44</v>
+        <v>2.21</v>
       </c>
       <c r="AG40">
-        <v>2.88</v>
+        <v>1.61</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AK40">
-        <v>1.93</v>
+        <v>4</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.23</v>
+        <v>17</v>
       </c>
       <c r="O41">
-        <v>6.5</v>
+        <v>14</v>
       </c>
       <c r="P41">
-        <v>11</v>
+        <v>1.12</v>
       </c>
       <c r="Q41">
-        <v>1.63</v>
+        <v>10.7</v>
       </c>
       <c r="R41">
-        <v>2.54</v>
+        <v>4.45</v>
       </c>
       <c r="S41">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="T41">
-        <v>3.6</v>
+        <v>7</v>
       </c>
       <c r="U41">
-        <v>2.25</v>
+        <v>1.49</v>
       </c>
       <c r="V41">
-        <v>1.6</v>
+        <v>2.31</v>
       </c>
       <c r="W41">
+        <v>1.46</v>
+      </c>
+      <c r="X41">
+        <v>1</v>
+      </c>
+      <c r="Y41">
+        <v>1.01</v>
+      </c>
+      <c r="Z41">
+        <v>13</v>
+      </c>
+      <c r="AA41">
         <v>1.11</v>
       </c>
-      <c r="X41">
-        <v>1.03</v>
-      </c>
-      <c r="Y41">
-        <v>1.14</v>
-      </c>
-      <c r="Z41">
-        <v>5</v>
-      </c>
-      <c r="AA41">
-        <v>1.64</v>
-      </c>
       <c r="AB41">
-        <v>2.37</v>
+        <v>5.25</v>
       </c>
       <c r="AC41">
-        <v>2.44</v>
+        <v>1.37</v>
       </c>
       <c r="AD41">
-        <v>1.56</v>
+        <v>2.8</v>
       </c>
       <c r="AE41">
-        <v>1.18</v>
+        <v>1.89</v>
       </c>
       <c r="AF41">
-        <v>2.17</v>
+        <v>1.65</v>
       </c>
       <c r="AG41">
-        <v>1.63</v>
+        <v>2.08</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.14</v>
+        <v>8.6</v>
       </c>
       <c r="AK41">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,37 +7155,37 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O42">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="P42">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="Q42">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="R42">
         <v>2.4</v>
       </c>
       <c r="S42">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T42">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="U42">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="V42">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="W42">
         <v>1.11</v>
       </c>
       <c r="X42">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
         <v>1.14</v>
@@ -7194,13 +7194,13 @@
         <v>5</v>
       </c>
       <c r="AA42">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="AB42">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="AC42">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="AD42">
         <v>1.5</v>
@@ -7209,10 +7209,10 @@
         <v>1.18</v>
       </c>
       <c r="AF42">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AG42">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AK42">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>20</v>
+        <v>1.92</v>
       </c>
       <c r="O43">
-        <v>13.5</v>
+        <v>3.7</v>
       </c>
       <c r="P43">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="Q43">
-        <v>12.17</v>
+        <v>2.31</v>
       </c>
       <c r="R43">
-        <v>4.47</v>
+        <v>2.37</v>
       </c>
       <c r="S43">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="T43">
-        <v>7</v>
+        <v>3.35</v>
       </c>
       <c r="U43">
-        <v>1.49</v>
+        <v>2.18</v>
       </c>
       <c r="V43">
-        <v>2.29</v>
+        <v>1.66</v>
       </c>
       <c r="W43">
+        <v>1.18</v>
+      </c>
+      <c r="X43">
+        <v>1.01</v>
+      </c>
+      <c r="Y43">
+        <v>1.11</v>
+      </c>
+      <c r="Z43">
+        <v>6</v>
+      </c>
+      <c r="AA43">
+        <v>1.53</v>
+      </c>
+      <c r="AB43">
+        <v>2.53</v>
+      </c>
+      <c r="AC43">
+        <v>2.2</v>
+      </c>
+      <c r="AD43">
+        <v>1.62</v>
+      </c>
+      <c r="AE43">
+        <v>1.25</v>
+      </c>
+      <c r="AF43">
         <v>1.44</v>
       </c>
-      <c r="X43">
-        <v>1</v>
-      </c>
-      <c r="Y43">
-        <v>1.01</v>
-      </c>
-      <c r="Z43">
-        <v>13</v>
-      </c>
-      <c r="AA43">
-        <v>1.11</v>
-      </c>
-      <c r="AB43">
-        <v>4.95</v>
-      </c>
-      <c r="AC43">
-        <v>1.36</v>
-      </c>
-      <c r="AD43">
-        <v>3</v>
-      </c>
-      <c r="AE43">
-        <v>1.9</v>
-      </c>
-      <c r="AF43">
-        <v>1.65</v>
-      </c>
       <c r="AG43">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="AK43">
-        <v>1</v>
+        <v>1.93</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="N44">
-        <v>6.6</v>
+        <v>9.5</v>
       </c>
       <c r="O44">
         <v>6.7</v>
@@ -7538,7 +7538,7 @@
         <v>1.44</v>
       </c>
       <c r="AG44">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>3.92</v>
       </c>
       <c r="AK44">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,19 +7644,19 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.75</v>
+        <v>1.97</v>
       </c>
       <c r="O45">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="P45">
-        <v>3.63</v>
+        <v>3.9</v>
       </c>
       <c r="Q45">
-        <v>2.32</v>
+        <v>2.21</v>
       </c>
       <c r="R45">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="S45">
         <v>1.17</v>
@@ -7717,7 +7717,7 @@
         <v>1.15</v>
       </c>
       <c r="AK45">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,40 +7807,40 @@
         </is>
       </c>
       <c r="N46">
-        <v>3.2</v>
+        <v>1.64</v>
       </c>
       <c r="O46">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="P46">
-        <v>2</v>
+        <v>5.56</v>
       </c>
       <c r="Q46">
-        <v>3.61</v>
+        <v>2.12</v>
       </c>
       <c r="R46">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="S46">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T46">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U46">
-        <v>2.4</v>
+        <v>2.61</v>
       </c>
       <c r="V46">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="W46">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X46">
         <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z46">
         <v>4.33</v>
@@ -7849,22 +7849,22 @@
         <v>1.69</v>
       </c>
       <c r="AB46">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AC46">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AD46">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AE46">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF46">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="AG46">
-        <v>2.18</v>
+        <v>1.99</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.8</v>
+        <v>1.17</v>
       </c>
       <c r="AK46">
-        <v>1.27</v>
+        <v>2.25</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="O47">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="P47">
-        <v>5.56</v>
+        <v>2.05</v>
       </c>
       <c r="Q47">
-        <v>2.12</v>
+        <v>3.61</v>
       </c>
       <c r="R47">
+        <v>2.2</v>
+      </c>
+      <c r="S47">
+        <v>1.29</v>
+      </c>
+      <c r="T47">
+        <v>3.4</v>
+      </c>
+      <c r="U47">
         <v>2.4</v>
       </c>
-      <c r="S47">
-        <v>1.3</v>
-      </c>
-      <c r="T47">
-        <v>3.6</v>
-      </c>
-      <c r="U47">
-        <v>2.61</v>
-      </c>
       <c r="V47">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="W47">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X47">
         <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z47">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA47">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AB47">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AC47">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AD47">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AE47">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF47">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AG47">
-        <v>1.99</v>
+        <v>2.18</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="AK47">
-        <v>2.25</v>
+        <v>1.27</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8136,77 +8136,77 @@
         <v>1.95</v>
       </c>
       <c r="O48">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="P48">
-        <v>3.99</v>
+        <v>3.9</v>
       </c>
       <c r="Q48">
-        <v>2.31</v>
+        <v>2.05</v>
       </c>
       <c r="R48">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="S48">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="T48">
+        <v>2.29</v>
+      </c>
+      <c r="U48">
+        <v>3.44</v>
+      </c>
+      <c r="V48">
+        <v>1.23</v>
+      </c>
+      <c r="W48">
+        <v>1.04</v>
+      </c>
+      <c r="X48">
+        <v>1.07</v>
+      </c>
+      <c r="Y48">
+        <v>1.47</v>
+      </c>
+      <c r="Z48">
+        <v>2.63</v>
+      </c>
+      <c r="AA48">
+        <v>2.35</v>
+      </c>
+      <c r="AB48">
+        <v>1.5</v>
+      </c>
+      <c r="AC48">
+        <v>5</v>
+      </c>
+      <c r="AD48">
+        <v>1.17</v>
+      </c>
+      <c r="AE48">
+        <v>1.03</v>
+      </c>
+      <c r="AF48">
+        <v>2.45</v>
+      </c>
+      <c r="AG48">
+        <v>1.46</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ48">
+        <v>1.21</v>
+      </c>
+      <c r="AK48">
         <v>2.27</v>
-      </c>
-      <c r="U48">
-        <v>3.58</v>
-      </c>
-      <c r="V48">
-        <v>1.21</v>
-      </c>
-      <c r="W48">
-        <v>1.03</v>
-      </c>
-      <c r="X48">
-        <v>1.08</v>
-      </c>
-      <c r="Y48">
-        <v>1.5</v>
-      </c>
-      <c r="Z48">
-        <v>2.55</v>
-      </c>
-      <c r="AA48">
-        <v>2.49</v>
-      </c>
-      <c r="AB48">
-        <v>1.47</v>
-      </c>
-      <c r="AC48">
-        <v>5.5</v>
-      </c>
-      <c r="AD48">
-        <v>1.14</v>
-      </c>
-      <c r="AE48">
-        <v>1.02</v>
-      </c>
-      <c r="AF48">
-        <v>2.4</v>
-      </c>
-      <c r="AG48">
-        <v>1.5</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ48">
-        <v>1.24</v>
-      </c>
-      <c r="AK48">
-        <v>2.03</v>
       </c>
       <c r="AL48">
         <v>0</v>

--- a/jogos_2026-10-13.xlsx
+++ b/jogos_2026-10-13.xlsx
@@ -635,10 +635,10 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O2">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P2">
         <v>3.2</v>
@@ -650,7 +650,7 @@
         <v>2.09</v>
       </c>
       <c r="S2">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T2">
         <v>2.73</v>
@@ -674,10 +674,10 @@
         <v>3.28</v>
       </c>
       <c r="AA2">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AB2">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AC2">
         <v>3.2</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,43 +1124,43 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="O5">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="P5">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="Q5">
-        <v>3.38</v>
+        <v>2.82</v>
       </c>
       <c r="R5">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="S5">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="T5">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="U5">
-        <v>3.52</v>
+        <v>3.85</v>
       </c>
       <c r="V5">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="W5">
         <v>1.02</v>
       </c>
       <c r="X5">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y5">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="Z5">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="AA5">
         <v>2.74</v>
@@ -1169,19 +1169,19 @@
         <v>1.35</v>
       </c>
       <c r="AC5">
-        <v>5.55</v>
+        <v>5.75</v>
       </c>
       <c r="AD5">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AE5">
         <v>1.01</v>
       </c>
       <c r="AF5">
-        <v>2.23</v>
+        <v>2.32</v>
       </c>
       <c r="AG5">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK5">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,43 +1287,43 @@
         </is>
       </c>
       <c r="N6">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="O6">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="P6">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="Q6">
-        <v>2.82</v>
+        <v>3.38</v>
       </c>
       <c r="R6">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="S6">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="T6">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="U6">
-        <v>3.85</v>
+        <v>3.52</v>
       </c>
       <c r="V6">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="W6">
         <v>1.02</v>
       </c>
       <c r="X6">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y6">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Z6">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AA6">
         <v>2.74</v>
@@ -1332,19 +1332,19 @@
         <v>1.35</v>
       </c>
       <c r="AC6">
-        <v>5.75</v>
+        <v>5.55</v>
       </c>
       <c r="AD6">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AE6">
         <v>1.01</v>
       </c>
       <c r="AF6">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="AG6">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AK6">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="O10">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="P10">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="Q10">
         <v>2.4</v>
@@ -1963,7 +1963,7 @@
         <v>2.73</v>
       </c>
       <c r="V10">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W10">
         <v>1.05</v>
@@ -1975,16 +1975,16 @@
         <v>1.3</v>
       </c>
       <c r="Z10">
-        <v>2.97</v>
+        <v>3.24</v>
       </c>
       <c r="AA10">
         <v>2</v>
       </c>
       <c r="AB10">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC10">
-        <v>3.66</v>
+        <v>3.72</v>
       </c>
       <c r="AD10">
         <v>1.27</v>
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="N13">
-        <v>4.25</v>
+        <v>4.9</v>
       </c>
       <c r="O13">
         <v>4.05</v>
@@ -2437,7 +2437,7 @@
         <v>1.66</v>
       </c>
       <c r="Q13">
-        <v>3.75</v>
+        <v>3.41</v>
       </c>
       <c r="R13">
         <v>2.2</v>
@@ -2446,16 +2446,16 @@
         <v>1.18</v>
       </c>
       <c r="T13">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="U13">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="V13">
         <v>1.5</v>
       </c>
       <c r="W13">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X13">
         <v>1.01</v>
@@ -2467,13 +2467,13 @@
         <v>4.8</v>
       </c>
       <c r="AA13">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AB13">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="AC13">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AD13">
         <v>1.62</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AK13">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -3572,13 +3572,13 @@
         <v>1.18</v>
       </c>
       <c r="O20">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="P20">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q20">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="R20">
         <v>2.96</v>
@@ -3617,7 +3617,7 @@
         <v>1.99</v>
       </c>
       <c r="AD20">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AE20">
         <v>1.3</v>
@@ -3732,7 +3732,7 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="O21">
         <v>3.4</v>
@@ -3744,7 +3744,7 @@
         <v>2.9</v>
       </c>
       <c r="R21">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="S21">
         <v>1.25</v>
@@ -3753,7 +3753,7 @@
         <v>3.5</v>
       </c>
       <c r="U21">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="V21">
         <v>1.55</v>
@@ -3768,19 +3768,19 @@
         <v>1.2</v>
       </c>
       <c r="Z21">
-        <v>4.5</v>
+        <v>4.49</v>
       </c>
       <c r="AA21">
         <v>1.66</v>
       </c>
       <c r="AB21">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AC21">
         <v>2.63</v>
       </c>
       <c r="AD21">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AE21">
         <v>1.2</v>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK21">
         <v>1.45</v>
@@ -3904,10 +3904,10 @@
         <v>2.2</v>
       </c>
       <c r="Q22">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="R22">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="S22">
         <v>1.25</v>
@@ -3919,7 +3919,7 @@
         <v>2.15</v>
       </c>
       <c r="V22">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="W22">
         <v>1.14</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.91</v>
+        <v>1.48</v>
       </c>
       <c r="O23">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="P23">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q23">
-        <v>2.9</v>
+        <v>1.91</v>
       </c>
       <c r="R23">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="S23">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="T23">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="U23">
-        <v>1.91</v>
+        <v>2.26</v>
       </c>
       <c r="V23">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="W23">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z23">
-        <v>7.5</v>
+        <v>4.9</v>
       </c>
       <c r="AA23">
-        <v>1.31</v>
+        <v>1.57</v>
       </c>
       <c r="AB23">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="AC23">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="AD23">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="AE23">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AF23">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="AG23">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.73</v>
+        <v>1.14</v>
       </c>
       <c r="AK23">
-        <v>1.31</v>
+        <v>2.45</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.48</v>
+        <v>2.91</v>
       </c>
       <c r="O24">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="P24">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="Q24">
+        <v>2.91</v>
+      </c>
+      <c r="R24">
+        <v>2.49</v>
+      </c>
+      <c r="S24">
+        <v>1.13</v>
+      </c>
+      <c r="T24">
+        <v>4.5</v>
+      </c>
+      <c r="U24">
         <v>1.91</v>
       </c>
-      <c r="R24">
-        <v>2.5</v>
-      </c>
-      <c r="S24">
-        <v>1.22</v>
-      </c>
-      <c r="T24">
-        <v>3.75</v>
-      </c>
-      <c r="U24">
-        <v>2.26</v>
-      </c>
       <c r="V24">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="W24">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X24">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z24">
-        <v>4.92</v>
+        <v>6.5</v>
       </c>
       <c r="AA24">
-        <v>1.57</v>
+        <v>1.31</v>
       </c>
       <c r="AB24">
-        <v>2.38</v>
+        <v>3.1</v>
       </c>
       <c r="AC24">
-        <v>2.36</v>
+        <v>1.9</v>
       </c>
       <c r="AD24">
-        <v>1.57</v>
+        <v>1.87</v>
       </c>
       <c r="AE24">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AF24">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AG24">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.14</v>
+        <v>1.67</v>
       </c>
       <c r="AK24">
-        <v>2.45</v>
+        <v>1.31</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4390,13 +4390,13 @@
         <v>3.9</v>
       </c>
       <c r="P25">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="Q25">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="R25">
-        <v>2.43</v>
+        <v>2.39</v>
       </c>
       <c r="S25">
         <v>1.19</v>
@@ -4426,13 +4426,13 @@
         <v>1.33</v>
       </c>
       <c r="AB25">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="AC25">
         <v>2.2</v>
       </c>
       <c r="AD25">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AE25">
         <v>1.25</v>
@@ -4457,7 +4457,7 @@
         <v>1.17</v>
       </c>
       <c r="AK25">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4553,7 +4553,7 @@
         <v>3.85</v>
       </c>
       <c r="P26">
-        <v>4.5</v>
+        <v>4.29</v>
       </c>
       <c r="Q26">
         <v>2.05</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,80 +4710,80 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.16</v>
+        <v>2.06</v>
       </c>
       <c r="O27">
-        <v>5.55</v>
+        <v>2.87</v>
       </c>
       <c r="P27">
-        <v>13</v>
+        <v>3.25</v>
       </c>
       <c r="Q27">
-        <v>1.62</v>
+        <v>2.88</v>
       </c>
       <c r="R27">
-        <v>2.6</v>
+        <v>1.91</v>
       </c>
       <c r="S27">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="T27">
-        <v>2.9</v>
+        <v>2.31</v>
       </c>
       <c r="U27">
-        <v>2.72</v>
+        <v>3.5</v>
       </c>
       <c r="V27">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="W27">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y27">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="Z27">
-        <v>3.2</v>
+        <v>2.63</v>
       </c>
       <c r="AA27">
-        <v>1.9</v>
+        <v>2.55</v>
       </c>
       <c r="AB27">
-        <v>1.9</v>
+        <v>1.45</v>
       </c>
       <c r="AC27">
-        <v>3.08</v>
+        <v>4.9</v>
       </c>
       <c r="AD27">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AE27">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF27">
-        <v>3.18</v>
+        <v>2.05</v>
       </c>
       <c r="AG27">
+        <v>1.73</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
         <v>1.33</v>
       </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>1.07</v>
-      </c>
       <c r="AK27">
-        <v>4.1</v>
+        <v>1.57</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,25 +5036,25 @@
         </is>
       </c>
       <c r="N29">
-        <v>8.5</v>
+        <v>1.16</v>
       </c>
       <c r="O29">
-        <v>4.8</v>
+        <v>5.55</v>
       </c>
       <c r="P29">
-        <v>1.28</v>
+        <v>13</v>
       </c>
       <c r="Q29">
-        <v>9.300000000000001</v>
+        <v>1.62</v>
       </c>
       <c r="R29">
-        <v>2.29</v>
+        <v>2.6</v>
       </c>
       <c r="S29">
         <v>1.36</v>
       </c>
       <c r="T29">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="U29">
         <v>2.72</v>
@@ -5069,31 +5069,31 @@
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z29">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AA29">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AB29">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AC29">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="AD29">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE29">
         <v>1.07</v>
       </c>
       <c r="AF29">
-        <v>2.45</v>
+        <v>3.18</v>
       </c>
       <c r="AG29">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AK29">
-        <v>1.06</v>
+        <v>4.1</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,80 +5199,80 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.06</v>
+        <v>8.5</v>
       </c>
       <c r="O30">
-        <v>2.87</v>
+        <v>4.8</v>
       </c>
       <c r="P30">
-        <v>3.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q30">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="R30">
+        <v>2.29</v>
+      </c>
+      <c r="S30">
+        <v>1.36</v>
+      </c>
+      <c r="T30">
         <v>2.88</v>
       </c>
-      <c r="R30">
-        <v>1.91</v>
-      </c>
-      <c r="S30">
-        <v>1.52</v>
-      </c>
-      <c r="T30">
-        <v>2.31</v>
-      </c>
       <c r="U30">
-        <v>3.5</v>
+        <v>2.72</v>
       </c>
       <c r="V30">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="W30">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X30">
+        <v>1.01</v>
+      </c>
+      <c r="Y30">
+        <v>1.29</v>
+      </c>
+      <c r="Z30">
+        <v>3.14</v>
+      </c>
+      <c r="AA30">
+        <v>1.88</v>
+      </c>
+      <c r="AB30">
+        <v>1.79</v>
+      </c>
+      <c r="AC30">
+        <v>3.3</v>
+      </c>
+      <c r="AD30">
+        <v>1.29</v>
+      </c>
+      <c r="AE30">
+        <v>1.07</v>
+      </c>
+      <c r="AF30">
+        <v>2.45</v>
+      </c>
+      <c r="AG30">
+        <v>1.45</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30">
+        <v>1.2</v>
+      </c>
+      <c r="AK30">
         <v>1.06</v>
-      </c>
-      <c r="Y30">
-        <v>1.47</v>
-      </c>
-      <c r="Z30">
-        <v>2.63</v>
-      </c>
-      <c r="AA30">
-        <v>2.55</v>
-      </c>
-      <c r="AB30">
-        <v>1.45</v>
-      </c>
-      <c r="AC30">
-        <v>4.9</v>
-      </c>
-      <c r="AD30">
-        <v>1.17</v>
-      </c>
-      <c r="AE30">
-        <v>1.04</v>
-      </c>
-      <c r="AF30">
-        <v>2.05</v>
-      </c>
-      <c r="AG30">
-        <v>1.73</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ30">
-        <v>1.33</v>
-      </c>
-      <c r="AK30">
-        <v>1.57</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5365,10 +5365,10 @@
         <v>1.55</v>
       </c>
       <c r="O31">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P31">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="Q31">
         <v>2.11</v>
@@ -5389,16 +5389,16 @@
         <v>1.32</v>
       </c>
       <c r="W31">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X31">
         <v>1.03</v>
       </c>
       <c r="Y31">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Z31">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="AA31">
         <v>2.15</v>
@@ -5531,7 +5531,7 @@
         <v>3.55</v>
       </c>
       <c r="P32">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="Q32">
         <v>4.24</v>
@@ -5552,7 +5552,7 @@
         <v>1.4</v>
       </c>
       <c r="W32">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X32">
         <v>1.04</v>
@@ -5564,7 +5564,7 @@
         <v>3.5</v>
       </c>
       <c r="AA32">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB32">
         <v>1.8</v>
@@ -5688,7 +5688,7 @@
         </is>
       </c>
       <c r="N33">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O33">
         <v>3.4</v>
@@ -5697,7 +5697,7 @@
         <v>3.66</v>
       </c>
       <c r="Q33">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="R33">
         <v>2.1</v>
@@ -5706,7 +5706,7 @@
         <v>1.36</v>
       </c>
       <c r="T33">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="U33">
         <v>2.7</v>
@@ -5721,16 +5721,16 @@
         <v>1.04</v>
       </c>
       <c r="Y33">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z33">
         <v>3.5</v>
       </c>
       <c r="AA33">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="AB33">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AC33">
         <v>3.25</v>
@@ -5872,10 +5872,10 @@
         <v>3.8</v>
       </c>
       <c r="U34">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="V34">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="W34">
         <v>1.15</v>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O35">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="P35">
         <v>3.1</v>
@@ -6026,7 +6026,7 @@
         <v>2.88</v>
       </c>
       <c r="R35">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="S35">
         <v>1.36</v>
@@ -6050,13 +6050,13 @@
         <v>1.28</v>
       </c>
       <c r="Z35">
-        <v>3.08</v>
+        <v>3.42</v>
       </c>
       <c r="AA35">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AB35">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AC35">
         <v>3.28</v>
@@ -6189,13 +6189,13 @@
         <v>2.88</v>
       </c>
       <c r="R36">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="S36">
         <v>1.33</v>
       </c>
       <c r="T36">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="U36">
         <v>2.83</v>
@@ -6349,7 +6349,7 @@
         <v>7.19</v>
       </c>
       <c r="Q37">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="R37">
         <v>2.5</v>
@@ -6361,7 +6361,7 @@
         <v>3.5</v>
       </c>
       <c r="U37">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="V37">
         <v>1.57</v>
@@ -6385,7 +6385,7 @@
         <v>2.21</v>
       </c>
       <c r="AC37">
-        <v>2.42</v>
+        <v>2.59</v>
       </c>
       <c r="AD37">
         <v>1.5</v>
@@ -6509,7 +6509,7 @@
         <v>4</v>
       </c>
       <c r="P38">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="Q38">
         <v>2.16</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>17</v>
+        <v>2.15</v>
       </c>
       <c r="O41">
-        <v>14</v>
+        <v>3.6</v>
       </c>
       <c r="P41">
-        <v>1.12</v>
+        <v>3.1</v>
       </c>
       <c r="Q41">
-        <v>10.7</v>
+        <v>2.65</v>
       </c>
       <c r="R41">
-        <v>4.45</v>
+        <v>2.4</v>
       </c>
       <c r="S41">
-        <v>1.1</v>
+        <v>1.31</v>
       </c>
       <c r="T41">
-        <v>7</v>
+        <v>3.42</v>
       </c>
       <c r="U41">
-        <v>1.49</v>
+        <v>2.38</v>
       </c>
       <c r="V41">
-        <v>2.31</v>
+        <v>1.58</v>
       </c>
       <c r="W41">
-        <v>1.46</v>
+        <v>1.11</v>
       </c>
       <c r="X41">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="Z41">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AA41">
-        <v>1.11</v>
+        <v>1.61</v>
       </c>
       <c r="AB41">
-        <v>5.25</v>
+        <v>2.38</v>
       </c>
       <c r="AC41">
-        <v>1.37</v>
+        <v>2.47</v>
       </c>
       <c r="AD41">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="AE41">
-        <v>1.89</v>
+        <v>1.18</v>
       </c>
       <c r="AF41">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AG41">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>8.6</v>
+        <v>1.29</v>
       </c>
       <c r="AK41">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="O42">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P42">
         <v>3.1</v>
       </c>
       <c r="Q42">
-        <v>2.65</v>
+        <v>2.31</v>
       </c>
       <c r="R42">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="S42">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T42">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="U42">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="V42">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="W42">
+        <v>1.18</v>
+      </c>
+      <c r="X42">
+        <v>1.01</v>
+      </c>
+      <c r="Y42">
         <v>1.11</v>
       </c>
-      <c r="X42">
-        <v>1.02</v>
-      </c>
-      <c r="Y42">
-        <v>1.14</v>
-      </c>
       <c r="Z42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA42">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AB42">
-        <v>2.38</v>
+        <v>2.53</v>
       </c>
       <c r="AC42">
-        <v>2.47</v>
+        <v>2.2</v>
       </c>
       <c r="AD42">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AE42">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AF42">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG42">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AK42">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.92</v>
+        <v>17</v>
       </c>
       <c r="O43">
-        <v>3.7</v>
+        <v>14</v>
       </c>
       <c r="P43">
-        <v>3.1</v>
+        <v>1.12</v>
       </c>
       <c r="Q43">
+        <v>10.7</v>
+      </c>
+      <c r="R43">
+        <v>4.45</v>
+      </c>
+      <c r="S43">
+        <v>1.1</v>
+      </c>
+      <c r="T43">
+        <v>7</v>
+      </c>
+      <c r="U43">
+        <v>1.49</v>
+      </c>
+      <c r="V43">
         <v>2.31</v>
       </c>
-      <c r="R43">
-        <v>2.37</v>
-      </c>
-      <c r="S43">
-        <v>1.25</v>
-      </c>
-      <c r="T43">
-        <v>3.35</v>
-      </c>
-      <c r="U43">
-        <v>2.18</v>
-      </c>
-      <c r="V43">
-        <v>1.66</v>
-      </c>
       <c r="W43">
-        <v>1.18</v>
+        <v>1.46</v>
       </c>
       <c r="X43">
+        <v>1</v>
+      </c>
+      <c r="Y43">
         <v>1.01</v>
       </c>
-      <c r="Y43">
+      <c r="Z43">
+        <v>13</v>
+      </c>
+      <c r="AA43">
         <v>1.11</v>
       </c>
-      <c r="Z43">
-        <v>6</v>
-      </c>
-      <c r="AA43">
-        <v>1.53</v>
-      </c>
       <c r="AB43">
-        <v>2.53</v>
+        <v>5.25</v>
       </c>
       <c r="AC43">
-        <v>2.2</v>
+        <v>1.37</v>
       </c>
       <c r="AD43">
-        <v>1.62</v>
+        <v>2.8</v>
       </c>
       <c r="AE43">
-        <v>1.25</v>
+        <v>1.89</v>
       </c>
       <c r="AF43">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AG43">
-        <v>2.8</v>
+        <v>2.08</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.19</v>
+        <v>8.6</v>
       </c>
       <c r="AK43">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7807,19 +7807,19 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="O46">
         <v>4</v>
       </c>
       <c r="P46">
-        <v>5.56</v>
+        <v>5.25</v>
       </c>
       <c r="Q46">
         <v>2.12</v>
       </c>
       <c r="R46">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S46">
         <v>1.3</v>
@@ -7828,7 +7828,7 @@
         <v>3.3</v>
       </c>
       <c r="U46">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="V46">
         <v>1.49</v>
@@ -7840,7 +7840,7 @@
         <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z46">
         <v>4.33</v>
@@ -7852,10 +7852,10 @@
         <v>2.1</v>
       </c>
       <c r="AC46">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AD46">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AE46">
         <v>1.12</v>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK46">
         <v>2.25</v>
@@ -7970,7 +7970,7 @@
         </is>
       </c>
       <c r="N47">
-        <v>3.4</v>
+        <v>3.43</v>
       </c>
       <c r="O47">
         <v>3.75</v>
@@ -7979,10 +7979,10 @@
         <v>2.05</v>
       </c>
       <c r="Q47">
-        <v>3.61</v>
+        <v>3.62</v>
       </c>
       <c r="R47">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="S47">
         <v>1.29</v>
@@ -8305,7 +8305,7 @@
         <v>1.73</v>
       </c>
       <c r="Q49">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="R49">
         <v>1.91</v>
@@ -8335,7 +8335,7 @@
         <v>2.48</v>
       </c>
       <c r="AA49">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="AB49">
         <v>1.47</v>
@@ -8350,7 +8350,7 @@
         <v>1.02</v>
       </c>
       <c r="AF49">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG49">
         <v>1.73</v>

--- a/jogos_2026-10-13.xlsx
+++ b/jogos_2026-10-13.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O2">
         <v>3.3</v>
@@ -647,19 +647,19 @@
         <v>2.5</v>
       </c>
       <c r="R2">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="S2">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T2">
         <v>2.73</v>
       </c>
       <c r="U2">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="V2">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W2">
         <v>1.1</v>
@@ -674,10 +674,10 @@
         <v>3.28</v>
       </c>
       <c r="AA2">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AB2">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AC2">
         <v>3.2</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK2">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,10 +798,10 @@
         </is>
       </c>
       <c r="N3">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O3">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P3">
         <v>1.7</v>
@@ -1290,7 +1290,7 @@
         <v>2.6</v>
       </c>
       <c r="O6">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="P6">
         <v>2.7</v>
@@ -1945,25 +1945,25 @@
         <v>3.15</v>
       </c>
       <c r="P10">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q10">
         <v>2.4</v>
       </c>
       <c r="R10">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="S10">
         <v>1.36</v>
       </c>
       <c r="T10">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="U10">
         <v>2.73</v>
       </c>
       <c r="V10">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W10">
         <v>1.05</v>
@@ -1978,7 +1978,7 @@
         <v>3.24</v>
       </c>
       <c r="AA10">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB10">
         <v>1.75</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AK10">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2111,7 +2111,7 @@
         <v>3</v>
       </c>
       <c r="Q11">
-        <v>2.61</v>
+        <v>2.4</v>
       </c>
       <c r="R11">
         <v>2.25</v>
@@ -2265,16 +2265,16 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="O12">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P12">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q12">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="R12">
         <v>2.59</v>
@@ -2283,13 +2283,13 @@
         <v>1.2</v>
       </c>
       <c r="T12">
-        <v>4.45</v>
+        <v>4.33</v>
       </c>
       <c r="U12">
         <v>2.04</v>
       </c>
       <c r="V12">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="W12">
         <v>1.2</v>
@@ -2307,7 +2307,7 @@
         <v>1.33</v>
       </c>
       <c r="AB12">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AC12">
         <v>1.9</v>
@@ -2322,7 +2322,7 @@
         <v>1.33</v>
       </c>
       <c r="AG12">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK12">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>1.66</v>
       </c>
       <c r="Q13">
-        <v>3.41</v>
+        <v>3.68</v>
       </c>
       <c r="R13">
         <v>2.2</v>
@@ -2449,13 +2449,13 @@
         <v>3.7</v>
       </c>
       <c r="U13">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="V13">
         <v>1.5</v>
       </c>
       <c r="W13">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X13">
         <v>1.01</v>
@@ -2467,16 +2467,16 @@
         <v>4.8</v>
       </c>
       <c r="AA13">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AB13">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AC13">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AD13">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AE13">
         <v>1.25</v>
@@ -2603,7 +2603,7 @@
         <v>1.95</v>
       </c>
       <c r="R14">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="S14">
         <v>1.29</v>
@@ -2612,43 +2612,43 @@
         <v>2.39</v>
       </c>
       <c r="U14">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V14">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W14">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X14">
         <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z14">
-        <v>4.15</v>
+        <v>3.96</v>
       </c>
       <c r="AA14">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AB14">
         <v>2.1</v>
       </c>
       <c r="AC14">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="AD14">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AE14">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF14">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG14">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AK14">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3569,19 +3569,19 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="O20">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="P20">
         <v>11</v>
       </c>
       <c r="Q20">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="R20">
-        <v>2.96</v>
+        <v>3.01</v>
       </c>
       <c r="S20">
         <v>1.2</v>
@@ -3590,13 +3590,13 @@
         <v>4.5</v>
       </c>
       <c r="U20">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="V20">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="W20">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X20">
         <v>1.01</v>
@@ -3608,25 +3608,25 @@
         <v>6.5</v>
       </c>
       <c r="AA20">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB20">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AC20">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AD20">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AE20">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AF20">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AG20">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>1.1</v>
       </c>
       <c r="AK20">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3738,28 +3738,28 @@
         <v>3.4</v>
       </c>
       <c r="P21">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="Q21">
         <v>2.9</v>
       </c>
       <c r="R21">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="S21">
         <v>1.25</v>
       </c>
       <c r="T21">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U21">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="V21">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="W21">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X21">
         <v>1.01</v>
@@ -3768,19 +3768,19 @@
         <v>1.2</v>
       </c>
       <c r="Z21">
-        <v>4.49</v>
+        <v>4.63</v>
       </c>
       <c r="AA21">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB21">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AC21">
         <v>2.63</v>
       </c>
       <c r="AD21">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AE21">
         <v>1.2</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK21">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="O22">
         <v>3.75</v>
@@ -3904,13 +3904,13 @@
         <v>2.2</v>
       </c>
       <c r="Q22">
-        <v>3</v>
+        <v>3.34</v>
       </c>
       <c r="R22">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="S22">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T22">
         <v>3.5</v>
@@ -3919,7 +3919,7 @@
         <v>2.15</v>
       </c>
       <c r="V22">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W22">
         <v>1.14</v>
@@ -3928,25 +3928,25 @@
         <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z22">
-        <v>4.78</v>
+        <v>4.82</v>
       </c>
       <c r="AA22">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AB22">
         <v>2.28</v>
       </c>
       <c r="AC22">
-        <v>2</v>
+        <v>2.49</v>
       </c>
       <c r="AD22">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AE22">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF22">
         <v>1.44</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK22">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4079,7 +4079,7 @@
         <v>3.75</v>
       </c>
       <c r="U23">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="V23">
         <v>1.65</v>
@@ -4094,7 +4094,7 @@
         <v>1.14</v>
       </c>
       <c r="Z23">
-        <v>4.9</v>
+        <v>4.96</v>
       </c>
       <c r="AA23">
         <v>1.57</v>
@@ -4230,7 +4230,7 @@
         <v>2.1</v>
       </c>
       <c r="Q24">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="R24">
         <v>2.49</v>
@@ -4245,7 +4245,7 @@
         <v>1.91</v>
       </c>
       <c r="V24">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="W24">
         <v>1.15</v>
@@ -4384,22 +4384,22 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="O25">
         <v>3.9</v>
       </c>
       <c r="P25">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="Q25">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="R25">
-        <v>2.39</v>
+        <v>2.43</v>
       </c>
       <c r="S25">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="T25">
         <v>2.9</v>
@@ -4426,7 +4426,7 @@
         <v>1.33</v>
       </c>
       <c r="AB25">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AC25">
         <v>2.2</v>
@@ -4457,7 +4457,7 @@
         <v>1.17</v>
       </c>
       <c r="AK25">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4553,10 +4553,10 @@
         <v>3.85</v>
       </c>
       <c r="P26">
-        <v>4.29</v>
+        <v>4.5</v>
       </c>
       <c r="Q26">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="R26">
         <v>2.2</v>
@@ -4577,19 +4577,19 @@
         <v>1.1</v>
       </c>
       <c r="X26">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
         <v>1.21</v>
       </c>
       <c r="Z26">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AA26">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB26">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AC26">
         <v>2.92</v>
@@ -4620,7 +4620,7 @@
         <v>1.18</v>
       </c>
       <c r="AK26">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.06</v>
+        <v>1.7</v>
       </c>
       <c r="O27">
-        <v>2.87</v>
+        <v>3.25</v>
       </c>
       <c r="P27">
-        <v>3.25</v>
+        <v>4.9</v>
       </c>
       <c r="Q27">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="R27">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="S27">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="T27">
-        <v>2.31</v>
+        <v>2.63</v>
       </c>
       <c r="U27">
-        <v>3.5</v>
+        <v>3.18</v>
       </c>
       <c r="V27">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W27">
         <v>1.04</v>
       </c>
       <c r="X27">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y27">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="Z27">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AA27">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AB27">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AC27">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="AD27">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE27">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF27">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AG27">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AK27">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,28 +4873,28 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.7</v>
+        <v>2.06</v>
       </c>
       <c r="O28">
-        <v>3.3</v>
+        <v>2.87</v>
       </c>
       <c r="P28">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="Q28">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="R28">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="S28">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="T28">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="U28">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="V28">
         <v>1.25</v>
@@ -4903,7 +4903,7 @@
         <v>1.04</v>
       </c>
       <c r="X28">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y28">
         <v>1.47</v>
@@ -4912,13 +4912,13 @@
         <v>2.63</v>
       </c>
       <c r="AA28">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AB28">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AC28">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AD28">
         <v>1.17</v>
@@ -4927,26 +4927,26 @@
         <v>1.04</v>
       </c>
       <c r="AF28">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AG28">
+        <v>1.73</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28">
+        <v>1.33</v>
+      </c>
+      <c r="AK28">
         <v>1.57</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28">
-        <v>1.13</v>
-      </c>
-      <c r="AK28">
-        <v>2</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,25 +5036,25 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.16</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="O29">
-        <v>5.55</v>
+        <v>4.8</v>
       </c>
       <c r="P29">
-        <v>13</v>
+        <v>1.26</v>
       </c>
       <c r="Q29">
-        <v>1.62</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="R29">
-        <v>2.6</v>
+        <v>2.29</v>
       </c>
       <c r="S29">
         <v>1.36</v>
       </c>
       <c r="T29">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U29">
         <v>2.72</v>
@@ -5069,31 +5069,31 @@
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z29">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AA29">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AB29">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AC29">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="AD29">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE29">
         <v>1.07</v>
       </c>
       <c r="AF29">
-        <v>3.18</v>
+        <v>2.45</v>
       </c>
       <c r="AG29">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AK29">
-        <v>4.1</v>
+        <v>1.06</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,25 +5199,25 @@
         </is>
       </c>
       <c r="N30">
-        <v>8.5</v>
+        <v>1.2</v>
       </c>
       <c r="O30">
-        <v>4.8</v>
+        <v>5.55</v>
       </c>
       <c r="P30">
-        <v>1.28</v>
+        <v>13</v>
       </c>
       <c r="Q30">
-        <v>9.300000000000001</v>
+        <v>1.62</v>
       </c>
       <c r="R30">
-        <v>2.29</v>
+        <v>2.6</v>
       </c>
       <c r="S30">
         <v>1.36</v>
       </c>
       <c r="T30">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="U30">
         <v>2.72</v>
@@ -5232,31 +5232,31 @@
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z30">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AA30">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AB30">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AC30">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="AD30">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE30">
         <v>1.07</v>
       </c>
       <c r="AF30">
-        <v>2.45</v>
+        <v>3.18</v>
       </c>
       <c r="AG30">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AK30">
-        <v>1.06</v>
+        <v>4.1</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5365,16 +5365,16 @@
         <v>1.55</v>
       </c>
       <c r="O31">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P31">
         <v>5.25</v>
       </c>
       <c r="Q31">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="R31">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S31">
         <v>1.44</v>
@@ -5401,25 +5401,25 @@
         <v>2.87</v>
       </c>
       <c r="AA31">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB31">
         <v>1.65</v>
       </c>
       <c r="AC31">
-        <v>3.84</v>
+        <v>4</v>
       </c>
       <c r="AD31">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE31">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF31">
         <v>2.15</v>
       </c>
       <c r="AG31">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AK31">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5531,25 +5531,25 @@
         <v>3.55</v>
       </c>
       <c r="P32">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="Q32">
-        <v>4.24</v>
+        <v>4.36</v>
       </c>
       <c r="R32">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="S32">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T32">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="U32">
         <v>2.72</v>
       </c>
       <c r="V32">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W32">
         <v>1.06</v>
@@ -5564,10 +5564,10 @@
         <v>3.5</v>
       </c>
       <c r="AA32">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB32">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AC32">
         <v>3.25</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,80 +5851,80 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.65</v>
+        <v>2.45</v>
       </c>
       <c r="O34">
-        <v>4.3</v>
+        <v>3.44</v>
       </c>
       <c r="P34">
-        <v>4.09</v>
+        <v>2.7</v>
       </c>
       <c r="Q34">
-        <v>2.14</v>
+        <v>2.88</v>
       </c>
       <c r="R34">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="S34">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="T34">
+        <v>2.75</v>
+      </c>
+      <c r="U34">
+        <v>2.83</v>
+      </c>
+      <c r="V34">
+        <v>1.4</v>
+      </c>
+      <c r="W34">
+        <v>1.07</v>
+      </c>
+      <c r="X34">
+        <v>1.04</v>
+      </c>
+      <c r="Y34">
+        <v>1.25</v>
+      </c>
+      <c r="Z34">
         <v>3.8</v>
       </c>
-      <c r="U34">
-        <v>2.15</v>
-      </c>
-      <c r="V34">
-        <v>1.65</v>
-      </c>
-      <c r="W34">
-        <v>1.15</v>
-      </c>
-      <c r="X34">
-        <v>1.01</v>
-      </c>
-      <c r="Y34">
-        <v>1.13</v>
-      </c>
-      <c r="Z34">
-        <v>6</v>
-      </c>
       <c r="AA34">
-        <v>1.44</v>
+        <v>1.93</v>
       </c>
       <c r="AB34">
-        <v>2.43</v>
+        <v>1.94</v>
       </c>
       <c r="AC34">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD34">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="AE34">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AF34">
+        <v>1.67</v>
+      </c>
+      <c r="AG34">
+        <v>2.1</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ34">
+        <v>1.25</v>
+      </c>
+      <c r="AK34">
         <v>1.5</v>
-      </c>
-      <c r="AG34">
-        <v>2.42</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ34">
-        <v>1.2</v>
-      </c>
-      <c r="AK34">
-        <v>2.1</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,80 +6014,80 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="O35">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="P35">
-        <v>3.1</v>
+        <v>4.09</v>
       </c>
       <c r="Q35">
-        <v>2.88</v>
+        <v>2.14</v>
       </c>
       <c r="R35">
+        <v>2.44</v>
+      </c>
+      <c r="S35">
+        <v>1.22</v>
+      </c>
+      <c r="T35">
+        <v>3.8</v>
+      </c>
+      <c r="U35">
+        <v>2.15</v>
+      </c>
+      <c r="V35">
+        <v>1.65</v>
+      </c>
+      <c r="W35">
+        <v>1.15</v>
+      </c>
+      <c r="X35">
+        <v>1.01</v>
+      </c>
+      <c r="Y35">
+        <v>1.13</v>
+      </c>
+      <c r="Z35">
+        <v>6</v>
+      </c>
+      <c r="AA35">
+        <v>1.44</v>
+      </c>
+      <c r="AB35">
+        <v>2.43</v>
+      </c>
+      <c r="AC35">
+        <v>2.2</v>
+      </c>
+      <c r="AD35">
+        <v>1.65</v>
+      </c>
+      <c r="AE35">
+        <v>1.2</v>
+      </c>
+      <c r="AF35">
+        <v>1.5</v>
+      </c>
+      <c r="AG35">
+        <v>2.42</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35">
+        <v>1.2</v>
+      </c>
+      <c r="AK35">
         <v>2.1</v>
-      </c>
-      <c r="S35">
-        <v>1.36</v>
-      </c>
-      <c r="T35">
-        <v>2.82</v>
-      </c>
-      <c r="U35">
-        <v>3.01</v>
-      </c>
-      <c r="V35">
-        <v>1.36</v>
-      </c>
-      <c r="W35">
-        <v>1.05</v>
-      </c>
-      <c r="X35">
-        <v>1.05</v>
-      </c>
-      <c r="Y35">
-        <v>1.28</v>
-      </c>
-      <c r="Z35">
-        <v>3.42</v>
-      </c>
-      <c r="AA35">
-        <v>2.05</v>
-      </c>
-      <c r="AB35">
-        <v>1.83</v>
-      </c>
-      <c r="AC35">
-        <v>3.28</v>
-      </c>
-      <c r="AD35">
-        <v>1.25</v>
-      </c>
-      <c r="AE35">
-        <v>1.08</v>
-      </c>
-      <c r="AF35">
-        <v>1.8</v>
-      </c>
-      <c r="AG35">
-        <v>2</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ35">
-        <v>1.33</v>
-      </c>
-      <c r="AK35">
-        <v>1.57</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,80 +6177,80 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="O36">
-        <v>3.44</v>
+        <v>3.25</v>
       </c>
       <c r="P36">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="Q36">
         <v>2.88</v>
       </c>
       <c r="R36">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S36">
+        <v>1.36</v>
+      </c>
+      <c r="T36">
+        <v>2.82</v>
+      </c>
+      <c r="U36">
+        <v>3.01</v>
+      </c>
+      <c r="V36">
+        <v>1.36</v>
+      </c>
+      <c r="W36">
+        <v>1.05</v>
+      </c>
+      <c r="X36">
+        <v>1.05</v>
+      </c>
+      <c r="Y36">
+        <v>1.28</v>
+      </c>
+      <c r="Z36">
+        <v>3.42</v>
+      </c>
+      <c r="AA36">
+        <v>2.05</v>
+      </c>
+      <c r="AB36">
+        <v>1.83</v>
+      </c>
+      <c r="AC36">
+        <v>3.28</v>
+      </c>
+      <c r="AD36">
+        <v>1.25</v>
+      </c>
+      <c r="AE36">
+        <v>1.08</v>
+      </c>
+      <c r="AF36">
+        <v>1.8</v>
+      </c>
+      <c r="AG36">
+        <v>2</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ36">
         <v>1.33</v>
       </c>
-      <c r="T36">
-        <v>2.75</v>
-      </c>
-      <c r="U36">
-        <v>2.83</v>
-      </c>
-      <c r="V36">
-        <v>1.4</v>
-      </c>
-      <c r="W36">
-        <v>1.07</v>
-      </c>
-      <c r="X36">
-        <v>1.04</v>
-      </c>
-      <c r="Y36">
-        <v>1.25</v>
-      </c>
-      <c r="Z36">
-        <v>3.8</v>
-      </c>
-      <c r="AA36">
-        <v>1.93</v>
-      </c>
-      <c r="AB36">
-        <v>1.94</v>
-      </c>
-      <c r="AC36">
-        <v>3.1</v>
-      </c>
-      <c r="AD36">
-        <v>1.36</v>
-      </c>
-      <c r="AE36">
-        <v>1.1</v>
-      </c>
-      <c r="AF36">
-        <v>1.67</v>
-      </c>
-      <c r="AG36">
-        <v>2.1</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ36">
-        <v>1.25</v>
-      </c>
       <c r="AK36">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,40 +7807,40 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.57</v>
+        <v>3.43</v>
       </c>
       <c r="O46">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="P46">
-        <v>5.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q46">
-        <v>2.12</v>
+        <v>3.62</v>
       </c>
       <c r="R46">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="S46">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T46">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U46">
-        <v>2.64</v>
+        <v>2.4</v>
       </c>
       <c r="V46">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="W46">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X46">
         <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z46">
         <v>4.33</v>
@@ -7849,22 +7849,22 @@
         <v>1.69</v>
       </c>
       <c r="AB46">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AC46">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AD46">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE46">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF46">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AG46">
-        <v>1.99</v>
+        <v>2.18</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="AK46">
-        <v>2.25</v>
+        <v>1.27</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,40 +7970,40 @@
         </is>
       </c>
       <c r="N47">
-        <v>3.43</v>
+        <v>1.57</v>
       </c>
       <c r="O47">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="P47">
-        <v>2.05</v>
+        <v>5.25</v>
       </c>
       <c r="Q47">
-        <v>3.62</v>
+        <v>2.12</v>
       </c>
       <c r="R47">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="S47">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T47">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U47">
-        <v>2.4</v>
+        <v>2.64</v>
       </c>
       <c r="V47">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="W47">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X47">
         <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z47">
         <v>4.33</v>
@@ -8012,22 +8012,22 @@
         <v>1.69</v>
       </c>
       <c r="AB47">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AC47">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AD47">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AE47">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF47">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="AG47">
-        <v>2.18</v>
+        <v>1.99</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="AK47">
-        <v>1.27</v>
+        <v>2.25</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="O49">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="P49">
-        <v>1.73</v>
+        <v>2.4</v>
       </c>
       <c r="Q49">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="R49">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="S49">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="T49">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="U49">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="V49">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W49">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X49">
+        <v>1.09</v>
+      </c>
+      <c r="Y49">
+        <v>1.66</v>
+      </c>
+      <c r="Z49">
+        <v>2.17</v>
+      </c>
+      <c r="AA49">
+        <v>3</v>
+      </c>
+      <c r="AB49">
+        <v>1.33</v>
+      </c>
+      <c r="AC49">
+        <v>7</v>
+      </c>
+      <c r="AD49">
         <v>1.07</v>
-      </c>
-      <c r="Y49">
-        <v>1.49</v>
-      </c>
-      <c r="Z49">
-        <v>2.48</v>
-      </c>
-      <c r="AA49">
-        <v>2.4</v>
-      </c>
-      <c r="AB49">
-        <v>1.47</v>
-      </c>
-      <c r="AC49">
-        <v>5.25</v>
-      </c>
-      <c r="AD49">
-        <v>1.13</v>
       </c>
       <c r="AE49">
         <v>1.02</v>
       </c>
       <c r="AF49">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AG49">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AK49">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AL49">
         <v>0</v>

--- a/jogos_2026-10-13.xlsx
+++ b/jogos_2026-10-13.xlsx
@@ -1130,7 +1130,7 @@
         <v>2.9</v>
       </c>
       <c r="P5">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Q5">
         <v>2.82</v>
@@ -1945,7 +1945,7 @@
         <v>3.15</v>
       </c>
       <c r="P10">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q10">
         <v>2.4</v>
@@ -1975,13 +1975,13 @@
         <v>1.3</v>
       </c>
       <c r="Z10">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="AA10">
         <v>2.05</v>
       </c>
       <c r="AB10">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC10">
         <v>3.72</v>
@@ -1990,10 +1990,10 @@
         <v>1.27</v>
       </c>
       <c r="AE10">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF10">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG10">
         <v>1.88</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK10">
         <v>1.65</v>
@@ -2102,19 +2102,19 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="O11">
         <v>3.66</v>
       </c>
       <c r="P11">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="Q11">
         <v>2.4</v>
       </c>
       <c r="R11">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S11">
         <v>1.3</v>
@@ -2123,43 +2123,43 @@
         <v>3.2</v>
       </c>
       <c r="U11">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="V11">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W11">
+        <v>1.11</v>
+      </c>
+      <c r="X11">
+        <v>1.01</v>
+      </c>
+      <c r="Y11">
+        <v>1.2</v>
+      </c>
+      <c r="Z11">
+        <v>4</v>
+      </c>
+      <c r="AA11">
+        <v>1.65</v>
+      </c>
+      <c r="AB11">
+        <v>2.1</v>
+      </c>
+      <c r="AC11">
+        <v>2.75</v>
+      </c>
+      <c r="AD11">
+        <v>1.4</v>
+      </c>
+      <c r="AE11">
         <v>1.1</v>
-      </c>
-      <c r="X11">
-        <v>1.02</v>
-      </c>
-      <c r="Y11">
-        <v>1.22</v>
-      </c>
-      <c r="Z11">
-        <v>4.2</v>
-      </c>
-      <c r="AA11">
-        <v>1.73</v>
-      </c>
-      <c r="AB11">
-        <v>2</v>
-      </c>
-      <c r="AC11">
-        <v>2.88</v>
-      </c>
-      <c r="AD11">
-        <v>1.38</v>
-      </c>
-      <c r="AE11">
-        <v>1.09</v>
       </c>
       <c r="AF11">
         <v>1.6</v>
       </c>
       <c r="AG11">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK11">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2600,10 +2600,10 @@
         <v>4.77</v>
       </c>
       <c r="Q14">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="R14">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="S14">
         <v>1.29</v>
@@ -2612,34 +2612,34 @@
         <v>2.39</v>
       </c>
       <c r="U14">
-        <v>2.34</v>
+        <v>2.04</v>
       </c>
       <c r="V14">
         <v>1.48</v>
       </c>
       <c r="W14">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X14">
         <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z14">
-        <v>3.96</v>
+        <v>4.1</v>
       </c>
       <c r="AA14">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB14">
         <v>2.1</v>
       </c>
       <c r="AC14">
-        <v>2.66</v>
+        <v>2.59</v>
       </c>
       <c r="AD14">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AE14">
         <v>1.11</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AK14">
-        <v>2.23</v>
+        <v>2.46</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3572,61 +3572,61 @@
         <v>1.2</v>
       </c>
       <c r="O20">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="P20">
         <v>11</v>
       </c>
       <c r="Q20">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="R20">
-        <v>3.01</v>
+        <v>3.04</v>
       </c>
       <c r="S20">
         <v>1.2</v>
       </c>
       <c r="T20">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="U20">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="V20">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="W20">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z20">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA20">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB20">
         <v>2.88</v>
       </c>
       <c r="AC20">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="AD20">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AE20">
         <v>1.33</v>
       </c>
       <c r="AF20">
+        <v>1.87</v>
+      </c>
+      <c r="AG20">
         <v>1.9</v>
-      </c>
-      <c r="AG20">
-        <v>1.87</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>3.85</v>
       </c>
       <c r="P26">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Q26">
         <v>2.09</v>
@@ -4562,25 +4562,25 @@
         <v>2.2</v>
       </c>
       <c r="S26">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T26">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="U26">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="V26">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W26">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X26">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y26">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z26">
         <v>3.6</v>
@@ -4589,22 +4589,22 @@
         <v>1.85</v>
       </c>
       <c r="AB26">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="AC26">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="AD26">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AE26">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF26">
         <v>1.8</v>
       </c>
       <c r="AG26">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AK26">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="O31">
         <v>3.5</v>
       </c>
       <c r="P31">
-        <v>5.25</v>
+        <v>4.75</v>
       </c>
       <c r="Q31">
         <v>2.12</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,16 +5688,16 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="O33">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P33">
-        <v>3.66</v>
+        <v>3.1</v>
       </c>
       <c r="Q33">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="R33">
         <v>2.1</v>
@@ -5706,62 +5706,62 @@
         <v>1.36</v>
       </c>
       <c r="T33">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="U33">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="V33">
         <v>1.36</v>
       </c>
       <c r="W33">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X33">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y33">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z33">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="AA33">
-        <v>1.99</v>
+        <v>2.11</v>
       </c>
       <c r="AB33">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AC33">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="AD33">
+        <v>1.25</v>
+      </c>
+      <c r="AE33">
+        <v>1.08</v>
+      </c>
+      <c r="AF33">
+        <v>1.8</v>
+      </c>
+      <c r="AG33">
+        <v>2</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ33">
         <v>1.33</v>
       </c>
-      <c r="AE33">
-        <v>1.1</v>
-      </c>
-      <c r="AF33">
-        <v>1.73</v>
-      </c>
-      <c r="AG33">
-        <v>1.97</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ33">
-        <v>1.27</v>
-      </c>
       <c r="AK33">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
+        <v>2.1</v>
+      </c>
+      <c r="O34">
+        <v>3.4</v>
+      </c>
+      <c r="P34">
+        <v>3.66</v>
+      </c>
+      <c r="Q34">
         <v>2.45</v>
       </c>
-      <c r="O34">
-        <v>3.44</v>
-      </c>
-      <c r="P34">
-        <v>2.7</v>
-      </c>
-      <c r="Q34">
-        <v>2.88</v>
-      </c>
       <c r="R34">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S34">
         <v>1.33</v>
       </c>
       <c r="T34">
+        <v>2.66</v>
+      </c>
+      <c r="U34">
         <v>2.75</v>
       </c>
-      <c r="U34">
-        <v>2.83</v>
-      </c>
       <c r="V34">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W34">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X34">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y34">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="Z34">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="AA34">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="AB34">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AC34">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AD34">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE34">
         <v>1.1</v>
       </c>
       <c r="AF34">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AG34">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>1.25</v>
       </c>
       <c r="AK34">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6017,10 +6017,10 @@
         <v>1.65</v>
       </c>
       <c r="O35">
-        <v>4.3</v>
+        <v>4.05</v>
       </c>
       <c r="P35">
-        <v>4.09</v>
+        <v>4.4</v>
       </c>
       <c r="Q35">
         <v>2.14</v>
@@ -6038,7 +6038,7 @@
         <v>2.15</v>
       </c>
       <c r="V35">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="W35">
         <v>1.15</v>
@@ -6047,10 +6047,10 @@
         <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z35">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AA35">
         <v>1.44</v>
@@ -6059,10 +6059,10 @@
         <v>2.43</v>
       </c>
       <c r="AC35">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD35">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AE35">
         <v>1.2</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AK35">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="O36">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="P36">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="Q36">
         <v>2.88</v>
@@ -6195,46 +6195,46 @@
         <v>1.36</v>
       </c>
       <c r="T36">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="U36">
-        <v>3.01</v>
+        <v>2.7</v>
       </c>
       <c r="V36">
+        <v>1.4</v>
+      </c>
+      <c r="W36">
+        <v>1.07</v>
+      </c>
+      <c r="X36">
+        <v>1.04</v>
+      </c>
+      <c r="Y36">
+        <v>1.25</v>
+      </c>
+      <c r="Z36">
+        <v>3.8</v>
+      </c>
+      <c r="AA36">
+        <v>1.95</v>
+      </c>
+      <c r="AB36">
+        <v>1.93</v>
+      </c>
+      <c r="AC36">
+        <v>3.1</v>
+      </c>
+      <c r="AD36">
         <v>1.36</v>
       </c>
-      <c r="W36">
-        <v>1.05</v>
-      </c>
-      <c r="X36">
-        <v>1.05</v>
-      </c>
-      <c r="Y36">
-        <v>1.28</v>
-      </c>
-      <c r="Z36">
-        <v>3.42</v>
-      </c>
-      <c r="AA36">
-        <v>2.05</v>
-      </c>
-      <c r="AB36">
-        <v>1.83</v>
-      </c>
-      <c r="AC36">
-        <v>3.28</v>
-      </c>
-      <c r="AD36">
-        <v>1.25</v>
-      </c>
       <c r="AE36">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF36">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AG36">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK36">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="O37">
         <v>4.85</v>
       </c>
       <c r="P37">
-        <v>7.19</v>
+        <v>7</v>
       </c>
       <c r="Q37">
         <v>1.83</v>
@@ -6361,7 +6361,7 @@
         <v>3.5</v>
       </c>
       <c r="U37">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="V37">
         <v>1.57</v>
@@ -6382,10 +6382,10 @@
         <v>1.52</v>
       </c>
       <c r="AB37">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="AC37">
-        <v>2.59</v>
+        <v>2.42</v>
       </c>
       <c r="AD37">
         <v>1.5</v>
@@ -6509,7 +6509,7 @@
         <v>4</v>
       </c>
       <c r="P38">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="Q38">
         <v>2.16</v>
@@ -6521,13 +6521,13 @@
         <v>1.31</v>
       </c>
       <c r="T38">
-        <v>3.1</v>
+        <v>3.19</v>
       </c>
       <c r="U38">
         <v>2.5</v>
       </c>
       <c r="V38">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W38">
         <v>1.07</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.92</v>
+        <v>17</v>
       </c>
       <c r="O42">
-        <v>3.7</v>
+        <v>14</v>
       </c>
       <c r="P42">
-        <v>3.1</v>
+        <v>1.12</v>
       </c>
       <c r="Q42">
+        <v>10.7</v>
+      </c>
+      <c r="R42">
+        <v>4.45</v>
+      </c>
+      <c r="S42">
+        <v>1.1</v>
+      </c>
+      <c r="T42">
+        <v>7</v>
+      </c>
+      <c r="U42">
+        <v>1.49</v>
+      </c>
+      <c r="V42">
         <v>2.31</v>
       </c>
-      <c r="R42">
-        <v>2.37</v>
-      </c>
-      <c r="S42">
-        <v>1.25</v>
-      </c>
-      <c r="T42">
-        <v>3.35</v>
-      </c>
-      <c r="U42">
-        <v>2.18</v>
-      </c>
-      <c r="V42">
-        <v>1.66</v>
-      </c>
       <c r="W42">
-        <v>1.18</v>
+        <v>1.46</v>
       </c>
       <c r="X42">
+        <v>1</v>
+      </c>
+      <c r="Y42">
         <v>1.01</v>
       </c>
-      <c r="Y42">
+      <c r="Z42">
+        <v>13</v>
+      </c>
+      <c r="AA42">
         <v>1.11</v>
       </c>
-      <c r="Z42">
-        <v>6</v>
-      </c>
-      <c r="AA42">
-        <v>1.53</v>
-      </c>
       <c r="AB42">
-        <v>2.53</v>
+        <v>5.25</v>
       </c>
       <c r="AC42">
-        <v>2.2</v>
+        <v>1.37</v>
       </c>
       <c r="AD42">
-        <v>1.62</v>
+        <v>2.8</v>
       </c>
       <c r="AE42">
-        <v>1.25</v>
+        <v>1.89</v>
       </c>
       <c r="AF42">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AG42">
-        <v>2.8</v>
+        <v>2.08</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.19</v>
+        <v>8.6</v>
       </c>
       <c r="AK42">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,65 +7318,65 @@
         </is>
       </c>
       <c r="N43">
-        <v>17</v>
+        <v>1.92</v>
       </c>
       <c r="O43">
-        <v>14</v>
+        <v>3.7</v>
       </c>
       <c r="P43">
-        <v>1.12</v>
+        <v>3.1</v>
       </c>
       <c r="Q43">
-        <v>10.7</v>
+        <v>2.31</v>
       </c>
       <c r="R43">
-        <v>4.45</v>
+        <v>2.37</v>
       </c>
       <c r="S43">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="T43">
-        <v>7</v>
+        <v>3.35</v>
       </c>
       <c r="U43">
-        <v>1.49</v>
+        <v>2.18</v>
       </c>
       <c r="V43">
-        <v>2.31</v>
+        <v>1.66</v>
       </c>
       <c r="W43">
-        <v>1.46</v>
+        <v>1.18</v>
       </c>
       <c r="X43">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="Z43">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="AA43">
-        <v>1.11</v>
+        <v>1.53</v>
       </c>
       <c r="AB43">
-        <v>5.25</v>
+        <v>2.53</v>
       </c>
       <c r="AC43">
-        <v>1.37</v>
+        <v>2.2</v>
       </c>
       <c r="AD43">
+        <v>1.62</v>
+      </c>
+      <c r="AE43">
+        <v>1.25</v>
+      </c>
+      <c r="AF43">
+        <v>1.44</v>
+      </c>
+      <c r="AG43">
         <v>2.8</v>
       </c>
-      <c r="AE43">
-        <v>1.89</v>
-      </c>
-      <c r="AF43">
-        <v>1.65</v>
-      </c>
-      <c r="AG43">
-        <v>2.08</v>
-      </c>
       <c r="AH43" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>8.6</v>
+        <v>1.19</v>
       </c>
       <c r="AK43">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7810,28 +7810,28 @@
         <v>3.43</v>
       </c>
       <c r="O46">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P46">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q46">
-        <v>3.62</v>
+        <v>3.74</v>
       </c>
       <c r="R46">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="S46">
         <v>1.29</v>
       </c>
       <c r="T46">
-        <v>3.4</v>
+        <v>3.26</v>
       </c>
       <c r="U46">
         <v>2.4</v>
       </c>
       <c r="V46">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W46">
         <v>1.08</v>
@@ -7840,10 +7840,10 @@
         <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z46">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AA46">
         <v>1.69</v>
@@ -7858,10 +7858,10 @@
         <v>1.38</v>
       </c>
       <c r="AE46">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF46">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG46">
         <v>2.18</v>
@@ -7973,13 +7973,13 @@
         <v>1.57</v>
       </c>
       <c r="O47">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P47">
-        <v>5.25</v>
+        <v>5.64</v>
       </c>
       <c r="Q47">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="R47">
         <v>2.3</v>
@@ -7994,7 +7994,7 @@
         <v>2.64</v>
       </c>
       <c r="V47">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W47">
         <v>1.07</v>
@@ -8003,13 +8003,13 @@
         <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z47">
         <v>4.33</v>
       </c>
       <c r="AA47">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AB47">
         <v>2.1</v>
@@ -8018,16 +8018,16 @@
         <v>2.88</v>
       </c>
       <c r="AD47">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AE47">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF47">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AG47">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK47">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8299,7 +8299,7 @@
         <v>2.9</v>
       </c>
       <c r="O49">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="P49">
         <v>2.4</v>
@@ -8311,16 +8311,16 @@
         <v>1.85</v>
       </c>
       <c r="S49">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="T49">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="U49">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="V49">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W49">
         <v>1.01</v>
@@ -8350,7 +8350,7 @@
         <v>1.02</v>
       </c>
       <c r="AF49">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AG49">
         <v>1.57</v>
@@ -8369,7 +8369,7 @@
         <v>1.47</v>
       </c>
       <c r="AK49">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AL49">
         <v>0</v>

--- a/jogos_2026-10-13.xlsx
+++ b/jogos_2026-10-13.xlsx
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -624,14 +624,14 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
@@ -696,12 +696,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["83"]</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["66"]</t>
         </is>
       </c>
       <c r="AJ2">
@@ -714,28 +714,28 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -775,26 +775,26 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
@@ -859,12 +859,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["83"]</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["3", "24"]</t>
         </is>
       </c>
       <c r="AJ3">
@@ -941,7 +941,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -953,72 +953,72 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
         <v>2.35</v>
       </c>
       <c r="O4">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P4">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="Q4">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="R4">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="S4">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="T4">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="U4">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="V4">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W4">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X4">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y4">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="Z4">
-        <v>3.72</v>
+        <v>3.14</v>
       </c>
       <c r="AA4">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AB4">
-        <v>2.04</v>
+        <v>1.81</v>
       </c>
       <c r="AC4">
-        <v>2.74</v>
+        <v>3.28</v>
       </c>
       <c r="AD4">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AE4">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF4">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AG4">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1027,41 +1027,41 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["76", "84", "90+1", "90+3"]</t>
         </is>
       </c>
       <c r="AJ4">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK4">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1101,10 +1101,10 @@
         </is>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["-1", "-1"]</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["-1"]</t>
         </is>
       </c>
       <c r="AJ5">
@@ -1264,13 +1264,13 @@
         </is>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1279,11 +1279,11 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["4"]</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["87", "90+6"]</t>
         </is>
       </c>
       <c r="AJ6">
@@ -1450,55 +1450,55 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="O7">
         <v>2.6</v>
       </c>
       <c r="P7">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="Q7">
-        <v>3.04</v>
+        <v>3.27</v>
       </c>
       <c r="R7">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="S7">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="T7">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="U7">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="V7">
         <v>1.17</v>
       </c>
       <c r="W7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X7">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Y7">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Z7">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AA7">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AB7">
         <v>1.33</v>
       </c>
       <c r="AC7">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AD7">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AE7">
         <v>1.01</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK7">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.89</v>
+        <v>1.67</v>
       </c>
       <c r="O8">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="P8">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="Q8">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="R8">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="S8">
         <v>1.44</v>
       </c>
       <c r="T8">
-        <v>2.27</v>
+        <v>2.55</v>
       </c>
       <c r="U8">
         <v>3.6</v>
       </c>
       <c r="V8">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="W8">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X8">
         <v>1.1</v>
       </c>
       <c r="Y8">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="Z8">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="AA8">
-        <v>2.37</v>
+        <v>2.31</v>
       </c>
       <c r="AB8">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AC8">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AD8">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AE8">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF8">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AG8">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AK8">
-        <v>1.72</v>
+        <v>2.18</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="O9">
         <v>2.87</v>
       </c>
       <c r="P9">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="Q9">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="R9">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="S9">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="T9">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="U9">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="V9">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="W9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X9">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y9">
         <v>1.5</v>
       </c>
       <c r="Z9">
-        <v>2.52</v>
+        <v>2.36</v>
       </c>
       <c r="AA9">
-        <v>2.62</v>
+        <v>2.86</v>
       </c>
       <c r="AB9">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AC9">
         <v>5.5</v>
       </c>
       <c r="AD9">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AE9">
         <v>1</v>
       </c>
       <c r="AF9">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AG9">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK9">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1916,26 +1916,26 @@
         </is>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["81"]</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["7", "15", "23", "75"]</t>
         </is>
       </c>
       <c r="AJ10">
@@ -2018,28 +2018,28 @@
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP10">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
@@ -2181,28 +2181,28 @@
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP11">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
@@ -2233,139 +2233,139 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
-        <v>1.95</v>
+        <v>4.9</v>
       </c>
       <c r="O12">
-        <v>3.6</v>
+        <v>4.05</v>
       </c>
       <c r="P12">
-        <v>3</v>
+        <v>1.66</v>
       </c>
       <c r="Q12">
-        <v>2.4</v>
+        <v>3.65</v>
       </c>
       <c r="R12">
-        <v>2.59</v>
+        <v>2.25</v>
       </c>
       <c r="S12">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T12">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="U12">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="V12">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="W12">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
         <v>1.1</v>
       </c>
       <c r="Z12">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="AA12">
         <v>1.33</v>
       </c>
       <c r="AB12">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="AC12">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AD12">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AE12">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AF12">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="AG12">
-        <v>2.9</v>
+        <v>2.42</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["34", "72"]</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["53", "87"]</t>
         </is>
       </c>
       <c r="AJ12">
+        <v>1.17</v>
+      </c>
+      <c r="AK12">
+        <v>1.17</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>3</v>
+      </c>
+      <c r="AN12">
+        <v>4</v>
+      </c>
+      <c r="AO12">
+        <v>11</v>
+      </c>
+      <c r="AP12">
+        <v>12</v>
+      </c>
+      <c r="AQ12">
         <v>1.26</v>
       </c>
-      <c r="AK12">
-        <v>1.72</v>
-      </c>
-      <c r="AL12">
-        <v>0</v>
-      </c>
-      <c r="AM12">
-        <v>-1</v>
-      </c>
-      <c r="AN12">
-        <v>-1</v>
-      </c>
-      <c r="AO12">
-        <v>-1</v>
-      </c>
-      <c r="AP12">
-        <v>-1</v>
-      </c>
-      <c r="AQ12">
-        <v>0</v>
-      </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
@@ -2396,139 +2396,139 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
-        <v>4.9</v>
+        <v>1.95</v>
       </c>
       <c r="O13">
-        <v>4.05</v>
+        <v>3.6</v>
       </c>
       <c r="P13">
-        <v>1.66</v>
+        <v>3</v>
       </c>
       <c r="Q13">
-        <v>3.68</v>
+        <v>2.4</v>
       </c>
       <c r="R13">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="S13">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T13">
-        <v>3.7</v>
+        <v>4.33</v>
       </c>
       <c r="U13">
-        <v>1.88</v>
+        <v>2.04</v>
       </c>
       <c r="V13">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="W13">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="X13">
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Z13">
-        <v>4.8</v>
+        <v>7.5</v>
       </c>
       <c r="AA13">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AB13">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="AC13">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AD13">
-        <v>1.58</v>
+        <v>1.9</v>
       </c>
       <c r="AE13">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF13">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AG13">
-        <v>2.38</v>
+        <v>2.9</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
+          <t>["5", "55"]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ13">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AK13">
-        <v>1.17</v>
+        <v>1.72</v>
       </c>
       <c r="AL13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN13">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP13">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -3080,34 +3080,34 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="O17">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P17">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="Q17">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="R17">
         <v>1.75</v>
       </c>
       <c r="S17">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="T17">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="U17">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="V17">
         <v>1.19</v>
       </c>
       <c r="W17">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X17">
         <v>1.1</v>
@@ -3116,28 +3116,28 @@
         <v>1.53</v>
       </c>
       <c r="Z17">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AA17">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="AB17">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AC17">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AD17">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE17">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF17">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AG17">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK17">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3249,25 +3249,25 @@
         <v>2.65</v>
       </c>
       <c r="P18">
-        <v>3.94</v>
+        <v>4.49</v>
       </c>
       <c r="Q18">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="R18">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="S18">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="T18">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="U18">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="V18">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W18">
         <v>1.03</v>
@@ -3276,25 +3276,25 @@
         <v>1.15</v>
       </c>
       <c r="Y18">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="Z18">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="AA18">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AB18">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AC18">
-        <v>6.35</v>
+        <v>6.15</v>
       </c>
       <c r="AD18">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AE18">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF18">
         <v>2.3</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AK18">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3409,61 +3409,61 @@
         <v>3</v>
       </c>
       <c r="O19">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="P19">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="Q19">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="R19">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="S19">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="T19">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="U19">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="V19">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W19">
+        <v>1.06</v>
+      </c>
+      <c r="X19">
         <v>1.07</v>
       </c>
-      <c r="X19">
-        <v>1.05</v>
-      </c>
       <c r="Y19">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="Z19">
         <v>2.88</v>
       </c>
       <c r="AA19">
-        <v>2.12</v>
+        <v>2.41</v>
       </c>
       <c r="AB19">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AC19">
-        <v>3.65</v>
+        <v>4.35</v>
       </c>
       <c r="AD19">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AE19">
         <v>1.06</v>
       </c>
       <c r="AF19">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AG19">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AK19">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3587,28 +3587,28 @@
         <v>1.2</v>
       </c>
       <c r="T20">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="U20">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="V20">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="W20">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z20">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="AA20">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB20">
         <v>2.88</v>
@@ -3620,13 +3620,13 @@
         <v>1.92</v>
       </c>
       <c r="AE20">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF20">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AG20">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>2.9</v>
       </c>
       <c r="R21">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="S21">
         <v>1.25</v>
@@ -3753,7 +3753,7 @@
         <v>3.4</v>
       </c>
       <c r="U21">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="V21">
         <v>1.43</v>
@@ -3765,31 +3765,31 @@
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z21">
-        <v>4.63</v>
+        <v>4.73</v>
       </c>
       <c r="AA21">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AB21">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="AC21">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AD21">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AE21">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AF21">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG21">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3895,19 +3895,19 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="O22">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="P22">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q22">
-        <v>3.34</v>
+        <v>2.88</v>
       </c>
       <c r="R22">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="S22">
         <v>1.2</v>
@@ -3916,13 +3916,13 @@
         <v>3.5</v>
       </c>
       <c r="U22">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="V22">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W22">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X22">
         <v>1.01</v>
@@ -3937,7 +3937,7 @@
         <v>1.57</v>
       </c>
       <c r="AB22">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="AC22">
         <v>2.49</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="AK22">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,28 +4058,28 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="O23">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="P23">
-        <v>5</v>
+        <v>5.17</v>
       </c>
       <c r="Q23">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="R23">
         <v>2.5</v>
       </c>
       <c r="S23">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T23">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="U23">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="V23">
         <v>1.65</v>
@@ -4091,31 +4091,31 @@
         <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z23">
-        <v>4.96</v>
+        <v>5</v>
       </c>
       <c r="AA23">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB23">
         <v>2.38</v>
       </c>
       <c r="AC23">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AD23">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AE23">
         <v>1.18</v>
       </c>
       <c r="AF23">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG23">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AK23">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4230,7 +4230,7 @@
         <v>2.1</v>
       </c>
       <c r="Q24">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="R24">
         <v>2.49</v>
@@ -4239,7 +4239,7 @@
         <v>1.13</v>
       </c>
       <c r="T24">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="U24">
         <v>1.91</v>
@@ -4254,10 +4254,10 @@
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z24">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AA24">
         <v>1.31</v>
@@ -4266,16 +4266,16 @@
         <v>3.1</v>
       </c>
       <c r="AC24">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AD24">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AE24">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AF24">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AG24">
         <v>3</v>
@@ -4294,7 +4294,7 @@
         <v>1.67</v>
       </c>
       <c r="AK24">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,22 +4384,22 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="O25">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="P25">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="Q25">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="R25">
-        <v>2.43</v>
+        <v>2.54</v>
       </c>
       <c r="S25">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="T25">
         <v>2.9</v>
@@ -4417,31 +4417,31 @@
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z25">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AA25">
         <v>1.33</v>
       </c>
       <c r="AB25">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AC25">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD25">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AE25">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF25">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AG25">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AK25">
-        <v>2.14</v>
+        <v>2.42</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4553,7 +4553,7 @@
         <v>3.85</v>
       </c>
       <c r="P26">
-        <v>4.4</v>
+        <v>4.29</v>
       </c>
       <c r="Q26">
         <v>2.09</v>
@@ -4710,19 +4710,19 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="O27">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P27">
-        <v>4.9</v>
+        <v>5.25</v>
       </c>
       <c r="Q27">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R27">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="S27">
         <v>1.44</v>
@@ -4731,7 +4731,7 @@
         <v>2.63</v>
       </c>
       <c r="U27">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="V27">
         <v>1.29</v>
@@ -4743,16 +4743,16 @@
         <v>1.07</v>
       </c>
       <c r="Y27">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Z27">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AA27">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AB27">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AC27">
         <v>4.5</v>
@@ -4767,7 +4767,7 @@
         <v>2.2</v>
       </c>
       <c r="AG27">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.06</v>
+        <v>1.2</v>
       </c>
       <c r="O28">
-        <v>2.87</v>
+        <v>5.55</v>
       </c>
       <c r="P28">
-        <v>3.25</v>
+        <v>12</v>
       </c>
       <c r="Q28">
-        <v>2.88</v>
+        <v>1.57</v>
       </c>
       <c r="R28">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="S28">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="T28">
-        <v>2.31</v>
+        <v>2.9</v>
       </c>
       <c r="U28">
-        <v>3.5</v>
+        <v>2.72</v>
       </c>
       <c r="V28">
+        <v>1.36</v>
+      </c>
+      <c r="W28">
+        <v>1.1</v>
+      </c>
+      <c r="X28">
+        <v>1.01</v>
+      </c>
+      <c r="Y28">
         <v>1.25</v>
       </c>
-      <c r="W28">
-        <v>1.04</v>
-      </c>
-      <c r="X28">
-        <v>1.06</v>
-      </c>
-      <c r="Y28">
-        <v>1.47</v>
-      </c>
       <c r="Z28">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="AA28">
-        <v>2.55</v>
+        <v>1.9</v>
       </c>
       <c r="AB28">
-        <v>1.45</v>
+        <v>1.9</v>
       </c>
       <c r="AC28">
-        <v>4.9</v>
+        <v>3.08</v>
       </c>
       <c r="AD28">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AE28">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF28">
-        <v>2.05</v>
+        <v>3.04</v>
       </c>
       <c r="AG28">
-        <v>1.73</v>
+        <v>1.32</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AK28">
-        <v>1.57</v>
+        <v>4</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,52 +5036,52 @@
         </is>
       </c>
       <c r="N29">
-        <v>9.869999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="O29">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="P29">
         <v>1.26</v>
       </c>
       <c r="Q29">
-        <v>9.300000000000001</v>
+        <v>8.65</v>
       </c>
       <c r="R29">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="S29">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T29">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U29">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="V29">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W29">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y29">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z29">
         <v>3.14</v>
       </c>
       <c r="AA29">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AB29">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AC29">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AD29">
         <v>1.29</v>
@@ -5090,10 +5090,10 @@
         <v>1.07</v>
       </c>
       <c r="AF29">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="AG29">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>1.2</v>
       </c>
       <c r="AK29">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
+        <v>2.18</v>
+      </c>
+      <c r="O30">
+        <v>3.02</v>
+      </c>
+      <c r="P30">
+        <v>2.97</v>
+      </c>
+      <c r="Q30">
+        <v>3.1</v>
+      </c>
+      <c r="R30">
+        <v>2</v>
+      </c>
+      <c r="S30">
+        <v>1.45</v>
+      </c>
+      <c r="T30">
+        <v>2.42</v>
+      </c>
+      <c r="U30">
+        <v>3.2</v>
+      </c>
+      <c r="V30">
+        <v>1.3</v>
+      </c>
+      <c r="W30">
+        <v>1.03</v>
+      </c>
+      <c r="X30">
+        <v>1.07</v>
+      </c>
+      <c r="Y30">
+        <v>1.4</v>
+      </c>
+      <c r="Z30">
+        <v>2.88</v>
+      </c>
+      <c r="AA30">
+        <v>2.25</v>
+      </c>
+      <c r="AB30">
+        <v>1.57</v>
+      </c>
+      <c r="AC30">
+        <v>4.1</v>
+      </c>
+      <c r="AD30">
         <v>1.2</v>
       </c>
-      <c r="O30">
-        <v>5.55</v>
-      </c>
-      <c r="P30">
-        <v>13</v>
-      </c>
-      <c r="Q30">
-        <v>1.62</v>
-      </c>
-      <c r="R30">
-        <v>2.6</v>
-      </c>
-      <c r="S30">
-        <v>1.36</v>
-      </c>
-      <c r="T30">
-        <v>2.9</v>
-      </c>
-      <c r="U30">
-        <v>2.72</v>
-      </c>
-      <c r="V30">
-        <v>1.36</v>
-      </c>
-      <c r="W30">
-        <v>1.08</v>
-      </c>
-      <c r="X30">
-        <v>1.01</v>
-      </c>
-      <c r="Y30">
-        <v>1.25</v>
-      </c>
-      <c r="Z30">
-        <v>3.2</v>
-      </c>
-      <c r="AA30">
-        <v>1.9</v>
-      </c>
-      <c r="AB30">
-        <v>1.9</v>
-      </c>
-      <c r="AC30">
-        <v>3.08</v>
-      </c>
-      <c r="AD30">
-        <v>1.28</v>
-      </c>
       <c r="AE30">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF30">
-        <v>3.18</v>
+        <v>1.87</v>
       </c>
       <c r="AG30">
-        <v>1.33</v>
+        <v>1.87</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.07</v>
+        <v>1.3</v>
       </c>
       <c r="AK30">
-        <v>4.1</v>
+        <v>1.44</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,49 +5362,49 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="O31">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P31">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="Q31">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="R31">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="S31">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="T31">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="U31">
-        <v>3.11</v>
+        <v>3.17</v>
       </c>
       <c r="V31">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W31">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X31">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y31">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Z31">
-        <v>2.87</v>
+        <v>2.81</v>
       </c>
       <c r="AA31">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AB31">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC31">
         <v>4</v>
@@ -5416,10 +5416,10 @@
         <v>1.05</v>
       </c>
       <c r="AF31">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AG31">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AK31">
-        <v>2.16</v>
+        <v>2.03</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,25 +5525,25 @@
         </is>
       </c>
       <c r="N32">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="O32">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="P32">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="Q32">
-        <v>4.36</v>
+        <v>4.39</v>
       </c>
       <c r="R32">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="S32">
         <v>1.38</v>
       </c>
       <c r="T32">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="U32">
         <v>2.72</v>
@@ -5567,22 +5567,22 @@
         <v>1.9</v>
       </c>
       <c r="AB32">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AC32">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AD32">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE32">
         <v>1.11</v>
       </c>
       <c r="AF32">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG32">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="AK32">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,16 +5688,16 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="O33">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P33">
-        <v>3.1</v>
+        <v>3.47</v>
       </c>
       <c r="Q33">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="R33">
         <v>2.1</v>
@@ -5706,10 +5706,10 @@
         <v>1.36</v>
       </c>
       <c r="T33">
-        <v>2.82</v>
+        <v>2.73</v>
       </c>
       <c r="U33">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="V33">
         <v>1.36</v>
@@ -5721,31 +5721,31 @@
         <v>1.05</v>
       </c>
       <c r="Y33">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Z33">
-        <v>3.36</v>
+        <v>3.4</v>
       </c>
       <c r="AA33">
-        <v>2.11</v>
+        <v>1.89</v>
       </c>
       <c r="AB33">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AC33">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AD33">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE33">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF33">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AG33">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AK33">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="O34">
-        <v>3.4</v>
+        <v>4.85</v>
       </c>
       <c r="P34">
-        <v>3.66</v>
+        <v>7.19</v>
       </c>
       <c r="Q34">
-        <v>2.45</v>
+        <v>1.83</v>
       </c>
       <c r="R34">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="S34">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="T34">
-        <v>2.66</v>
+        <v>3.75</v>
       </c>
       <c r="U34">
-        <v>2.75</v>
+        <v>2.19</v>
       </c>
       <c r="V34">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="W34">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X34">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="Z34">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="AA34">
-        <v>2.04</v>
+        <v>1.52</v>
       </c>
       <c r="AB34">
+        <v>2.25</v>
+      </c>
+      <c r="AC34">
+        <v>2.42</v>
+      </c>
+      <c r="AD34">
+        <v>1.53</v>
+      </c>
+      <c r="AE34">
+        <v>1.2</v>
+      </c>
+      <c r="AF34">
         <v>1.75</v>
       </c>
-      <c r="AC34">
-        <v>3.4</v>
-      </c>
-      <c r="AD34">
-        <v>1.3</v>
-      </c>
-      <c r="AE34">
-        <v>1.1</v>
-      </c>
-      <c r="AF34">
-        <v>1.78</v>
-      </c>
       <c r="AG34">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK34">
-        <v>1.72</v>
+        <v>2.91</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK35">
         <v>2.2</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="O36">
-        <v>3.44</v>
+        <v>3.25</v>
       </c>
       <c r="P36">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="Q36">
         <v>2.88</v>
@@ -6195,46 +6195,46 @@
         <v>1.36</v>
       </c>
       <c r="T36">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="U36">
-        <v>2.7</v>
+        <v>3.09</v>
       </c>
       <c r="V36">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W36">
+        <v>1.05</v>
+      </c>
+      <c r="X36">
+        <v>1.05</v>
+      </c>
+      <c r="Y36">
+        <v>1.28</v>
+      </c>
+      <c r="Z36">
+        <v>3.37</v>
+      </c>
+      <c r="AA36">
+        <v>2.1</v>
+      </c>
+      <c r="AB36">
+        <v>1.78</v>
+      </c>
+      <c r="AC36">
+        <v>3.28</v>
+      </c>
+      <c r="AD36">
+        <v>1.25</v>
+      </c>
+      <c r="AE36">
         <v>1.07</v>
       </c>
-      <c r="X36">
-        <v>1.04</v>
-      </c>
-      <c r="Y36">
-        <v>1.25</v>
-      </c>
-      <c r="Z36">
-        <v>3.8</v>
-      </c>
-      <c r="AA36">
-        <v>1.95</v>
-      </c>
-      <c r="AB36">
-        <v>1.93</v>
-      </c>
-      <c r="AC36">
-        <v>3.1</v>
-      </c>
-      <c r="AD36">
-        <v>1.36</v>
-      </c>
-      <c r="AE36">
-        <v>1.1</v>
-      </c>
       <c r="AF36">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG36">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK36">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
+        <v>2.37</v>
+      </c>
+      <c r="O37">
+        <v>3.38</v>
+      </c>
+      <c r="P37">
+        <v>2.82</v>
+      </c>
+      <c r="Q37">
+        <v>2.88</v>
+      </c>
+      <c r="R37">
+        <v>2.1</v>
+      </c>
+      <c r="S37">
+        <v>1.36</v>
+      </c>
+      <c r="T37">
+        <v>3</v>
+      </c>
+      <c r="U37">
+        <v>2.6</v>
+      </c>
+      <c r="V37">
         <v>1.4</v>
       </c>
-      <c r="O37">
-        <v>4.85</v>
-      </c>
-      <c r="P37">
-        <v>7</v>
-      </c>
-      <c r="Q37">
-        <v>1.83</v>
-      </c>
-      <c r="R37">
-        <v>2.5</v>
-      </c>
-      <c r="S37">
+      <c r="W37">
+        <v>1.07</v>
+      </c>
+      <c r="X37">
+        <v>1.04</v>
+      </c>
+      <c r="Y37">
         <v>1.25</v>
       </c>
-      <c r="T37">
-        <v>3.5</v>
-      </c>
-      <c r="U37">
-        <v>2.2</v>
-      </c>
-      <c r="V37">
-        <v>1.57</v>
-      </c>
-      <c r="W37">
-        <v>1.14</v>
-      </c>
-      <c r="X37">
-        <v>1.01</v>
-      </c>
-      <c r="Y37">
-        <v>1.17</v>
-      </c>
       <c r="Z37">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="AA37">
-        <v>1.52</v>
+        <v>1.88</v>
       </c>
       <c r="AB37">
-        <v>2.23</v>
+        <v>2.01</v>
       </c>
       <c r="AC37">
-        <v>2.42</v>
+        <v>3.1</v>
       </c>
       <c r="AD37">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AE37">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AF37">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG37">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AK37">
-        <v>2.91</v>
+        <v>1.53</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6512,22 +6512,22 @@
         <v>5</v>
       </c>
       <c r="Q38">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="R38">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="S38">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T38">
         <v>3.19</v>
       </c>
       <c r="U38">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="V38">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W38">
         <v>1.07</v>
@@ -6539,16 +6539,16 @@
         <v>1.25</v>
       </c>
       <c r="Z38">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AA38">
         <v>1.8</v>
       </c>
       <c r="AB38">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AC38">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AD38">
         <v>1.36</v>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AK38">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,34 +7807,34 @@
         </is>
       </c>
       <c r="N46">
-        <v>3.43</v>
+        <v>1.57</v>
       </c>
       <c r="O46">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="P46">
-        <v>2.1</v>
+        <v>6.02</v>
       </c>
       <c r="Q46">
-        <v>3.74</v>
+        <v>2.03</v>
       </c>
       <c r="R46">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="S46">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T46">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="U46">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="V46">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W46">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X46">
         <v>1.02</v>
@@ -7843,28 +7843,28 @@
         <v>1.24</v>
       </c>
       <c r="Z46">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA46">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AB46">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AC46">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AD46">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AE46">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AF46">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AG46">
-        <v>2.18</v>
+        <v>1.9</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="AK46">
-        <v>1.27</v>
+        <v>2.4</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,34 +7970,34 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.57</v>
+        <v>3.45</v>
       </c>
       <c r="O47">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="P47">
-        <v>5.64</v>
+        <v>1.95</v>
       </c>
       <c r="Q47">
-        <v>2.11</v>
+        <v>3.61</v>
       </c>
       <c r="R47">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="S47">
         <v>1.3</v>
       </c>
       <c r="T47">
-        <v>3.3</v>
+        <v>3.26</v>
       </c>
       <c r="U47">
-        <v>2.64</v>
+        <v>2.4</v>
       </c>
       <c r="V47">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W47">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X47">
         <v>1.02</v>
@@ -8006,28 +8006,28 @@
         <v>1.24</v>
       </c>
       <c r="Z47">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AA47">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AB47">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AC47">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AD47">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AE47">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF47">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AG47">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.17</v>
+        <v>1.8</v>
       </c>
       <c r="AK47">
-        <v>2.4</v>
+        <v>1.27</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,16 +8133,16 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.95</v>
+        <v>1.52</v>
       </c>
       <c r="O48">
-        <v>2.87</v>
+        <v>3.5</v>
       </c>
       <c r="P48">
-        <v>3.9</v>
+        <v>6</v>
       </c>
       <c r="Q48">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="R48">
         <v>1.87</v>
@@ -8206,7 +8206,7 @@
         <v>1.21</v>
       </c>
       <c r="AK48">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,16 +8296,16 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="O49">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="P49">
         <v>2.4</v>
       </c>
       <c r="Q49">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="R49">
         <v>1.85</v>
@@ -8326,31 +8326,31 @@
         <v>1.01</v>
       </c>
       <c r="X49">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y49">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="Z49">
-        <v>2.17</v>
+        <v>2.4</v>
       </c>
       <c r="AA49">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AB49">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AC49">
-        <v>7</v>
+        <v>5.75</v>
       </c>
       <c r="AD49">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AE49">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF49">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="AG49">
         <v>1.57</v>
@@ -8369,7 +8369,7 @@
         <v>1.47</v>
       </c>
       <c r="AK49">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,61 +8459,61 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="O50">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P50">
-        <v>3.43</v>
+        <v>3.6</v>
       </c>
       <c r="Q50">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="R50">
-        <v>1.93</v>
+        <v>2.16</v>
       </c>
       <c r="S50">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="T50">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="U50">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="V50">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W50">
         <v>1.05</v>
       </c>
       <c r="X50">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
         <v>1.36</v>
       </c>
       <c r="Z50">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="AA50">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="AB50">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC50">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AD50">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE50">
         <v>1.02</v>
       </c>
       <c r="AF50">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG50">
         <v>1.8</v>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK50">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AL50">
         <v>0</v>

--- a/jogos_2026-10-13.xlsx
+++ b/jogos_2026-10-13.xlsx
@@ -1430,7 +1430,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1442,11 +1442,11 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["76"]</t>
         </is>
       </c>
       <c r="AJ7">
@@ -1529,28 +1529,28 @@
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -1590,26 +1590,26 @@
         </is>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["5", "73", "90+5"]</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -1692,28 +1692,28 @@
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1753,10 +1753,10 @@
         </is>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -1765,14 +1765,14 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+4"]</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["66", "83"]</t>
         </is>
       </c>
       <c r="AJ9">
@@ -1855,28 +1855,28 @@
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
@@ -2568,10 +2568,10 @@
         </is>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -2580,14 +2580,14 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14">
@@ -2652,12 +2652,12 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["58"]</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["69"]</t>
         </is>
       </c>
       <c r="AJ14">
@@ -2670,28 +2670,28 @@
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AN14">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO14">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AP14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>0.61</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
@@ -2722,96 +2722,96 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G15">
         <v>0</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15">
         <v>0</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15">
-        <v>3.3</v>
+        <v>2.66</v>
       </c>
       <c r="O15">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="P15">
-        <v>2.05</v>
+        <v>2.65</v>
       </c>
       <c r="Q15">
-        <v>3.97</v>
+        <v>2.92</v>
       </c>
       <c r="R15">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="S15">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T15">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="U15">
         <v>2.25</v>
       </c>
       <c r="V15">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W15">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X15">
         <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="Z15">
-        <v>4.5</v>
+        <v>4.65</v>
       </c>
       <c r="AA15">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AB15">
-        <v>2.12</v>
+        <v>2.37</v>
       </c>
       <c r="AC15">
-        <v>2.5</v>
+        <v>2.21</v>
       </c>
       <c r="AD15">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AE15">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF15">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AG15">
-        <v>2.32</v>
+        <v>2.55</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2820,41 +2820,41 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["22", "74"]</t>
         </is>
       </c>
       <c r="AJ15">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="AK15">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AL15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO15">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AP15">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
@@ -2885,16 +2885,16 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -2906,118 +2906,118 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L16">
         <v>0</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16">
-        <v>2.53</v>
+        <v>3.5</v>
       </c>
       <c r="O16">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="P16">
-        <v>2.65</v>
+        <v>2.05</v>
       </c>
       <c r="Q16">
-        <v>2.78</v>
+        <v>4.15</v>
       </c>
       <c r="R16">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="S16">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T16">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U16">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="V16">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="W16">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X16">
         <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z16">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AA16">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB16">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="AC16">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="AD16">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AE16">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF16">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="AG16">
-        <v>2.49</v>
+        <v>2.39</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
+          <t>["49", "88"]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ16">
-        <v>1.44</v>
+        <v>1.87</v>
       </c>
       <c r="AK16">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AL16">
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO16">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP16">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
@@ -3057,26 +3057,26 @@
         </is>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17">
         <v>0</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17">
         <v>0</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17">
@@ -3110,7 +3110,7 @@
         <v>1.04</v>
       </c>
       <c r="X17">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Y17">
         <v>1.53</v>
@@ -3125,28 +3125,28 @@
         <v>1.45</v>
       </c>
       <c r="AC17">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="AD17">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AE17">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF17">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AG17">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["60"]</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["14"]</t>
         </is>
       </c>
       <c r="AJ17">
@@ -3159,28 +3159,28 @@
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
@@ -3220,66 +3220,66 @@
         </is>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="O18">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="P18">
-        <v>4.49</v>
+        <v>4</v>
       </c>
       <c r="Q18">
-        <v>2.73</v>
+        <v>2.81</v>
       </c>
       <c r="R18">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="S18">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="T18">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="U18">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="V18">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W18">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X18">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Y18">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="Z18">
-        <v>2.32</v>
+        <v>2.37</v>
       </c>
       <c r="AA18">
         <v>2.75</v>
@@ -3288,13 +3288,13 @@
         <v>1.4</v>
       </c>
       <c r="AC18">
-        <v>6.15</v>
+        <v>5.45</v>
       </c>
       <c r="AD18">
         <v>1.13</v>
       </c>
       <c r="AE18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF18">
         <v>2.3</v>
@@ -3304,12 +3304,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["10", "60"]</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["8"]</t>
         </is>
       </c>
       <c r="AJ18">
@@ -3322,28 +3322,28 @@
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN18">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO18">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
@@ -3383,26 +3383,26 @@
         </is>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I19">
         <v>0</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N19">
@@ -3415,13 +3415,13 @@
         <v>2.26</v>
       </c>
       <c r="Q19">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="R19">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="S19">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="T19">
         <v>2.6</v>
@@ -3436,77 +3436,77 @@
         <v>1.06</v>
       </c>
       <c r="X19">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y19">
         <v>1.4</v>
       </c>
       <c r="Z19">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AA19">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="AB19">
         <v>1.57</v>
       </c>
       <c r="AC19">
-        <v>4.35</v>
+        <v>4.8</v>
       </c>
       <c r="AD19">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AE19">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF19">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG19">
         <v>1.75</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["59", "66"]</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["6", "45+2"]</t>
         </is>
       </c>
       <c r="AJ19">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AK19">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AL19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO19">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
@@ -3546,26 +3546,26 @@
         </is>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H20">
         <v>0</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J20">
         <v>0</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N20">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["25", "38", "72", "87"]</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
@@ -3648,28 +3648,28 @@
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AN20">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO20">
-        <v>-1</v>
+        <v>29</v>
       </c>
       <c r="AP20">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
@@ -3709,26 +3709,26 @@
         </is>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I21">
         <v>0</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N21">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["51", "90"]</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["29", "34", "42", "81"]</t>
         </is>
       </c>
       <c r="AJ21">
@@ -3811,28 +3811,28 @@
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO21">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP21">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
@@ -3863,139 +3863,139 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22">
         <v>0</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22">
         <v>0</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N22">
+        <v>1.44</v>
+      </c>
+      <c r="O22">
+        <v>4.4</v>
+      </c>
+      <c r="P22">
+        <v>5.17</v>
+      </c>
+      <c r="Q22">
+        <v>1.96</v>
+      </c>
+      <c r="R22">
+        <v>2.5</v>
+      </c>
+      <c r="S22">
+        <v>1.25</v>
+      </c>
+      <c r="T22">
+        <v>3.6</v>
+      </c>
+      <c r="U22">
+        <v>2.28</v>
+      </c>
+      <c r="V22">
+        <v>1.65</v>
+      </c>
+      <c r="W22">
+        <v>1.14</v>
+      </c>
+      <c r="X22">
+        <v>1.02</v>
+      </c>
+      <c r="Y22">
+        <v>1.11</v>
+      </c>
+      <c r="Z22">
+        <v>5</v>
+      </c>
+      <c r="AA22">
+        <v>1.53</v>
+      </c>
+      <c r="AB22">
+        <v>2.38</v>
+      </c>
+      <c r="AC22">
+        <v>1.98</v>
+      </c>
+      <c r="AD22">
+        <v>1.62</v>
+      </c>
+      <c r="AE22">
+        <v>1.18</v>
+      </c>
+      <c r="AF22">
+        <v>1.57</v>
+      </c>
+      <c r="AG22">
+        <v>2.3</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>["20", "82"]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22">
+        <v>1.16</v>
+      </c>
+      <c r="AK22">
         <v>2.6</v>
       </c>
-      <c r="O22">
-        <v>3.85</v>
-      </c>
-      <c r="P22">
-        <v>2.25</v>
-      </c>
-      <c r="Q22">
-        <v>2.88</v>
-      </c>
-      <c r="R22">
-        <v>2.25</v>
-      </c>
-      <c r="S22">
-        <v>1.2</v>
-      </c>
-      <c r="T22">
-        <v>3.5</v>
-      </c>
-      <c r="U22">
-        <v>2.19</v>
-      </c>
-      <c r="V22">
-        <v>1.45</v>
-      </c>
-      <c r="W22">
-        <v>1.13</v>
-      </c>
-      <c r="X22">
-        <v>1.01</v>
-      </c>
-      <c r="Y22">
-        <v>1.18</v>
-      </c>
-      <c r="Z22">
-        <v>4.82</v>
-      </c>
-      <c r="AA22">
-        <v>1.57</v>
-      </c>
-      <c r="AB22">
-        <v>2.35</v>
-      </c>
-      <c r="AC22">
-        <v>2.49</v>
-      </c>
-      <c r="AD22">
-        <v>1.42</v>
-      </c>
-      <c r="AE22">
-        <v>1.13</v>
-      </c>
-      <c r="AF22">
-        <v>1.44</v>
-      </c>
-      <c r="AG22">
-        <v>2.45</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22">
-        <v>1.53</v>
-      </c>
-      <c r="AK22">
-        <v>1.44</v>
-      </c>
       <c r="AL22">
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN22">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO22">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
@@ -4026,22 +4026,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -4050,115 +4050,115 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N23">
+        <v>2.6</v>
+      </c>
+      <c r="O23">
+        <v>3.85</v>
+      </c>
+      <c r="P23">
+        <v>2.25</v>
+      </c>
+      <c r="Q23">
+        <v>2.88</v>
+      </c>
+      <c r="R23">
+        <v>2.25</v>
+      </c>
+      <c r="S23">
+        <v>1.2</v>
+      </c>
+      <c r="T23">
+        <v>3.5</v>
+      </c>
+      <c r="U23">
+        <v>2.19</v>
+      </c>
+      <c r="V23">
+        <v>1.45</v>
+      </c>
+      <c r="W23">
+        <v>1.13</v>
+      </c>
+      <c r="X23">
+        <v>1.01</v>
+      </c>
+      <c r="Y23">
+        <v>1.18</v>
+      </c>
+      <c r="Z23">
+        <v>4.82</v>
+      </c>
+      <c r="AA23">
+        <v>1.57</v>
+      </c>
+      <c r="AB23">
+        <v>2.35</v>
+      </c>
+      <c r="AC23">
+        <v>2.49</v>
+      </c>
+      <c r="AD23">
+        <v>1.42</v>
+      </c>
+      <c r="AE23">
+        <v>1.13</v>
+      </c>
+      <c r="AF23">
         <v>1.44</v>
       </c>
-      <c r="O23">
-        <v>4.4</v>
-      </c>
-      <c r="P23">
-        <v>5.17</v>
-      </c>
-      <c r="Q23">
-        <v>1.96</v>
-      </c>
-      <c r="R23">
-        <v>2.5</v>
-      </c>
-      <c r="S23">
-        <v>1.25</v>
-      </c>
-      <c r="T23">
-        <v>3.6</v>
-      </c>
-      <c r="U23">
-        <v>2.28</v>
-      </c>
-      <c r="V23">
-        <v>1.65</v>
-      </c>
-      <c r="W23">
-        <v>1.14</v>
-      </c>
-      <c r="X23">
-        <v>1.02</v>
-      </c>
-      <c r="Y23">
-        <v>1.11</v>
-      </c>
-      <c r="Z23">
+      <c r="AG23">
+        <v>2.45</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>["24", "35"]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>["70", "90+2"]</t>
+        </is>
+      </c>
+      <c r="AJ23">
+        <v>1.53</v>
+      </c>
+      <c r="AK23">
+        <v>1.44</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
         <v>5</v>
       </c>
-      <c r="AA23">
-        <v>1.53</v>
-      </c>
-      <c r="AB23">
-        <v>2.38</v>
-      </c>
-      <c r="AC23">
-        <v>1.98</v>
-      </c>
-      <c r="AD23">
-        <v>1.62</v>
-      </c>
-      <c r="AE23">
-        <v>1.18</v>
-      </c>
-      <c r="AF23">
-        <v>1.57</v>
-      </c>
-      <c r="AG23">
-        <v>2.3</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23">
-        <v>1.16</v>
-      </c>
-      <c r="AK23">
-        <v>2.6</v>
-      </c>
-      <c r="AL23">
-        <v>0</v>
-      </c>
-      <c r="AM23">
-        <v>-1</v>
-      </c>
       <c r="AN23">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO23">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP23">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
@@ -4198,26 +4198,26 @@
         </is>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N24">
@@ -4282,12 +4282,12 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["7", "9", "73"]</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["36", "68"]</t>
         </is>
       </c>
       <c r="AJ24">
@@ -4300,28 +4300,28 @@
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP24">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ24">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="AR24">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AS24">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AT24">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>0</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -4376,11 +4376,11 @@
         <v>0</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N25">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["73", "89"]</t>
         </is>
       </c>
       <c r="AJ25">
@@ -4463,28 +4463,28 @@
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN25">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO25">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ25">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AR25">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="AS25">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="AT25">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
@@ -4524,10 +4524,10 @@
         </is>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -4536,14 +4536,14 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N26">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["49"]</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["60", "88"]</t>
         </is>
       </c>
       <c r="AJ26">
@@ -4626,28 +4626,28 @@
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO26">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP26">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ26">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AR26">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AS26">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AT26">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
@@ -4687,10 +4687,10 @@
         </is>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -4699,24 +4699,24 @@
         <v>0</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N27">
         <v>1.65</v>
       </c>
       <c r="O27">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P27">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="Q27">
         <v>2.3</v>
@@ -4740,13 +4740,13 @@
         <v>1.04</v>
       </c>
       <c r="X27">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y27">
         <v>1.4</v>
       </c>
       <c r="Z27">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AA27">
         <v>2.25</v>
@@ -4755,13 +4755,13 @@
         <v>1.57</v>
       </c>
       <c r="AC27">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AD27">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AE27">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF27">
         <v>2.2</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["58"]</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["48"]</t>
         </is>
       </c>
       <c r="AJ27">
@@ -4789,28 +4789,28 @@
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN27">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO27">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ27">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR27">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AS27">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AT27">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
@@ -4841,139 +4841,139 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I28">
         <v>0</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28">
         <v>0</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N28">
-        <v>1.2</v>
+        <v>2.18</v>
       </c>
       <c r="O28">
-        <v>5.55</v>
+        <v>3.08</v>
       </c>
       <c r="P28">
-        <v>12</v>
+        <v>3.25</v>
       </c>
       <c r="Q28">
-        <v>1.57</v>
+        <v>3.1</v>
       </c>
       <c r="R28">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="S28">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T28">
+        <v>2.51</v>
+      </c>
+      <c r="U28">
         <v>2.9</v>
       </c>
-      <c r="U28">
-        <v>2.72</v>
-      </c>
       <c r="V28">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W28">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X28">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z28">
         <v>3.2</v>
       </c>
       <c r="AA28">
-        <v>1.9</v>
+        <v>2.13</v>
       </c>
       <c r="AB28">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="AC28">
-        <v>3.08</v>
+        <v>3.8</v>
       </c>
       <c r="AD28">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AE28">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF28">
-        <v>3.04</v>
+        <v>1.8</v>
       </c>
       <c r="AG28">
-        <v>1.32</v>
+        <v>1.91</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["72"]</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["7", "45+1"]</t>
         </is>
       </c>
       <c r="AJ28">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AK28">
-        <v>4</v>
+        <v>1.44</v>
       </c>
       <c r="AL28">
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN28">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO28">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AP28">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AQ28">
-        <v>0</v>
+        <v>0.74</v>
       </c>
       <c r="AR28">
-        <v>0</v>
+        <v>0.57</v>
       </c>
       <c r="AS28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AT28">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
@@ -5013,26 +5013,26 @@
         </is>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K29">
         <v>0</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N29">
@@ -5066,25 +5066,25 @@
         <v>1.1</v>
       </c>
       <c r="X29">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z29">
         <v>3.14</v>
       </c>
       <c r="AA29">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AB29">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AC29">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AD29">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE29">
         <v>1.07</v>
@@ -5093,16 +5093,16 @@
         <v>2.32</v>
       </c>
       <c r="AG29">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["22"]</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["18", "37", "48", "59"]</t>
         </is>
       </c>
       <c r="AJ29">
@@ -5115,16 +5115,16 @@
         <v>0</v>
       </c>
       <c r="AM29">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP29">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="AQ29">
         <v>0</v>
@@ -5167,139 +5167,139 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H30">
         <v>0</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30">
         <v>0</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L30">
         <v>0</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N30">
-        <v>2.18</v>
+        <v>1.04</v>
       </c>
       <c r="O30">
-        <v>3.02</v>
+        <v>5.55</v>
       </c>
       <c r="P30">
-        <v>2.97</v>
+        <v>11</v>
       </c>
       <c r="Q30">
-        <v>3.1</v>
+        <v>1.57</v>
       </c>
       <c r="R30">
-        <v>2</v>
+        <v>2.63</v>
       </c>
       <c r="S30">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="T30">
-        <v>2.42</v>
+        <v>3.3</v>
       </c>
       <c r="U30">
-        <v>3.2</v>
+        <v>2.51</v>
       </c>
       <c r="V30">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="W30">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="X30">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="Z30">
-        <v>2.88</v>
+        <v>4</v>
       </c>
       <c r="AA30">
-        <v>2.25</v>
+        <v>1.73</v>
       </c>
       <c r="AB30">
-        <v>1.57</v>
+        <v>2.07</v>
       </c>
       <c r="AC30">
-        <v>4.1</v>
+        <v>2.74</v>
       </c>
       <c r="AD30">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AE30">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF30">
-        <v>1.87</v>
+        <v>2.79</v>
       </c>
       <c r="AG30">
-        <v>1.87</v>
+        <v>1.36</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
+          <t>["18", "50", "76"]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ30">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AK30">
-        <v>1.44</v>
+        <v>4.33</v>
       </c>
       <c r="AL30">
         <v>0</v>
       </c>
       <c r="AM30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN30">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO30">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ30">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AR30">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AS30">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AT30">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
@@ -5339,26 +5339,26 @@
         </is>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I31">
         <v>0</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L31">
         <v>0</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N31">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["56", "88"]</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["5", "8"]</t>
         </is>
       </c>
       <c r="AJ31">
@@ -5441,28 +5441,28 @@
         <v>0</v>
       </c>
       <c r="AM31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN31">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO31">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AR31">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="AS31">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="AT31">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
@@ -5525,34 +5525,34 @@
         </is>
       </c>
       <c r="N32">
-        <v>4.7</v>
+        <v>5.25</v>
       </c>
       <c r="O32">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P32">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="Q32">
-        <v>4.39</v>
+        <v>5.5</v>
       </c>
       <c r="R32">
         <v>2.13</v>
       </c>
       <c r="S32">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T32">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="U32">
         <v>2.72</v>
       </c>
       <c r="V32">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="W32">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X32">
         <v>1.04</v>
@@ -5564,7 +5564,7 @@
         <v>3.5</v>
       </c>
       <c r="AA32">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AB32">
         <v>1.88</v>
@@ -5579,7 +5579,7 @@
         <v>1.11</v>
       </c>
       <c r="AF32">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AG32">
         <v>1.81</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.1</v>
+        <v>1.61</v>
       </c>
       <c r="O33">
-        <v>3.3</v>
+        <v>4.05</v>
       </c>
       <c r="P33">
-        <v>3.47</v>
+        <v>4.6</v>
       </c>
       <c r="Q33">
-        <v>2.45</v>
+        <v>2.08</v>
       </c>
       <c r="R33">
-        <v>2.1</v>
+        <v>2.47</v>
       </c>
       <c r="S33">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="T33">
-        <v>2.73</v>
+        <v>3.8</v>
       </c>
       <c r="U33">
-        <v>2.88</v>
+        <v>2.15</v>
       </c>
       <c r="V33">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="W33">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="X33">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="Z33">
-        <v>3.4</v>
+        <v>6</v>
       </c>
       <c r="AA33">
-        <v>1.89</v>
+        <v>1.43</v>
       </c>
       <c r="AB33">
-        <v>1.8</v>
+        <v>2.46</v>
       </c>
       <c r="AC33">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="AD33">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="AE33">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AF33">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AG33">
-        <v>2.05</v>
+        <v>2.39</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AK33">
-        <v>1.73</v>
+        <v>2.25</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,61 +5851,61 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="O34">
-        <v>4.85</v>
+        <v>4</v>
       </c>
       <c r="P34">
-        <v>7.19</v>
+        <v>5</v>
       </c>
       <c r="Q34">
-        <v>1.83</v>
+        <v>2.16</v>
       </c>
       <c r="R34">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="S34">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="T34">
-        <v>3.75</v>
+        <v>3.19</v>
       </c>
       <c r="U34">
-        <v>2.19</v>
+        <v>2.48</v>
       </c>
       <c r="V34">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="W34">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X34">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z34">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="AA34">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="AB34">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="AC34">
-        <v>2.42</v>
+        <v>2.88</v>
       </c>
       <c r="AD34">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AE34">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AF34">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG34">
         <v>2</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AK34">
-        <v>2.91</v>
+        <v>2.23</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="O35">
-        <v>4.05</v>
+        <v>3.2</v>
       </c>
       <c r="P35">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="Q35">
-        <v>2.14</v>
+        <v>2.8</v>
       </c>
       <c r="R35">
-        <v>2.44</v>
+        <v>2</v>
       </c>
       <c r="S35">
+        <v>1.36</v>
+      </c>
+      <c r="T35">
+        <v>2.75</v>
+      </c>
+      <c r="U35">
+        <v>3.15</v>
+      </c>
+      <c r="V35">
+        <v>1.33</v>
+      </c>
+      <c r="W35">
+        <v>1.05</v>
+      </c>
+      <c r="X35">
+        <v>1.05</v>
+      </c>
+      <c r="Y35">
+        <v>1.31</v>
+      </c>
+      <c r="Z35">
+        <v>3.23</v>
+      </c>
+      <c r="AA35">
+        <v>2.16</v>
+      </c>
+      <c r="AB35">
+        <v>1.71</v>
+      </c>
+      <c r="AC35">
+        <v>3.5</v>
+      </c>
+      <c r="AD35">
         <v>1.22</v>
       </c>
-      <c r="T35">
-        <v>3.8</v>
-      </c>
-      <c r="U35">
-        <v>2.15</v>
-      </c>
-      <c r="V35">
-        <v>1.6</v>
-      </c>
-      <c r="W35">
-        <v>1.15</v>
-      </c>
-      <c r="X35">
-        <v>1.01</v>
-      </c>
-      <c r="Y35">
-        <v>1.14</v>
-      </c>
-      <c r="Z35">
-        <v>5.5</v>
-      </c>
-      <c r="AA35">
-        <v>1.44</v>
-      </c>
-      <c r="AB35">
-        <v>2.43</v>
-      </c>
-      <c r="AC35">
-        <v>2.25</v>
-      </c>
-      <c r="AD35">
-        <v>1.62</v>
-      </c>
       <c r="AE35">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AF35">
-        <v>1.5</v>
+        <v>1.81</v>
       </c>
       <c r="AG35">
-        <v>2.42</v>
+        <v>1.9</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AK35">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="O36">
-        <v>3.25</v>
+        <v>4.85</v>
       </c>
       <c r="P36">
-        <v>3.1</v>
+        <v>7.19</v>
       </c>
       <c r="Q36">
-        <v>2.88</v>
+        <v>1.8</v>
       </c>
       <c r="R36">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="S36">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="T36">
-        <v>2.82</v>
+        <v>3.75</v>
       </c>
       <c r="U36">
-        <v>3.09</v>
+        <v>2.17</v>
       </c>
       <c r="V36">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="W36">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X36">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="Z36">
-        <v>3.37</v>
+        <v>5.5</v>
       </c>
       <c r="AA36">
-        <v>2.1</v>
+        <v>1.52</v>
       </c>
       <c r="AB36">
-        <v>1.78</v>
+        <v>2.26</v>
       </c>
       <c r="AC36">
-        <v>3.28</v>
+        <v>2.42</v>
       </c>
       <c r="AD36">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AE36">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="AF36">
         <v>1.75</v>
       </c>
       <c r="AG36">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AK36">
-        <v>1.57</v>
+        <v>2.91</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,16 +6340,16 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="O37">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="P37">
-        <v>2.82</v>
+        <v>3.47</v>
       </c>
       <c r="Q37">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="R37">
         <v>2.1</v>
@@ -6358,46 +6358,46 @@
         <v>1.36</v>
       </c>
       <c r="T37">
-        <v>3</v>
+        <v>2.66</v>
       </c>
       <c r="U37">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="V37">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W37">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X37">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y37">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="Z37">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="AA37">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AB37">
-        <v>2.01</v>
+        <v>1.76</v>
       </c>
       <c r="AC37">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="AD37">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AE37">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF37">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG37">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AK37">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.6</v>
+        <v>2.37</v>
       </c>
       <c r="O38">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="P38">
-        <v>5</v>
+        <v>2.85</v>
       </c>
       <c r="Q38">
-        <v>2.22</v>
+        <v>3.04</v>
       </c>
       <c r="R38">
-        <v>2.22</v>
+        <v>2.05</v>
       </c>
       <c r="S38">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="T38">
-        <v>3.19</v>
+        <v>2.8</v>
       </c>
       <c r="U38">
-        <v>2.53</v>
+        <v>2.8</v>
       </c>
       <c r="V38">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="W38">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X38">
+        <v>1.05</v>
+      </c>
+      <c r="Y38">
+        <v>1.33</v>
+      </c>
+      <c r="Z38">
+        <v>3.25</v>
+      </c>
+      <c r="AA38">
+        <v>2.01</v>
+      </c>
+      <c r="AB38">
+        <v>1.75</v>
+      </c>
+      <c r="AC38">
+        <v>3.5</v>
+      </c>
+      <c r="AD38">
+        <v>1.29</v>
+      </c>
+      <c r="AE38">
         <v>1.04</v>
       </c>
-      <c r="Y38">
-        <v>1.25</v>
-      </c>
-      <c r="Z38">
-        <v>3.42</v>
-      </c>
-      <c r="AA38">
-        <v>1.8</v>
-      </c>
-      <c r="AB38">
-        <v>1.92</v>
-      </c>
-      <c r="AC38">
-        <v>2.92</v>
-      </c>
-      <c r="AD38">
-        <v>1.36</v>
-      </c>
-      <c r="AE38">
-        <v>1.09</v>
-      </c>
       <c r="AF38">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AG38">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AK38">
-        <v>2.16</v>
+        <v>1.53</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6669,61 +6669,61 @@
         <v>1.26</v>
       </c>
       <c r="O39">
-        <v>6.4</v>
+        <v>6.9</v>
       </c>
       <c r="P39">
         <v>10</v>
       </c>
       <c r="Q39">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="R39">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="S39">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="T39">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="U39">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="V39">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="W39">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="X39">
         <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="Z39">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA39">
+        <v>1.33</v>
+      </c>
+      <c r="AB39">
+        <v>3.14</v>
+      </c>
+      <c r="AC39">
+        <v>1.77</v>
+      </c>
+      <c r="AD39">
+        <v>2</v>
+      </c>
+      <c r="AE39">
         <v>1.4</v>
       </c>
-      <c r="AB39">
-        <v>2.68</v>
-      </c>
-      <c r="AC39">
-        <v>1.97</v>
-      </c>
-      <c r="AD39">
-        <v>1.81</v>
-      </c>
-      <c r="AE39">
-        <v>1.28</v>
-      </c>
       <c r="AF39">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AG39">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AK39">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6832,61 +6832,61 @@
         <v>1.2</v>
       </c>
       <c r="O40">
-        <v>6.8</v>
+        <v>6.95</v>
       </c>
       <c r="P40">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q40">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="R40">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="S40">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T40">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="U40">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
       <c r="V40">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="W40">
         <v>1.14</v>
       </c>
       <c r="X40">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA40">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB40">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="AC40">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AD40">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AE40">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AF40">
-        <v>2.21</v>
+        <v>2.11</v>
       </c>
       <c r="AG40">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>1.13</v>
       </c>
       <c r="AK40">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7001,52 +7001,52 @@
         <v>3.1</v>
       </c>
       <c r="Q41">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="R41">
         <v>2.4</v>
       </c>
       <c r="S41">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T41">
-        <v>3.42</v>
+        <v>3.36</v>
       </c>
       <c r="U41">
         <v>2.38</v>
       </c>
       <c r="V41">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W41">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X41">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y41">
+        <v>1.18</v>
+      </c>
+      <c r="Z41">
+        <v>4.5</v>
+      </c>
+      <c r="AA41">
+        <v>1.71</v>
+      </c>
+      <c r="AB41">
+        <v>2.23</v>
+      </c>
+      <c r="AC41">
+        <v>2.63</v>
+      </c>
+      <c r="AD41">
+        <v>1.44</v>
+      </c>
+      <c r="AE41">
         <v>1.14</v>
       </c>
-      <c r="Z41">
-        <v>5</v>
-      </c>
-      <c r="AA41">
-        <v>1.61</v>
-      </c>
-      <c r="AB41">
-        <v>2.38</v>
-      </c>
-      <c r="AC41">
-        <v>2.47</v>
-      </c>
-      <c r="AD41">
-        <v>1.5</v>
-      </c>
-      <c r="AE41">
-        <v>1.18</v>
-      </c>
       <c r="AF41">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG41">
         <v>2.4</v>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AK41">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>17</v>
+        <v>1.84</v>
       </c>
       <c r="O42">
-        <v>14</v>
+        <v>3.7</v>
       </c>
       <c r="P42">
+        <v>2.75</v>
+      </c>
+      <c r="Q42">
+        <v>2.52</v>
+      </c>
+      <c r="R42">
+        <v>2.26</v>
+      </c>
+      <c r="S42">
+        <v>1.32</v>
+      </c>
+      <c r="T42">
+        <v>3</v>
+      </c>
+      <c r="U42">
+        <v>2.4</v>
+      </c>
+      <c r="V42">
+        <v>1.59</v>
+      </c>
+      <c r="W42">
         <v>1.12</v>
       </c>
-      <c r="Q42">
-        <v>10.7</v>
-      </c>
-      <c r="R42">
-        <v>4.45</v>
-      </c>
-      <c r="S42">
-        <v>1.1</v>
-      </c>
-      <c r="T42">
-        <v>7</v>
-      </c>
-      <c r="U42">
-        <v>1.49</v>
-      </c>
-      <c r="V42">
-        <v>2.31</v>
-      </c>
-      <c r="W42">
-        <v>1.46</v>
-      </c>
       <c r="X42">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="Z42">
-        <v>13</v>
+        <v>4.4</v>
       </c>
       <c r="AA42">
-        <v>1.11</v>
+        <v>1.67</v>
       </c>
       <c r="AB42">
-        <v>5.25</v>
+        <v>2.27</v>
       </c>
       <c r="AC42">
-        <v>1.37</v>
+        <v>2.63</v>
       </c>
       <c r="AD42">
-        <v>2.8</v>
+        <v>1.44</v>
       </c>
       <c r="AE42">
-        <v>1.89</v>
+        <v>1.14</v>
       </c>
       <c r="AF42">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AG42">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>8.6</v>
+        <v>1.29</v>
       </c>
       <c r="AK42">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.92</v>
+        <v>14</v>
       </c>
       <c r="O43">
-        <v>3.7</v>
+        <v>12</v>
       </c>
       <c r="P43">
-        <v>3.1</v>
+        <v>1.15</v>
       </c>
       <c r="Q43">
-        <v>2.31</v>
+        <v>9.4</v>
       </c>
       <c r="R43">
-        <v>2.37</v>
+        <v>4.15</v>
       </c>
       <c r="S43">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="T43">
-        <v>3.35</v>
+        <v>7</v>
       </c>
       <c r="U43">
-        <v>2.18</v>
+        <v>1.49</v>
       </c>
       <c r="V43">
-        <v>1.66</v>
+        <v>2.32</v>
       </c>
       <c r="W43">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="X43">
+        <v>1</v>
+      </c>
+      <c r="Y43">
         <v>1.01</v>
       </c>
-      <c r="Y43">
-        <v>1.11</v>
-      </c>
       <c r="Z43">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AA43">
-        <v>1.53</v>
+        <v>1.13</v>
       </c>
       <c r="AB43">
-        <v>2.53</v>
+        <v>5</v>
       </c>
       <c r="AC43">
-        <v>2.2</v>
+        <v>1.36</v>
       </c>
       <c r="AD43">
-        <v>1.62</v>
+        <v>3</v>
       </c>
       <c r="AE43">
-        <v>1.25</v>
+        <v>1.91</v>
       </c>
       <c r="AF43">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AG43">
-        <v>2.8</v>
+        <v>2.19</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.19</v>
+        <v>7.2</v>
       </c>
       <c r="AK43">
-        <v>1.93</v>
+        <v>1.02</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,34 +7481,34 @@
         </is>
       </c>
       <c r="N44">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="O44">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="P44">
         <v>1.28</v>
       </c>
       <c r="Q44">
-        <v>6.63</v>
+        <v>7.17</v>
       </c>
       <c r="R44">
-        <v>3.01</v>
+        <v>3.2</v>
       </c>
       <c r="S44">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="T44">
-        <v>5.7</v>
+        <v>5.55</v>
       </c>
       <c r="U44">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V44">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="W44">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="X44">
         <v>1</v>
@@ -7520,19 +7520,19 @@
         <v>8.6</v>
       </c>
       <c r="AA44">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AB44">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="AC44">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AD44">
-        <v>2.47</v>
+        <v>2.42</v>
       </c>
       <c r="AE44">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AF44">
         <v>1.44</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>3.92</v>
+        <v>1.11</v>
       </c>
       <c r="AK44">
         <v>1.05</v>
@@ -7647,61 +7647,61 @@
         <v>1.97</v>
       </c>
       <c r="O45">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="P45">
         <v>3.9</v>
       </c>
       <c r="Q45">
-        <v>2.21</v>
+        <v>2.06</v>
       </c>
       <c r="R45">
-        <v>2.53</v>
+        <v>3.1</v>
       </c>
       <c r="S45">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="T45">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U45">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="V45">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="W45">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="X45">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y45">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Z45">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA45">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AB45">
-        <v>3.26</v>
+        <v>4</v>
       </c>
       <c r="AC45">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AD45">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AE45">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AF45">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AG45">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AK45">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7822,31 +7822,31 @@
         <v>2.4</v>
       </c>
       <c r="S46">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T46">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="U46">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="V46">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W46">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X46">
         <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z46">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA46">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AB46">
         <v>2.1</v>
@@ -7855,13 +7855,13 @@
         <v>2.88</v>
       </c>
       <c r="AD46">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AE46">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF46">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AG46">
         <v>1.9</v>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK46">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="O47">
         <v>3.65</v>
       </c>
       <c r="P47">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="Q47">
         <v>3.61</v>
@@ -7985,49 +7985,49 @@
         <v>2.19</v>
       </c>
       <c r="S47">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T47">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="U47">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="V47">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W47">
         <v>1.08</v>
       </c>
       <c r="X47">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y47">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z47">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA47">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="AB47">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="AC47">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AD47">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE47">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF47">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AG47">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AK47">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="O48">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P48">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="Q48">
         <v>2</v>
@@ -8459,25 +8459,25 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="O50">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="P50">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="Q50">
-        <v>2.63</v>
+        <v>2.49</v>
       </c>
       <c r="R50">
-        <v>2.16</v>
+        <v>1.99</v>
       </c>
       <c r="S50">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T50">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="U50">
         <v>2.92</v>
@@ -8486,28 +8486,28 @@
         <v>1.33</v>
       </c>
       <c r="W50">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X50">
         <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z50">
-        <v>3.04</v>
+        <v>2.81</v>
       </c>
       <c r="AA50">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="AB50">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AC50">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="AD50">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE50">
         <v>1.02</v>
@@ -8532,7 +8532,7 @@
         <v>1.3</v>
       </c>
       <c r="AK50">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AL50">
         <v>0</v>
